--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G36">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="G41">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G48">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G52">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G57">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G73">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G76">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G88">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G100">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G112">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G127">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G141">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G166">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G167">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G174">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G175">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G176">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G177">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G186">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G188">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G192">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.83</v>
+        <v>3.01</v>
       </c>
       <c r="O195">
-        <v>3.68</v>
+        <v>3.56</v>
       </c>
       <c r="P195">
-        <v>3.97</v>
+        <v>2.19</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB195">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>3.01</v>
+        <v>1.72</v>
       </c>
       <c r="O196">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="P196">
-        <v>2.19</v>
+        <v>4.46</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32296,10 +32296,10 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="O197">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="P197">
-        <v>2.83</v>
+        <v>3.97</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="O198">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="P198">
-        <v>4.46</v>
+        <v>2.83</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32622,10 +32622,10 @@
         <v>0</v>
       </c>
       <c r="AA198">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB198">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC198">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G206">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G225">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G230">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G263">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G264">
@@ -43826,7 +43826,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N267">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G275">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G276">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G287">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G288">
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G327">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G328">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G332">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G334">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G335">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G336">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G337">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G338">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G343">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G344">
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G349">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G350">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G352">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G353">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G354">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G355">

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G23">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G37">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G77">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G114">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G236">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G337">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G338">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G340">

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G114">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G129">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G165">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G296">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G337">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G338">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G340">

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G164">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G165">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G340">

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q214">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21538,10 +21538,10 @@
         <v>0</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC130">
         <v>0</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC144">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27406,10 +27406,10 @@
         <v>0</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC166">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O209">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34415,10 +34415,10 @@
         <v>0</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC209">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O241">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P241">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46314,10 +46314,10 @@
         <v>0</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC282">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G90">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="O164">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="P164">
-        <v>4.42</v>
+        <v>1.85</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="O165">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="P165">
-        <v>1.85</v>
+        <v>4.42</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB172">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,14 +28671,14 @@
         </is>
       </c>
       <c r="N174">
+        <v>2.04</v>
+      </c>
+      <c r="O174">
+        <v>3.48</v>
+      </c>
+      <c r="P174">
         <v>3.32</v>
       </c>
-      <c r="O174">
-        <v>3.56</v>
-      </c>
-      <c r="P174">
-        <v>2.01</v>
-      </c>
       <c r="Q174">
         <v>0</v>
       </c>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB174">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O188">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P188">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>3.46</v>
+        <v>1.46</v>
       </c>
       <c r="O193">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="P193">
-        <v>1.96</v>
+        <v>5.83</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="O203">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="P203">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.24</v>
+        <v>3.17</v>
       </c>
       <c r="O205">
-        <v>6</v>
+        <v>3.54</v>
       </c>
       <c r="P205">
-        <v>10.5</v>
+        <v>2.12</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>3.17</v>
+        <v>2.84</v>
       </c>
       <c r="O206">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P206">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.74</v>
+        <v>2.04</v>
       </c>
       <c r="O208">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="P208">
-        <v>4.03</v>
+        <v>3.42</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44684,10 +44684,10 @@
         <v>0</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC272">
         <v>0</v>
@@ -47086,7 +47086,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N287">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47781,10 +47781,10 @@
         <v>0</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC291">
         <v>0</v>
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O297">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P297">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -53773,13 +53773,13 @@
         </is>
       </c>
       <c r="N328">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O328">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P328">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q328">
         <v>0</v>
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q329">
         <v>0</v>
@@ -54425,13 +54425,13 @@
         </is>
       </c>
       <c r="N332">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O332">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P332">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q332">
         <v>0</v>
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O333">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P333">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AA333">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB333">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC333">
         <v>0</v>
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O343">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P343">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56257,10 +56257,10 @@
         <v>0</v>
       </c>
       <c r="AA343">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB343">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC343">
         <v>0</v>
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O344">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P344">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O348">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P348">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O349">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P349">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q349">
         <v>0</v>
@@ -57235,10 +57235,10 @@
         <v>0</v>
       </c>
       <c r="AA349">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB349">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC349">
         <v>0</v>
@@ -57522,13 +57522,13 @@
         </is>
       </c>
       <c r="N351">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O351">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P351">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q351">
         <v>0</v>
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O352">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P352">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q352">
         <v>0</v>
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G356">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G357">

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="O164">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="P164">
-        <v>1.85</v>
+        <v>4.42</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="O165">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="P165">
-        <v>4.42</v>
+        <v>1.85</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,14 +28508,14 @@
         </is>
       </c>
       <c r="N173">
+        <v>2.04</v>
+      </c>
+      <c r="O173">
+        <v>3.48</v>
+      </c>
+      <c r="P173">
         <v>3.32</v>
       </c>
-      <c r="O173">
-        <v>3.56</v>
-      </c>
-      <c r="P173">
-        <v>2.01</v>
-      </c>
       <c r="Q173">
         <v>0</v>
       </c>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB173">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.04</v>
+        <v>2.67</v>
       </c>
       <c r="O174">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="P174">
-        <v>3.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB174">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.67</v>
+        <v>2.16</v>
       </c>
       <c r="O175">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="P175">
-        <v>2.47</v>
+        <v>3.06</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB175">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="O176">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="P176">
-        <v>3.06</v>
+        <v>3.36</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,14 +29160,14 @@
         </is>
       </c>
       <c r="N177">
+        <v>3.32</v>
+      </c>
+      <c r="O177">
+        <v>3.56</v>
+      </c>
+      <c r="P177">
         <v>2.01</v>
       </c>
-      <c r="O177">
-        <v>3.52</v>
-      </c>
-      <c r="P177">
-        <v>3.36</v>
-      </c>
       <c r="Q177">
         <v>0</v>
       </c>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB177">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="O178">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="P178">
-        <v>3.87</v>
+        <v>4.33</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB178">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="O179">
-        <v>4</v>
+        <v>3.72</v>
       </c>
       <c r="P179">
-        <v>4.33</v>
+        <v>3.87</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB179">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>3.17</v>
+        <v>1.74</v>
       </c>
       <c r="O205">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="P205">
-        <v>2.12</v>
+        <v>4.03</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="O206">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="P206">
-        <v>2.31</v>
+        <v>4.56</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -33926,10 +33926,10 @@
         <v>0</v>
       </c>
       <c r="AA206">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB206">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.74</v>
+        <v>3.17</v>
       </c>
       <c r="O207">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="P207">
-        <v>4.03</v>
+        <v>2.12</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.67</v>
+        <v>2.84</v>
       </c>
       <c r="O209">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="P209">
-        <v>4.56</v>
+        <v>2.31</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34415,10 +34415,10 @@
         <v>0</v>
       </c>
       <c r="AA209">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB209">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC209">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G340">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G351">
@@ -57522,13 +57522,13 @@
         </is>
       </c>
       <c r="N351">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="O351">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="P351">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="Q351">
         <v>0</v>
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G352">
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O352">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="P352">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="Q352">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nagykanizsai TE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Nagykanizsai TE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G60">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G151">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.27</v>
+        <v>3.5</v>
       </c>
       <c r="O162">
-        <v>5.1</v>
+        <v>3.58</v>
       </c>
       <c r="P162">
-        <v>8.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>3.65</v>
+        <v>1.27</v>
       </c>
       <c r="O163">
-        <v>3.54</v>
+        <v>5.1</v>
       </c>
       <c r="P163">
-        <v>1.82</v>
+        <v>8.15</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="O164">
-        <v>3.92</v>
+        <v>3.54</v>
       </c>
       <c r="P164">
-        <v>4.42</v>
+        <v>1.82</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="O165">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="P165">
-        <v>1.85</v>
+        <v>4.42</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="O170">
         <v>3.56</v>
       </c>
       <c r="P170">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB170">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="O171">
-        <v>4.45</v>
+        <v>3.52</v>
       </c>
       <c r="P171">
-        <v>5.31</v>
+        <v>3.36</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="O172">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P172">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB172">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="O173">
-        <v>3.48</v>
+        <v>4.45</v>
       </c>
       <c r="P173">
-        <v>3.32</v>
+        <v>5.31</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB173">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.67</v>
+        <v>3.4</v>
       </c>
       <c r="O174">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="P174">
-        <v>2.47</v>
+        <v>1.94</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AB174">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="O175">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P175">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.01</v>
+        <v>2.67</v>
       </c>
       <c r="O176">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="P176">
-        <v>3.36</v>
+        <v>2.47</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB176">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.32</v>
+        <v>2.16</v>
       </c>
       <c r="O177">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="P177">
-        <v>2.01</v>
+        <v>3.06</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB177">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.95</v>
+        <v>3.17</v>
       </c>
       <c r="O201">
-        <v>3.36</v>
+        <v>3.54</v>
       </c>
       <c r="P201">
-        <v>3.85</v>
+        <v>2.12</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O202">
-        <v>3.54</v>
+        <v>3.98</v>
       </c>
       <c r="P202">
-        <v>2.83</v>
+        <v>4.56</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33274,10 +33274,10 @@
         <v>0</v>
       </c>
       <c r="AA202">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB202">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="O203">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="P203">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="O204">
-        <v>6</v>
+        <v>3.54</v>
       </c>
       <c r="P204">
-        <v>10.5</v>
+        <v>2.83</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="O205">
-        <v>4.05</v>
+        <v>3.64</v>
       </c>
       <c r="P205">
-        <v>4.03</v>
+        <v>2.75</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="O206">
-        <v>3.98</v>
+        <v>6</v>
       </c>
       <c r="P206">
-        <v>4.56</v>
+        <v>10.5</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -33926,10 +33926,10 @@
         <v>0</v>
       </c>
       <c r="AA206">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB206">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>3.17</v>
+        <v>1.74</v>
       </c>
       <c r="O207">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="P207">
-        <v>2.12</v>
+        <v>4.03</v>
       </c>
       <c r="Q207">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G58">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB85">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G90">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.47</v>
+        <v>2.02</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P115">
-        <v>2.09</v>
+        <v>3.49</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.87</v>
+        <v>3.47</v>
       </c>
       <c r="O116">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P116">
-        <v>3.89</v>
+        <v>2.09</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB116">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="O117">
         <v>3.6</v>
       </c>
       <c r="P117">
-        <v>3.49</v>
+        <v>3.89</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA117">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AB117">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC117">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G127">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="O152">
-        <v>3.99</v>
+        <v>4.21</v>
       </c>
       <c r="P152">
-        <v>2.9</v>
+        <v>4.11</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25130,10 +25130,10 @@
         <v>0</v>
       </c>
       <c r="AC152">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD152">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="O153">
-        <v>4.21</v>
+        <v>3.99</v>
       </c>
       <c r="P153">
-        <v>4.11</v>
+        <v>2.9</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25293,10 +25293,10 @@
         <v>0</v>
       </c>
       <c r="AC153">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD153">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AE153">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="O171">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="P171">
-        <v>3.36</v>
+        <v>3.06</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28221,10 +28221,10 @@
         <v>0</v>
       </c>
       <c r="AA171">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB171">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="O172">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="P172">
-        <v>2.38</v>
+        <v>3.36</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB172">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="O173">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="P173">
-        <v>5.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="O174">
-        <v>3.72</v>
+        <v>4.45</v>
       </c>
       <c r="P174">
-        <v>1.94</v>
+        <v>5.31</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB174">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="O175">
-        <v>3.48</v>
+        <v>3.72</v>
       </c>
       <c r="P175">
-        <v>3.32</v>
+        <v>1.94</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB175">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="O176">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P176">
-        <v>2.47</v>
+        <v>3.32</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB176">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.16</v>
+        <v>2.67</v>
       </c>
       <c r="O177">
-        <v>3.44</v>
+        <v>3.26</v>
       </c>
       <c r="P177">
-        <v>3.06</v>
+        <v>2.47</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="O187">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="P187">
-        <v>2.87</v>
+        <v>4.29</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O192">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P192">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.46</v>
+        <v>3.46</v>
       </c>
       <c r="O193">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="P193">
-        <v>5.83</v>
+        <v>1.96</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="O194">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="P194">
-        <v>4.29</v>
+        <v>5.83</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G288">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G289">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G313">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G314">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G315">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G316">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G317">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G333">
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O333">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P333">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AA333">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB333">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC333">
         <v>0</v>
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G334">
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O334">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P334">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -54790,10 +54790,10 @@
         <v>0</v>
       </c>
       <c r="AA334">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB334">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC334">
         <v>0</v>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G336">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G337">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G338">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G339">

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G100">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G108">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G110">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G133">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23168,10 +23168,10 @@
         <v>0</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC140">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="G143">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23983,10 +23983,10 @@
         <v>0</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC145">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.38</v>
+        <v>4.68</v>
       </c>
       <c r="O153">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="P153">
-        <v>2.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25293,10 +25293,10 @@
         <v>0</v>
       </c>
       <c r="AC153">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD153">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AE153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>4.68</v>
+        <v>2.38</v>
       </c>
       <c r="O154">
-        <v>4.57</v>
+        <v>3.99</v>
       </c>
       <c r="P154">
-        <v>1.72</v>
+        <v>2.9</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AC154">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD154">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AE154">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="O157">
-        <v>4.57</v>
+        <v>7.7</v>
       </c>
       <c r="P157">
-        <v>6.57</v>
+        <v>13.6</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25945,10 +25945,10 @@
         <v>0</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.86</v>
+        <v>1.55</v>
       </c>
       <c r="O158">
-        <v>3.85</v>
+        <v>4.57</v>
       </c>
       <c r="P158">
-        <v>2.47</v>
+        <v>6.57</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.23</v>
+        <v>2.86</v>
       </c>
       <c r="O159">
-        <v>7.7</v>
+        <v>3.85</v>
       </c>
       <c r="P159">
-        <v>13.6</v>
+        <v>2.47</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26271,10 +26271,10 @@
         <v>0</v>
       </c>
       <c r="AC159">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD159">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE159">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="O163">
-        <v>5.1</v>
+        <v>3.92</v>
       </c>
       <c r="P163">
-        <v>8.15</v>
+        <v>4.42</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>3.65</v>
+        <v>1.27</v>
       </c>
       <c r="O164">
-        <v>3.54</v>
+        <v>5.1</v>
       </c>
       <c r="P164">
-        <v>1.82</v>
+        <v>8.15</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.6</v>
+        <v>3.65</v>
       </c>
       <c r="O165">
-        <v>3.92</v>
+        <v>3.54</v>
       </c>
       <c r="P165">
-        <v>4.42</v>
+        <v>1.82</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="O173">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="P173">
-        <v>2.38</v>
+        <v>4.33</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB173">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="O174">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="P174">
-        <v>5.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="O175">
-        <v>3.72</v>
+        <v>4.45</v>
       </c>
       <c r="P175">
-        <v>1.94</v>
+        <v>5.31</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB175">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="O176">
-        <v>3.48</v>
+        <v>3.72</v>
       </c>
       <c r="P176">
-        <v>3.32</v>
+        <v>1.94</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB176">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="O177">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P177">
-        <v>2.47</v>
+        <v>3.32</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB177">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.67</v>
+        <v>2.67</v>
       </c>
       <c r="O178">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="P178">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AB178">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.76</v>
+        <v>3.46</v>
       </c>
       <c r="O187">
         <v>3.65</v>
       </c>
       <c r="P187">
-        <v>4.29</v>
+        <v>1.96</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="O188">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P188">
-        <v>2.87</v>
+        <v>4.19</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>3.46</v>
+        <v>1.99</v>
       </c>
       <c r="O193">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P193">
-        <v>1.96</v>
+        <v>3.56</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39142,10 +39142,10 @@
         <v>0</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC238">
         <v>0</v>
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O242">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39794,10 +39794,10 @@
         <v>0</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC242">
         <v>0</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G290">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -52469,13 +52469,13 @@
         </is>
       </c>
       <c r="N320">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O320">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P320">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q320">
         <v>0</v>
@@ -52514,10 +52514,10 @@
         <v>0</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE320">
         <v>0</v>
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O336">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P336">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q336">
         <v>0</v>
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O338">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P338">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55442,10 +55442,10 @@
         <v>0</v>
       </c>
       <c r="AA338">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB338">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC338">
         <v>0</v>
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O339">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P339">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55611,10 +55611,10 @@
         <v>0</v>
       </c>
       <c r="AC339">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD339">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE339">
         <v>0</v>
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O340">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P340">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O345">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P345">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56583,10 +56583,10 @@
         <v>0</v>
       </c>
       <c r="AA345">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB345">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC345">
         <v>0</v>
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G346">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G347">
@@ -58174,13 +58174,13 @@
         </is>
       </c>
       <c r="N355">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O355">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P355">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q355">
         <v>0</v>
@@ -58219,10 +58219,10 @@
         <v>0</v>
       </c>
       <c r="AC355">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD355">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE355">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.84</v>
+        <v>2.52</v>
       </c>
       <c r="O73">
-        <v>3.92</v>
+        <v>3.55</v>
       </c>
       <c r="P73">
-        <v>3.69</v>
+        <v>2.52</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.52</v>
+        <v>1.84</v>
       </c>
       <c r="O74">
-        <v>3.55</v>
+        <v>3.92</v>
       </c>
       <c r="P74">
-        <v>2.52</v>
+        <v>3.69</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G111">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G121">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="O130">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P130">
-        <v>2.41</v>
+        <v>2.98</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21538,10 +21538,10 @@
         <v>0</v>
       </c>
       <c r="AA130">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB130">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="O131">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P131">
-        <v>2.98</v>
+        <v>2.41</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21701,10 +21701,10 @@
         <v>0</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC131">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>3.46</v>
+        <v>1.8</v>
       </c>
       <c r="O187">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P187">
-        <v>1.96</v>
+        <v>4.19</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="O188">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P188">
-        <v>4.19</v>
+        <v>2.97</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.24</v>
+        <v>1.76</v>
       </c>
       <c r="O189">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P189">
-        <v>2.97</v>
+        <v>4.29</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.76</v>
+        <v>3.46</v>
       </c>
       <c r="O190">
         <v>3.65</v>
       </c>
       <c r="P190">
-        <v>4.29</v>
+        <v>1.96</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.4</v>
+        <v>1.46</v>
       </c>
       <c r="O191">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="P191">
-        <v>2.87</v>
+        <v>5.83</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="O192">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P192">
-        <v>4.38</v>
+        <v>2.87</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="O193">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="P193">
-        <v>3.56</v>
+        <v>4.38</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.46</v>
+        <v>1.99</v>
       </c>
       <c r="O194">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="P194">
-        <v>5.83</v>
+        <v>3.56</v>
       </c>
       <c r="Q194">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="O183">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="P183">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="O184">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="P184">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q283">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47286,10 +47286,10 @@
         <v>0</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA288">
         <v>0</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47449,10 +47449,10 @@
         <v>0</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA289">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47612,10 +47612,10 @@
         <v>0</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA290">
         <v>0</v>
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48427,10 +48427,10 @@
         <v>0</v>
       </c>
       <c r="Y295">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z295">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA295">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O311">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P311">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q311">
         <v>0</v>
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51361,10 +51361,10 @@
         <v>0</v>
       </c>
       <c r="Y313">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z313">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA313">
         <v>0</v>
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O314">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P314">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -51524,10 +51524,10 @@
         <v>0</v>
       </c>
       <c r="Y314">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z314">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA314">
         <v>0</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O315">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P315">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51980,13 +51980,13 @@
         </is>
       </c>
       <c r="N317">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O317">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P317">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q317">
         <v>0</v>
@@ -52019,10 +52019,10 @@
         <v>0</v>
       </c>
       <c r="AA317">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB317">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC317">
         <v>0</v>
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O322">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P322">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52828,10 +52828,10 @@
         <v>0</v>
       </c>
       <c r="Y322">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z322">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA322">
         <v>0</v>
@@ -57848,13 +57848,13 @@
         </is>
       </c>
       <c r="N353">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O353">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P353">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q353">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.98</v>
+        <v>2.26</v>
       </c>
       <c r="O5">
-        <v>3.58</v>
+        <v>3.13</v>
       </c>
       <c r="P5">
-        <v>2.04</v>
+        <v>3.17</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="O6">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="P6">
-        <v>2.51</v>
+        <v>2.04</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="O7">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="P7">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="P8">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB8">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.57</v>
+        <v>2.39</v>
       </c>
       <c r="O9">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>5.11</v>
+        <v>2.58</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="O10">
-        <v>3.13</v>
+        <v>3.66</v>
       </c>
       <c r="P10">
-        <v>3.17</v>
+        <v>5.11</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G236">

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G4">
@@ -964,61 +964,61 @@
         <v>2.26</v>
       </c>
       <c r="O4">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="P4">
-        <v>2.84</v>
+        <v>3.17</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA4">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB4">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="O5">
-        <v>3.13</v>
+        <v>3.66</v>
       </c>
       <c r="P5">
-        <v>3.17</v>
+        <v>5.11</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.57</v>
+        <v>2.39</v>
       </c>
       <c r="O6">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>5.11</v>
+        <v>2.58</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AA6">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P7">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB7">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.98</v>
+        <v>2.59</v>
       </c>
       <c r="O8">
-        <v>3.58</v>
+        <v>3.19</v>
       </c>
       <c r="P8">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>3.58</v>
       </c>
       <c r="P9">
-        <v>2.51</v>
+        <v>2.04</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="O10">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="P10">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA10">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AB10">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>5.55</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>2.15</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA12">
         <v>1.8</v>
@@ -2310,19 +2310,19 @@
         <v>1.96</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,58 +2428,58 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.74</v>
+        <v>1.36</v>
       </c>
       <c r="O13">
-        <v>3.74</v>
+        <v>5.52</v>
       </c>
       <c r="P13">
-        <v>1.95</v>
+        <v>7.5</v>
       </c>
       <c r="Q13">
-        <v>3.75</v>
+        <v>1.74</v>
       </c>
       <c r="R13">
-        <v>2.17</v>
+        <v>2.72</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="U13">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z13">
-        <v>3.96</v>
+        <v>5.4</v>
       </c>
       <c r="AA13">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AB13">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="AC13">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF13">
         <v>1.64</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>1.29</v>
+        <v>3.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,58 +2591,58 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.36</v>
+        <v>3.74</v>
       </c>
       <c r="O14">
-        <v>5.52</v>
+        <v>3.74</v>
       </c>
       <c r="P14">
-        <v>7.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
-        <v>1.74</v>
+        <v>3.75</v>
       </c>
       <c r="R14">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="S14">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.06</v>
+        <v>2.48</v>
       </c>
       <c r="V14">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>5.4</v>
+        <v>3.96</v>
       </c>
       <c r="AA14">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AB14">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC14">
-        <v>2.09</v>
+        <v>2.83</v>
       </c>
       <c r="AD14">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
         <v>1.64</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.77</v>
+        <v>1.52</v>
       </c>
       <c r="O17">
-        <v>3.65</v>
+        <v>4.47</v>
       </c>
       <c r="P17">
-        <v>2.43</v>
+        <v>6.05</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="R17">
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="AA17">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AB17">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AC17">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="AD17">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AE17">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.2</v>
+      </c>
+      <c r="AK17">
         <v>2.63</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.28</v>
-      </c>
-      <c r="AK17">
-        <v>1.43</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.52</v>
+        <v>2.77</v>
       </c>
       <c r="O18">
-        <v>4.47</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>6.05</v>
+        <v>2.43</v>
       </c>
       <c r="Q18">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
         <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T18">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA18">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AD18">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK18">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>4.61</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>4.35</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>2.66</v>
       </c>
       <c r="O23">
+        <v>3.24</v>
+      </c>
+      <c r="P23">
+        <v>2.31</v>
+      </c>
+      <c r="Q23">
         <v>3.52</v>
       </c>
-      <c r="P23">
-        <v>4.1</v>
-      </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA23">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.66</v>
+        <v>1.73</v>
       </c>
       <c r="O24">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="P24">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA24">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4882,34 +4882,34 @@
         <v>3.32</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA28">
         <v>1.84</v>
@@ -4918,19 +4918,19 @@
         <v>1.92</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>2.23</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>3.42</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.44</v>
+        <v>3.03</v>
       </c>
       <c r="O66">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="P66">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="Q66">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="R66">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
+        <v>1.4</v>
+      </c>
+      <c r="T66">
+        <v>2.82</v>
+      </c>
+      <c r="U66">
+        <v>2.88</v>
+      </c>
+      <c r="V66">
         <v>1.36</v>
       </c>
-      <c r="T66">
-        <v>3.03</v>
-      </c>
-      <c r="U66">
-        <v>2.81</v>
-      </c>
-      <c r="V66">
-        <v>1.4</v>
-      </c>
       <c r="W66">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y66">
+        <v>1.33</v>
+      </c>
+      <c r="Z66">
+        <v>3.21</v>
+      </c>
+      <c r="AA66">
+        <v>2.05</v>
+      </c>
+      <c r="AB66">
+        <v>1.75</v>
+      </c>
+      <c r="AC66">
+        <v>3.61</v>
+      </c>
+      <c r="AD66">
+        <v>1.27</v>
+      </c>
+      <c r="AE66">
+        <v>1.03</v>
+      </c>
+      <c r="AF66">
+        <v>1.75</v>
+      </c>
+      <c r="AG66">
+        <v>1.95</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.25</v>
       </c>
-      <c r="Z66">
-        <v>3.55</v>
-      </c>
-      <c r="AA66">
-        <v>1.91</v>
-      </c>
-      <c r="AB66">
-        <v>1.86</v>
-      </c>
-      <c r="AC66">
-        <v>3.25</v>
-      </c>
-      <c r="AD66">
-        <v>1.33</v>
-      </c>
-      <c r="AE66">
-        <v>1.12</v>
-      </c>
-      <c r="AF66">
-        <v>1.69</v>
-      </c>
-      <c r="AG66">
-        <v>2.05</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.38</v>
-      </c>
       <c r="AK66">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,65 +11230,65 @@
         </is>
       </c>
       <c r="N67">
+        <v>2.44</v>
+      </c>
+      <c r="O67">
+        <v>3.36</v>
+      </c>
+      <c r="P67">
+        <v>2.64</v>
+      </c>
+      <c r="Q67">
+        <v>2.87</v>
+      </c>
+      <c r="R67">
+        <v>2.15</v>
+      </c>
+      <c r="S67">
+        <v>1.36</v>
+      </c>
+      <c r="T67">
         <v>3.03</v>
       </c>
-      <c r="O67">
-        <v>3.26</v>
-      </c>
-      <c r="P67">
-        <v>2.26</v>
-      </c>
-      <c r="Q67">
-        <v>3.8</v>
-      </c>
-      <c r="R67">
-        <v>2.1</v>
-      </c>
-      <c r="S67">
+      <c r="U67">
+        <v>2.81</v>
+      </c>
+      <c r="V67">
         <v>1.4</v>
       </c>
-      <c r="T67">
-        <v>2.82</v>
-      </c>
-      <c r="U67">
-        <v>2.88</v>
-      </c>
-      <c r="V67">
-        <v>1.36</v>
-      </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
+        <v>1.25</v>
+      </c>
+      <c r="Z67">
+        <v>3.55</v>
+      </c>
+      <c r="AA67">
+        <v>1.91</v>
+      </c>
+      <c r="AB67">
+        <v>1.86</v>
+      </c>
+      <c r="AC67">
+        <v>3.25</v>
+      </c>
+      <c r="AD67">
         <v>1.33</v>
       </c>
-      <c r="Z67">
-        <v>3.21</v>
-      </c>
-      <c r="AA67">
+      <c r="AE67">
+        <v>1.12</v>
+      </c>
+      <c r="AF67">
+        <v>1.69</v>
+      </c>
+      <c r="AG67">
         <v>2.05</v>
       </c>
-      <c r="AB67">
-        <v>1.75</v>
-      </c>
-      <c r="AC67">
-        <v>3.61</v>
-      </c>
-      <c r="AD67">
-        <v>1.27</v>
-      </c>
-      <c r="AE67">
-        <v>1.03</v>
-      </c>
-      <c r="AF67">
-        <v>1.75</v>
-      </c>
-      <c r="AG67">
-        <v>1.95</v>
-      </c>
       <c r="AH67" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK67">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>4.2</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,55 +12869,55 @@
         <v>0</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>3.71</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O86">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="P86">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O87">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="P87">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>1.34</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G103">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.73</v>
+        <v>2.53</v>
       </c>
       <c r="O109">
-        <v>3.18</v>
+        <v>2.98</v>
       </c>
       <c r="P109">
-        <v>1.91</v>
+        <v>2.58</v>
       </c>
       <c r="Q109">
-        <v>4.59</v>
+        <v>3.27</v>
       </c>
       <c r="R109">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S109">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T109">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="U109">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V109">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W109">
         <v>1.02</v>
       </c>
       <c r="X109">
+        <v>1.03</v>
+      </c>
+      <c r="Y109">
+        <v>1.36</v>
+      </c>
+      <c r="Z109">
+        <v>3.02</v>
+      </c>
+      <c r="AA109">
+        <v>2.16</v>
+      </c>
+      <c r="AB109">
+        <v>1.67</v>
+      </c>
+      <c r="AC109">
+        <v>3.89</v>
+      </c>
+      <c r="AD109">
+        <v>1.23</v>
+      </c>
+      <c r="AE109">
         <v>1.02</v>
       </c>
-      <c r="Y109">
-        <v>1.34</v>
-      </c>
-      <c r="Z109">
-        <v>3.12</v>
-      </c>
-      <c r="AA109">
-        <v>2.1</v>
-      </c>
-      <c r="AB109">
-        <v>1.71</v>
-      </c>
-      <c r="AC109">
-        <v>3.7</v>
-      </c>
-      <c r="AD109">
-        <v>1.25</v>
-      </c>
-      <c r="AE109">
-        <v>1.03</v>
-      </c>
       <c r="AF109">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AG109">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK109">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
+        <v>3.23</v>
+      </c>
+      <c r="O111">
+        <v>3.14</v>
+      </c>
+      <c r="P111">
+        <v>2.09</v>
+      </c>
+      <c r="Q111">
+        <v>4.11</v>
+      </c>
+      <c r="R111">
+        <v>2</v>
+      </c>
+      <c r="S111">
+        <v>1.38</v>
+      </c>
+      <c r="T111">
+        <v>2.69</v>
+      </c>
+      <c r="U111">
+        <v>2.77</v>
+      </c>
+      <c r="V111">
+        <v>1.38</v>
+      </c>
+      <c r="W111">
+        <v>1.05</v>
+      </c>
+      <c r="X111">
+        <v>1.01</v>
+      </c>
+      <c r="Y111">
+        <v>1.29</v>
+      </c>
+      <c r="Z111">
+        <v>3.04</v>
+      </c>
+      <c r="AA111">
+        <v>1.99</v>
+      </c>
+      <c r="AB111">
+        <v>1.7</v>
+      </c>
+      <c r="AC111">
         <v>3.42</v>
       </c>
-      <c r="O111">
-        <v>3.42</v>
-      </c>
-      <c r="P111">
-        <v>1.92</v>
-      </c>
-      <c r="Q111">
-        <v>4.1</v>
-      </c>
-      <c r="R111">
-        <v>2.32</v>
-      </c>
-      <c r="S111">
-        <v>1.28</v>
-      </c>
-      <c r="T111">
-        <v>3.12</v>
-      </c>
-      <c r="U111">
-        <v>2.61</v>
-      </c>
-      <c r="V111">
-        <v>1.44</v>
-      </c>
-      <c r="W111">
-        <v>1.08</v>
-      </c>
-      <c r="X111">
-        <v>1.03</v>
-      </c>
-      <c r="Y111">
-        <v>1.22</v>
-      </c>
-      <c r="Z111">
-        <v>3.97</v>
-      </c>
-      <c r="AA111">
-        <v>1.73</v>
-      </c>
-      <c r="AB111">
-        <v>1.95</v>
-      </c>
-      <c r="AC111">
-        <v>2.85</v>
-      </c>
       <c r="AD111">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AE111">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AG111">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK111">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,65 +18565,65 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.53</v>
+        <v>3.13</v>
       </c>
       <c r="O112">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P112">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="Q112">
-        <v>3.27</v>
+        <v>3.99</v>
       </c>
       <c r="R112">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S112">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T112">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U112">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="V112">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W112">
+        <v>1.05</v>
+      </c>
+      <c r="X112">
         <v>1.02</v>
       </c>
-      <c r="X112">
+      <c r="Y112">
+        <v>1.31</v>
+      </c>
+      <c r="Z112">
+        <v>2.92</v>
+      </c>
+      <c r="AA112">
+        <v>2.05</v>
+      </c>
+      <c r="AB112">
+        <v>1.66</v>
+      </c>
+      <c r="AC112">
+        <v>3.58</v>
+      </c>
+      <c r="AD112">
+        <v>1.21</v>
+      </c>
+      <c r="AE112">
         <v>1.03</v>
       </c>
-      <c r="Y112">
-        <v>1.36</v>
-      </c>
-      <c r="Z112">
-        <v>3.02</v>
-      </c>
-      <c r="AA112">
-        <v>2.16</v>
-      </c>
-      <c r="AB112">
-        <v>1.67</v>
-      </c>
-      <c r="AC112">
-        <v>3.89</v>
-      </c>
-      <c r="AD112">
-        <v>1.23</v>
-      </c>
-      <c r="AE112">
-        <v>1.02</v>
-      </c>
       <c r="AF112">
+        <v>1.82</v>
+      </c>
+      <c r="AG112">
         <v>1.84</v>
       </c>
-      <c r="AG112">
-        <v>1.85</v>
-      </c>
       <c r="AH112" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK112">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="O113">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="P113">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="Q113">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="R113">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="S113">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="U113">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="V113">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>3.04</v>
+        <v>3.97</v>
       </c>
       <c r="AA113">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="AB113">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC113">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="AD113">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF113">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG113">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK113">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="O114">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="P114">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q114">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="R114">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S114">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T114">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="U114">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="V114">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W114">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z114">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AA114">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB114">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC114">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="AD114">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE114">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF114">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AG114">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="O115">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P115">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="Q115">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="R115">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="S115">
+        <v>1.35</v>
+      </c>
+      <c r="T115">
+        <v>2.95</v>
+      </c>
+      <c r="U115">
+        <v>2.89</v>
+      </c>
+      <c r="V115">
         <v>1.38</v>
       </c>
-      <c r="T115">
-        <v>2.65</v>
-      </c>
-      <c r="U115">
-        <v>2.81</v>
-      </c>
-      <c r="V115">
-        <v>1.34</v>
-      </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z115">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
       <c r="AA115">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB115">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC115">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="AD115">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE115">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG115">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -20367,55 +20367,55 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,80 +21336,80 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="Q129">
-        <v>3.1</v>
+        <v>1.69</v>
       </c>
       <c r="R129">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="S129">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U129">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="V129">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="W129">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X129">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z129">
-        <v>3.34</v>
+        <v>4.6</v>
       </c>
       <c r="AA129">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AB129">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AC129">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="AD129">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AE129">
+        <v>1.21</v>
+      </c>
+      <c r="AF129">
+        <v>1.9</v>
+      </c>
+      <c r="AG129">
+        <v>1.8</v>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ129">
         <v>1.07</v>
       </c>
-      <c r="AF129">
-        <v>1.68</v>
-      </c>
-      <c r="AG129">
-        <v>2.03</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>1.3</v>
-      </c>
       <c r="AK129">
-        <v>1.48</v>
+        <v>3.44</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>3.1</v>
+      </c>
+      <c r="R131">
+        <v>2.1</v>
+      </c>
+      <c r="S131">
+        <v>1.33</v>
+      </c>
+      <c r="T131">
+        <v>3</v>
+      </c>
+      <c r="U131">
+        <v>2.88</v>
+      </c>
+      <c r="V131">
+        <v>1.36</v>
+      </c>
+      <c r="W131">
+        <v>1.06</v>
+      </c>
+      <c r="X131">
+        <v>1.01</v>
+      </c>
+      <c r="Y131">
+        <v>1.24</v>
+      </c>
+      <c r="Z131">
+        <v>3.34</v>
+      </c>
+      <c r="AA131">
+        <v>1.87</v>
+      </c>
+      <c r="AB131">
+        <v>1.85</v>
+      </c>
+      <c r="AC131">
+        <v>3.08</v>
+      </c>
+      <c r="AD131">
         <v>1.28</v>
       </c>
-      <c r="O131">
-        <v>4.8</v>
-      </c>
-      <c r="P131">
-        <v>8.65</v>
-      </c>
-      <c r="Q131">
-        <v>1.69</v>
-      </c>
-      <c r="R131">
-        <v>2.63</v>
-      </c>
-      <c r="S131">
-        <v>1.22</v>
-      </c>
-      <c r="T131">
-        <v>3.8</v>
-      </c>
-      <c r="U131">
-        <v>2.2</v>
-      </c>
-      <c r="V131">
-        <v>1.6</v>
-      </c>
-      <c r="W131">
-        <v>1.15</v>
-      </c>
-      <c r="X131">
-        <v>1.02</v>
-      </c>
-      <c r="Y131">
-        <v>1.13</v>
-      </c>
-      <c r="Z131">
-        <v>4.6</v>
-      </c>
-      <c r="AA131">
-        <v>1.55</v>
-      </c>
-      <c r="AB131">
-        <v>2.33</v>
-      </c>
-      <c r="AC131">
-        <v>2.3</v>
-      </c>
-      <c r="AD131">
-        <v>1.56</v>
-      </c>
       <c r="AE131">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AF131">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AG131">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AK131">
-        <v>3.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21834,34 +21834,34 @@
         <v>2.41</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA132">
         <v>1.83</v>
@@ -21870,19 +21870,19 @@
         <v>1.94</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21997,55 +21997,55 @@
         <v>2.98</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="O141">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="P141">
-        <v>4.06</v>
+        <v>1.94</v>
       </c>
       <c r="Q141">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="R141">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="S141">
+        <v>1.22</v>
+      </c>
+      <c r="T141">
+        <v>3.54</v>
+      </c>
+      <c r="U141">
+        <v>2.34</v>
+      </c>
+      <c r="V141">
+        <v>1.57</v>
+      </c>
+      <c r="W141">
+        <v>1.13</v>
+      </c>
+      <c r="X141">
+        <v>1.01</v>
+      </c>
+      <c r="Y141">
+        <v>1.17</v>
+      </c>
+      <c r="Z141">
+        <v>4.68</v>
+      </c>
+      <c r="AA141">
+        <v>1.55</v>
+      </c>
+      <c r="AB141">
+        <v>2.24</v>
+      </c>
+      <c r="AC141">
+        <v>2.43</v>
+      </c>
+      <c r="AD141">
+        <v>1.53</v>
+      </c>
+      <c r="AE141">
         <v>1.21</v>
-      </c>
-      <c r="T141">
-        <v>3.75</v>
-      </c>
-      <c r="U141">
-        <v>2.22</v>
-      </c>
-      <c r="V141">
-        <v>1.62</v>
-      </c>
-      <c r="W141">
-        <v>1.16</v>
-      </c>
-      <c r="X141">
-        <v>1.02</v>
-      </c>
-      <c r="Y141">
-        <v>1.11</v>
-      </c>
-      <c r="Z141">
-        <v>4.8</v>
-      </c>
-      <c r="AA141">
-        <v>1.45</v>
-      </c>
-      <c r="AB141">
-        <v>2.41</v>
-      </c>
-      <c r="AC141">
-        <v>2.27</v>
-      </c>
-      <c r="AD141">
-        <v>1.61</v>
-      </c>
-      <c r="AE141">
-        <v>1.24</v>
       </c>
       <c r="AF141">
         <v>1.49</v>
       </c>
       <c r="AG141">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK141">
-        <v>1.99</v>
+        <v>1.26</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="O142">
-        <v>3.44</v>
+        <v>3.94</v>
       </c>
       <c r="P142">
-        <v>3.44</v>
+        <v>4.06</v>
       </c>
       <c r="Q142">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="R142">
-        <v>2.16</v>
+        <v>2.41</v>
       </c>
       <c r="S142">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="T142">
-        <v>2.89</v>
+        <v>3.75</v>
       </c>
       <c r="U142">
-        <v>2.61</v>
+        <v>2.22</v>
       </c>
       <c r="V142">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="W142">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X142">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y142">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z142">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA142">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="AB142">
-        <v>1.94</v>
+        <v>2.41</v>
       </c>
       <c r="AC142">
-        <v>2.92</v>
+        <v>2.27</v>
       </c>
       <c r="AD142">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="AE142">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AF142">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AG142">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK142">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,80 +23618,80 @@
         </is>
       </c>
       <c r="N143">
-        <v>3.2</v>
+        <v>2.01</v>
       </c>
       <c r="O143">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="P143">
+        <v>3.44</v>
+      </c>
+      <c r="Q143">
+        <v>2.43</v>
+      </c>
+      <c r="R143">
+        <v>2.16</v>
+      </c>
+      <c r="S143">
+        <v>1.32</v>
+      </c>
+      <c r="T143">
+        <v>2.89</v>
+      </c>
+      <c r="U143">
+        <v>2.61</v>
+      </c>
+      <c r="V143">
+        <v>1.39</v>
+      </c>
+      <c r="W143">
+        <v>1.08</v>
+      </c>
+      <c r="X143">
+        <v>1</v>
+      </c>
+      <c r="Y143">
+        <v>1.22</v>
+      </c>
+      <c r="Z143">
+        <v>3.5</v>
+      </c>
+      <c r="AA143">
+        <v>1.81</v>
+      </c>
+      <c r="AB143">
         <v>1.94</v>
       </c>
-      <c r="Q143">
-        <v>3.78</v>
-      </c>
-      <c r="R143">
-        <v>2.28</v>
-      </c>
-      <c r="S143">
-        <v>1.22</v>
-      </c>
-      <c r="T143">
-        <v>3.54</v>
-      </c>
-      <c r="U143">
-        <v>2.34</v>
-      </c>
-      <c r="V143">
-        <v>1.57</v>
-      </c>
-      <c r="W143">
-        <v>1.13</v>
-      </c>
-      <c r="X143">
-        <v>1.01</v>
-      </c>
-      <c r="Y143">
-        <v>1.17</v>
-      </c>
-      <c r="Z143">
-        <v>4.68</v>
-      </c>
-      <c r="AA143">
-        <v>1.55</v>
-      </c>
-      <c r="AB143">
-        <v>2.24</v>
-      </c>
       <c r="AC143">
-        <v>2.43</v>
+        <v>2.92</v>
       </c>
       <c r="AD143">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AE143">
+        <v>1.08</v>
+      </c>
+      <c r="AF143">
+        <v>1.68</v>
+      </c>
+      <c r="AG143">
+        <v>2.04</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ143">
         <v>1.21</v>
       </c>
-      <c r="AF143">
-        <v>1.49</v>
-      </c>
-      <c r="AG143">
-        <v>2.42</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>1.22</v>
-      </c>
       <c r="AK143">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,64 +25574,64 @@
         </is>
       </c>
       <c r="N155">
-        <v>4.68</v>
+        <v>2.38</v>
       </c>
       <c r="O155">
-        <v>4.57</v>
+        <v>3.99</v>
       </c>
       <c r="P155">
-        <v>1.72</v>
+        <v>2.9</v>
       </c>
       <c r="Q155">
-        <v>5.04</v>
+        <v>2.87</v>
       </c>
       <c r="R155">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="S155">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T155">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U155">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="V155">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="W155">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X155">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y155">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z155">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AA155">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB155">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="AC155">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD155">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AE155">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF155">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AG155">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK155">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.38</v>
+        <v>4.68</v>
       </c>
       <c r="O156">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="P156">
-        <v>2.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q156">
-        <v>2.87</v>
+        <v>5.04</v>
       </c>
       <c r="R156">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="S156">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T156">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U156">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V156">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="W156">
+        <v>1.18</v>
+      </c>
+      <c r="X156">
+        <v>1.01</v>
+      </c>
+      <c r="Y156">
+        <v>1.09</v>
+      </c>
+      <c r="Z156">
+        <v>5.3</v>
+      </c>
+      <c r="AA156">
+        <v>1.44</v>
+      </c>
+      <c r="AB156">
+        <v>2.6</v>
+      </c>
+      <c r="AC156">
+        <v>2</v>
+      </c>
+      <c r="AD156">
+        <v>1.72</v>
+      </c>
+      <c r="AE156">
+        <v>1.23</v>
+      </c>
+      <c r="AF156">
+        <v>1.5</v>
+      </c>
+      <c r="AG156">
+        <v>2.4</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
         <v>1.17</v>
       </c>
-      <c r="X156">
-        <v>1.02</v>
-      </c>
-      <c r="Y156">
-        <v>1.08</v>
-      </c>
-      <c r="Z156">
-        <v>5.7</v>
-      </c>
-      <c r="AA156">
-        <v>1.4</v>
-      </c>
-      <c r="AB156">
-        <v>2.68</v>
-      </c>
-      <c r="AC156">
-        <v>2.1</v>
-      </c>
-      <c r="AD156">
-        <v>1.65</v>
-      </c>
-      <c r="AE156">
-        <v>1.27</v>
-      </c>
-      <c r="AF156">
-        <v>1.37</v>
-      </c>
-      <c r="AG156">
-        <v>2.84</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.25</v>
-      </c>
       <c r="AK156">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.56</v>
+        <v>2.49</v>
       </c>
       <c r="O168">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="P168">
-        <v>5.16</v>
+        <v>2.49</v>
       </c>
       <c r="Q168">
-        <v>2.14</v>
+        <v>3.18</v>
       </c>
       <c r="R168">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S168">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T168">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="U168">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V168">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W168">
         <v>1.06</v>
       </c>
       <c r="X168">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z168">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AA168">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB168">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AC168">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD168">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE168">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF168">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AG168">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>1.25</v>
       </c>
       <c r="AK168">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,65 +27856,65 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.49</v>
+        <v>3.16</v>
       </c>
       <c r="O169">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="P169">
-        <v>2.49</v>
+        <v>2.18</v>
       </c>
       <c r="Q169">
-        <v>3.18</v>
+        <v>3.82</v>
       </c>
       <c r="R169">
         <v>2.05</v>
       </c>
       <c r="S169">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="T169">
-        <v>2.73</v>
+        <v>2.39</v>
       </c>
       <c r="U169">
-        <v>2.77</v>
+        <v>3.12</v>
       </c>
       <c r="V169">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W169">
         <v>1.06</v>
       </c>
       <c r="X169">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y169">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z169">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AA169">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="AB169">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AC169">
-        <v>3.48</v>
+        <v>3.92</v>
       </c>
       <c r="AD169">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE169">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF169">
+        <v>1.9</v>
+      </c>
+      <c r="AG169">
         <v>1.87</v>
       </c>
-      <c r="AG169">
-        <v>1.9</v>
-      </c>
       <c r="AH169" t="inlineStr">
         <is>
           <t>[]</t>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AK169">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>3.16</v>
+        <v>1.56</v>
       </c>
       <c r="O170">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
       <c r="P170">
-        <v>2.18</v>
+        <v>5.16</v>
       </c>
       <c r="Q170">
-        <v>3.82</v>
+        <v>2.14</v>
       </c>
       <c r="R170">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S170">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="T170">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="U170">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="V170">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W170">
         <v>1.06</v>
       </c>
       <c r="X170">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y170">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="Z170">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AA170">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AB170">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC170">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD170">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE170">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF170">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG170">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AK170">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,16 +28345,16 @@
         </is>
       </c>
       <c r="N172">
-        <v>3.32</v>
+        <v>1.67</v>
       </c>
       <c r="O172">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="P172">
-        <v>2.01</v>
+        <v>4.33</v>
       </c>
       <c r="Q172">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="R172">
         <v>2.3</v>
@@ -28366,43 +28366,43 @@
         <v>3.3</v>
       </c>
       <c r="U172">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="V172">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W172">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X172">
         <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z172">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="AA172">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB172">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AC172">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AD172">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE172">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF172">
         <v>1.57</v>
       </c>
       <c r="AG172">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK172">
-        <v>1.28</v>
+        <v>2.11</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,28 +28508,28 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="O173">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="P173">
-        <v>3.06</v>
+        <v>3.36</v>
       </c>
       <c r="Q173">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="R173">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S173">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T173">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U173">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V173">
         <v>1.42</v>
@@ -28538,34 +28538,34 @@
         <v>1.07</v>
       </c>
       <c r="X173">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z173">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA173">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AB173">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC173">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AD173">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE173">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF173">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG173">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK173">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="O174">
-        <v>3.52</v>
+        <v>4.45</v>
       </c>
       <c r="P174">
-        <v>3.36</v>
+        <v>5.31</v>
       </c>
       <c r="Q174">
-        <v>2.73</v>
+        <v>1.75</v>
       </c>
       <c r="R174">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="S174">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="T174">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="U174">
-        <v>2.75</v>
+        <v>2.09</v>
       </c>
       <c r="V174">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="W174">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X174">
         <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z174">
-        <v>3.5</v>
+        <v>6.12</v>
       </c>
       <c r="AA174">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AB174">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="AC174">
-        <v>3.04</v>
+        <v>2.06</v>
       </c>
       <c r="AD174">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AE174">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AF174">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG174">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AK174">
-        <v>1.66</v>
+        <v>3</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,80 +28834,80 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="O175">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="P175">
-        <v>4.33</v>
+        <v>3.06</v>
       </c>
       <c r="Q175">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="R175">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S175">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T175">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U175">
-        <v>2.32</v>
+        <v>2.81</v>
       </c>
       <c r="V175">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W175">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y175">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z175">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA175">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AB175">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AC175">
-        <v>2.79</v>
+        <v>3.14</v>
       </c>
       <c r="AD175">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE175">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF175">
+        <v>1.7</v>
+      </c>
+      <c r="AG175">
+        <v>2.04</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ175">
+        <v>1.24</v>
+      </c>
+      <c r="AK175">
         <v>1.57</v>
-      </c>
-      <c r="AG175">
-        <v>2.25</v>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ175">
-        <v>1.21</v>
-      </c>
-      <c r="AK175">
-        <v>2.11</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,80 +28997,80 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.5</v>
+        <v>3.32</v>
       </c>
       <c r="O176">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="P176">
-        <v>5.31</v>
+        <v>2.01</v>
       </c>
       <c r="Q176">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="R176">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="S176">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T176">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="U176">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="V176">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="W176">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z176">
-        <v>6.12</v>
+        <v>3.94</v>
       </c>
       <c r="AA176">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AB176">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="AC176">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AD176">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AE176">
+        <v>1.15</v>
+      </c>
+      <c r="AF176">
+        <v>1.57</v>
+      </c>
+      <c r="AG176">
+        <v>2.22</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
         <v>1.25</v>
       </c>
-      <c r="AF176">
-        <v>1.6</v>
-      </c>
-      <c r="AG176">
-        <v>2.14</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.13</v>
-      </c>
       <c r="AK176">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29984,55 +29984,55 @@
         <v>2.85</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U182">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V182">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W182">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X182">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK182">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.31</v>
+        <v>3.68</v>
       </c>
       <c r="O185">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="P185">
-        <v>2.65</v>
+        <v>1.74</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.68</v>
+        <v>2.31</v>
       </c>
       <c r="O186">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="P186">
-        <v>1.74</v>
+        <v>2.65</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.95</v>
+        <v>4.04</v>
       </c>
       <c r="O187">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="P187">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X187">
         <v>0</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>4.04</v>
+        <v>1.95</v>
       </c>
       <c r="O188">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="P188">
+        <v>2.8</v>
+      </c>
+      <c r="Q188">
+        <v>2.47</v>
+      </c>
+      <c r="R188">
+        <v>2.7</v>
+      </c>
+      <c r="S188">
+        <v>1.11</v>
+      </c>
+      <c r="T188">
+        <v>5.05</v>
+      </c>
+      <c r="U188">
+        <v>1.79</v>
+      </c>
+      <c r="V188">
+        <v>1.99</v>
+      </c>
+      <c r="W188">
+        <v>1.27</v>
+      </c>
+      <c r="X188">
+        <v>1.01</v>
+      </c>
+      <c r="Y188">
+        <v>1.02</v>
+      </c>
+      <c r="Z188">
+        <v>8.1</v>
+      </c>
+      <c r="AA188">
+        <v>1.22</v>
+      </c>
+      <c r="AB188">
+        <v>3.5</v>
+      </c>
+      <c r="AC188">
         <v>1.67</v>
       </c>
-      <c r="Q188">
-        <v>0</v>
-      </c>
-      <c r="R188">
-        <v>0</v>
-      </c>
-      <c r="S188">
-        <v>0</v>
-      </c>
-      <c r="T188">
-        <v>0</v>
-      </c>
-      <c r="U188">
-        <v>0</v>
-      </c>
-      <c r="V188">
-        <v>0</v>
-      </c>
-      <c r="W188">
-        <v>0</v>
-      </c>
-      <c r="X188">
-        <v>0</v>
-      </c>
-      <c r="Y188">
-        <v>0</v>
-      </c>
-      <c r="Z188">
-        <v>0</v>
-      </c>
-      <c r="AA188">
-        <v>0</v>
-      </c>
-      <c r="AB188">
-        <v>0</v>
-      </c>
-      <c r="AC188">
-        <v>0</v>
-      </c>
       <c r="AD188">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,80 +32909,80 @@
         </is>
       </c>
       <c r="N200">
-        <v>3.01</v>
+        <v>2.33</v>
       </c>
       <c r="O200">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="P200">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="Q200">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="R200">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="S200">
+        <v>1.3</v>
+      </c>
+      <c r="T200">
+        <v>3.3</v>
+      </c>
+      <c r="U200">
+        <v>2.53</v>
+      </c>
+      <c r="V200">
+        <v>1.44</v>
+      </c>
+      <c r="W200">
+        <v>1.07</v>
+      </c>
+      <c r="X200">
+        <v>1.03</v>
+      </c>
+      <c r="Y200">
+        <v>1.19</v>
+      </c>
+      <c r="Z200">
+        <v>3.78</v>
+      </c>
+      <c r="AA200">
+        <v>1.74</v>
+      </c>
+      <c r="AB200">
+        <v>2.02</v>
+      </c>
+      <c r="AC200">
+        <v>2.7</v>
+      </c>
+      <c r="AD200">
+        <v>1.36</v>
+      </c>
+      <c r="AE200">
+        <v>1.1</v>
+      </c>
+      <c r="AF200">
+        <v>1.62</v>
+      </c>
+      <c r="AG200">
+        <v>2.21</v>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ200">
         <v>1.28</v>
       </c>
-      <c r="T200">
-        <v>3.24</v>
-      </c>
-      <c r="U200">
-        <v>2.3</v>
-      </c>
-      <c r="V200">
-        <v>1.53</v>
-      </c>
-      <c r="W200">
-        <v>1.1</v>
-      </c>
-      <c r="X200">
-        <v>1.01</v>
-      </c>
-      <c r="Y200">
-        <v>1.15</v>
-      </c>
-      <c r="Z200">
-        <v>4.3</v>
-      </c>
-      <c r="AA200">
-        <v>1.57</v>
-      </c>
-      <c r="AB200">
-        <v>2.27</v>
-      </c>
-      <c r="AC200">
-        <v>2.35</v>
-      </c>
-      <c r="AD200">
-        <v>1.47</v>
-      </c>
-      <c r="AE200">
-        <v>1.16</v>
-      </c>
-      <c r="AF200">
-        <v>1.55</v>
-      </c>
-      <c r="AG200">
-        <v>2.33</v>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ200">
-        <v>1.25</v>
-      </c>
       <c r="AK200">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.72</v>
+        <v>3.01</v>
       </c>
       <c r="O201">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="P201">
-        <v>4.46</v>
+        <v>2.19</v>
       </c>
       <c r="Q201">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="R201">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S201">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T201">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="U201">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="V201">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W201">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X201">
         <v>1.01</v>
       </c>
       <c r="Y201">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z201">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="AA201">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB201">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AC201">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AD201">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE201">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF201">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AG201">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>1.25</v>
       </c>
       <c r="AK201">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="O202">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="P202">
-        <v>2.83</v>
+        <v>4.46</v>
       </c>
       <c r="Q202">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="R202">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S202">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T202">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U202">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="V202">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W202">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X202">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z202">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="AA202">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB202">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC202">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD202">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE202">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF202">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG202">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK202">
-        <v>1.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O204">
-        <v>3.98</v>
+        <v>3.36</v>
       </c>
       <c r="P204">
-        <v>4.56</v>
+        <v>3.85</v>
       </c>
       <c r="Q204">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="R204">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="S204">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T204">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U204">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="V204">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W204">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X204">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y204">
+        <v>1.31</v>
+      </c>
+      <c r="Z204">
+        <v>2.92</v>
+      </c>
+      <c r="AA204">
+        <v>2.08</v>
+      </c>
+      <c r="AB204">
+        <v>1.7</v>
+      </c>
+      <c r="AC204">
+        <v>3.58</v>
+      </c>
+      <c r="AD204">
         <v>1.21</v>
       </c>
-      <c r="Z204">
-        <v>4.27</v>
-      </c>
-      <c r="AA204">
-        <v>1.79</v>
-      </c>
-      <c r="AB204">
-        <v>2</v>
-      </c>
-      <c r="AC204">
-        <v>2.56</v>
-      </c>
-      <c r="AD204">
-        <v>1.4</v>
-      </c>
       <c r="AE204">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF204">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AG204">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK204">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.32</v>
+        <v>2.84</v>
       </c>
       <c r="O205">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P205">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="Q205">
-        <v>2.81</v>
+        <v>3.23</v>
       </c>
       <c r="R205">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="S205">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T205">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="U205">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="V205">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W205">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X205">
         <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z205">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA205">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB205">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC205">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="AD205">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE205">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF205">
         <v>1.5</v>
       </c>
       <c r="AG205">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK205">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="O206">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P206">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="Q206">
-        <v>3.23</v>
+        <v>2.81</v>
       </c>
       <c r="R206">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="S206">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T206">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="U206">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V206">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W206">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X206">
         <v>1.01</v>
       </c>
       <c r="Y206">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z206">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA206">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB206">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC206">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="AD206">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE206">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF206">
         <v>1.5</v>
       </c>
       <c r="AG206">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK206">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O207">
-        <v>3.36</v>
+        <v>3.98</v>
       </c>
       <c r="P207">
-        <v>3.85</v>
+        <v>4.56</v>
       </c>
       <c r="Q207">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="R207">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="S207">
+        <v>1.3</v>
+      </c>
+      <c r="T207">
+        <v>3.12</v>
+      </c>
+      <c r="U207">
+        <v>2.42</v>
+      </c>
+      <c r="V207">
+        <v>1.48</v>
+      </c>
+      <c r="W207">
+        <v>1.09</v>
+      </c>
+      <c r="X207">
+        <v>1.01</v>
+      </c>
+      <c r="Y207">
+        <v>1.21</v>
+      </c>
+      <c r="Z207">
+        <v>4.27</v>
+      </c>
+      <c r="AA207">
+        <v>1.79</v>
+      </c>
+      <c r="AB207">
+        <v>2</v>
+      </c>
+      <c r="AC207">
+        <v>2.56</v>
+      </c>
+      <c r="AD207">
         <v>1.4</v>
       </c>
-      <c r="T207">
-        <v>2.75</v>
-      </c>
-      <c r="U207">
-        <v>2.88</v>
-      </c>
-      <c r="V207">
-        <v>1.35</v>
-      </c>
-      <c r="W207">
-        <v>1.05</v>
-      </c>
-      <c r="X207">
-        <v>1.05</v>
-      </c>
-      <c r="Y207">
-        <v>1.31</v>
-      </c>
-      <c r="Z207">
-        <v>2.92</v>
-      </c>
-      <c r="AA207">
-        <v>2.08</v>
-      </c>
-      <c r="AB207">
-        <v>1.7</v>
-      </c>
-      <c r="AC207">
-        <v>3.58</v>
-      </c>
-      <c r="AD207">
-        <v>1.21</v>
-      </c>
       <c r="AE207">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF207">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AG207">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK207">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -37482,55 +37482,55 @@
         <v>0</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -38134,55 +38134,55 @@
         <v>2.25</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -40742,55 +40742,55 @@
         <v>2.41</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG248">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK248">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -42698,55 +42698,55 @@
         <v>9.449999999999999</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE260">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,13 +57848,13 @@
         </is>
       </c>
       <c r="N353">
-        <v>2.1</v>
+        <v>2.81</v>
       </c>
       <c r="O353">
-        <v>3.6</v>
+        <v>4.03</v>
       </c>
       <c r="P353">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q353">
         <v>0</v>
@@ -57887,16 +57887,16 @@
         <v>0</v>
       </c>
       <c r="AA353">
+        <v>0</v>
+      </c>
+      <c r="AB353">
+        <v>0</v>
+      </c>
+      <c r="AC353">
+        <v>2</v>
+      </c>
+      <c r="AD353">
         <v>1.68</v>
-      </c>
-      <c r="AB353">
-        <v>2.05</v>
-      </c>
-      <c r="AC353">
-        <v>0</v>
-      </c>
-      <c r="AD353">
-        <v>0</v>
       </c>
       <c r="AE353">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,13 +58011,13 @@
         </is>
       </c>
       <c r="N354">
-        <v>2.81</v>
+        <v>2.1</v>
       </c>
       <c r="O354">
-        <v>4.03</v>
+        <v>3.6</v>
       </c>
       <c r="P354">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q354">
         <v>0</v>
@@ -58050,16 +58050,16 @@
         <v>0</v>
       </c>
       <c r="AA354">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB354">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC354">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD354">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE354">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.52</v>
+        <v>2.77</v>
       </c>
       <c r="O17">
-        <v>4.47</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
-        <v>6.05</v>
+        <v>2.43</v>
       </c>
       <c r="Q17">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T17">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z17">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA17">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AB17">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AC17">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AD17">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.77</v>
+        <v>1.52</v>
       </c>
       <c r="O18">
-        <v>3.65</v>
+        <v>4.47</v>
       </c>
       <c r="P18">
-        <v>2.43</v>
+        <v>6.05</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="R18">
         <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="AA18">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AB18">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AC18">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AE18">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
+        <v>2</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.2</v>
+      </c>
+      <c r="AK18">
         <v>2.63</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.28</v>
-      </c>
-      <c r="AK18">
-        <v>1.43</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.76</v>
+        <v>2.34</v>
       </c>
       <c r="O51">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>3.84</v>
+        <v>2.77</v>
       </c>
       <c r="Q51">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="R51">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>5.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA51">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="AB51">
-        <v>2.89</v>
+        <v>2.11</v>
       </c>
       <c r="AC51">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>2.73</v>
+        <v>2.26</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P52">
-        <v>2.77</v>
+        <v>3.84</v>
       </c>
       <c r="Q52">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="W52">
+        <v>1.16</v>
+      </c>
+      <c r="X52">
+        <v>1.02</v>
+      </c>
+      <c r="Y52">
         <v>1.12</v>
       </c>
-      <c r="X52">
-        <v>1</v>
-      </c>
-      <c r="Y52">
-        <v>1.18</v>
-      </c>
       <c r="Z52">
-        <v>3.9</v>
+        <v>5.35</v>
       </c>
       <c r="AA52">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AB52">
-        <v>2.11</v>
+        <v>2.89</v>
       </c>
       <c r="AC52">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="AD52">
+        <v>1.83</v>
+      </c>
+      <c r="AE52">
+        <v>1.33</v>
+      </c>
+      <c r="AF52">
         <v>1.4</v>
       </c>
-      <c r="AE52">
-        <v>1.13</v>
-      </c>
-      <c r="AF52">
-        <v>1.55</v>
-      </c>
       <c r="AG52">
-        <v>2.26</v>
+        <v>2.73</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,65 +11067,65 @@
         </is>
       </c>
       <c r="N66">
+        <v>2.44</v>
+      </c>
+      <c r="O66">
+        <v>3.36</v>
+      </c>
+      <c r="P66">
+        <v>2.64</v>
+      </c>
+      <c r="Q66">
+        <v>2.87</v>
+      </c>
+      <c r="R66">
+        <v>2.15</v>
+      </c>
+      <c r="S66">
+        <v>1.36</v>
+      </c>
+      <c r="T66">
         <v>3.03</v>
       </c>
-      <c r="O66">
-        <v>3.26</v>
-      </c>
-      <c r="P66">
-        <v>2.26</v>
-      </c>
-      <c r="Q66">
-        <v>3.8</v>
-      </c>
-      <c r="R66">
-        <v>2.1</v>
-      </c>
-      <c r="S66">
+      <c r="U66">
+        <v>2.81</v>
+      </c>
+      <c r="V66">
         <v>1.4</v>
       </c>
-      <c r="T66">
-        <v>2.82</v>
-      </c>
-      <c r="U66">
-        <v>2.88</v>
-      </c>
-      <c r="V66">
-        <v>1.36</v>
-      </c>
       <c r="W66">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
+        <v>1.25</v>
+      </c>
+      <c r="Z66">
+        <v>3.55</v>
+      </c>
+      <c r="AA66">
+        <v>1.91</v>
+      </c>
+      <c r="AB66">
+        <v>1.86</v>
+      </c>
+      <c r="AC66">
+        <v>3.25</v>
+      </c>
+      <c r="AD66">
         <v>1.33</v>
       </c>
-      <c r="Z66">
-        <v>3.21</v>
-      </c>
-      <c r="AA66">
+      <c r="AE66">
+        <v>1.12</v>
+      </c>
+      <c r="AF66">
+        <v>1.69</v>
+      </c>
+      <c r="AG66">
         <v>2.05</v>
       </c>
-      <c r="AB66">
-        <v>1.75</v>
-      </c>
-      <c r="AC66">
-        <v>3.61</v>
-      </c>
-      <c r="AD66">
-        <v>1.27</v>
-      </c>
-      <c r="AE66">
-        <v>1.03</v>
-      </c>
-      <c r="AF66">
-        <v>1.75</v>
-      </c>
-      <c r="AG66">
-        <v>1.95</v>
-      </c>
       <c r="AH66" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK66">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.44</v>
+        <v>3.03</v>
       </c>
       <c r="O67">
-        <v>3.36</v>
+        <v>3.26</v>
       </c>
       <c r="P67">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="Q67">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="R67">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
+        <v>1.4</v>
+      </c>
+      <c r="T67">
+        <v>2.82</v>
+      </c>
+      <c r="U67">
+        <v>2.88</v>
+      </c>
+      <c r="V67">
         <v>1.36</v>
       </c>
-      <c r="T67">
-        <v>3.03</v>
-      </c>
-      <c r="U67">
-        <v>2.81</v>
-      </c>
-      <c r="V67">
-        <v>1.4</v>
-      </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y67">
+        <v>1.33</v>
+      </c>
+      <c r="Z67">
+        <v>3.21</v>
+      </c>
+      <c r="AA67">
+        <v>2.05</v>
+      </c>
+      <c r="AB67">
+        <v>1.75</v>
+      </c>
+      <c r="AC67">
+        <v>3.61</v>
+      </c>
+      <c r="AD67">
+        <v>1.27</v>
+      </c>
+      <c r="AE67">
+        <v>1.03</v>
+      </c>
+      <c r="AF67">
+        <v>1.75</v>
+      </c>
+      <c r="AG67">
+        <v>1.95</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.25</v>
       </c>
-      <c r="Z67">
-        <v>3.55</v>
-      </c>
-      <c r="AA67">
-        <v>1.91</v>
-      </c>
-      <c r="AB67">
-        <v>1.86</v>
-      </c>
-      <c r="AC67">
-        <v>3.25</v>
-      </c>
-      <c r="AD67">
-        <v>1.33</v>
-      </c>
-      <c r="AE67">
-        <v>1.12</v>
-      </c>
-      <c r="AF67">
-        <v>1.69</v>
-      </c>
-      <c r="AG67">
-        <v>2.05</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.38</v>
-      </c>
       <c r="AK67">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.95</v>
+        <v>2.02</v>
       </c>
       <c r="O88">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="P88">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.02</v>
+        <v>2.95</v>
       </c>
       <c r="O89">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="P89">
-        <v>2.99</v>
+        <v>2</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="O111">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="P111">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="Q111">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="R111">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="S111">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T111">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="U111">
-        <v>2.77</v>
+        <v>2.61</v>
       </c>
       <c r="V111">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z111">
-        <v>3.04</v>
+        <v>3.97</v>
       </c>
       <c r="AA111">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="AB111">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC111">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="AD111">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF111">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK111">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="O113">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="P113">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q113">
-        <v>4.1</v>
+        <v>4.59</v>
       </c>
       <c r="R113">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S113">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="T113">
+        <v>2.76</v>
+      </c>
+      <c r="U113">
         <v>3.12</v>
       </c>
-      <c r="U113">
-        <v>2.61</v>
-      </c>
       <c r="V113">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W113">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X113">
+        <v>1.02</v>
+      </c>
+      <c r="Y113">
+        <v>1.34</v>
+      </c>
+      <c r="Z113">
+        <v>3.12</v>
+      </c>
+      <c r="AA113">
+        <v>2.1</v>
+      </c>
+      <c r="AB113">
+        <v>1.71</v>
+      </c>
+      <c r="AC113">
+        <v>3.7</v>
+      </c>
+      <c r="AD113">
+        <v>1.25</v>
+      </c>
+      <c r="AE113">
         <v>1.03</v>
       </c>
-      <c r="Y113">
-        <v>1.22</v>
-      </c>
-      <c r="Z113">
-        <v>3.97</v>
-      </c>
-      <c r="AA113">
-        <v>1.73</v>
-      </c>
-      <c r="AB113">
-        <v>1.95</v>
-      </c>
-      <c r="AC113">
-        <v>2.85</v>
-      </c>
-      <c r="AD113">
-        <v>1.39</v>
-      </c>
-      <c r="AE113">
-        <v>1.14</v>
-      </c>
       <c r="AF113">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AG113">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,80 +18891,80 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.73</v>
+        <v>3.23</v>
       </c>
       <c r="O114">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="P114">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="Q114">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="R114">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S114">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T114">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="U114">
-        <v>3.12</v>
+        <v>2.77</v>
       </c>
       <c r="V114">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W114">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z114">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="AA114">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AB114">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC114">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD114">
+        <v>1.23</v>
+      </c>
+      <c r="AE114">
+        <v>1.04</v>
+      </c>
+      <c r="AF114">
+        <v>1.79</v>
+      </c>
+      <c r="AG114">
+        <v>1.87</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ114">
+        <v>1.26</v>
+      </c>
+      <c r="AK114">
         <v>1.25</v>
-      </c>
-      <c r="AE114">
-        <v>1.03</v>
-      </c>
-      <c r="AF114">
-        <v>1.89</v>
-      </c>
-      <c r="AG114">
-        <v>1.8</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>1.25</v>
-      </c>
-      <c r="AK114">
-        <v>1.19</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="O129">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="P129">
-        <v>8.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q129">
-        <v>1.69</v>
+        <v>2.54</v>
       </c>
       <c r="R129">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T129">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U129">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V129">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W129">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X129">
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z129">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA129">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB129">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AC129">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD129">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AE129">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF129">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AG129">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>3.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="O130">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P130">
-        <v>3.3</v>
+        <v>8.65</v>
       </c>
       <c r="Q130">
-        <v>2.54</v>
+        <v>1.69</v>
       </c>
       <c r="R130">
+        <v>2.63</v>
+      </c>
+      <c r="S130">
+        <v>1.22</v>
+      </c>
+      <c r="T130">
+        <v>3.8</v>
+      </c>
+      <c r="U130">
         <v>2.2</v>
       </c>
-      <c r="S130">
-        <v>1.29</v>
-      </c>
-      <c r="T130">
-        <v>3.3</v>
-      </c>
-      <c r="U130">
-        <v>2.42</v>
-      </c>
       <c r="V130">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W130">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X130">
         <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA130">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB130">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AC130">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD130">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AE130">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF130">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AG130">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK130">
-        <v>1.73</v>
+        <v>3.44</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,31 +24270,31 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.26</v>
+        <v>2.79</v>
       </c>
       <c r="O147">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P147">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="Q147">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R147">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="S147">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="T147">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U147">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="V147">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W147">
         <v>1.1</v>
@@ -24303,31 +24303,31 @@
         <v>1.01</v>
       </c>
       <c r="Y147">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z147">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA147">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="AB147">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AC147">
-        <v>3.13</v>
+        <v>2.4</v>
       </c>
       <c r="AD147">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AE147">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF147">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG147">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AK147">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,31 +24433,31 @@
         </is>
       </c>
       <c r="N148">
-        <v>2.79</v>
+        <v>2.26</v>
       </c>
       <c r="O148">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P148">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="Q148">
+        <v>2.8</v>
+      </c>
+      <c r="R148">
+        <v>2.13</v>
+      </c>
+      <c r="S148">
+        <v>1.34</v>
+      </c>
+      <c r="T148">
         <v>3.1</v>
       </c>
-      <c r="R148">
-        <v>2.29</v>
-      </c>
-      <c r="S148">
-        <v>1.27</v>
-      </c>
-      <c r="T148">
-        <v>3.6</v>
-      </c>
       <c r="U148">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="V148">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W148">
         <v>1.1</v>
@@ -24466,31 +24466,31 @@
         <v>1.01</v>
       </c>
       <c r="Y148">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z148">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA148">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AB148">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AC148">
-        <v>2.4</v>
+        <v>3.13</v>
       </c>
       <c r="AD148">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AE148">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF148">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG148">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
+        <v>1.27</v>
+      </c>
+      <c r="AK148">
         <v>1.57</v>
-      </c>
-      <c r="AK148">
-        <v>1.36</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,80 +28671,80 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.5</v>
+        <v>3.32</v>
       </c>
       <c r="O174">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="P174">
-        <v>5.31</v>
+        <v>2.01</v>
       </c>
       <c r="Q174">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="R174">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="S174">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T174">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="U174">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="V174">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="W174">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X174">
         <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z174">
-        <v>6.12</v>
+        <v>3.94</v>
       </c>
       <c r="AA174">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AB174">
-        <v>2.7</v>
+        <v>1.99</v>
       </c>
       <c r="AC174">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="AD174">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AE174">
+        <v>1.15</v>
+      </c>
+      <c r="AF174">
+        <v>1.57</v>
+      </c>
+      <c r="AG174">
+        <v>2.22</v>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ174">
         <v>1.25</v>
       </c>
-      <c r="AF174">
-        <v>1.6</v>
-      </c>
-      <c r="AG174">
-        <v>2.14</v>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ174">
-        <v>1.13</v>
-      </c>
       <c r="AK174">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="O175">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="P175">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="Q175">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="R175">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S175">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T175">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="U175">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="V175">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X175">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z175">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AA175">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB175">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AC175">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="AD175">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE175">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF175">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AG175">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>3.32</v>
+        <v>1.5</v>
       </c>
       <c r="O176">
-        <v>3.56</v>
+        <v>4.45</v>
       </c>
       <c r="P176">
-        <v>2.01</v>
+        <v>5.31</v>
       </c>
       <c r="Q176">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="R176">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S176">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T176">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="U176">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="V176">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W176">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z176">
-        <v>3.94</v>
+        <v>6.12</v>
       </c>
       <c r="AA176">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AB176">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="AC176">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AD176">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AE176">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF176">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG176">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK176">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="O177">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="P177">
-        <v>2.38</v>
+        <v>3.06</v>
       </c>
       <c r="Q177">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="R177">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T177">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="U177">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V177">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W177">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y177">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z177">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA177">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB177">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AC177">
-        <v>2.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD177">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE177">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF177">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AG177">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK177">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="O204">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="P204">
-        <v>3.85</v>
+        <v>2.31</v>
       </c>
       <c r="Q204">
-        <v>2.45</v>
+        <v>3.23</v>
       </c>
       <c r="R204">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="S204">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T204">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="U204">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="V204">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W204">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X204">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y204">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z204">
-        <v>2.92</v>
+        <v>4.15</v>
       </c>
       <c r="AA204">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AB204">
-        <v>1.7</v>
+        <v>2.21</v>
       </c>
       <c r="AC204">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD204">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AE204">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF204">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AG204">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK204">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,19 +33724,19 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="O205">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="P205">
-        <v>2.31</v>
+        <v>4.56</v>
       </c>
       <c r="Q205">
-        <v>3.23</v>
+        <v>2.19</v>
       </c>
       <c r="R205">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="S205">
         <v>1.3</v>
@@ -33745,43 +33745,43 @@
         <v>3.12</v>
       </c>
       <c r="U205">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="V205">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W205">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X205">
         <v>1.01</v>
       </c>
       <c r="Y205">
+        <v>1.21</v>
+      </c>
+      <c r="Z205">
+        <v>4.27</v>
+      </c>
+      <c r="AA205">
+        <v>1.79</v>
+      </c>
+      <c r="AB205">
+        <v>2</v>
+      </c>
+      <c r="AC205">
+        <v>2.56</v>
+      </c>
+      <c r="AD205">
+        <v>1.4</v>
+      </c>
+      <c r="AE205">
         <v>1.16</v>
       </c>
-      <c r="Z205">
-        <v>4.15</v>
-      </c>
-      <c r="AA205">
-        <v>1.67</v>
-      </c>
-      <c r="AB205">
-        <v>2.21</v>
-      </c>
-      <c r="AC205">
-        <v>2.63</v>
-      </c>
-      <c r="AD205">
-        <v>1.47</v>
-      </c>
-      <c r="AE205">
-        <v>1.18</v>
-      </c>
       <c r="AF205">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG205">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK205">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="O206">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="P206">
+        <v>3.85</v>
+      </c>
+      <c r="Q206">
+        <v>2.45</v>
+      </c>
+      <c r="R206">
+        <v>2.1</v>
+      </c>
+      <c r="S206">
+        <v>1.4</v>
+      </c>
+      <c r="T206">
         <v>2.75</v>
       </c>
-      <c r="Q206">
-        <v>2.81</v>
-      </c>
-      <c r="R206">
-        <v>2.28</v>
-      </c>
-      <c r="S206">
-        <v>1.27</v>
-      </c>
-      <c r="T206">
-        <v>3.32</v>
-      </c>
       <c r="U206">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="V206">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="W206">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X206">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y206">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z206">
-        <v>4.33</v>
+        <v>2.92</v>
       </c>
       <c r="AA206">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="AB206">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC206">
-        <v>2.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD206">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE206">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AF206">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG206">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK206">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,31 +34050,31 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="O207">
-        <v>3.98</v>
+        <v>3.64</v>
       </c>
       <c r="P207">
-        <v>4.56</v>
+        <v>2.75</v>
       </c>
       <c r="Q207">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="R207">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S207">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T207">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="U207">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="V207">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W207">
         <v>1.09</v>
@@ -34083,31 +34083,31 @@
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z207">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="AA207">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AB207">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC207">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AD207">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE207">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF207">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG207">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK207">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G249">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G250">
@@ -52469,13 +52469,13 @@
         </is>
       </c>
       <c r="N320">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O320">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P320">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q320">
         <v>0</v>
@@ -52508,10 +52508,10 @@
         <v>0</v>
       </c>
       <c r="AA320">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB320">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC320">
         <v>0</v>
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O334">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P334">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -54790,10 +54790,10 @@
         <v>0</v>
       </c>
       <c r="AA334">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB334">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC334">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.77</v>
+        <v>1.52</v>
       </c>
       <c r="O17">
-        <v>3.65</v>
+        <v>4.47</v>
       </c>
       <c r="P17">
-        <v>2.43</v>
+        <v>6.05</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="R17">
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="AA17">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AB17">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AC17">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="AD17">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AE17">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.2</v>
+      </c>
+      <c r="AK17">
         <v>2.63</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.28</v>
-      </c>
-      <c r="AK17">
-        <v>1.43</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.52</v>
+        <v>2.77</v>
       </c>
       <c r="O18">
-        <v>4.47</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>6.05</v>
+        <v>2.43</v>
       </c>
       <c r="Q18">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
         <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T18">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA18">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AD18">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK18">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="O89">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="P89">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="O90">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="P90">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="O111">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="P111">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q111">
-        <v>4.1</v>
+        <v>4.57</v>
       </c>
       <c r="R111">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="S111">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T111">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="U111">
-        <v>2.61</v>
+        <v>2.89</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W111">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z111">
-        <v>3.97</v>
+        <v>3.43</v>
       </c>
       <c r="AA111">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AB111">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC111">
-        <v>2.85</v>
+        <v>3.31</v>
       </c>
       <c r="AD111">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE111">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AG111">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="O112">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P112">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q112">
-        <v>3.99</v>
+        <v>4.11</v>
       </c>
       <c r="R112">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S112">
         <v>1.38</v>
       </c>
       <c r="T112">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U112">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V112">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W112">
         <v>1.05</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z112">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AA112">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB112">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC112">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AD112">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE112">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF112">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG112">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>1.26</v>
       </c>
       <c r="AK112">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="O114">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P114">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q114">
-        <v>4.11</v>
+        <v>3.99</v>
       </c>
       <c r="R114">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S114">
         <v>1.38</v>
       </c>
       <c r="T114">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U114">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V114">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W114">
         <v>1.05</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z114">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA114">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB114">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC114">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD114">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE114">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF114">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG114">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.26</v>
       </c>
       <c r="AK114">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="O115">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="P115">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q115">
-        <v>4.57</v>
+        <v>4.1</v>
       </c>
       <c r="R115">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="S115">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T115">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="U115">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="V115">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z115">
-        <v>3.43</v>
+        <v>3.97</v>
       </c>
       <c r="AA115">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB115">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC115">
-        <v>3.31</v>
+        <v>2.85</v>
       </c>
       <c r="AD115">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE115">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF115">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG115">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK115">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -20367,55 +20367,55 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R123">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S123">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T123">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U123">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V123">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W123">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X123">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y123">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z123">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA123">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC123">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD123">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE123">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF123">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG123">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK123">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="O129">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P129">
-        <v>3.3</v>
+        <v>8.65</v>
       </c>
       <c r="Q129">
-        <v>2.54</v>
+        <v>1.69</v>
       </c>
       <c r="R129">
+        <v>2.63</v>
+      </c>
+      <c r="S129">
+        <v>1.22</v>
+      </c>
+      <c r="T129">
+        <v>3.8</v>
+      </c>
+      <c r="U129">
         <v>2.2</v>
       </c>
-      <c r="S129">
-        <v>1.29</v>
-      </c>
-      <c r="T129">
-        <v>3.3</v>
-      </c>
-      <c r="U129">
-        <v>2.42</v>
-      </c>
       <c r="V129">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W129">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X129">
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z129">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA129">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB129">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AC129">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD129">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AE129">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF129">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AG129">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK129">
-        <v>1.73</v>
+        <v>3.44</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="O130">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="P130">
-        <v>8.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q130">
-        <v>1.69</v>
+        <v>2.54</v>
       </c>
       <c r="R130">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="S130">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T130">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U130">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V130">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W130">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X130">
         <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z130">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA130">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB130">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AC130">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD130">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AE130">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF130">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AG130">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK130">
-        <v>3.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="O175">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="P175">
-        <v>2.38</v>
+        <v>3.06</v>
       </c>
       <c r="Q175">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="R175">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S175">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T175">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="U175">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V175">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W175">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y175">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z175">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA175">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB175">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AC175">
-        <v>2.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD175">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE175">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF175">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AG175">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK175">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,80 +28997,80 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="O176">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="P176">
-        <v>5.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q176">
-        <v>1.75</v>
+        <v>3.12</v>
       </c>
       <c r="R176">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="S176">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>4.2</v>
+        <v>3.46</v>
       </c>
       <c r="U176">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="V176">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>6.12</v>
+        <v>4.2</v>
       </c>
       <c r="AA176">
+        <v>1.88</v>
+      </c>
+      <c r="AB176">
+        <v>1.96</v>
+      </c>
+      <c r="AC176">
+        <v>2.42</v>
+      </c>
+      <c r="AD176">
         <v>1.44</v>
       </c>
-      <c r="AB176">
-        <v>2.7</v>
-      </c>
-      <c r="AC176">
-        <v>2.06</v>
-      </c>
-      <c r="AD176">
-        <v>1.7</v>
-      </c>
       <c r="AE176">
+        <v>1.15</v>
+      </c>
+      <c r="AF176">
+        <v>1.51</v>
+      </c>
+      <c r="AG176">
+        <v>2.35</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
         <v>1.25</v>
       </c>
-      <c r="AF176">
-        <v>1.6</v>
-      </c>
-      <c r="AG176">
-        <v>2.14</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.13</v>
-      </c>
       <c r="AK176">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,80 +29160,80 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.16</v>
+        <v>1.5</v>
       </c>
       <c r="O177">
-        <v>3.44</v>
+        <v>4.45</v>
       </c>
       <c r="P177">
-        <v>3.06</v>
+        <v>5.31</v>
       </c>
       <c r="Q177">
-        <v>2.78</v>
+        <v>1.75</v>
       </c>
       <c r="R177">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="S177">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T177">
+        <v>4.2</v>
+      </c>
+      <c r="U177">
+        <v>2.09</v>
+      </c>
+      <c r="V177">
+        <v>1.7</v>
+      </c>
+      <c r="W177">
+        <v>1.17</v>
+      </c>
+      <c r="X177">
+        <v>1.01</v>
+      </c>
+      <c r="Y177">
+        <v>1.08</v>
+      </c>
+      <c r="Z177">
+        <v>6.12</v>
+      </c>
+      <c r="AA177">
+        <v>1.44</v>
+      </c>
+      <c r="AB177">
+        <v>2.7</v>
+      </c>
+      <c r="AC177">
+        <v>2.06</v>
+      </c>
+      <c r="AD177">
+        <v>1.7</v>
+      </c>
+      <c r="AE177">
+        <v>1.25</v>
+      </c>
+      <c r="AF177">
+        <v>1.6</v>
+      </c>
+      <c r="AG177">
+        <v>2.14</v>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ177">
+        <v>1.13</v>
+      </c>
+      <c r="AK177">
         <v>3</v>
-      </c>
-      <c r="U177">
-        <v>2.81</v>
-      </c>
-      <c r="V177">
-        <v>1.42</v>
-      </c>
-      <c r="W177">
-        <v>1.07</v>
-      </c>
-      <c r="X177">
-        <v>1</v>
-      </c>
-      <c r="Y177">
-        <v>1.24</v>
-      </c>
-      <c r="Z177">
-        <v>3.34</v>
-      </c>
-      <c r="AA177">
-        <v>1.87</v>
-      </c>
-      <c r="AB177">
-        <v>1.86</v>
-      </c>
-      <c r="AC177">
-        <v>3.14</v>
-      </c>
-      <c r="AD177">
-        <v>1.27</v>
-      </c>
-      <c r="AE177">
-        <v>1.06</v>
-      </c>
-      <c r="AF177">
-        <v>1.7</v>
-      </c>
-      <c r="AG177">
-        <v>2.04</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ177">
-        <v>1.24</v>
-      </c>
-      <c r="AK177">
-        <v>1.57</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="O179">
-        <v>3.48</v>
+        <v>3.72</v>
       </c>
       <c r="P179">
-        <v>3.32</v>
+        <v>3.87</v>
       </c>
       <c r="Q179">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="R179">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S179">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T179">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="U179">
         <v>2.6</v>
       </c>
       <c r="V179">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W179">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X179">
         <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z179">
-        <v>3.99</v>
+        <v>3.5</v>
       </c>
       <c r="AA179">
         <v>1.83</v>
       </c>
       <c r="AB179">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC179">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="AD179">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE179">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF179">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG179">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK179">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,31 +29649,31 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="O180">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P180">
-        <v>2.47</v>
+        <v>3.32</v>
       </c>
       <c r="Q180">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="R180">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S180">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T180">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="U180">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="V180">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W180">
         <v>1.08</v>
@@ -29682,31 +29682,31 @@
         <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z180">
-        <v>3.82</v>
+        <v>3.99</v>
       </c>
       <c r="AA180">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB180">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC180">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="AD180">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE180">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF180">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG180">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK180">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.81</v>
+        <v>2.67</v>
       </c>
       <c r="O181">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="P181">
-        <v>3.87</v>
+        <v>2.47</v>
       </c>
       <c r="Q181">
+        <v>3.2</v>
+      </c>
+      <c r="R181">
         <v>2.2</v>
       </c>
-      <c r="R181">
-        <v>2.25</v>
-      </c>
       <c r="S181">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T181">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="U181">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="V181">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W181">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X181">
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z181">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA181">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB181">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC181">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="AD181">
         <v>1.35</v>
       </c>
       <c r="AE181">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF181">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG181">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK181">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="O194">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P194">
-        <v>2.87</v>
+        <v>4.38</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="O195">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P195">
-        <v>4.38</v>
+        <v>2.87</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,31 +33724,31 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="O205">
-        <v>3.98</v>
+        <v>3.64</v>
       </c>
       <c r="P205">
-        <v>4.56</v>
+        <v>2.75</v>
       </c>
       <c r="Q205">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="R205">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S205">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T205">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="U205">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="V205">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W205">
         <v>1.09</v>
@@ -33757,31 +33757,31 @@
         <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z205">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="AA205">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AB205">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC205">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AD205">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE205">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF205">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG205">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK205">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,31 +34050,31 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="O207">
-        <v>3.64</v>
+        <v>3.98</v>
       </c>
       <c r="P207">
-        <v>2.75</v>
+        <v>4.56</v>
       </c>
       <c r="Q207">
-        <v>2.81</v>
+        <v>2.19</v>
       </c>
       <c r="R207">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="S207">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T207">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="U207">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V207">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W207">
         <v>1.09</v>
@@ -34083,31 +34083,31 @@
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z207">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="AA207">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AB207">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC207">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AD207">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE207">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF207">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG207">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK207">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -37482,55 +37482,55 @@
         <v>0</v>
       </c>
       <c r="Q228">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R228">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S228">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T228">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U228">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V228">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W228">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X228">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y228">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z228">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="AA228">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB228">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC228">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD228">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE228">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF228">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG228">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK228">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44328,55 +44328,55 @@
         <v>8</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O272">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P272">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="O315">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P315">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51693,10 +51693,10 @@
         <v>0</v>
       </c>
       <c r="AA315">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB315">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC315">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="O322">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="P322">
-        <v>4.12</v>
+        <v>3.12</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52828,10 +52828,10 @@
         <v>0</v>
       </c>
       <c r="Y322">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z322">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="O323">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="P323">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -52991,10 +52991,10 @@
         <v>0</v>
       </c>
       <c r="Y323">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z323">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA323">
         <v>0</v>
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q324">
         <v>0</v>
@@ -53154,10 +53154,10 @@
         <v>0</v>
       </c>
       <c r="Y324">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z324">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA324">
         <v>0</v>
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O333">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P333">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O343">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P343">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56263,10 +56263,10 @@
         <v>0</v>
       </c>
       <c r="AC343">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD343">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE343">
         <v>0</v>
@@ -57359,13 +57359,13 @@
         </is>
       </c>
       <c r="N350">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O350">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P350">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q350">
         <v>0</v>
@@ -57398,10 +57398,10 @@
         <v>0</v>
       </c>
       <c r="AA350">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB350">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC350">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.52</v>
+        <v>2.77</v>
       </c>
       <c r="O17">
-        <v>4.47</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
-        <v>6.05</v>
+        <v>2.43</v>
       </c>
       <c r="Q17">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T17">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z17">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="AA17">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AB17">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AC17">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="AD17">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AE17">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>2.63</v>
+        <v>1.43</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.77</v>
+        <v>1.52</v>
       </c>
       <c r="O18">
-        <v>3.65</v>
+        <v>4.47</v>
       </c>
       <c r="P18">
-        <v>2.43</v>
+        <v>6.05</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="R18">
         <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4.85</v>
+        <v>4.25</v>
       </c>
       <c r="AA18">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AB18">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AC18">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AE18">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
+        <v>2</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.2</v>
+      </c>
+      <c r="AK18">
         <v>2.63</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.28</v>
-      </c>
-      <c r="AK18">
-        <v>1.43</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>2.7</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
+        <v>2.02</v>
+      </c>
+      <c r="O87">
+        <v>3.52</v>
+      </c>
+      <c r="P87">
+        <v>2.99</v>
+      </c>
+      <c r="Q87">
+        <v>2.54</v>
+      </c>
+      <c r="R87">
+        <v>2.28</v>
+      </c>
+      <c r="S87">
+        <v>1.25</v>
+      </c>
+      <c r="T87">
+        <v>3.28</v>
+      </c>
+      <c r="U87">
         <v>2.25</v>
       </c>
-      <c r="O87">
-        <v>3.45</v>
-      </c>
-      <c r="P87">
-        <v>2.6</v>
-      </c>
-      <c r="Q87">
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <v>0</v>
-      </c>
-      <c r="S87">
-        <v>0</v>
-      </c>
-      <c r="T87">
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <v>0</v>
-      </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="O88">
-        <v>3.52</v>
+        <v>3.64</v>
       </c>
       <c r="P88">
-        <v>2.99</v>
+        <v>2.41</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O89">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="P89">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>2</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="O111">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="P111">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q111">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="R111">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S111">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T111">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="U111">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="V111">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z111">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AA111">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AB111">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AC111">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="AD111">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF111">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AG111">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="O113">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="P113">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q113">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="R113">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S113">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="T113">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="U113">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="V113">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W113">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X113">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z113">
-        <v>3.12</v>
+        <v>3.43</v>
       </c>
       <c r="AA113">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB113">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC113">
-        <v>3.7</v>
+        <v>3.31</v>
       </c>
       <c r="AD113">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE113">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF113">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AG113">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -20367,55 +20367,55 @@
         <v>0</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="O129">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="P129">
-        <v>8.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q129">
-        <v>1.69</v>
+        <v>2.54</v>
       </c>
       <c r="R129">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T129">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U129">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V129">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W129">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X129">
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z129">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA129">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB129">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AC129">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD129">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AE129">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF129">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AG129">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK129">
-        <v>3.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="O130">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P130">
-        <v>3.3</v>
+        <v>8.65</v>
       </c>
       <c r="Q130">
-        <v>2.54</v>
+        <v>1.69</v>
       </c>
       <c r="R130">
+        <v>2.63</v>
+      </c>
+      <c r="S130">
+        <v>1.22</v>
+      </c>
+      <c r="T130">
+        <v>3.8</v>
+      </c>
+      <c r="U130">
         <v>2.2</v>
       </c>
-      <c r="S130">
-        <v>1.29</v>
-      </c>
-      <c r="T130">
-        <v>3.3</v>
-      </c>
-      <c r="U130">
-        <v>2.42</v>
-      </c>
       <c r="V130">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W130">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X130">
         <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z130">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA130">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AB130">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AC130">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD130">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AE130">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AF130">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AG130">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK130">
-        <v>1.73</v>
+        <v>3.44</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>3.16</v>
+        <v>1.56</v>
       </c>
       <c r="O169">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
       <c r="P169">
-        <v>2.18</v>
+        <v>5.16</v>
       </c>
       <c r="Q169">
-        <v>3.82</v>
+        <v>2.14</v>
       </c>
       <c r="R169">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S169">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="T169">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="U169">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="V169">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W169">
         <v>1.06</v>
       </c>
       <c r="X169">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y169">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="Z169">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AA169">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AB169">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC169">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD169">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE169">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF169">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG169">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AK169">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.56</v>
+        <v>3.16</v>
       </c>
       <c r="O170">
-        <v>3.68</v>
+        <v>3.02</v>
       </c>
       <c r="P170">
-        <v>5.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q170">
-        <v>2.14</v>
+        <v>3.82</v>
       </c>
       <c r="R170">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S170">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="T170">
-        <v>2.68</v>
+        <v>2.39</v>
       </c>
       <c r="U170">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="V170">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W170">
         <v>1.06</v>
       </c>
       <c r="X170">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y170">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Z170">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AA170">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AB170">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC170">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD170">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE170">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF170">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG170">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AK170">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="O175">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="P175">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="Q175">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="R175">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S175">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T175">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="U175">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="V175">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X175">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z175">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AA175">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB175">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AC175">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="AD175">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE175">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF175">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AG175">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="O176">
-        <v>3.56</v>
+        <v>4.45</v>
       </c>
       <c r="P176">
-        <v>2.38</v>
+        <v>5.31</v>
       </c>
       <c r="Q176">
-        <v>3.12</v>
+        <v>1.75</v>
       </c>
       <c r="R176">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="S176">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T176">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="U176">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="V176">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="W176">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z176">
-        <v>4.2</v>
+        <v>6.12</v>
       </c>
       <c r="AA176">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AB176">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="AC176">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="AD176">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AE176">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF176">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AG176">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK176">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O177">
-        <v>4.45</v>
+        <v>3.72</v>
       </c>
       <c r="P177">
-        <v>5.31</v>
+        <v>3.87</v>
       </c>
       <c r="Q177">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="R177">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="S177">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="T177">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="U177">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="V177">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="W177">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z177">
-        <v>6.12</v>
+        <v>3.5</v>
       </c>
       <c r="AA177">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AB177">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC177">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="AD177">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AE177">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AF177">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG177">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK177">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="O179">
-        <v>3.72</v>
+        <v>3.44</v>
       </c>
       <c r="P179">
-        <v>3.87</v>
+        <v>3.06</v>
       </c>
       <c r="Q179">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="R179">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S179">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T179">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U179">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="V179">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W179">
         <v>1.07</v>
       </c>
       <c r="X179">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y179">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z179">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA179">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB179">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC179">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD179">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE179">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF179">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG179">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK179">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="O204">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P204">
-        <v>2.31</v>
+        <v>3.85</v>
       </c>
       <c r="Q204">
-        <v>3.23</v>
+        <v>2.45</v>
       </c>
       <c r="R204">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S204">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T204">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U204">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="V204">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W204">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X204">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y204">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="Z204">
-        <v>4.15</v>
+        <v>2.92</v>
       </c>
       <c r="AA204">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="AB204">
-        <v>2.21</v>
+        <v>1.7</v>
       </c>
       <c r="AC204">
-        <v>2.63</v>
+        <v>3.58</v>
       </c>
       <c r="AD204">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AE204">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="AF204">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG204">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK204">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.32</v>
+        <v>2.84</v>
       </c>
       <c r="O205">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P205">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="Q205">
-        <v>2.81</v>
+        <v>3.23</v>
       </c>
       <c r="R205">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="S205">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T205">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="U205">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="V205">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W205">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X205">
         <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z205">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA205">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB205">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC205">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="AD205">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE205">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF205">
         <v>1.5</v>
       </c>
       <c r="AG205">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK205">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="O206">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="P206">
-        <v>3.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q206">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="R206">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S206">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T206">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="U206">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="V206">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W206">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X206">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y206">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z206">
-        <v>2.92</v>
+        <v>4.33</v>
       </c>
       <c r="AA206">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AB206">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC206">
-        <v>3.58</v>
+        <v>2.42</v>
       </c>
       <c r="AD206">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE206">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF206">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AG206">
-        <v>1.83</v>
+        <v>2.42</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK206">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -35200,55 +35200,55 @@
         <v>2.75</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -36341,55 +36341,55 @@
         <v>0</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S221">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T221">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U221">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V221">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W221">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X221">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y221">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z221">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA221">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB221">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC221">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD221">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG221">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK221">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36667,55 +36667,55 @@
         <v>1.72</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V223">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W223">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X223">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC223">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD223">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK223">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37482,55 +37482,55 @@
         <v>0</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37971,55 +37971,55 @@
         <v>0</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38297,55 +38297,55 @@
         <v>1.33</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>6.97</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G236">
@@ -39601,34 +39601,34 @@
         <v>2.22</v>
       </c>
       <c r="Q241">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R241">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S241">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T241">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U241">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V241">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W241">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y241">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z241">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AA241">
         <v>1.66</v>
@@ -39637,19 +39637,19 @@
         <v>2.05</v>
       </c>
       <c r="AC241">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD241">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE241">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF241">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG241">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK241">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39764,40 +39764,40 @@
         <v>1.36</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T242">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U242">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V242">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X242">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y242">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z242">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AC242">
         <v>1.98</v>
@@ -39806,13 +39806,13 @@
         <v>1.88</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG242">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK242">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -40090,55 +40090,55 @@
         <v>6</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40253,34 +40253,34 @@
         <v>3.18</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S245">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T245">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U245">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V245">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W245">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X245">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z245">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA245">
         <v>1.79</v>
@@ -40289,19 +40289,19 @@
         <v>1.98</v>
       </c>
       <c r="AC245">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD245">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG245">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK245">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40579,55 +40579,55 @@
         <v>2.97</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T247">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U247">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V247">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W247">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X247">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG247">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK247">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41883,55 +41883,55 @@
         <v>11.4</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42076,10 +42076,10 @@
         <v>0</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC256">
         <v>0</v>
@@ -42526,64 +42526,64 @@
         </is>
       </c>
       <c r="N259">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O259">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P259">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U259">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V259">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X259">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y259">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z259">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA259">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB259">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC259">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD259">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE259">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF259">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG259">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK259">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42852,64 +42852,64 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q261">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R261">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S261">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T261">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U261">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V261">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W261">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X261">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y261">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z261">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA261">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB261">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC261">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD261">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE261">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF261">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG261">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK261">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43187,55 +43187,55 @@
         <v>3.7</v>
       </c>
       <c r="Q263">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R263">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S263">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T263">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U263">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V263">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W263">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X263">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y263">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z263">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC263">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD263">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE263">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF263">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG263">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK263">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -44491,55 +44491,55 @@
         <v>1.65</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44654,55 +44654,55 @@
         <v>2.7</v>
       </c>
       <c r="Q272">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R272">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S272">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T272">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U272">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V272">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W272">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X272">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y272">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z272">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC272">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD272">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE272">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF272">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG272">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK272">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44817,55 +44817,55 @@
         <v>3.71</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44980,55 +44980,55 @@
         <v>3.34</v>
       </c>
       <c r="Q274">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R274">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S274">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T274">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U274">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V274">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W274">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X274">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y274">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z274">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC274">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD274">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE274">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF274">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG274">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK274">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45143,55 +45143,55 @@
         <v>3.94</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W275">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X275">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE275">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45306,34 +45306,34 @@
         <v>1.38</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>7.24</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA276">
         <v>1.8</v>
@@ -45342,19 +45342,19 @@
         <v>2</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y278">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z278">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG278">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -46121,55 +46121,55 @@
         <v>2.11</v>
       </c>
       <c r="Q281">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R281">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S281">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T281">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U281">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V281">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W281">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X281">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y281">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z281">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA281">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB281">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC281">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD281">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE281">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF281">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG281">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK281">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46447,55 +46447,55 @@
         <v>11.9</v>
       </c>
       <c r="Q283">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="R283">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T283">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U283">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V283">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="W283">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y283">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z283">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AE283">
         <v>1.77</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG283">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK283">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46936,55 +46936,55 @@
         <v>1.92</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47099,55 +47099,55 @@
         <v>5</v>
       </c>
       <c r="Q287">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R287">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T287">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U287">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V287">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W287">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X287">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA287">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB287">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC287">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD287">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE287">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG287">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK287">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47262,55 +47262,55 @@
         <v>2.1</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG288">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47588,34 +47588,34 @@
         <v>3.25</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA290">
         <v>2.05</v>
@@ -47624,19 +47624,19 @@
         <v>1.66</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47751,55 +47751,55 @@
         <v>2.83</v>
       </c>
       <c r="Q291">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R291">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S291">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T291">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U291">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V291">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W291">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X291">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y291">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z291">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC291">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD291">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE291">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF291">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG291">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK291">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47914,34 +47914,34 @@
         <v>2.79</v>
       </c>
       <c r="Q292">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R292">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S292">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T292">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U292">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V292">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W292">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X292">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y292">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z292">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA292">
         <v>1.9</v>
@@ -47950,19 +47950,19 @@
         <v>1.9</v>
       </c>
       <c r="AC292">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD292">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE292">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF292">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG292">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK292">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q294">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R294">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S294">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T294">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U294">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V294">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W294">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y294">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z294">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AA294">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB294">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC294">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD294">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE294">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF294">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG294">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK294">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="O296">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="P296">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48590,10 +48590,10 @@
         <v>0</v>
       </c>
       <c r="Y296">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Z296">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AA296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="O297">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="P297">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="O298">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P298">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -48916,10 +48916,10 @@
         <v>0</v>
       </c>
       <c r="Y298">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Z298">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AA298">
         <v>0</v>
@@ -49055,34 +49055,34 @@
         <v>2.13</v>
       </c>
       <c r="Q299">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R299">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S299">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T299">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U299">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V299">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W299">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X299">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y299">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z299">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA299">
         <v>1.85</v>
@@ -49091,19 +49091,19 @@
         <v>1.94</v>
       </c>
       <c r="AC299">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD299">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE299">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF299">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG299">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK299">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49381,40 +49381,40 @@
         <v>1.36</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y301">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z301">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AC301">
         <v>1.83</v>
@@ -49423,13 +49423,13 @@
         <v>1.98</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49544,55 +49544,55 @@
         <v>2.37</v>
       </c>
       <c r="Q302">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R302">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S302">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T302">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U302">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V302">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W302">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y302">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z302">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AA302">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB302">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC302">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD302">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE302">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF302">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG302">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK302">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50033,55 +50033,55 @@
         <v>3.11</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T305">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U305">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V305">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X305">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y305">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z305">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC305">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD305">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF305">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG305">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK305">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50522,55 +50522,55 @@
         <v>6.4</v>
       </c>
       <c r="Q308">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R308">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S308">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T308">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U308">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V308">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W308">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X308">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z308">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA308">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB308">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC308">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD308">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE308">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF308">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG308">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK308">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50685,55 +50685,55 @@
         <v>5.91</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA309">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB309">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50848,55 +50848,55 @@
         <v>1.78</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51174,55 +51174,55 @@
         <v>9.9</v>
       </c>
       <c r="Q312">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R312">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S312">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T312">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U312">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V312">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W312">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X312">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z312">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA312">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB312">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC312">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD312">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE312">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF312">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG312">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK312">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51337,55 +51337,55 @@
         <v>1.99</v>
       </c>
       <c r="Q313">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R313">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S313">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T313">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U313">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V313">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W313">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X313">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y313">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z313">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA313">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB313">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC313">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD313">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE313">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF313">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG313">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK313">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51500,55 +51500,55 @@
         <v>2.25</v>
       </c>
       <c r="Q314">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R314">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S314">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T314">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U314">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V314">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W314">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X314">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y314">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z314">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AA314">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB314">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC314">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD314">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE314">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF314">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG314">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK314">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51817,64 +51817,64 @@
         </is>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O316">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P316">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q316">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R316">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S316">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T316">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U316">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V316">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W316">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X316">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y316">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z316">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA316">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB316">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC316">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD316">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE316">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF316">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG316">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK316">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -51989,34 +51989,34 @@
         <v>1.37</v>
       </c>
       <c r="Q317">
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="R317">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S317">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T317">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U317">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V317">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W317">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X317">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y317">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z317">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="AA317">
         <v>1.53</v>
@@ -52025,19 +52025,19 @@
         <v>2.3</v>
       </c>
       <c r="AC317">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD317">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE317">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF317">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG317">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,10 +52050,10 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK317">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL317">
         <v>0</v>
@@ -52152,55 +52152,55 @@
         <v>5.31</v>
       </c>
       <c r="Q318">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R318">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S318">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T318">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U318">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V318">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W318">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X318">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y318">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z318">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="AA318">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB318">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC318">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD318">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE318">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF318">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG318">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
@@ -52213,10 +52213,10 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK318">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL318">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="O322">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="P322">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52828,10 +52828,10 @@
         <v>0</v>
       </c>
       <c r="Y322">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z322">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="O323">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="P323">
-        <v>4.12</v>
+        <v>3.12</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -52991,10 +52991,10 @@
         <v>0</v>
       </c>
       <c r="Y323">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z323">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA323">
         <v>0</v>
@@ -54271,55 +54271,55 @@
         <v>4.35</v>
       </c>
       <c r="Q331">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R331">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S331">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T331">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U331">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V331">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W331">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X331">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y331">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z331">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA331">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB331">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC331">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD331">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE331">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF331">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG331">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH331" t="inlineStr">
         <is>
@@ -54332,10 +54332,10 @@
         </is>
       </c>
       <c r="AJ331">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK331">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL331">
         <v>0</v>
@@ -56227,40 +56227,40 @@
         <v>8.300000000000001</v>
       </c>
       <c r="Q343">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R343">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S343">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T343">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U343">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V343">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W343">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X343">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y343">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z343">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA343">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB343">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC343">
         <v>1.98</v>
@@ -56269,13 +56269,13 @@
         <v>1.83</v>
       </c>
       <c r="AE343">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF343">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG343">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH343" t="inlineStr">
         <is>
@@ -56288,10 +56288,10 @@
         </is>
       </c>
       <c r="AJ343">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK343">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL343">
         <v>0</v>
@@ -58672,34 +58672,34 @@
         <v>2.05</v>
       </c>
       <c r="Q358">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R358">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S358">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T358">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U358">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V358">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W358">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X358">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y358">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z358">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA358">
         <v>1.6</v>
@@ -58708,19 +58708,19 @@
         <v>2.15</v>
       </c>
       <c r="AC358">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD358">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE358">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF358">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG358">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH358" t="inlineStr">
         <is>
@@ -58733,10 +58733,10 @@
         </is>
       </c>
       <c r="AJ358">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK358">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL358">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.26</v>
+        <v>1.57</v>
       </c>
       <c r="O4">
-        <v>3.13</v>
+        <v>3.66</v>
       </c>
       <c r="P4">
-        <v>3.17</v>
+        <v>5.11</v>
       </c>
       <c r="Q4">
-        <v>3.07</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U4">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V4">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>3.48</v>
+        <v>3.33</v>
       </c>
       <c r="AA4">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AB4">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC4">
-        <v>3.49</v>
+        <v>3.38</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.57</v>
+        <v>2.59</v>
       </c>
       <c r="O5">
-        <v>3.66</v>
+        <v>3.19</v>
       </c>
       <c r="P5">
-        <v>5.11</v>
+        <v>2.66</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.86</v>
       </c>
       <c r="R5">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z5">
-        <v>3.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA5">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AB5">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.38</v>
+        <v>2.74</v>
       </c>
       <c r="AD5">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF5">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P6">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="Q6">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="R6">
         <v>2.06</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1323,28 +1323,28 @@
         <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK6">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G7">
@@ -1453,58 +1453,58 @@
         <v>2.26</v>
       </c>
       <c r="O7">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="P7">
-        <v>2.84</v>
+        <v>3.17</v>
       </c>
       <c r="Q7">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U7">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z7">
-        <v>3.41</v>
+        <v>3.48</v>
       </c>
       <c r="AA7">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC7">
-        <v>3.35</v>
+        <v>3.49</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
         <v>2</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK7">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="O8">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q8">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U8">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>4.15</v>
+        <v>3.43</v>
       </c>
       <c r="AA8">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC8">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.71</v>
+        <v>2.66</v>
       </c>
       <c r="O22">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="P22">
-        <v>4.35</v>
+        <v>2.31</v>
       </c>
       <c r="Q22">
-        <v>2.41</v>
+        <v>3.52</v>
       </c>
       <c r="R22">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>2.79</v>
+        <v>3.07</v>
       </c>
       <c r="U22">
+        <v>2.62</v>
+      </c>
+      <c r="V22">
+        <v>1.39</v>
+      </c>
+      <c r="W22">
+        <v>1.1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1.26</v>
+      </c>
+      <c r="Z22">
+        <v>3.68</v>
+      </c>
+      <c r="AA22">
+        <v>1.91</v>
+      </c>
+      <c r="AB22">
+        <v>1.85</v>
+      </c>
+      <c r="AC22">
         <v>3.09</v>
       </c>
-      <c r="V22">
-        <v>1.34</v>
-      </c>
-      <c r="W22">
-        <v>1.06</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
+      <c r="AD22">
+        <v>1.35</v>
+      </c>
+      <c r="AE22">
+        <v>1.08</v>
+      </c>
+      <c r="AF22">
+        <v>1.65</v>
+      </c>
+      <c r="AG22">
+        <v>2.08</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.33</v>
+      </c>
+      <c r="AK22">
         <v>1.36</v>
-      </c>
-      <c r="Z22">
-        <v>3.05</v>
-      </c>
-      <c r="AA22">
-        <v>2.08</v>
-      </c>
-      <c r="AB22">
-        <v>1.73</v>
-      </c>
-      <c r="AC22">
-        <v>3.68</v>
-      </c>
-      <c r="AD22">
-        <v>1.26</v>
-      </c>
-      <c r="AE22">
-        <v>1.04</v>
-      </c>
-      <c r="AF22">
-        <v>1.87</v>
-      </c>
-      <c r="AG22">
-        <v>1.82</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.21</v>
-      </c>
-      <c r="AK22">
-        <v>1.91</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="O23">
-        <v>3.24</v>
+        <v>3.44</v>
       </c>
       <c r="P23">
-        <v>2.31</v>
+        <v>4.35</v>
       </c>
       <c r="Q23">
-        <v>3.52</v>
+        <v>2.41</v>
       </c>
       <c r="R23">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>3.07</v>
+        <v>2.79</v>
       </c>
       <c r="U23">
-        <v>2.62</v>
+        <v>3.09</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
+        <v>1.36</v>
+      </c>
+      <c r="Z23">
+        <v>3.05</v>
+      </c>
+      <c r="AA23">
+        <v>2.08</v>
+      </c>
+      <c r="AB23">
+        <v>1.73</v>
+      </c>
+      <c r="AC23">
+        <v>3.68</v>
+      </c>
+      <c r="AD23">
         <v>1.26</v>
       </c>
-      <c r="Z23">
-        <v>3.68</v>
-      </c>
-      <c r="AA23">
+      <c r="AE23">
+        <v>1.04</v>
+      </c>
+      <c r="AF23">
+        <v>1.87</v>
+      </c>
+      <c r="AG23">
+        <v>1.82</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.21</v>
+      </c>
+      <c r="AK23">
         <v>1.91</v>
-      </c>
-      <c r="AB23">
-        <v>1.85</v>
-      </c>
-      <c r="AC23">
-        <v>3.09</v>
-      </c>
-      <c r="AD23">
-        <v>1.35</v>
-      </c>
-      <c r="AE23">
-        <v>1.08</v>
-      </c>
-      <c r="AF23">
-        <v>1.65</v>
-      </c>
-      <c r="AG23">
-        <v>2.08</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.33</v>
-      </c>
-      <c r="AK23">
-        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="O86">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="P86">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="Q86">
-        <v>2.71</v>
+        <v>2.54</v>
       </c>
       <c r="R86">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="S86">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U86">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V86">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W86">
         <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z86">
-        <v>5.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB86">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="AC86">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AD86">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AE86">
+        <v>1.18</v>
+      </c>
+      <c r="AF86">
+        <v>1.48</v>
+      </c>
+      <c r="AG86">
+        <v>2.45</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
         <v>1.2</v>
       </c>
-      <c r="AF86">
-        <v>1.41</v>
-      </c>
-      <c r="AG86">
-        <v>2.66</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.19</v>
-      </c>
       <c r="AK86">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,80 +14490,80 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="O87">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="P87">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="Q87">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="R87">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S87">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T87">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U87">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V87">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W87">
         <v>1.14</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z87">
-        <v>4.45</v>
+        <v>5.2</v>
       </c>
       <c r="AA87">
+        <v>1.44</v>
+      </c>
+      <c r="AB87">
+        <v>2.43</v>
+      </c>
+      <c r="AC87">
+        <v>2.18</v>
+      </c>
+      <c r="AD87">
+        <v>1.58</v>
+      </c>
+      <c r="AE87">
+        <v>1.2</v>
+      </c>
+      <c r="AF87">
+        <v>1.41</v>
+      </c>
+      <c r="AG87">
+        <v>2.66</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
+        <v>1.19</v>
+      </c>
+      <c r="AK87">
         <v>1.53</v>
-      </c>
-      <c r="AB87">
-        <v>2.29</v>
-      </c>
-      <c r="AC87">
-        <v>2.28</v>
-      </c>
-      <c r="AD87">
-        <v>1.5</v>
-      </c>
-      <c r="AE87">
-        <v>1.18</v>
-      </c>
-      <c r="AF87">
-        <v>1.48</v>
-      </c>
-      <c r="AG87">
-        <v>2.45</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.2</v>
-      </c>
-      <c r="AK87">
-        <v>1.62</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O88">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="P88">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="Q88">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R88">
+        <v>2.25</v>
+      </c>
+      <c r="S88">
+        <v>1.25</v>
+      </c>
+      <c r="T88">
+        <v>3.5</v>
+      </c>
+      <c r="U88">
         <v>2.38</v>
       </c>
-      <c r="S88">
-        <v>1.2</v>
-      </c>
-      <c r="T88">
-        <v>4</v>
-      </c>
-      <c r="U88">
-        <v>2.1</v>
-      </c>
       <c r="V88">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z88">
-        <v>5.45</v>
+        <v>4.15</v>
       </c>
       <c r="AA88">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB88">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="AC88">
-        <v>2.11</v>
+        <v>2.43</v>
       </c>
       <c r="AD88">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE88">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF88">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AG88">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK88">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O89">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="P89">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q89">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V89">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="W89">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z89">
-        <v>4.15</v>
+        <v>5.45</v>
       </c>
       <c r="AA89">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AB89">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AC89">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AD89">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AE89">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF89">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AG89">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK89">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,34 +18565,34 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="O112">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="P112">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="Q112">
-        <v>4.11</v>
+        <v>4.57</v>
       </c>
       <c r="R112">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="S112">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T112">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="U112">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="V112">
         <v>1.38</v>
       </c>
       <c r="W112">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
         <v>1.01</v>
@@ -18601,28 +18601,28 @@
         <v>1.29</v>
       </c>
       <c r="Z112">
-        <v>3.04</v>
+        <v>3.43</v>
       </c>
       <c r="AA112">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AB112">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="AD112">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE112">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG112">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="O113">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="P113">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q113">
-        <v>4.57</v>
+        <v>4.1</v>
       </c>
       <c r="R113">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="S113">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="U113">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="V113">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>3.43</v>
+        <v>3.97</v>
       </c>
       <c r="AA113">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB113">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC113">
-        <v>3.31</v>
+        <v>2.85</v>
       </c>
       <c r="AD113">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE113">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF113">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG113">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK113">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="O114">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P114">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q114">
-        <v>3.99</v>
+        <v>4.11</v>
       </c>
       <c r="R114">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S114">
         <v>1.38</v>
       </c>
       <c r="T114">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U114">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V114">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W114">
         <v>1.05</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z114">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AA114">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB114">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC114">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AD114">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE114">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF114">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG114">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.26</v>
       </c>
       <c r="AK114">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.42</v>
+        <v>3.13</v>
       </c>
       <c r="O115">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="Q115">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="R115">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="S115">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T115">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="U115">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="V115">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
+        <v>1.02</v>
+      </c>
+      <c r="Y115">
+        <v>1.31</v>
+      </c>
+      <c r="Z115">
+        <v>2.92</v>
+      </c>
+      <c r="AA115">
+        <v>2.05</v>
+      </c>
+      <c r="AB115">
+        <v>1.66</v>
+      </c>
+      <c r="AC115">
+        <v>3.58</v>
+      </c>
+      <c r="AD115">
+        <v>1.21</v>
+      </c>
+      <c r="AE115">
         <v>1.03</v>
       </c>
-      <c r="Y115">
-        <v>1.22</v>
-      </c>
-      <c r="Z115">
-        <v>3.97</v>
-      </c>
-      <c r="AA115">
-        <v>1.73</v>
-      </c>
-      <c r="AB115">
-        <v>1.95</v>
-      </c>
-      <c r="AC115">
-        <v>2.85</v>
-      </c>
-      <c r="AD115">
-        <v>1.39</v>
-      </c>
-      <c r="AE115">
-        <v>1.14</v>
-      </c>
       <c r="AF115">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AG115">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK115">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>4.68</v>
+        <v>4.16</v>
       </c>
       <c r="O156">
-        <v>4.57</v>
+        <v>4.08</v>
       </c>
       <c r="P156">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q156">
-        <v>5.04</v>
+        <v>4.1</v>
       </c>
       <c r="R156">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="S156">
         <v>1.22</v>
       </c>
       <c r="T156">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U156">
         <v>2.05</v>
       </c>
       <c r="V156">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W156">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z156">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AA156">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AB156">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="AC156">
+        <v>1.9</v>
+      </c>
+      <c r="AD156">
+        <v>1.8</v>
+      </c>
+      <c r="AE156">
+        <v>1.34</v>
+      </c>
+      <c r="AF156">
+        <v>1.35</v>
+      </c>
+      <c r="AG156">
+        <v>2.93</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
         <v>2</v>
       </c>
-      <c r="AD156">
-        <v>1.72</v>
-      </c>
-      <c r="AE156">
-        <v>1.23</v>
-      </c>
-      <c r="AF156">
-        <v>1.5</v>
-      </c>
-      <c r="AG156">
-        <v>2.4</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.17</v>
-      </c>
       <c r="AK156">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>4.16</v>
+        <v>4.68</v>
       </c>
       <c r="O157">
-        <v>4.08</v>
+        <v>4.57</v>
       </c>
       <c r="P157">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Q157">
-        <v>4.1</v>
+        <v>5.04</v>
       </c>
       <c r="R157">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="S157">
         <v>1.22</v>
       </c>
       <c r="T157">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="U157">
         <v>2.05</v>
       </c>
       <c r="V157">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W157">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X157">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z157">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA157">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AB157">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="AC157">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD157">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AE157">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AF157">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AG157">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AK157">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,80 +27367,80 @@
         </is>
       </c>
       <c r="N166">
+        <v>3.65</v>
+      </c>
+      <c r="O166">
+        <v>3.54</v>
+      </c>
+      <c r="P166">
+        <v>1.82</v>
+      </c>
+      <c r="Q166">
+        <v>4.28</v>
+      </c>
+      <c r="R166">
+        <v>2.19</v>
+      </c>
+      <c r="S166">
         <v>1.27</v>
       </c>
-      <c r="O166">
-        <v>5.1</v>
-      </c>
-      <c r="P166">
-        <v>8.15</v>
-      </c>
-      <c r="Q166">
-        <v>1.7</v>
-      </c>
-      <c r="R166">
-        <v>2.62</v>
-      </c>
-      <c r="S166">
+      <c r="T166">
+        <v>3.18</v>
+      </c>
+      <c r="U166">
+        <v>2.61</v>
+      </c>
+      <c r="V166">
+        <v>1.46</v>
+      </c>
+      <c r="W166">
+        <v>1.09</v>
+      </c>
+      <c r="X166">
+        <v>1.03</v>
+      </c>
+      <c r="Y166">
+        <v>1.18</v>
+      </c>
+      <c r="Z166">
+        <v>3.84</v>
+      </c>
+      <c r="AA166">
+        <v>1.75</v>
+      </c>
+      <c r="AB166">
+        <v>2.04</v>
+      </c>
+      <c r="AC166">
+        <v>2.78</v>
+      </c>
+      <c r="AD166">
+        <v>1.34</v>
+      </c>
+      <c r="AE166">
+        <v>1.15</v>
+      </c>
+      <c r="AF166">
+        <v>1.63</v>
+      </c>
+      <c r="AG166">
+        <v>2.2</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ166">
         <v>1.2</v>
       </c>
-      <c r="T166">
-        <v>4</v>
-      </c>
-      <c r="U166">
-        <v>2.18</v>
-      </c>
-      <c r="V166">
-        <v>1.58</v>
-      </c>
-      <c r="W166">
-        <v>1.17</v>
-      </c>
-      <c r="X166">
-        <v>1.02</v>
-      </c>
-      <c r="Y166">
-        <v>1.12</v>
-      </c>
-      <c r="Z166">
-        <v>4.91</v>
-      </c>
-      <c r="AA166">
-        <v>1.51</v>
-      </c>
-      <c r="AB166">
-        <v>2.5</v>
-      </c>
-      <c r="AC166">
-        <v>2.34</v>
-      </c>
-      <c r="AD166">
-        <v>1.57</v>
-      </c>
-      <c r="AE166">
-        <v>1.21</v>
-      </c>
-      <c r="AF166">
-        <v>1.8</v>
-      </c>
-      <c r="AG166">
-        <v>1.86</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ166">
-        <v>1.08</v>
-      </c>
       <c r="AK166">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>3.65</v>
+        <v>1.27</v>
       </c>
       <c r="O167">
-        <v>3.54</v>
+        <v>5.1</v>
       </c>
       <c r="P167">
-        <v>1.82</v>
+        <v>8.15</v>
       </c>
       <c r="Q167">
-        <v>4.28</v>
+        <v>1.7</v>
       </c>
       <c r="R167">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="S167">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T167">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="U167">
-        <v>2.61</v>
+        <v>2.18</v>
       </c>
       <c r="V167">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="W167">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X167">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y167">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z167">
-        <v>3.84</v>
+        <v>4.91</v>
       </c>
       <c r="AA167">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AB167">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AC167">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="AD167">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AE167">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF167">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG167">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK167">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.56</v>
+        <v>3.16</v>
       </c>
       <c r="O169">
-        <v>3.68</v>
+        <v>3.02</v>
       </c>
       <c r="P169">
-        <v>5.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q169">
-        <v>2.14</v>
+        <v>3.82</v>
       </c>
       <c r="R169">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S169">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="T169">
-        <v>2.68</v>
+        <v>2.39</v>
       </c>
       <c r="U169">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="V169">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W169">
         <v>1.06</v>
       </c>
       <c r="X169">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y169">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Z169">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AA169">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AB169">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC169">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD169">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE169">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF169">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG169">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AK169">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>3.16</v>
+        <v>1.56</v>
       </c>
       <c r="O170">
-        <v>3.02</v>
+        <v>3.68</v>
       </c>
       <c r="P170">
-        <v>2.18</v>
+        <v>5.16</v>
       </c>
       <c r="Q170">
-        <v>3.82</v>
+        <v>2.14</v>
       </c>
       <c r="R170">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S170">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="T170">
-        <v>2.39</v>
+        <v>2.68</v>
       </c>
       <c r="U170">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="V170">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W170">
         <v>1.06</v>
       </c>
       <c r="X170">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y170">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="Z170">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AA170">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AB170">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC170">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD170">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE170">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF170">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG170">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AK170">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="O175">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="P175">
-        <v>2.38</v>
+        <v>3.06</v>
       </c>
       <c r="Q175">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="R175">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S175">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T175">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="U175">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V175">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W175">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y175">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z175">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA175">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB175">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AC175">
-        <v>2.42</v>
+        <v>3.14</v>
       </c>
       <c r="AD175">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE175">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF175">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AG175">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK175">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="O177">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P177">
-        <v>3.87</v>
+        <v>2.38</v>
       </c>
       <c r="Q177">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="R177">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S177">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T177">
-        <v>3.08</v>
+        <v>3.46</v>
       </c>
       <c r="U177">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V177">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W177">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z177">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA177">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB177">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC177">
-        <v>3.05</v>
+        <v>2.42</v>
       </c>
       <c r="AD177">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AE177">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AG177">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="O179">
-        <v>3.44</v>
+        <v>3.72</v>
       </c>
       <c r="P179">
-        <v>3.06</v>
+        <v>3.87</v>
       </c>
       <c r="Q179">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="R179">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S179">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T179">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U179">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="V179">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W179">
         <v>1.07</v>
       </c>
       <c r="X179">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z179">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA179">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB179">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC179">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AD179">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE179">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF179">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG179">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK179">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,65 +33887,65 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O206">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="P206">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="Q206">
         <v>2.81</v>
       </c>
       <c r="R206">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="S206">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T206">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="U206">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V206">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W206">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X206">
         <v>1.01</v>
       </c>
       <c r="Y206">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z206">
-        <v>4.33</v>
+        <v>4.56</v>
       </c>
       <c r="AA206">
+        <v>1.65</v>
+      </c>
+      <c r="AB206">
+        <v>2.1</v>
+      </c>
+      <c r="AC206">
+        <v>2.43</v>
+      </c>
+      <c r="AD206">
+        <v>1.46</v>
+      </c>
+      <c r="AE206">
+        <v>1.17</v>
+      </c>
+      <c r="AF206">
         <v>1.57</v>
       </c>
-      <c r="AB206">
+      <c r="AG206">
         <v>2.25</v>
       </c>
-      <c r="AC206">
-        <v>2.42</v>
-      </c>
-      <c r="AD206">
-        <v>1.44</v>
-      </c>
-      <c r="AE206">
-        <v>1.15</v>
-      </c>
-      <c r="AF206">
-        <v>1.5</v>
-      </c>
-      <c r="AG206">
-        <v>2.42</v>
-      </c>
       <c r="AH206" t="inlineStr">
         <is>
           <t>[]</t>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK206">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,31 +34050,31 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="O207">
-        <v>3.98</v>
+        <v>3.64</v>
       </c>
       <c r="P207">
-        <v>4.56</v>
+        <v>2.75</v>
       </c>
       <c r="Q207">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="R207">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S207">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T207">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="U207">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="V207">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W207">
         <v>1.09</v>
@@ -34083,31 +34083,31 @@
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z207">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="AA207">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AB207">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC207">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AD207">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE207">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF207">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG207">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK207">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O208">
-        <v>3.54</v>
+        <v>3.98</v>
       </c>
       <c r="P208">
-        <v>2.83</v>
+        <v>4.56</v>
       </c>
       <c r="Q208">
-        <v>2.81</v>
+        <v>2.19</v>
       </c>
       <c r="R208">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="S208">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T208">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="U208">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="V208">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W208">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
+        <v>1.21</v>
+      </c>
+      <c r="Z208">
+        <v>4.27</v>
+      </c>
+      <c r="AA208">
+        <v>1.79</v>
+      </c>
+      <c r="AB208">
+        <v>2</v>
+      </c>
+      <c r="AC208">
+        <v>2.56</v>
+      </c>
+      <c r="AD208">
+        <v>1.4</v>
+      </c>
+      <c r="AE208">
         <v>1.16</v>
       </c>
-      <c r="Z208">
-        <v>4.56</v>
-      </c>
-      <c r="AA208">
-        <v>1.65</v>
-      </c>
-      <c r="AB208">
-        <v>2.1</v>
-      </c>
-      <c r="AC208">
-        <v>2.43</v>
-      </c>
-      <c r="AD208">
-        <v>1.46</v>
-      </c>
-      <c r="AE208">
-        <v>1.17</v>
-      </c>
       <c r="AF208">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG208">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK208">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -45469,55 +45469,55 @@
         <v>3.74</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC277">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD277">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -47455,10 +47455,10 @@
         <v>0</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC289">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.59</v>
+        <v>4.58</v>
       </c>
       <c r="O309">
-        <v>4.58</v>
+        <v>4.27</v>
       </c>
       <c r="P309">
-        <v>5.91</v>
+        <v>1.78</v>
       </c>
       <c r="Q309">
-        <v>2.33</v>
+        <v>4.45</v>
       </c>
       <c r="R309">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="S309">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T309">
         <v>3.42</v>
       </c>
       <c r="U309">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V309">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W309">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X309">
         <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z309">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA309">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AB309">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC309">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="AD309">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AE309">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF309">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG309">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK309">
-        <v>2.05</v>
+        <v>1.26</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
+        <v>1.59</v>
+      </c>
+      <c r="O310">
         <v>4.58</v>
       </c>
-      <c r="O310">
-        <v>4.27</v>
-      </c>
       <c r="P310">
-        <v>1.78</v>
+        <v>5.91</v>
       </c>
       <c r="Q310">
-        <v>4.45</v>
+        <v>2.33</v>
       </c>
       <c r="R310">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="S310">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T310">
         <v>3.42</v>
       </c>
       <c r="U310">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V310">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W310">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X310">
         <v>1.01</v>
       </c>
       <c r="Y310">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z310">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA310">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AB310">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC310">
-        <v>2.33</v>
+        <v>2.61</v>
       </c>
       <c r="AD310">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AE310">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF310">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG310">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK310">
-        <v>1.26</v>
+        <v>2.05</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51011,55 +51011,55 @@
         <v>1.7</v>
       </c>
       <c r="Q311">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R311">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S311">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T311">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U311">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V311">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W311">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X311">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y311">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z311">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="AA311">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB311">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC311">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD311">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE311">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF311">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG311">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK311">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51663,34 +51663,34 @@
         <v>2.1</v>
       </c>
       <c r="Q315">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R315">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S315">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T315">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U315">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V315">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W315">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X315">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y315">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z315">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA315">
         <v>1.85</v>
@@ -51699,19 +51699,19 @@
         <v>1.9</v>
       </c>
       <c r="AC315">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AD315">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE315">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF315">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG315">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK315">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -52315,55 +52315,55 @@
         <v>1.62</v>
       </c>
       <c r="Q319">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R319">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S319">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T319">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="U319">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V319">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W319">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X319">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y319">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z319">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA319">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB319">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC319">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD319">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE319">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF319">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG319">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK319">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -53486,10 +53486,10 @@
         <v>0</v>
       </c>
       <c r="AA326">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB326">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC326">
         <v>1.8</v>
@@ -53945,40 +53945,40 @@
         <v>7.13</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S329">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T329">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U329">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V329">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W329">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X329">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA329">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB329">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC329">
         <v>2.3</v>
@@ -53987,13 +53987,13 @@
         <v>1.53</v>
       </c>
       <c r="AE329">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF329">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG329">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK329">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54434,34 +54434,34 @@
         <v>6.75</v>
       </c>
       <c r="Q332">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R332">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S332">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T332">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U332">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V332">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W332">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X332">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y332">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z332">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA332">
         <v>1.78</v>
@@ -54470,19 +54470,19 @@
         <v>1.9</v>
       </c>
       <c r="AC332">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD332">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE332">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF332">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG332">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK332">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL332">
         <v>0</v>
@@ -54597,55 +54597,55 @@
         <v>2.9</v>
       </c>
       <c r="Q333">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R333">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S333">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T333">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U333">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V333">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W333">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X333">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y333">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z333">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA333">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB333">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC333">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD333">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE333">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF333">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG333">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
@@ -54658,10 +54658,10 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK333">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL333">
         <v>0</v>
@@ -54923,55 +54923,55 @@
         <v>2.47</v>
       </c>
       <c r="Q335">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R335">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S335">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T335">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U335">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V335">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W335">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X335">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y335">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z335">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA335">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB335">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC335">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD335">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE335">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF335">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG335">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK335">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,64 +55240,64 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.63</v>
+        <v>2.86</v>
       </c>
       <c r="O337">
-        <v>3.88</v>
+        <v>3.54</v>
       </c>
       <c r="P337">
-        <v>4.28</v>
+        <v>2.11</v>
       </c>
       <c r="Q337">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R337">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S337">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T337">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U337">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V337">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W337">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X337">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y337">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z337">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA337">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB337">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC337">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD337">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE337">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF337">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG337">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK337">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,64 +55403,64 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.86</v>
+        <v>1.32</v>
       </c>
       <c r="O338">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="P338">
-        <v>2.11</v>
+        <v>7.13</v>
       </c>
       <c r="Q338">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R338">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S338">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T338">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U338">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V338">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W338">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X338">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y338">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z338">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA338">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB338">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC338">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD338">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE338">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF338">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG338">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,10 +55473,10 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK338">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,64 +55566,64 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="O339">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="P339">
-        <v>7.13</v>
+        <v>4.28</v>
       </c>
       <c r="Q339">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R339">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S339">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T339">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U339">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V339">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W339">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X339">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y339">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z339">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA339">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB339">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC339">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD339">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE339">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF339">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG339">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK339">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55738,55 +55738,55 @@
         <v>2.44</v>
       </c>
       <c r="Q340">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R340">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S340">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T340">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U340">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V340">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W340">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X340">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y340">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z340">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA340">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB340">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC340">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD340">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE340">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF340">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG340">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK340">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -55901,55 +55901,55 @@
         <v>4.31</v>
       </c>
       <c r="Q341">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R341">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S341">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T341">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U341">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V341">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W341">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X341">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y341">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z341">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA341">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB341">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC341">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD341">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE341">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF341">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG341">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH341" t="inlineStr">
         <is>
@@ -55962,10 +55962,10 @@
         </is>
       </c>
       <c r="AJ341">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK341">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -56064,34 +56064,34 @@
         <v>4.48</v>
       </c>
       <c r="Q342">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R342">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S342">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T342">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U342">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V342">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W342">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X342">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y342">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z342">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AA342">
         <v>1.92</v>
@@ -56100,19 +56100,19 @@
         <v>1.84</v>
       </c>
       <c r="AC342">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD342">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE342">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF342">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG342">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH342" t="inlineStr">
         <is>
@@ -56125,10 +56125,10 @@
         </is>
       </c>
       <c r="AJ342">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK342">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="O345">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P345">
-        <v>4.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56589,10 +56589,10 @@
         <v>0</v>
       </c>
       <c r="AC345">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD345">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE345">
         <v>0</v>
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O346">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="P346">
-        <v>2.38</v>
+        <v>4.38</v>
       </c>
       <c r="Q346">
         <v>0</v>
@@ -56746,16 +56746,16 @@
         <v>0</v>
       </c>
       <c r="AA346">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB346">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC346">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD346">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE346">
         <v>0</v>
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,13 +56870,13 @@
         </is>
       </c>
       <c r="N347">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O347">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P347">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="Q347">
         <v>0</v>
@@ -56909,16 +56909,16 @@
         <v>0</v>
       </c>
       <c r="AA347">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB347">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC347">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD347">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O348">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P348">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57078,10 +57078,10 @@
         <v>0</v>
       </c>
       <c r="AC348">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD348">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE348">
         <v>0</v>
@@ -57368,34 +57368,34 @@
         <v>3.32</v>
       </c>
       <c r="Q350">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R350">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S350">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T350">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U350">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V350">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W350">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X350">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y350">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z350">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA350">
         <v>2.05</v>
@@ -57404,19 +57404,19 @@
         <v>1.66</v>
       </c>
       <c r="AC350">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD350">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE350">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF350">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG350">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH350" t="inlineStr">
         <is>
@@ -57429,10 +57429,10 @@
         </is>
       </c>
       <c r="AJ350">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK350">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL350">
         <v>0</v>
@@ -57531,34 +57531,34 @@
         <v>3.4</v>
       </c>
       <c r="Q351">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R351">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S351">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T351">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U351">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V351">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W351">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X351">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y351">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z351">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA351">
         <v>1.84</v>
@@ -57567,19 +57567,19 @@
         <v>1.92</v>
       </c>
       <c r="AC351">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD351">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE351">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF351">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG351">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH351" t="inlineStr">
         <is>
@@ -57592,10 +57592,10 @@
         </is>
       </c>
       <c r="AJ351">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK351">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL351">
         <v>0</v>
@@ -57694,55 +57694,55 @@
         <v>3.46</v>
       </c>
       <c r="Q352">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R352">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S352">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T352">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U352">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V352">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W352">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X352">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y352">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z352">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA352">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB352">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC352">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD352">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE352">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF352">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG352">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH352" t="inlineStr">
         <is>
@@ -57755,10 +57755,10 @@
         </is>
       </c>
       <c r="AJ352">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK352">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL352">
         <v>0</v>
@@ -58346,55 +58346,55 @@
         <v>2.75</v>
       </c>
       <c r="Q356">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R356">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S356">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T356">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U356">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V356">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W356">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X356">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y356">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z356">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA356">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB356">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC356">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD356">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE356">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF356">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG356">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH356" t="inlineStr">
         <is>
@@ -58407,10 +58407,10 @@
         </is>
       </c>
       <c r="AJ356">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK356">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58509,34 +58509,34 @@
         <v>2.41</v>
       </c>
       <c r="Q357">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R357">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S357">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T357">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U357">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V357">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W357">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X357">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y357">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z357">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA357">
         <v>1.9</v>
@@ -58545,19 +58545,19 @@
         <v>1.85</v>
       </c>
       <c r="AC357">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD357">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE357">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF357">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG357">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH357" t="inlineStr">
         <is>
@@ -58570,10 +58570,10 @@
         </is>
       </c>
       <c r="AJ357">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK357">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL357">
         <v>0</v>
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G359">
@@ -58826,64 +58826,64 @@
         </is>
       </c>
       <c r="N359">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O359">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="P359">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="Q359">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R359">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S359">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T359">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U359">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V359">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W359">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X359">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y359">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z359">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA359">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB359">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC359">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD359">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE359">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF359">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG359">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH359" t="inlineStr">
         <is>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="AJ359">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK359">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL359">
         <v>0</v>
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G360">
@@ -58989,64 +58989,64 @@
         </is>
       </c>
       <c r="N360">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="O360">
-        <v>3.49</v>
+        <v>3.55</v>
       </c>
       <c r="P360">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="Q360">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R360">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S360">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T360">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U360">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V360">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W360">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X360">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y360">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z360">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA360">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB360">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC360">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD360">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE360">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF360">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG360">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH360" t="inlineStr">
         <is>
@@ -59059,10 +59059,10 @@
         </is>
       </c>
       <c r="AJ360">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK360">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL360">
         <v>0</v>
@@ -59161,55 +59161,55 @@
         <v>2.02</v>
       </c>
       <c r="Q361">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R361">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S361">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T361">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U361">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V361">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W361">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X361">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y361">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z361">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA361">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB361">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC361">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD361">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE361">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF361">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG361">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH361" t="inlineStr">
         <is>
@@ -59222,10 +59222,10 @@
         </is>
       </c>
       <c r="AJ361">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK361">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL361">
         <v>0</v>
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G362">
@@ -59315,13 +59315,13 @@
         </is>
       </c>
       <c r="N362">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="O362">
-        <v>3.98</v>
+        <v>4.09</v>
       </c>
       <c r="P362">
-        <v>2.94</v>
+        <v>3.34</v>
       </c>
       <c r="Q362">
         <v>0</v>
@@ -59360,10 +59360,10 @@
         <v>0</v>
       </c>
       <c r="AC362">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD362">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AE362">
         <v>0</v>
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G363">
@@ -59478,13 +59478,13 @@
         </is>
       </c>
       <c r="N363">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="O363">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="P363">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="Q363">
         <v>0</v>
@@ -59526,7 +59526,7 @@
         <v>2.15</v>
       </c>
       <c r="AD363">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE363">
         <v>0</v>
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G364">
@@ -59641,13 +59641,13 @@
         </is>
       </c>
       <c r="N364">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O364">
-        <v>4.09</v>
+        <v>3.8</v>
       </c>
       <c r="P364">
-        <v>3.34</v>
+        <v>1.98</v>
       </c>
       <c r="Q364">
         <v>0</v>
@@ -59686,10 +59686,10 @@
         <v>0</v>
       </c>
       <c r="AC364">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD364">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AE364">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU365"/>
+  <dimension ref="A1:AU366"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.59</v>
+        <v>2.26</v>
       </c>
       <c r="O5">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="P5">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="Q5">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="R5">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U5">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>4.15</v>
+        <v>3.41</v>
       </c>
       <c r="AA5">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC5">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="AD5">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK5">
         <v>1.55</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G6">
@@ -1290,58 +1290,58 @@
         <v>2.26</v>
       </c>
       <c r="O6">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="P6">
-        <v>2.84</v>
+        <v>3.17</v>
       </c>
       <c r="Q6">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="R6">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="U6">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.41</v>
+        <v>3.48</v>
       </c>
       <c r="AA6">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB6">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC6">
-        <v>3.35</v>
+        <v>3.49</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK6">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="O7">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>3.17</v>
+        <v>2.58</v>
       </c>
       <c r="Q7">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="R7">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="U7">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
         <v>1.08</v>
@@ -1483,31 +1483,31 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.48</v>
+        <v>3.43</v>
       </c>
       <c r="AA7">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
         <v>1.81</v>
       </c>
       <c r="AC7">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="P8">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>3.43</v>
+        <v>4.15</v>
       </c>
       <c r="AA8">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB8">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AD8">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG8">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.52</v>
+        <v>1.84</v>
       </c>
       <c r="O73">
-        <v>3.55</v>
+        <v>3.92</v>
       </c>
       <c r="P73">
-        <v>2.52</v>
+        <v>3.69</v>
       </c>
       <c r="Q73">
-        <v>3.38</v>
+        <v>2.38</v>
       </c>
       <c r="R73">
+        <v>2.5</v>
+      </c>
+      <c r="S73">
+        <v>1.25</v>
+      </c>
+      <c r="T73">
+        <v>3.6</v>
+      </c>
+      <c r="U73">
         <v>2.32</v>
       </c>
-      <c r="S73">
-        <v>1.26</v>
-      </c>
-      <c r="T73">
-        <v>3.4</v>
-      </c>
-      <c r="U73">
-        <v>2.3</v>
-      </c>
       <c r="V73">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W73">
         <v>1.11</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
         <v>1.17</v>
       </c>
       <c r="Z73">
-        <v>4</v>
+        <v>4.82</v>
       </c>
       <c r="AA73">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB73">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="AC73">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="AD73">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AE73">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF73">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.84</v>
+        <v>2.52</v>
       </c>
       <c r="O74">
-        <v>3.92</v>
+        <v>3.55</v>
       </c>
       <c r="P74">
-        <v>3.69</v>
+        <v>2.52</v>
       </c>
       <c r="Q74">
-        <v>2.38</v>
+        <v>3.38</v>
       </c>
       <c r="R74">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S74">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T74">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U74">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V74">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W74">
         <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
         <v>1.17</v>
       </c>
       <c r="Z74">
-        <v>4.82</v>
+        <v>4</v>
       </c>
       <c r="AA74">
+        <v>1.65</v>
+      </c>
+      <c r="AB74">
+        <v>2.2</v>
+      </c>
+      <c r="AC74">
+        <v>2.72</v>
+      </c>
+      <c r="AD74">
+        <v>1.45</v>
+      </c>
+      <c r="AE74">
+        <v>1.13</v>
+      </c>
+      <c r="AF74">
         <v>1.57</v>
       </c>
-      <c r="AB74">
-        <v>2.39</v>
-      </c>
-      <c r="AC74">
-        <v>2.44</v>
-      </c>
-      <c r="AD74">
-        <v>1.55</v>
-      </c>
-      <c r="AE74">
-        <v>1.15</v>
-      </c>
-      <c r="AF74">
-        <v>1.53</v>
-      </c>
       <c r="AG74">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AK74">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="O86">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="P86">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="Q86">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="R86">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S86">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V86">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W86">
         <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>4.45</v>
+        <v>5.2</v>
       </c>
       <c r="AA86">
+        <v>1.44</v>
+      </c>
+      <c r="AB86">
+        <v>2.43</v>
+      </c>
+      <c r="AC86">
+        <v>2.18</v>
+      </c>
+      <c r="AD86">
+        <v>1.58</v>
+      </c>
+      <c r="AE86">
+        <v>1.2</v>
+      </c>
+      <c r="AF86">
+        <v>1.41</v>
+      </c>
+      <c r="AG86">
+        <v>2.66</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
+        <v>1.19</v>
+      </c>
+      <c r="AK86">
         <v>1.53</v>
-      </c>
-      <c r="AB86">
-        <v>2.29</v>
-      </c>
-      <c r="AC86">
-        <v>2.28</v>
-      </c>
-      <c r="AD86">
-        <v>1.5</v>
-      </c>
-      <c r="AE86">
-        <v>1.18</v>
-      </c>
-      <c r="AF86">
-        <v>1.48</v>
-      </c>
-      <c r="AG86">
-        <v>2.45</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.2</v>
-      </c>
-      <c r="AK86">
-        <v>1.62</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O87">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="P87">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q87">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R87">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S87">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T87">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U87">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V87">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W87">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z87">
-        <v>5.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA87">
+        <v>1.6</v>
+      </c>
+      <c r="AB87">
+        <v>2.15</v>
+      </c>
+      <c r="AC87">
+        <v>2.43</v>
+      </c>
+      <c r="AD87">
         <v>1.44</v>
       </c>
-      <c r="AB87">
-        <v>2.43</v>
-      </c>
-      <c r="AC87">
-        <v>2.18</v>
-      </c>
-      <c r="AD87">
-        <v>1.58</v>
-      </c>
       <c r="AE87">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF87">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AG87">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK87">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O88">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="P88">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="Q88">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R88">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S88">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V88">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="W88">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>4.15</v>
+        <v>5.45</v>
       </c>
       <c r="AA88">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AB88">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AC88">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AD88">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AE88">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF88">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AG88">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.33</v>
+        <v>2.95</v>
       </c>
       <c r="O89">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="P89">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="Q89">
-        <v>2.82</v>
+        <v>3.48</v>
       </c>
       <c r="R89">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S89">
         <v>1.2</v>
@@ -14852,28 +14852,28 @@
         <v>1.08</v>
       </c>
       <c r="Z89">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AA89">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AC89">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD89">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE89">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF89">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AG89">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK89">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.95</v>
+        <v>2.02</v>
       </c>
       <c r="O90">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="P90">
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="Q90">
-        <v>3.48</v>
+        <v>2.54</v>
       </c>
       <c r="R90">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="S90">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U90">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V90">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
-        <v>5.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA90">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB90">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AC90">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AD90">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AE90">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF90">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AG90">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="O112">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="P112">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q112">
-        <v>4.57</v>
+        <v>4.1</v>
       </c>
       <c r="R112">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="S112">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="U112">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="V112">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z112">
-        <v>3.43</v>
+        <v>3.97</v>
       </c>
       <c r="AA112">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AB112">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC112">
-        <v>3.31</v>
+        <v>2.85</v>
       </c>
       <c r="AD112">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE112">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF112">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AG112">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
+        <v>3.23</v>
+      </c>
+      <c r="O113">
+        <v>3.14</v>
+      </c>
+      <c r="P113">
+        <v>2.09</v>
+      </c>
+      <c r="Q113">
+        <v>4.11</v>
+      </c>
+      <c r="R113">
+        <v>2</v>
+      </c>
+      <c r="S113">
+        <v>1.38</v>
+      </c>
+      <c r="T113">
+        <v>2.69</v>
+      </c>
+      <c r="U113">
+        <v>2.77</v>
+      </c>
+      <c r="V113">
+        <v>1.38</v>
+      </c>
+      <c r="W113">
+        <v>1.05</v>
+      </c>
+      <c r="X113">
+        <v>1.01</v>
+      </c>
+      <c r="Y113">
+        <v>1.29</v>
+      </c>
+      <c r="Z113">
+        <v>3.04</v>
+      </c>
+      <c r="AA113">
+        <v>1.99</v>
+      </c>
+      <c r="AB113">
+        <v>1.7</v>
+      </c>
+      <c r="AC113">
         <v>3.42</v>
       </c>
-      <c r="O113">
-        <v>3.42</v>
-      </c>
-      <c r="P113">
-        <v>1.92</v>
-      </c>
-      <c r="Q113">
-        <v>4.1</v>
-      </c>
-      <c r="R113">
-        <v>2.32</v>
-      </c>
-      <c r="S113">
-        <v>1.28</v>
-      </c>
-      <c r="T113">
-        <v>3.12</v>
-      </c>
-      <c r="U113">
-        <v>2.61</v>
-      </c>
-      <c r="V113">
-        <v>1.44</v>
-      </c>
-      <c r="W113">
-        <v>1.08</v>
-      </c>
-      <c r="X113">
-        <v>1.03</v>
-      </c>
-      <c r="Y113">
-        <v>1.22</v>
-      </c>
-      <c r="Z113">
-        <v>3.97</v>
-      </c>
-      <c r="AA113">
-        <v>1.73</v>
-      </c>
-      <c r="AB113">
-        <v>1.95</v>
-      </c>
-      <c r="AC113">
-        <v>2.85</v>
-      </c>
       <c r="AD113">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AE113">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AG113">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK113">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="O114">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P114">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q114">
-        <v>4.11</v>
+        <v>3.99</v>
       </c>
       <c r="R114">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S114">
         <v>1.38</v>
       </c>
       <c r="T114">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U114">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V114">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W114">
         <v>1.05</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z114">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA114">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB114">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC114">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD114">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE114">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF114">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG114">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.26</v>
       </c>
       <c r="AK114">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="O115">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P115">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="Q115">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="R115">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="S115">
+        <v>1.35</v>
+      </c>
+      <c r="T115">
+        <v>2.95</v>
+      </c>
+      <c r="U115">
+        <v>2.89</v>
+      </c>
+      <c r="V115">
         <v>1.38</v>
       </c>
-      <c r="T115">
-        <v>2.65</v>
-      </c>
-      <c r="U115">
-        <v>2.81</v>
-      </c>
-      <c r="V115">
-        <v>1.34</v>
-      </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z115">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
       <c r="AA115">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB115">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC115">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="AD115">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE115">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG115">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>4.16</v>
+        <v>4.68</v>
       </c>
       <c r="O156">
-        <v>4.08</v>
+        <v>4.57</v>
       </c>
       <c r="P156">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Q156">
-        <v>4.1</v>
+        <v>5.04</v>
       </c>
       <c r="R156">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="S156">
         <v>1.22</v>
       </c>
       <c r="T156">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="U156">
         <v>2.05</v>
       </c>
       <c r="V156">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W156">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X156">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z156">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA156">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AB156">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="AC156">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD156">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AE156">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AF156">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AG156">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AK156">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>4.68</v>
+        <v>3.07</v>
       </c>
       <c r="O157">
-        <v>4.57</v>
+        <v>3.78</v>
       </c>
       <c r="P157">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="Q157">
-        <v>5.04</v>
+        <v>3.04</v>
       </c>
       <c r="R157">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="S157">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T157">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U157">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V157">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="W157">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z157">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA157">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB157">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC157">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD157">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AE157">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF157">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG157">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK157">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.07</v>
+        <v>4.16</v>
       </c>
       <c r="O158">
-        <v>3.78</v>
+        <v>4.08</v>
       </c>
       <c r="P158">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="Q158">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="R158">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="S158">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T158">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="U158">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V158">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="W158">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X158">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z158">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA158">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AB158">
-        <v>2.2</v>
+        <v>2.93</v>
       </c>
       <c r="AC158">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AD158">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AE158">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AF158">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AG158">
-        <v>2.46</v>
+        <v>2.93</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="AK158">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="O172">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="P172">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="Q172">
-        <v>2.18</v>
+        <v>2.73</v>
       </c>
       <c r="R172">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S172">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T172">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U172">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="V172">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="W172">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X172">
         <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z172">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA172">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AB172">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC172">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="AD172">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE172">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF172">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG172">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK172">
-        <v>2.11</v>
+        <v>1.66</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
+        <v>3.32</v>
+      </c>
+      <c r="O173">
+        <v>3.56</v>
+      </c>
+      <c r="P173">
         <v>2.01</v>
       </c>
-      <c r="O173">
-        <v>3.52</v>
-      </c>
-      <c r="P173">
-        <v>3.36</v>
-      </c>
       <c r="Q173">
-        <v>2.73</v>
+        <v>3.7</v>
       </c>
       <c r="R173">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S173">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T173">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U173">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="V173">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W173">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X173">
         <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z173">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AA173">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB173">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AC173">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="AD173">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE173">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF173">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG173">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK173">
-        <v>1.66</v>
+        <v>1.28</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,80 +28671,80 @@
         </is>
       </c>
       <c r="N174">
-        <v>3.32</v>
+        <v>2.16</v>
       </c>
       <c r="O174">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="P174">
-        <v>2.01</v>
+        <v>3.06</v>
       </c>
       <c r="Q174">
-        <v>3.7</v>
+        <v>2.78</v>
       </c>
       <c r="R174">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S174">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T174">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U174">
-        <v>2.54</v>
+        <v>2.81</v>
       </c>
       <c r="V174">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W174">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y174">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z174">
-        <v>3.94</v>
+        <v>3.34</v>
       </c>
       <c r="AA174">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB174">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AC174">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD174">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AE174">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF174">
+        <v>1.7</v>
+      </c>
+      <c r="AG174">
+        <v>2.04</v>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ174">
+        <v>1.24</v>
+      </c>
+      <c r="AK174">
         <v>1.57</v>
-      </c>
-      <c r="AG174">
-        <v>2.22</v>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ174">
-        <v>1.25</v>
-      </c>
-      <c r="AK174">
-        <v>1.28</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="O175">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="P175">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="Q175">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="R175">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S175">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T175">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="U175">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="V175">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X175">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z175">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AA175">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB175">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AC175">
-        <v>3.14</v>
+        <v>2.42</v>
       </c>
       <c r="AD175">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE175">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF175">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AG175">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="O176">
-        <v>4.45</v>
+        <v>3.72</v>
       </c>
       <c r="P176">
-        <v>5.31</v>
+        <v>3.87</v>
       </c>
       <c r="Q176">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="R176">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="S176">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="T176">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="U176">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="V176">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="W176">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z176">
-        <v>6.12</v>
+        <v>3.5</v>
       </c>
       <c r="AA176">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AB176">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC176">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="AD176">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AE176">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AF176">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG176">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK176">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="O177">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="P177">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="Q177">
-        <v>3.12</v>
+        <v>4.11</v>
       </c>
       <c r="R177">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T177">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="U177">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V177">
         <v>1.52</v>
       </c>
       <c r="W177">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z177">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA177">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB177">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC177">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AD177">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE177">
         <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AG177">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
+        <v>1.24</v>
+      </c>
+      <c r="AK177">
         <v>1.25</v>
-      </c>
-      <c r="AK177">
-        <v>1.43</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="O178">
-        <v>3.72</v>
+        <v>4.45</v>
       </c>
       <c r="P178">
-        <v>1.94</v>
+        <v>5.31</v>
       </c>
       <c r="Q178">
-        <v>4.11</v>
+        <v>1.75</v>
       </c>
       <c r="R178">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="S178">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T178">
-        <v>3.32</v>
+        <v>4.2</v>
       </c>
       <c r="U178">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="V178">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="W178">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X178">
         <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z178">
-        <v>4.25</v>
+        <v>6.12</v>
       </c>
       <c r="AA178">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="AB178">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="AC178">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="AD178">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AE178">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF178">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG178">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK178">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.81</v>
+        <v>2.67</v>
       </c>
       <c r="O179">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="P179">
-        <v>3.87</v>
+        <v>2.47</v>
       </c>
       <c r="Q179">
+        <v>3.2</v>
+      </c>
+      <c r="R179">
         <v>2.2</v>
       </c>
-      <c r="R179">
-        <v>2.25</v>
-      </c>
       <c r="S179">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T179">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="U179">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="V179">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W179">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X179">
         <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z179">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA179">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB179">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC179">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="AD179">
         <v>1.35</v>
       </c>
       <c r="AE179">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF179">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG179">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK179">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,31 +29649,31 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.04</v>
+        <v>1.67</v>
       </c>
       <c r="O180">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P180">
-        <v>3.32</v>
+        <v>4.33</v>
       </c>
       <c r="Q180">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="R180">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S180">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T180">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U180">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="V180">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W180">
         <v>1.08</v>
@@ -29682,31 +29682,31 @@
         <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z180">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="AA180">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB180">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AC180">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="AD180">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE180">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF180">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG180">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK180">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,31 +29812,31 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.67</v>
+        <v>2.04</v>
       </c>
       <c r="O181">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="P181">
-        <v>2.47</v>
+        <v>3.32</v>
       </c>
       <c r="Q181">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="R181">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S181">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T181">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="U181">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="V181">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W181">
         <v>1.08</v>
@@ -29845,31 +29845,31 @@
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z181">
-        <v>3.82</v>
+        <v>3.99</v>
       </c>
       <c r="AA181">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AB181">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AC181">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="AD181">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE181">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF181">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG181">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK181">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,34 +33724,34 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="O205">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P205">
-        <v>2.31</v>
+        <v>2.83</v>
       </c>
       <c r="Q205">
-        <v>3.23</v>
+        <v>2.81</v>
       </c>
       <c r="R205">
         <v>2.39</v>
       </c>
       <c r="S205">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T205">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
       <c r="U205">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="V205">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W205">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X205">
         <v>1.01</v>
@@ -33760,28 +33760,28 @@
         <v>1.16</v>
       </c>
       <c r="Z205">
-        <v>4.15</v>
+        <v>4.56</v>
       </c>
       <c r="AA205">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB205">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AC205">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AD205">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE205">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF205">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG205">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK205">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,34 +33887,34 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="O206">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P206">
-        <v>2.83</v>
+        <v>2.31</v>
       </c>
       <c r="Q206">
-        <v>2.81</v>
+        <v>3.23</v>
       </c>
       <c r="R206">
         <v>2.39</v>
       </c>
       <c r="S206">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T206">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="U206">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="V206">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W206">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X206">
         <v>1.01</v>
@@ -33923,28 +33923,28 @@
         <v>1.16</v>
       </c>
       <c r="Z206">
-        <v>4.56</v>
+        <v>4.15</v>
       </c>
       <c r="AA206">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB206">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC206">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AD206">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE206">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF206">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG206">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK206">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="O207">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="P207">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="Q207">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="R207">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S207">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T207">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="U207">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="V207">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W207">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z207">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AA207">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB207">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC207">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="AD207">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AE207">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF207">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG207">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK207">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,31 +34213,31 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="O208">
-        <v>3.98</v>
+        <v>3.64</v>
       </c>
       <c r="P208">
-        <v>4.56</v>
+        <v>2.75</v>
       </c>
       <c r="Q208">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="R208">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S208">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T208">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="U208">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="V208">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W208">
         <v>1.09</v>
@@ -34246,31 +34246,31 @@
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z208">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="AA208">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AB208">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC208">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AD208">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE208">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF208">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG208">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK208">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="O209">
-        <v>6</v>
+        <v>3.98</v>
       </c>
       <c r="P209">
-        <v>10.5</v>
+        <v>4.56</v>
       </c>
       <c r="Q209">
-        <v>1.62</v>
+        <v>2.19</v>
       </c>
       <c r="R209">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="S209">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T209">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="U209">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="V209">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="W209">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z209">
-        <v>5.55</v>
+        <v>4.27</v>
       </c>
       <c r="AA209">
-        <v>1.39</v>
+        <v>1.79</v>
       </c>
       <c r="AB209">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="AC209">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="AD209">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AE209">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AF209">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG209">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK209">
-        <v>3.94</v>
+        <v>2.15</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="O210">
-        <v>4.05</v>
+        <v>6</v>
       </c>
       <c r="P210">
-        <v>4.03</v>
+        <v>10.5</v>
       </c>
       <c r="Q210">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="R210">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="S210">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T210">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U210">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="V210">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W210">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X210">
         <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z210">
-        <v>4.55</v>
+        <v>5.55</v>
       </c>
       <c r="AA210">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AB210">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="AC210">
-        <v>2.41</v>
+        <v>2.11</v>
       </c>
       <c r="AD210">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AE210">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF210">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AG210">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK210">
-        <v>1.91</v>
+        <v>3.94</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="O211">
-        <v>3.48</v>
+        <v>4.05</v>
       </c>
       <c r="P211">
-        <v>3.42</v>
+        <v>4.03</v>
       </c>
       <c r="Q211">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R211">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S211">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T211">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="U211">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="V211">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W211">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X211">
         <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z211">
-        <v>3.58</v>
+        <v>4.55</v>
       </c>
       <c r="AA211">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AB211">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="AC211">
-        <v>2.92</v>
+        <v>2.41</v>
       </c>
       <c r="AD211">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AE211">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AF211">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG211">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK211">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="O272">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P272">
+        <v>3.71</v>
+      </c>
+      <c r="Q272">
+        <v>2.34</v>
+      </c>
+      <c r="R272">
+        <v>2.23</v>
+      </c>
+      <c r="S272">
+        <v>1.3</v>
+      </c>
+      <c r="T272">
+        <v>3.3</v>
+      </c>
+      <c r="U272">
+        <v>2.32</v>
+      </c>
+      <c r="V272">
+        <v>1.52</v>
+      </c>
+      <c r="W272">
+        <v>1.1</v>
+      </c>
+      <c r="X272">
+        <v>1.01</v>
+      </c>
+      <c r="Y272">
+        <v>1.16</v>
+      </c>
+      <c r="Z272">
+        <v>4.15</v>
+      </c>
+      <c r="AA272">
+        <v>1.65</v>
+      </c>
+      <c r="AB272">
+        <v>2.07</v>
+      </c>
+      <c r="AC272">
         <v>2.7</v>
       </c>
-      <c r="Q272">
-        <v>3.24</v>
-      </c>
-      <c r="R272">
-        <v>1.95</v>
-      </c>
-      <c r="S272">
-        <v>1.45</v>
-      </c>
-      <c r="T272">
-        <v>2.5</v>
-      </c>
-      <c r="U272">
-        <v>3.12</v>
-      </c>
-      <c r="V272">
-        <v>1.3</v>
-      </c>
-      <c r="W272">
-        <v>1.02</v>
-      </c>
-      <c r="X272">
-        <v>1.03</v>
-      </c>
-      <c r="Y272">
-        <v>1.33</v>
-      </c>
-      <c r="Z272">
-        <v>2.81</v>
-      </c>
-      <c r="AA272">
-        <v>2.16</v>
-      </c>
-      <c r="AB272">
-        <v>1.64</v>
-      </c>
-      <c r="AC272">
-        <v>3.8</v>
-      </c>
       <c r="AD272">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AE272">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF272">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AG272">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK272">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="O273">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P273">
-        <v>3.71</v>
+        <v>2.7</v>
       </c>
       <c r="Q273">
-        <v>2.34</v>
+        <v>3.24</v>
       </c>
       <c r="R273">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="S273">
+        <v>1.45</v>
+      </c>
+      <c r="T273">
+        <v>2.5</v>
+      </c>
+      <c r="U273">
+        <v>3.12</v>
+      </c>
+      <c r="V273">
         <v>1.3</v>
       </c>
-      <c r="T273">
-        <v>3.3</v>
-      </c>
-      <c r="U273">
-        <v>2.32</v>
-      </c>
-      <c r="V273">
-        <v>1.52</v>
-      </c>
       <c r="W273">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X273">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y273">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z273">
-        <v>4.15</v>
+        <v>2.81</v>
       </c>
       <c r="AA273">
-        <v>1.65</v>
+        <v>2.16</v>
       </c>
       <c r="AB273">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AC273">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD273">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AE273">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF273">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="AG273">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AK273">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -52590,7 +52590,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O321">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P321">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q321">
         <v>0</v>
@@ -52665,10 +52665,10 @@
         <v>0</v>
       </c>
       <c r="Y321">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z321">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.94</v>
+        <v>2.52</v>
       </c>
       <c r="O322">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="P322">
-        <v>4.12</v>
+        <v>2.82</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52828,7 +52828,7 @@
         <v>0</v>
       </c>
       <c r="Y322">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z322">
         <v>2.2</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="O323">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="P323">
-        <v>3.12</v>
+        <v>4.12</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -52991,10 +52991,10 @@
         <v>0</v>
       </c>
       <c r="Y323">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z323">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O324">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="P324">
-        <v>3.97</v>
+        <v>3.12</v>
       </c>
       <c r="Q324">
         <v>0</v>
@@ -53154,10 +53154,10 @@
         <v>0</v>
       </c>
       <c r="Y324">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z324">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="O325">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="P325">
-        <v>7.7</v>
+        <v>3.97</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53317,16 +53317,16 @@
         <v>0</v>
       </c>
       <c r="Y325">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z325">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA325">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB325">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC325">
         <v>0</v>
@@ -53405,7 +53405,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="O326">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="P326">
-        <v>11.4</v>
+        <v>7.7</v>
       </c>
       <c r="Q326">
         <v>0</v>
@@ -53486,16 +53486,16 @@
         <v>0</v>
       </c>
       <c r="AA326">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB326">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="AC326">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD326">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE326">
         <v>0</v>
@@ -53568,22 +53568,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,13 +53610,13 @@
         </is>
       </c>
       <c r="N327">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O327">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P327">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="Q327">
         <v>0</v>
@@ -53649,16 +53649,16 @@
         <v>0</v>
       </c>
       <c r="AA327">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB327">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC327">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD327">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE327">
         <v>0</v>
@@ -53726,27 +53726,27 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,13 +53773,13 @@
         </is>
       </c>
       <c r="N328">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O328">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P328">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q328">
         <v>0</v>
@@ -53818,10 +53818,10 @@
         <v>0</v>
       </c>
       <c r="AC328">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD328">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE328">
         <v>0</v>
@@ -53877,7 +53877,7 @@
       </c>
       <c r="AU328" t="inlineStr">
         <is>
-          <t>2026-10-17 17:30:00</t>
+          <t>2026-10-17 17:00:00</t>
         </is>
       </c>
     </row>
@@ -53889,12 +53889,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="O329">
-        <v>4.91</v>
+        <v>3.9</v>
       </c>
       <c r="P329">
-        <v>7.13</v>
+        <v>2.63</v>
       </c>
       <c r="Q329">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R329">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S329">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T329">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U329">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="V329">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W329">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X329">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y329">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z329">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA329">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB329">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC329">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD329">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE329">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF329">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG329">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK329">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54040,7 +54040,7 @@
       </c>
       <c r="AU329" t="inlineStr">
         <is>
-          <t>2026-10-17 18:00:00</t>
+          <t>2026-10-17 17:30:00</t>
         </is>
       </c>
     </row>
@@ -54057,7 +54057,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G330">
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="O330">
-        <v>3.14</v>
+        <v>4.91</v>
       </c>
       <c r="P330">
-        <v>5.19</v>
+        <v>7.13</v>
       </c>
       <c r="Q330">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R330">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S330">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T330">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U330">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V330">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W330">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X330">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y330">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="Z330">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="AA330">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB330">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC330">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD330">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE330">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF330">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG330">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK330">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54215,12 +54215,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G331">
@@ -54262,64 +54262,64 @@
         </is>
       </c>
       <c r="N331">
+        <v>1.68</v>
+      </c>
+      <c r="O331">
+        <v>3.14</v>
+      </c>
+      <c r="P331">
+        <v>5.19</v>
+      </c>
+      <c r="Q331">
+        <v>0</v>
+      </c>
+      <c r="R331">
+        <v>0</v>
+      </c>
+      <c r="S331">
+        <v>0</v>
+      </c>
+      <c r="T331">
+        <v>0</v>
+      </c>
+      <c r="U331">
+        <v>0</v>
+      </c>
+      <c r="V331">
+        <v>0</v>
+      </c>
+      <c r="W331">
+        <v>0</v>
+      </c>
+      <c r="X331">
+        <v>0</v>
+      </c>
+      <c r="Y331">
         <v>1.55</v>
       </c>
-      <c r="O331">
-        <v>3.95</v>
-      </c>
-      <c r="P331">
-        <v>4.35</v>
-      </c>
-      <c r="Q331">
-        <v>2.13</v>
-      </c>
-      <c r="R331">
-        <v>2.38</v>
-      </c>
-      <c r="S331">
-        <v>1.21</v>
-      </c>
-      <c r="T331">
-        <v>3.9</v>
-      </c>
-      <c r="U331">
-        <v>2.08</v>
-      </c>
-      <c r="V331">
-        <v>1.64</v>
-      </c>
-      <c r="W331">
-        <v>1.16</v>
-      </c>
-      <c r="X331">
-        <v>1.02</v>
-      </c>
-      <c r="Y331">
-        <v>1.1</v>
-      </c>
       <c r="Z331">
-        <v>5.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA331">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB331">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC331">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD331">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE331">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF331">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG331">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH331" t="inlineStr">
         <is>
@@ -54332,10 +54332,10 @@
         </is>
       </c>
       <c r="AJ331">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK331">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL331">
         <v>0</v>
@@ -54366,7 +54366,7 @@
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>2026-10-17 18:15:00</t>
+          <t>2026-10-17 18:00:00</t>
         </is>
       </c>
     </row>
@@ -54378,12 +54378,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G332">
@@ -54425,64 +54425,64 @@
         </is>
       </c>
       <c r="N332">
+        <v>1.55</v>
+      </c>
+      <c r="O332">
+        <v>3.95</v>
+      </c>
+      <c r="P332">
+        <v>4.35</v>
+      </c>
+      <c r="Q332">
+        <v>2.13</v>
+      </c>
+      <c r="R332">
+        <v>2.38</v>
+      </c>
+      <c r="S332">
+        <v>1.21</v>
+      </c>
+      <c r="T332">
+        <v>3.9</v>
+      </c>
+      <c r="U332">
+        <v>2.08</v>
+      </c>
+      <c r="V332">
+        <v>1.64</v>
+      </c>
+      <c r="W332">
+        <v>1.16</v>
+      </c>
+      <c r="X332">
+        <v>1.02</v>
+      </c>
+      <c r="Y332">
+        <v>1.1</v>
+      </c>
+      <c r="Z332">
+        <v>5.05</v>
+      </c>
+      <c r="AA332">
+        <v>1.44</v>
+      </c>
+      <c r="AB332">
+        <v>2.43</v>
+      </c>
+      <c r="AC332">
+        <v>2.15</v>
+      </c>
+      <c r="AD332">
+        <v>1.6</v>
+      </c>
+      <c r="AE332">
+        <v>1.21</v>
+      </c>
+      <c r="AF332">
         <v>1.5</v>
       </c>
-      <c r="O332">
-        <v>4.44</v>
-      </c>
-      <c r="P332">
-        <v>6.75</v>
-      </c>
-      <c r="Q332">
-        <v>2</v>
-      </c>
-      <c r="R332">
-        <v>2.25</v>
-      </c>
-      <c r="S332">
-        <v>1.33</v>
-      </c>
-      <c r="T332">
-        <v>2.96</v>
-      </c>
-      <c r="U332">
-        <v>2.67</v>
-      </c>
-      <c r="V332">
-        <v>1.4</v>
-      </c>
-      <c r="W332">
-        <v>1.04</v>
-      </c>
-      <c r="X332">
-        <v>1</v>
-      </c>
-      <c r="Y332">
-        <v>1.22</v>
-      </c>
-      <c r="Z332">
-        <v>3.5</v>
-      </c>
-      <c r="AA332">
-        <v>1.78</v>
-      </c>
-      <c r="AB332">
-        <v>1.9</v>
-      </c>
-      <c r="AC332">
-        <v>2.97</v>
-      </c>
-      <c r="AD332">
-        <v>1.33</v>
-      </c>
-      <c r="AE332">
-        <v>1.07</v>
-      </c>
-      <c r="AF332">
-        <v>1.95</v>
-      </c>
       <c r="AG332">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AH332" t="inlineStr">
         <is>
@@ -54495,10 +54495,10 @@
         </is>
       </c>
       <c r="AJ332">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK332">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="AL332">
         <v>0</v>
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-10-17 18:30:00</t>
+          <t>2026-10-17 18:15:00</t>
         </is>
       </c>
     </row>
@@ -54546,7 +54546,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G333">
@@ -54588,64 +54588,64 @@
         </is>
       </c>
       <c r="N333">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="O333">
-        <v>3.11</v>
+        <v>4.44</v>
       </c>
       <c r="P333">
-        <v>2.9</v>
+        <v>6.75</v>
       </c>
       <c r="Q333">
-        <v>3.57</v>
+        <v>2</v>
       </c>
       <c r="R333">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S333">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T333">
-        <v>2.51</v>
+        <v>2.96</v>
       </c>
       <c r="U333">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="V333">
+        <v>1.4</v>
+      </c>
+      <c r="W333">
+        <v>1.04</v>
+      </c>
+      <c r="X333">
+        <v>1</v>
+      </c>
+      <c r="Y333">
+        <v>1.22</v>
+      </c>
+      <c r="Z333">
+        <v>3.5</v>
+      </c>
+      <c r="AA333">
+        <v>1.78</v>
+      </c>
+      <c r="AB333">
+        <v>1.9</v>
+      </c>
+      <c r="AC333">
+        <v>2.97</v>
+      </c>
+      <c r="AD333">
         <v>1.33</v>
       </c>
-      <c r="W333">
-        <v>1.06</v>
-      </c>
-      <c r="X333">
-        <v>1.04</v>
-      </c>
-      <c r="Y333">
-        <v>1.38</v>
-      </c>
-      <c r="Z333">
-        <v>2.74</v>
-      </c>
-      <c r="AA333">
-        <v>2.13</v>
-      </c>
-      <c r="AB333">
-        <v>1.7</v>
-      </c>
-      <c r="AC333">
-        <v>3.82</v>
-      </c>
-      <c r="AD333">
-        <v>1.2</v>
-      </c>
       <c r="AE333">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF333">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AG333">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH333" t="inlineStr">
         <is>
@@ -54658,10 +54658,10 @@
         </is>
       </c>
       <c r="AJ333">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK333">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="AL333">
         <v>0</v>
@@ -54709,7 +54709,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G334">
@@ -54751,64 +54751,64 @@
         </is>
       </c>
       <c r="N334">
-        <v>3.72</v>
+        <v>2.48</v>
       </c>
       <c r="O334">
-        <v>3.35</v>
+        <v>3.11</v>
       </c>
       <c r="P334">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q334">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R334">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S334">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T334">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U334">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V334">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W334">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X334">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y334">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z334">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA334">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AB334">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC334">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD334">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE334">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF334">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG334">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH334" t="inlineStr">
         <is>
@@ -54821,10 +54821,10 @@
         </is>
       </c>
       <c r="AJ334">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK334">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL334">
         <v>0</v>
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,64 +54914,64 @@
         </is>
       </c>
       <c r="N335">
-        <v>2.93</v>
+        <v>3.72</v>
       </c>
       <c r="O335">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="P335">
-        <v>2.47</v>
+        <v>1.95</v>
       </c>
       <c r="Q335">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R335">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S335">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T335">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U335">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V335">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W335">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X335">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y335">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z335">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA335">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB335">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AC335">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AD335">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE335">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF335">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG335">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK335">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-10-17 19:30:00</t>
+          <t>2026-10-17 18:30:00</t>
         </is>
       </c>
     </row>
@@ -55035,7 +55035,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,64 +55077,64 @@
         </is>
       </c>
       <c r="N336">
-        <v>3.36</v>
+        <v>2.93</v>
       </c>
       <c r="O336">
-        <v>3.62</v>
+        <v>3.39</v>
       </c>
       <c r="P336">
-        <v>1.87</v>
+        <v>2.47</v>
       </c>
       <c r="Q336">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R336">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S336">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T336">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U336">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V336">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W336">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X336">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y336">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z336">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA336">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB336">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC336">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD336">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE336">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF336">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG336">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK336">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55193,12 +55193,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,64 +55240,64 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.86</v>
+        <v>3.36</v>
       </c>
       <c r="O337">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P337">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="Q337">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R337">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S337">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T337">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="U337">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V337">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W337">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X337">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y337">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z337">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA337">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB337">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC337">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD337">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE337">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF337">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG337">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK337">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -55344,7 +55344,7 @@
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>2026-10-17 20:00:00</t>
+          <t>2026-10-17 19:30:00</t>
         </is>
       </c>
     </row>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,64 +55403,64 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.32</v>
+        <v>2.86</v>
       </c>
       <c r="O338">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="P338">
-        <v>7.13</v>
+        <v>2.11</v>
       </c>
       <c r="Q338">
-        <v>1.72</v>
+        <v>3.46</v>
       </c>
       <c r="R338">
-        <v>2.63</v>
+        <v>2.27</v>
       </c>
       <c r="S338">
         <v>1.22</v>
       </c>
       <c r="T338">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="U338">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V338">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W338">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X338">
         <v>1.01</v>
       </c>
       <c r="Y338">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z338">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA338">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AB338">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AC338">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AD338">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE338">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF338">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="AG338">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="AH338" t="inlineStr">
         <is>
@@ -55473,10 +55473,10 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK338">
-        <v>2.88</v>
+        <v>1.32</v>
       </c>
       <c r="AL338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,19 +55566,19 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="O339">
-        <v>3.88</v>
+        <v>4.8</v>
       </c>
       <c r="P339">
-        <v>4.28</v>
+        <v>7.13</v>
       </c>
       <c r="Q339">
-        <v>2.16</v>
+        <v>1.72</v>
       </c>
       <c r="R339">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S339">
         <v>1.22</v>
@@ -55599,31 +55599,31 @@
         <v>1.01</v>
       </c>
       <c r="Y339">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z339">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AA339">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AB339">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AC339">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD339">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE339">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF339">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG339">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK339">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55687,7 +55687,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,64 +55729,64 @@
         </is>
       </c>
       <c r="N340">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="O340">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="P340">
-        <v>2.44</v>
+        <v>4.28</v>
       </c>
       <c r="Q340">
-        <v>2.86</v>
+        <v>2.16</v>
       </c>
       <c r="R340">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S340">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T340">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="U340">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="V340">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W340">
         <v>1.14</v>
       </c>
       <c r="X340">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y340">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z340">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="AA340">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB340">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AC340">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD340">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE340">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF340">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AG340">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK340">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -55845,12 +55845,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,64 +55892,64 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="O341">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P341">
-        <v>4.31</v>
+        <v>2.44</v>
       </c>
       <c r="Q341">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="R341">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S341">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="T341">
-        <v>2.51</v>
+        <v>3.4</v>
       </c>
       <c r="U341">
-        <v>3.12</v>
+        <v>1.96</v>
       </c>
       <c r="V341">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="W341">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="X341">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y341">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="Z341">
-        <v>2.74</v>
+        <v>4.45</v>
       </c>
       <c r="AA341">
-        <v>2.17</v>
+        <v>1.56</v>
       </c>
       <c r="AB341">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="AC341">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD341">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AE341">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AF341">
-        <v>2.01</v>
+        <v>1.36</v>
       </c>
       <c r="AG341">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AH341" t="inlineStr">
         <is>
@@ -55962,10 +55962,10 @@
         </is>
       </c>
       <c r="AJ341">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK341">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AL341">
         <v>0</v>
@@ -55996,7 +55996,7 @@
       </c>
       <c r="AU341" t="inlineStr">
         <is>
-          <t>2026-10-17 20:30:00</t>
+          <t>2026-10-17 20:00:00</t>
         </is>
       </c>
     </row>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,64 +56055,64 @@
         </is>
       </c>
       <c r="N342">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="O342">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="P342">
-        <v>4.48</v>
+        <v>4.31</v>
       </c>
       <c r="Q342">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="R342">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S342">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T342">
-        <v>2.71</v>
+        <v>2.51</v>
       </c>
       <c r="U342">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="V342">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W342">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X342">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y342">
         <v>1.35</v>
       </c>
       <c r="Z342">
-        <v>3.03</v>
+        <v>2.74</v>
       </c>
       <c r="AA342">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AB342">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AC342">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AD342">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE342">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF342">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG342">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH342" t="inlineStr">
         <is>
@@ -56125,10 +56125,10 @@
         </is>
       </c>
       <c r="AJ342">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK342">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AL342">
         <v>0</v>
@@ -56176,7 +56176,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,80 +56218,80 @@
         </is>
       </c>
       <c r="N343">
-        <v>1.26</v>
+        <v>1.84</v>
       </c>
       <c r="O343">
-        <v>5.2</v>
+        <v>2.95</v>
       </c>
       <c r="P343">
-        <v>8.300000000000001</v>
+        <v>4.48</v>
       </c>
       <c r="Q343">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="R343">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="S343">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="T343">
-        <v>4.5</v>
+        <v>2.71</v>
       </c>
       <c r="U343">
+        <v>2.94</v>
+      </c>
+      <c r="V343">
+        <v>1.31</v>
+      </c>
+      <c r="W343">
+        <v>1.06</v>
+      </c>
+      <c r="X343">
+        <v>1.05</v>
+      </c>
+      <c r="Y343">
+        <v>1.35</v>
+      </c>
+      <c r="Z343">
+        <v>3.03</v>
+      </c>
+      <c r="AA343">
+        <v>1.92</v>
+      </c>
+      <c r="AB343">
+        <v>1.84</v>
+      </c>
+      <c r="AC343">
+        <v>3.76</v>
+      </c>
+      <c r="AD343">
+        <v>1.25</v>
+      </c>
+      <c r="AE343">
+        <v>1.05</v>
+      </c>
+      <c r="AF343">
         <v>2</v>
       </c>
-      <c r="V343">
+      <c r="AG343">
         <v>1.73</v>
       </c>
-      <c r="W343">
-        <v>1.22</v>
-      </c>
-      <c r="X343">
-        <v>1.01</v>
-      </c>
-      <c r="Y343">
-        <v>1.08</v>
-      </c>
-      <c r="Z343">
-        <v>5.45</v>
-      </c>
-      <c r="AA343">
-        <v>1.36</v>
-      </c>
-      <c r="AB343">
-        <v>2.87</v>
-      </c>
-      <c r="AC343">
-        <v>1.98</v>
-      </c>
-      <c r="AD343">
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI343" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ343">
+        <v>1.33</v>
+      </c>
+      <c r="AK343">
         <v>1.83</v>
-      </c>
-      <c r="AE343">
-        <v>1.3</v>
-      </c>
-      <c r="AF343">
-        <v>1.62</v>
-      </c>
-      <c r="AG343">
-        <v>2.15</v>
-      </c>
-      <c r="AH343" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI343" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ343">
-        <v>1.1</v>
-      </c>
-      <c r="AK343">
-        <v>3.6</v>
       </c>
       <c r="AL343">
         <v>0</v>
@@ -56339,7 +56339,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,64 +56381,64 @@
         </is>
       </c>
       <c r="N344">
-        <v>3.9</v>
+        <v>1.26</v>
       </c>
       <c r="O344">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="P344">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q344">
+        <v>1.62</v>
+      </c>
+      <c r="R344">
+        <v>2.88</v>
+      </c>
+      <c r="S344">
+        <v>1.17</v>
+      </c>
+      <c r="T344">
+        <v>4.5</v>
+      </c>
+      <c r="U344">
+        <v>2</v>
+      </c>
+      <c r="V344">
         <v>1.73</v>
       </c>
-      <c r="Q344">
-        <v>0</v>
-      </c>
-      <c r="R344">
-        <v>0</v>
-      </c>
-      <c r="S344">
-        <v>0</v>
-      </c>
-      <c r="T344">
-        <v>0</v>
-      </c>
-      <c r="U344">
-        <v>0</v>
-      </c>
-      <c r="V344">
-        <v>0</v>
-      </c>
       <c r="W344">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X344">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y344">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z344">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA344">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB344">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC344">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD344">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE344">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF344">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG344">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH344" t="inlineStr">
         <is>
@@ -56451,10 +56451,10 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK344">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="O345">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P345">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="O346">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="P346">
-        <v>4.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q346">
         <v>0</v>
@@ -56752,10 +56752,10 @@
         <v>0</v>
       </c>
       <c r="AC346">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD346">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE346">
         <v>0</v>
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,13 +56870,13 @@
         </is>
       </c>
       <c r="N347">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O347">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="P347">
-        <v>2.38</v>
+        <v>4.38</v>
       </c>
       <c r="Q347">
         <v>0</v>
@@ -56909,16 +56909,16 @@
         <v>0</v>
       </c>
       <c r="AA347">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB347">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC347">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD347">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O348">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P348">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57072,16 +57072,16 @@
         <v>0</v>
       </c>
       <c r="AA348">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB348">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC348">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD348">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE348">
         <v>0</v>
@@ -57149,27 +57149,27 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G349">
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O349">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P349">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q349">
         <v>0</v>
@@ -57241,10 +57241,10 @@
         <v>0</v>
       </c>
       <c r="AC349">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD349">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE349">
         <v>0</v>
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AU349" t="inlineStr">
         <is>
-          <t>2026-10-17 21:00:00</t>
+          <t>2026-10-17 20:30:00</t>
         </is>
       </c>
     </row>
@@ -57317,22 +57317,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G350">
@@ -57359,64 +57359,64 @@
         </is>
       </c>
       <c r="N350">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O350">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P350">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q350">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R350">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S350">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T350">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U350">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V350">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W350">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X350">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y350">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z350">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA350">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB350">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC350">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD350">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE350">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF350">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG350">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH350" t="inlineStr">
         <is>
@@ -57429,10 +57429,10 @@
         </is>
       </c>
       <c r="AJ350">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK350">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL350">
         <v>0</v>
@@ -57480,7 +57480,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G351">
@@ -57522,64 +57522,64 @@
         </is>
       </c>
       <c r="N351">
-        <v>2.01</v>
+        <v>2.22</v>
       </c>
       <c r="O351">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="P351">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="Q351">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="R351">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S351">
+        <v>1.36</v>
+      </c>
+      <c r="T351">
+        <v>2.6</v>
+      </c>
+      <c r="U351">
+        <v>2.83</v>
+      </c>
+      <c r="V351">
+        <v>1.38</v>
+      </c>
+      <c r="W351">
+        <v>1.05</v>
+      </c>
+      <c r="X351">
+        <v>1.04</v>
+      </c>
+      <c r="Y351">
         <v>1.33</v>
       </c>
-      <c r="T351">
-        <v>3.13</v>
-      </c>
-      <c r="U351">
-        <v>2.6</v>
-      </c>
-      <c r="V351">
-        <v>1.44</v>
-      </c>
-      <c r="W351">
-        <v>1.1</v>
-      </c>
-      <c r="X351">
-        <v>1</v>
-      </c>
-      <c r="Y351">
-        <v>1.23</v>
-      </c>
       <c r="Z351">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="AA351">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB351">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AC351">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="AD351">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE351">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF351">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG351">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH351" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         </is>
       </c>
       <c r="AJ351">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK351">
         <v>1.65</v>
@@ -57638,7 +57638,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G352">
@@ -57685,31 +57685,31 @@
         </is>
       </c>
       <c r="N352">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="O352">
-        <v>3.65</v>
+        <v>3.49</v>
       </c>
       <c r="P352">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="Q352">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="R352">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S352">
         <v>1.33</v>
       </c>
       <c r="T352">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="U352">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V352">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W352">
         <v>1.1</v>
@@ -57724,10 +57724,10 @@
         <v>3.42</v>
       </c>
       <c r="AA352">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AB352">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC352">
         <v>2.92</v>
@@ -57736,13 +57736,13 @@
         <v>1.31</v>
       </c>
       <c r="AE352">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF352">
         <v>1.67</v>
       </c>
       <c r="AG352">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH352" t="inlineStr">
         <is>
@@ -57758,7 +57758,7 @@
         <v>1.22</v>
       </c>
       <c r="AK352">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL352">
         <v>0</v>
@@ -57789,7 +57789,7 @@
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>2026-10-17 21:30:00</t>
+          <t>2026-10-17 21:00:00</t>
         </is>
       </c>
     </row>
@@ -57806,7 +57806,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,64 +57848,64 @@
         </is>
       </c>
       <c r="N353">
-        <v>2.81</v>
+        <v>1.93</v>
       </c>
       <c r="O353">
-        <v>4.03</v>
+        <v>3.65</v>
       </c>
       <c r="P353">
-        <v>2.35</v>
+        <v>3.46</v>
       </c>
       <c r="Q353">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R353">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S353">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T353">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U353">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V353">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W353">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y353">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z353">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA353">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB353">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC353">
-        <v>2</v>
+        <v>2.92</v>
       </c>
       <c r="AD353">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="AE353">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF353">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG353">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH353" t="inlineStr">
         <is>
@@ -57918,10 +57918,10 @@
         </is>
       </c>
       <c r="AJ353">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK353">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL353">
         <v>0</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,13 +58011,13 @@
         </is>
       </c>
       <c r="N354">
-        <v>2.1</v>
+        <v>2.81</v>
       </c>
       <c r="O354">
-        <v>3.6</v>
+        <v>4.03</v>
       </c>
       <c r="P354">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q354">
         <v>0</v>
@@ -58050,16 +58050,16 @@
         <v>0</v>
       </c>
       <c r="AA354">
+        <v>0</v>
+      </c>
+      <c r="AB354">
+        <v>0</v>
+      </c>
+      <c r="AC354">
+        <v>2</v>
+      </c>
+      <c r="AD354">
         <v>1.68</v>
-      </c>
-      <c r="AB354">
-        <v>2.05</v>
-      </c>
-      <c r="AC354">
-        <v>0</v>
-      </c>
-      <c r="AD354">
-        <v>0</v>
       </c>
       <c r="AE354">
         <v>0</v>
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,55 +58174,55 @@
         </is>
       </c>
       <c r="N355">
-        <v>4.79</v>
+        <v>2.1</v>
       </c>
       <c r="O355">
-        <v>4.43</v>
+        <v>3.6</v>
       </c>
       <c r="P355">
+        <v>3.2</v>
+      </c>
+      <c r="Q355">
+        <v>0</v>
+      </c>
+      <c r="R355">
+        <v>0</v>
+      </c>
+      <c r="S355">
+        <v>0</v>
+      </c>
+      <c r="T355">
+        <v>0</v>
+      </c>
+      <c r="U355">
+        <v>0</v>
+      </c>
+      <c r="V355">
+        <v>0</v>
+      </c>
+      <c r="W355">
+        <v>0</v>
+      </c>
+      <c r="X355">
+        <v>0</v>
+      </c>
+      <c r="Y355">
+        <v>0</v>
+      </c>
+      <c r="Z355">
+        <v>0</v>
+      </c>
+      <c r="AA355">
         <v>1.68</v>
       </c>
-      <c r="Q355">
-        <v>0</v>
-      </c>
-      <c r="R355">
-        <v>0</v>
-      </c>
-      <c r="S355">
-        <v>0</v>
-      </c>
-      <c r="T355">
-        <v>0</v>
-      </c>
-      <c r="U355">
-        <v>0</v>
-      </c>
-      <c r="V355">
-        <v>0</v>
-      </c>
-      <c r="W355">
-        <v>0</v>
-      </c>
-      <c r="X355">
-        <v>0</v>
-      </c>
-      <c r="Y355">
-        <v>0</v>
-      </c>
-      <c r="Z355">
-        <v>0</v>
-      </c>
-      <c r="AA355">
-        <v>0</v>
-      </c>
       <c r="AB355">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC355">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD355">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE355">
         <v>0</v>
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G356">
@@ -58337,64 +58337,64 @@
         </is>
       </c>
       <c r="N356">
-        <v>2.1</v>
+        <v>4.79</v>
       </c>
       <c r="O356">
-        <v>3.5</v>
+        <v>4.43</v>
       </c>
       <c r="P356">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="Q356">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R356">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S356">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T356">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U356">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V356">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W356">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X356">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y356">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z356">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA356">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB356">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC356">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AD356">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AE356">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF356">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG356">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH356" t="inlineStr">
         <is>
@@ -58407,10 +58407,10 @@
         </is>
       </c>
       <c r="AJ356">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK356">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-10-17 21:45:00</t>
+          <t>2026-10-17 21:30:00</t>
         </is>
       </c>
     </row>
@@ -58453,12 +58453,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,64 +58500,64 @@
         </is>
       </c>
       <c r="N357">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="O357">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P357">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="Q357">
-        <v>3.46</v>
+        <v>2.38</v>
       </c>
       <c r="R357">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S357">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T357">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U357">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V357">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W357">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X357">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y357">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z357">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AA357">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="AB357">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AC357">
-        <v>3.08</v>
+        <v>2.43</v>
       </c>
       <c r="AD357">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE357">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF357">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG357">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AH357" t="inlineStr">
         <is>
@@ -58570,10 +58570,10 @@
         </is>
       </c>
       <c r="AJ357">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK357">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="AL357">
         <v>0</v>
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-10-17 22:00:00</t>
+          <t>2026-10-17 21:45:00</t>
         </is>
       </c>
     </row>
@@ -58616,27 +58616,27 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G358">
@@ -58663,64 +58663,64 @@
         </is>
       </c>
       <c r="N358">
-        <v>3.44</v>
+        <v>2.74</v>
       </c>
       <c r="O358">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="P358">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="Q358">
-        <v>3.11</v>
+        <v>3.46</v>
       </c>
       <c r="R358">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S358">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T358">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U358">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="V358">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W358">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X358">
         <v>1.01</v>
       </c>
       <c r="Y358">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z358">
-        <v>4.87</v>
+        <v>3.34</v>
       </c>
       <c r="AA358">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AB358">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC358">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AD358">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AE358">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF358">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG358">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AH358" t="inlineStr">
         <is>
@@ -58733,10 +58733,10 @@
         </is>
       </c>
       <c r="AJ358">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK358">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL358">
         <v>0</v>
@@ -58767,7 +58767,7 @@
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>2026-10-17 23:00:00</t>
+          <t>2026-10-17 22:00:00</t>
         </is>
       </c>
     </row>
@@ -58784,22 +58784,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="G359">
@@ -58826,64 +58826,64 @@
         </is>
       </c>
       <c r="N359">
-        <v>2.85</v>
+        <v>3.44</v>
       </c>
       <c r="O359">
-        <v>3.49</v>
+        <v>3.86</v>
       </c>
       <c r="P359">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q359">
-        <v>3.72</v>
+        <v>3.11</v>
       </c>
       <c r="R359">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S359">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T359">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U359">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V359">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W359">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X359">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y359">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z359">
-        <v>4.1</v>
+        <v>4.87</v>
       </c>
       <c r="AA359">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB359">
         <v>2.15</v>
       </c>
       <c r="AC359">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AD359">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE359">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF359">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG359">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="AH359" t="inlineStr">
         <is>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="AJ359">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK359">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL359">
         <v>0</v>
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G360">
@@ -58989,64 +58989,64 @@
         </is>
       </c>
       <c r="N360">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O360">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="P360">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="Q360">
-        <v>4.46</v>
+        <v>3.72</v>
       </c>
       <c r="R360">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="S360">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T360">
         <v>3.3</v>
       </c>
       <c r="U360">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V360">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="W360">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X360">
         <v>1.02</v>
       </c>
       <c r="Y360">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z360">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA360">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AB360">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC360">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD360">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE360">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF360">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG360">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AH360" t="inlineStr">
         <is>
@@ -59059,10 +59059,10 @@
         </is>
       </c>
       <c r="AJ360">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK360">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AL360">
         <v>0</v>
@@ -59105,7 +59105,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G361">
@@ -59152,64 +59152,64 @@
         </is>
       </c>
       <c r="N361">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O361">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="P361">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="Q361">
-        <v>3.64</v>
+        <v>4.46</v>
       </c>
       <c r="R361">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S361">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T361">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U361">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V361">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W361">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X361">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y361">
+        <v>1.17</v>
+      </c>
+      <c r="Z361">
+        <v>3.95</v>
+      </c>
+      <c r="AA361">
+        <v>1.7</v>
+      </c>
+      <c r="AB361">
+        <v>2.08</v>
+      </c>
+      <c r="AC361">
+        <v>2.56</v>
+      </c>
+      <c r="AD361">
+        <v>1.4</v>
+      </c>
+      <c r="AE361">
         <v>1.13</v>
       </c>
-      <c r="Z361">
-        <v>4.55</v>
-      </c>
-      <c r="AA361">
-        <v>1.56</v>
-      </c>
-      <c r="AB361">
-        <v>2.22</v>
-      </c>
-      <c r="AC361">
-        <v>2.41</v>
-      </c>
-      <c r="AD361">
-        <v>1.45</v>
-      </c>
-      <c r="AE361">
-        <v>1.14</v>
-      </c>
       <c r="AF361">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG361">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="AH361" t="inlineStr">
         <is>
@@ -59222,10 +59222,10 @@
         </is>
       </c>
       <c r="AJ361">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK361">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AL361">
         <v>0</v>
@@ -59256,7 +59256,7 @@
       </c>
       <c r="AU361" t="inlineStr">
         <is>
-          <t>2026-10-17 23:30:00</t>
+          <t>2026-10-17 23:00:00</t>
         </is>
       </c>
     </row>
@@ -59273,7 +59273,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G362">
@@ -59315,64 +59315,64 @@
         </is>
       </c>
       <c r="N362">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="O362">
-        <v>4.09</v>
+        <v>3.54</v>
       </c>
       <c r="P362">
-        <v>3.34</v>
+        <v>2.02</v>
       </c>
       <c r="Q362">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R362">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S362">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T362">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U362">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V362">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W362">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X362">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y362">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z362">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA362">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB362">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC362">
-        <v>1.9</v>
+        <v>2.41</v>
       </c>
       <c r="AD362">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AE362">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF362">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG362">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH362" t="inlineStr">
         <is>
@@ -59385,10 +59385,10 @@
         </is>
       </c>
       <c r="AJ362">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK362">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL362">
         <v>0</v>
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G363">
@@ -59478,13 +59478,13 @@
         </is>
       </c>
       <c r="N363">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="O363">
-        <v>3.98</v>
+        <v>4.09</v>
       </c>
       <c r="P363">
-        <v>2.94</v>
+        <v>3.34</v>
       </c>
       <c r="Q363">
         <v>0</v>
@@ -59523,10 +59523,10 @@
         <v>0</v>
       </c>
       <c r="AC363">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD363">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AE363">
         <v>0</v>
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G364">
@@ -59641,13 +59641,13 @@
         </is>
       </c>
       <c r="N364">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="O364">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="P364">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="Q364">
         <v>0</v>
@@ -59689,7 +59689,7 @@
         <v>2.15</v>
       </c>
       <c r="AD364">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE364">
         <v>0</v>
@@ -59772,141 +59772,304 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="G365">
+        <v>0</v>
+      </c>
+      <c r="H365">
+        <v>0</v>
+      </c>
+      <c r="I365">
+        <v>0</v>
+      </c>
+      <c r="J365">
+        <v>0</v>
+      </c>
+      <c r="K365">
+        <v>0</v>
+      </c>
+      <c r="L365">
+        <v>0</v>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N365">
+        <v>3.25</v>
+      </c>
+      <c r="O365">
+        <v>3.8</v>
+      </c>
+      <c r="P365">
+        <v>1.98</v>
+      </c>
+      <c r="Q365">
+        <v>0</v>
+      </c>
+      <c r="R365">
+        <v>0</v>
+      </c>
+      <c r="S365">
+        <v>0</v>
+      </c>
+      <c r="T365">
+        <v>0</v>
+      </c>
+      <c r="U365">
+        <v>0</v>
+      </c>
+      <c r="V365">
+        <v>0</v>
+      </c>
+      <c r="W365">
+        <v>0</v>
+      </c>
+      <c r="X365">
+        <v>0</v>
+      </c>
+      <c r="Y365">
+        <v>0</v>
+      </c>
+      <c r="Z365">
+        <v>0</v>
+      </c>
+      <c r="AA365">
+        <v>0</v>
+      </c>
+      <c r="AB365">
+        <v>0</v>
+      </c>
+      <c r="AC365">
+        <v>2.15</v>
+      </c>
+      <c r="AD365">
+        <v>1.6</v>
+      </c>
+      <c r="AE365">
+        <v>0</v>
+      </c>
+      <c r="AF365">
+        <v>0</v>
+      </c>
+      <c r="AG365">
+        <v>0</v>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ365">
+        <v>0</v>
+      </c>
+      <c r="AK365">
+        <v>0</v>
+      </c>
+      <c r="AL365">
+        <v>0</v>
+      </c>
+      <c r="AM365">
+        <v>-1</v>
+      </c>
+      <c r="AN365">
+        <v>-1</v>
+      </c>
+      <c r="AO365">
+        <v>-1</v>
+      </c>
+      <c r="AP365">
+        <v>-1</v>
+      </c>
+      <c r="AQ365">
+        <v>0</v>
+      </c>
+      <c r="AR365">
+        <v>0</v>
+      </c>
+      <c r="AS365">
+        <v>0</v>
+      </c>
+      <c r="AT365">
+        <v>0</v>
+      </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>2026-10-17 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
           <t>Seattle Sounders</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr">
+      <c r="F366" t="inlineStr">
         <is>
           <t>Montreal Impact</t>
         </is>
       </c>
-      <c r="G365">
-        <v>0</v>
-      </c>
-      <c r="H365">
-        <v>0</v>
-      </c>
-      <c r="I365">
-        <v>0</v>
-      </c>
-      <c r="J365">
-        <v>0</v>
-      </c>
-      <c r="K365">
-        <v>0</v>
-      </c>
-      <c r="L365">
-        <v>0</v>
-      </c>
-      <c r="M365" t="inlineStr">
+      <c r="G366">
+        <v>0</v>
+      </c>
+      <c r="H366">
+        <v>0</v>
+      </c>
+      <c r="I366">
+        <v>0</v>
+      </c>
+      <c r="J366">
+        <v>0</v>
+      </c>
+      <c r="K366">
+        <v>0</v>
+      </c>
+      <c r="L366">
+        <v>0</v>
+      </c>
+      <c r="M366" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N365">
+      <c r="N366">
         <v>1.58</v>
       </c>
-      <c r="O365">
+      <c r="O366">
         <v>4.69</v>
       </c>
-      <c r="P365">
+      <c r="P366">
         <v>5.36</v>
       </c>
-      <c r="Q365">
-        <v>0</v>
-      </c>
-      <c r="R365">
-        <v>0</v>
-      </c>
-      <c r="S365">
-        <v>0</v>
-      </c>
-      <c r="T365">
-        <v>0</v>
-      </c>
-      <c r="U365">
-        <v>0</v>
-      </c>
-      <c r="V365">
-        <v>0</v>
-      </c>
-      <c r="W365">
-        <v>0</v>
-      </c>
-      <c r="X365">
-        <v>0</v>
-      </c>
-      <c r="Y365">
-        <v>0</v>
-      </c>
-      <c r="Z365">
-        <v>0</v>
-      </c>
-      <c r="AA365">
-        <v>0</v>
-      </c>
-      <c r="AB365">
-        <v>0</v>
-      </c>
-      <c r="AC365">
-        <v>0</v>
-      </c>
-      <c r="AD365">
-        <v>0</v>
-      </c>
-      <c r="AE365">
-        <v>0</v>
-      </c>
-      <c r="AF365">
-        <v>0</v>
-      </c>
-      <c r="AG365">
-        <v>0</v>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ365">
-        <v>0</v>
-      </c>
-      <c r="AK365">
-        <v>0</v>
-      </c>
-      <c r="AL365">
-        <v>0</v>
-      </c>
-      <c r="AM365">
-        <v>-1</v>
-      </c>
-      <c r="AN365">
-        <v>-1</v>
-      </c>
-      <c r="AO365">
-        <v>-1</v>
-      </c>
-      <c r="AP365">
-        <v>-1</v>
-      </c>
-      <c r="AQ365">
-        <v>0</v>
-      </c>
-      <c r="AR365">
-        <v>0</v>
-      </c>
-      <c r="AS365">
-        <v>0</v>
-      </c>
-      <c r="AT365">
-        <v>0</v>
-      </c>
-      <c r="AU365" t="inlineStr">
+      <c r="Q366">
+        <v>0</v>
+      </c>
+      <c r="R366">
+        <v>0</v>
+      </c>
+      <c r="S366">
+        <v>0</v>
+      </c>
+      <c r="T366">
+        <v>0</v>
+      </c>
+      <c r="U366">
+        <v>0</v>
+      </c>
+      <c r="V366">
+        <v>0</v>
+      </c>
+      <c r="W366">
+        <v>0</v>
+      </c>
+      <c r="X366">
+        <v>0</v>
+      </c>
+      <c r="Y366">
+        <v>0</v>
+      </c>
+      <c r="Z366">
+        <v>0</v>
+      </c>
+      <c r="AA366">
+        <v>0</v>
+      </c>
+      <c r="AB366">
+        <v>0</v>
+      </c>
+      <c r="AC366">
+        <v>0</v>
+      </c>
+      <c r="AD366">
+        <v>0</v>
+      </c>
+      <c r="AE366">
+        <v>0</v>
+      </c>
+      <c r="AF366">
+        <v>0</v>
+      </c>
+      <c r="AG366">
+        <v>0</v>
+      </c>
+      <c r="AH366" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI366" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ366">
+        <v>0</v>
+      </c>
+      <c r="AK366">
+        <v>0</v>
+      </c>
+      <c r="AL366">
+        <v>0</v>
+      </c>
+      <c r="AM366">
+        <v>-1</v>
+      </c>
+      <c r="AN366">
+        <v>-1</v>
+      </c>
+      <c r="AO366">
+        <v>-1</v>
+      </c>
+      <c r="AP366">
+        <v>-1</v>
+      </c>
+      <c r="AQ366">
+        <v>0</v>
+      </c>
+      <c r="AR366">
+        <v>0</v>
+      </c>
+      <c r="AS366">
+        <v>0</v>
+      </c>
+      <c r="AT366">
+        <v>0</v>
+      </c>
+      <c r="AU366" t="inlineStr">
         <is>
           <t>2026-10-17 23:30:00</t>
         </is>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="P7">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="Q7">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z7">
-        <v>3.43</v>
+        <v>4.15</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB7">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AD7">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG7">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="O8">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q8">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U8">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>4.15</v>
+        <v>3.43</v>
       </c>
       <c r="AA8">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC8">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE8">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="O38">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="P38">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="Q38">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T38">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W38">
         <v>1.09</v>
@@ -6545,7 +6545,7 @@
         <v>1.7</v>
       </c>
       <c r="AB38">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC38">
         <v>2.75</v>
@@ -6557,10 +6557,10 @@
         <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG38">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AK38">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P51">
-        <v>2.77</v>
+        <v>3.84</v>
       </c>
       <c r="Q51">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="W51">
+        <v>1.16</v>
+      </c>
+      <c r="X51">
+        <v>1.02</v>
+      </c>
+      <c r="Y51">
         <v>1.12</v>
       </c>
-      <c r="X51">
-        <v>1</v>
-      </c>
-      <c r="Y51">
-        <v>1.18</v>
-      </c>
       <c r="Z51">
-        <v>3.9</v>
+        <v>5.35</v>
       </c>
       <c r="AA51">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AB51">
-        <v>2.11</v>
+        <v>2.89</v>
       </c>
       <c r="AC51">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="AD51">
+        <v>1.83</v>
+      </c>
+      <c r="AE51">
+        <v>1.33</v>
+      </c>
+      <c r="AF51">
         <v>1.4</v>
       </c>
-      <c r="AE51">
-        <v>1.13</v>
-      </c>
-      <c r="AF51">
-        <v>1.55</v>
-      </c>
       <c r="AG51">
-        <v>2.26</v>
+        <v>2.73</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="O52">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
-        <v>3.84</v>
+        <v>3.01</v>
       </c>
       <c r="Q52">
+        <v>2.6</v>
+      </c>
+      <c r="R52">
+        <v>2.32</v>
+      </c>
+      <c r="S52">
+        <v>1.25</v>
+      </c>
+      <c r="T52">
+        <v>3.7</v>
+      </c>
+      <c r="U52">
         <v>2.17</v>
       </c>
-      <c r="R52">
-        <v>2.73</v>
-      </c>
-      <c r="S52">
-        <v>1.24</v>
-      </c>
-      <c r="T52">
-        <v>3.4</v>
-      </c>
-      <c r="U52">
-        <v>2.06</v>
-      </c>
       <c r="V52">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W52">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>5.35</v>
+        <v>4.95</v>
       </c>
       <c r="AA52">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AB52">
-        <v>2.89</v>
+        <v>2.35</v>
       </c>
       <c r="AC52">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD52">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AE52">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="Q53">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W53">
+        <v>1.12</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>1.18</v>
+      </c>
+      <c r="Z53">
+        <v>3.9</v>
+      </c>
+      <c r="AA53">
+        <v>1.66</v>
+      </c>
+      <c r="AB53">
+        <v>2.11</v>
+      </c>
+      <c r="AC53">
+        <v>2.56</v>
+      </c>
+      <c r="AD53">
+        <v>1.4</v>
+      </c>
+      <c r="AE53">
         <v>1.13</v>
       </c>
-      <c r="X53">
-        <v>1.03</v>
-      </c>
-      <c r="Y53">
-        <v>1.11</v>
-      </c>
-      <c r="Z53">
-        <v>4.95</v>
-      </c>
-      <c r="AA53">
-        <v>1.53</v>
-      </c>
-      <c r="AB53">
-        <v>2.35</v>
-      </c>
-      <c r="AC53">
-        <v>2.25</v>
-      </c>
-      <c r="AD53">
-        <v>1.57</v>
-      </c>
-      <c r="AE53">
-        <v>1.18</v>
-      </c>
       <c r="AF53">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG53">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK53">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="O61">
         <v>3.01</v>
       </c>
       <c r="P61">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="Q61">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R61">
         <v>2.12</v>
@@ -10273,22 +10273,22 @@
         <v>2.65</v>
       </c>
       <c r="U61">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V61">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W61">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z61">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA61">
         <v>2</v>
@@ -10297,19 +10297,19 @@
         <v>1.71</v>
       </c>
       <c r="AC61">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AD61">
         <v>1.26</v>
       </c>
       <c r="AE61">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF61">
         <v>1.74</v>
       </c>
       <c r="AG61">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK61">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -16120,16 +16120,16 @@
         </is>
       </c>
       <c r="N97">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="O97">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P97">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q97">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="R97">
         <v>2.24</v>
@@ -16141,10 +16141,10 @@
         <v>3.1</v>
       </c>
       <c r="U97">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V97">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W97">
         <v>1.07</v>
@@ -16156,19 +16156,19 @@
         <v>1.21</v>
       </c>
       <c r="Z97">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AA97">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB97">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC97">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="AD97">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AE97">
         <v>1.14</v>
@@ -16289,16 +16289,16 @@
         <v>3.1</v>
       </c>
       <c r="P98">
-        <v>3.81</v>
+        <v>3.91</v>
       </c>
       <c r="Q98">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R98">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S98">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T98">
         <v>2.85</v>
@@ -16307,19 +16307,19 @@
         <v>2.6</v>
       </c>
       <c r="V98">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W98">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X98">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
         <v>1.32</v>
       </c>
       <c r="Z98">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA98">
         <v>1.83</v>
@@ -16334,10 +16334,10 @@
         <v>1.3</v>
       </c>
       <c r="AE98">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF98">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
         <v>1.8</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="O114">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="P114">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="Q114">
-        <v>3.99</v>
+        <v>4.57</v>
       </c>
       <c r="R114">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="S114">
+        <v>1.35</v>
+      </c>
+      <c r="T114">
+        <v>2.95</v>
+      </c>
+      <c r="U114">
+        <v>2.89</v>
+      </c>
+      <c r="V114">
         <v>1.38</v>
       </c>
-      <c r="T114">
-        <v>2.65</v>
-      </c>
-      <c r="U114">
-        <v>2.81</v>
-      </c>
-      <c r="V114">
-        <v>1.34</v>
-      </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z114">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
       <c r="AA114">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB114">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC114">
-        <v>3.58</v>
+        <v>3.31</v>
       </c>
       <c r="AD114">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE114">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG114">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.75</v>
+        <v>3.13</v>
       </c>
       <c r="O115">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q115">
-        <v>4.57</v>
+        <v>3.99</v>
       </c>
       <c r="R115">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="S115">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T115">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="U115">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="V115">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z115">
-        <v>3.43</v>
+        <v>2.92</v>
       </c>
       <c r="AA115">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AB115">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC115">
-        <v>3.31</v>
+        <v>3.58</v>
       </c>
       <c r="AD115">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE115">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF115">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG115">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK115">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,80 +25737,80 @@
         </is>
       </c>
       <c r="N156">
-        <v>4.68</v>
+        <v>4.16</v>
       </c>
       <c r="O156">
-        <v>4.57</v>
+        <v>4.08</v>
       </c>
       <c r="P156">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q156">
-        <v>5.04</v>
+        <v>4.1</v>
       </c>
       <c r="R156">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="S156">
         <v>1.22</v>
       </c>
       <c r="T156">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U156">
         <v>2.05</v>
       </c>
       <c r="V156">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W156">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z156">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AA156">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AB156">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="AC156">
+        <v>1.9</v>
+      </c>
+      <c r="AD156">
+        <v>1.8</v>
+      </c>
+      <c r="AE156">
+        <v>1.34</v>
+      </c>
+      <c r="AF156">
+        <v>1.35</v>
+      </c>
+      <c r="AG156">
+        <v>2.93</v>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
         <v>2</v>
       </c>
-      <c r="AD156">
-        <v>1.72</v>
-      </c>
-      <c r="AE156">
-        <v>1.23</v>
-      </c>
-      <c r="AF156">
-        <v>1.5</v>
-      </c>
-      <c r="AG156">
-        <v>2.4</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.17</v>
-      </c>
       <c r="AK156">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>3.07</v>
+        <v>4.68</v>
       </c>
       <c r="O157">
-        <v>3.78</v>
+        <v>4.57</v>
       </c>
       <c r="P157">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="Q157">
-        <v>3.04</v>
+        <v>5.04</v>
       </c>
       <c r="R157">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="S157">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T157">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U157">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V157">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="W157">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X157">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z157">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AA157">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB157">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC157">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AD157">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AE157">
+        <v>1.23</v>
+      </c>
+      <c r="AF157">
+        <v>1.5</v>
+      </c>
+      <c r="AG157">
+        <v>2.4</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>1.17</v>
       </c>
-      <c r="AF157">
-        <v>1.45</v>
-      </c>
-      <c r="AG157">
-        <v>2.46</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.24</v>
-      </c>
       <c r="AK157">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>4.16</v>
+        <v>3.07</v>
       </c>
       <c r="O158">
-        <v>4.08</v>
+        <v>3.78</v>
       </c>
       <c r="P158">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="Q158">
-        <v>4.1</v>
+        <v>3.04</v>
       </c>
       <c r="R158">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="S158">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T158">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="U158">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V158">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="W158">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X158">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y158">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z158">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA158">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="AB158">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="AC158">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD158">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AE158">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AF158">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AG158">
-        <v>2.93</v>
+        <v>2.46</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="AK158">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>3.16</v>
+        <v>2.62</v>
       </c>
       <c r="O169">
-        <v>3.02</v>
+        <v>3.24</v>
       </c>
       <c r="P169">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="Q169">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="R169">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S169">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="T169">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="U169">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="V169">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W169">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X169">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y169">
+        <v>1.21</v>
+      </c>
+      <c r="Z169">
+        <v>3.58</v>
+      </c>
+      <c r="AA169">
+        <v>1.92</v>
+      </c>
+      <c r="AB169">
+        <v>1.83</v>
+      </c>
+      <c r="AC169">
+        <v>2.95</v>
+      </c>
+      <c r="AD169">
         <v>1.37</v>
       </c>
-      <c r="Z169">
-        <v>2.66</v>
-      </c>
-      <c r="AA169">
-        <v>2.28</v>
-      </c>
-      <c r="AB169">
-        <v>1.61</v>
-      </c>
-      <c r="AC169">
-        <v>3.92</v>
-      </c>
-      <c r="AD169">
-        <v>1.21</v>
-      </c>
       <c r="AE169">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF169">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AG169">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AK169">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="O171">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="P171">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="Q171">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="R171">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S171">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="T171">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="U171">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="V171">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="W171">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X171">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y171">
+        <v>1.37</v>
+      </c>
+      <c r="Z171">
+        <v>2.66</v>
+      </c>
+      <c r="AA171">
+        <v>2.28</v>
+      </c>
+      <c r="AB171">
+        <v>1.61</v>
+      </c>
+      <c r="AC171">
+        <v>3.92</v>
+      </c>
+      <c r="AD171">
         <v>1.21</v>
       </c>
-      <c r="Z171">
-        <v>3.58</v>
-      </c>
-      <c r="AA171">
-        <v>1.92</v>
-      </c>
-      <c r="AB171">
-        <v>1.83</v>
-      </c>
-      <c r="AC171">
-        <v>2.95</v>
-      </c>
-      <c r="AD171">
-        <v>1.37</v>
-      </c>
       <c r="AE171">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF171">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AG171">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AK171">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
+        <v>1.81</v>
+      </c>
+      <c r="O175">
+        <v>3.72</v>
+      </c>
+      <c r="P175">
+        <v>3.87</v>
+      </c>
+      <c r="Q175">
+        <v>2.2</v>
+      </c>
+      <c r="R175">
+        <v>2.25</v>
+      </c>
+      <c r="S175">
+        <v>1.31</v>
+      </c>
+      <c r="T175">
+        <v>3.08</v>
+      </c>
+      <c r="U175">
         <v>2.6</v>
       </c>
-      <c r="O175">
-        <v>3.56</v>
-      </c>
-      <c r="P175">
-        <v>2.38</v>
-      </c>
-      <c r="Q175">
-        <v>3.12</v>
-      </c>
-      <c r="R175">
-        <v>2.29</v>
-      </c>
-      <c r="S175">
-        <v>1.25</v>
-      </c>
-      <c r="T175">
-        <v>3.46</v>
-      </c>
-      <c r="U175">
-        <v>2.45</v>
-      </c>
       <c r="V175">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W175">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
         <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z175">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA175">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB175">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC175">
-        <v>2.42</v>
+        <v>3.05</v>
       </c>
       <c r="AD175">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AE175">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF175">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AG175">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK175">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="O176">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="P176">
-        <v>3.87</v>
+        <v>4.33</v>
       </c>
       <c r="Q176">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R176">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S176">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T176">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U176">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="V176">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z176">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA176">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB176">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AC176">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AD176">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE176">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF176">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG176">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK176">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="O177">
-        <v>3.72</v>
+        <v>3.56</v>
       </c>
       <c r="P177">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="Q177">
-        <v>4.11</v>
+        <v>3.12</v>
       </c>
       <c r="R177">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="S177">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T177">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="U177">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="V177">
         <v>1.52</v>
       </c>
       <c r="W177">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z177">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA177">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AB177">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC177">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AD177">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE177">
         <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG177">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.67</v>
+        <v>3.4</v>
       </c>
       <c r="O179">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="P179">
-        <v>2.47</v>
+        <v>1.94</v>
       </c>
       <c r="Q179">
-        <v>3.2</v>
+        <v>4.11</v>
       </c>
       <c r="R179">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="S179">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T179">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="U179">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="V179">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W179">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X179">
         <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z179">
-        <v>3.82</v>
+        <v>4.25</v>
       </c>
       <c r="AA179">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AB179">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AC179">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD179">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE179">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF179">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG179">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
+        <v>1.24</v>
+      </c>
+      <c r="AK179">
         <v>1.25</v>
-      </c>
-      <c r="AK179">
-        <v>1.42</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,31 +29649,31 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.67</v>
+        <v>2.67</v>
       </c>
       <c r="O180">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="P180">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="Q180">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="R180">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S180">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T180">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U180">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V180">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W180">
         <v>1.08</v>
@@ -29682,31 +29682,31 @@
         <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z180">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA180">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AB180">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AC180">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="AD180">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE180">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF180">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG180">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK180">
-        <v>2.11</v>
+        <v>1.42</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="O206">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P206">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="Q206">
-        <v>3.23</v>
+        <v>2.81</v>
       </c>
       <c r="R206">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="S206">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T206">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="U206">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V206">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W206">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X206">
         <v>1.01</v>
       </c>
       <c r="Y206">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z206">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA206">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AB206">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC206">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="AD206">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE206">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF206">
         <v>1.5</v>
       </c>
       <c r="AG206">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK206">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="O207">
-        <v>3.48</v>
+        <v>6</v>
       </c>
       <c r="P207">
-        <v>3.42</v>
+        <v>10.5</v>
       </c>
       <c r="Q207">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="R207">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="S207">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T207">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="U207">
-        <v>2.53</v>
+        <v>2.06</v>
       </c>
       <c r="V207">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W207">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z207">
-        <v>3.58</v>
+        <v>5.55</v>
       </c>
       <c r="AA207">
-        <v>1.81</v>
+        <v>1.39</v>
       </c>
       <c r="AB207">
-        <v>1.95</v>
+        <v>2.59</v>
       </c>
       <c r="AC207">
-        <v>2.92</v>
+        <v>2.11</v>
       </c>
       <c r="AD207">
-        <v>1.31</v>
+        <v>1.68</v>
       </c>
       <c r="AE207">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AF207">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG207">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AK207">
-        <v>1.73</v>
+        <v>3.94</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,31 +34213,31 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="O208">
-        <v>3.64</v>
+        <v>3.98</v>
       </c>
       <c r="P208">
-        <v>2.75</v>
+        <v>4.56</v>
       </c>
       <c r="Q208">
-        <v>2.81</v>
+        <v>2.19</v>
       </c>
       <c r="R208">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="S208">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T208">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="U208">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V208">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="W208">
         <v>1.09</v>
@@ -34246,31 +34246,31 @@
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z208">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="AA208">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AB208">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC208">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AD208">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE208">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF208">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG208">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK208">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,34 +34376,34 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="O209">
-        <v>3.98</v>
+        <v>3.48</v>
       </c>
       <c r="P209">
-        <v>4.56</v>
+        <v>3.42</v>
       </c>
       <c r="Q209">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="R209">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="S209">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T209">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U209">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="V209">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W209">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X209">
         <v>1.01</v>
@@ -34412,28 +34412,28 @@
         <v>1.21</v>
       </c>
       <c r="Z209">
-        <v>4.27</v>
+        <v>3.58</v>
       </c>
       <c r="AA209">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB209">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC209">
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="AD209">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE209">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF209">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG209">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK209">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="O210">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P210">
-        <v>10.5</v>
+        <v>2.31</v>
       </c>
       <c r="Q210">
-        <v>1.62</v>
+        <v>3.23</v>
       </c>
       <c r="R210">
-        <v>2.76</v>
+        <v>2.39</v>
       </c>
       <c r="S210">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T210">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="U210">
-        <v>2.06</v>
+        <v>2.39</v>
       </c>
       <c r="V210">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="W210">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X210">
         <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z210">
-        <v>5.55</v>
+        <v>4.15</v>
       </c>
       <c r="AA210">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AB210">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="AC210">
-        <v>2.11</v>
+        <v>2.63</v>
       </c>
       <c r="AD210">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AE210">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF210">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG210">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK210">
-        <v>3.94</v>
+        <v>1.43</v>
       </c>
       <c r="AL210">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="O2">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="Q2">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="R2">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
         <v>1.39</v>
@@ -674,10 +674,10 @@
         <v>3.35</v>
       </c>
       <c r="AA2">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC2">
         <v>3.55</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK2">
         <v>1.51</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="O3">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
         <v>2.8</v>
@@ -813,16 +813,16 @@
         <v>2.12</v>
       </c>
       <c r="S3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U3">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.11</v>
@@ -837,10 +837,10 @@
         <v>3.58</v>
       </c>
       <c r="AA3">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AB3">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AC3">
         <v>2.88</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="O13">
-        <v>5.52</v>
+        <v>4.8</v>
       </c>
       <c r="P13">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="Q13">
         <v>1.74</v>
@@ -2446,7 +2446,7 @@
         <v>1.19</v>
       </c>
       <c r="T13">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U13">
         <v>2.06</v>
@@ -2455,7 +2455,7 @@
         <v>1.69</v>
       </c>
       <c r="W13">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2501,7 +2501,7 @@
         <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.74</v>
+        <v>3.35</v>
       </c>
       <c r="O14">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
         <v>3.75</v>
@@ -2609,13 +2609,13 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
         <v>2.48</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
         <v>1.11</v>
@@ -2624,13 +2624,13 @@
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="AA14">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
         <v>1.98</v>
@@ -2642,10 +2642,10 @@
         <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
         <v>2.13</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK14">
         <v>1.29</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>5.23</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="Q15">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
         <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA15">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AB15">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC15">
-        <v>3.58</v>
+        <v>3.92</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AG15">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="O16">
-        <v>4.2</v>
+        <v>3.57</v>
       </c>
       <c r="P16">
-        <v>4.4</v>
+        <v>3.11</v>
       </c>
       <c r="Q16">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="R16">
         <v>2.42</v>
@@ -2962,10 +2962,10 @@
         <v>2.17</v>
       </c>
       <c r="AC16">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE16">
         <v>1.18</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
         <v>1.85</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="O17">
         <v>3.65</v>
       </c>
       <c r="P17">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q17">
         <v>3.1</v>
@@ -3107,7 +3107,7 @@
         <v>1.6</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3122,7 +3122,7 @@
         <v>1.47</v>
       </c>
       <c r="AB17">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC17">
         <v>2.32</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="O18">
-        <v>4.47</v>
+        <v>4.2</v>
       </c>
       <c r="P18">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>1.97</v>
@@ -3258,10 +3258,10 @@
         <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U18">
         <v>2.4</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK18">
         <v>2.63</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="O19">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q19">
         <v>4.15</v>
@@ -3421,7 +3421,7 @@
         <v>2.09</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
         <v>2.74</v>
@@ -3445,10 +3445,10 @@
         <v>3.28</v>
       </c>
       <c r="AA19">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AB19">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AC19">
         <v>2.97</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="O25">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="Q25">
         <v>4.18</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="O27">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="P27">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q27">
         <v>4.1</v>
@@ -4755,10 +4755,10 @@
         <v>2.97</v>
       </c>
       <c r="AC27">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD27">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AE27">
         <v>1.35</v>
@@ -4767,7 +4767,7 @@
         <v>1.36</v>
       </c>
       <c r="AG27">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O34">
-        <v>4.31</v>
+        <v>4.05</v>
       </c>
       <c r="P34">
-        <v>5.03</v>
+        <v>4.6</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
@@ -5866,10 +5866,10 @@
         <v>2.4</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
         <v>2.31</v>
@@ -5890,7 +5890,7 @@
         <v>4.4</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB34">
         <v>2.36</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="O46">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="P46">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="Q46">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="R46">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="S46">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T46">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="U46">
-        <v>3.21</v>
+        <v>2.92</v>
       </c>
       <c r="V46">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W46">
         <v>1.04</v>
@@ -7880,7 +7880,7 @@
         <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="P50">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
         <v>2.38</v>
@@ -8480,13 +8480,13 @@
         <v>4</v>
       </c>
       <c r="U50">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="V50">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W50">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8498,7 +8498,7 @@
         <v>4.95</v>
       </c>
       <c r="AA50">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
         <v>2.35</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="O51">
-        <v>4.1</v>
+        <v>3.46</v>
       </c>
       <c r="P51">
-        <v>3.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q51">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="R51">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U51">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>5.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA51">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="AB51">
-        <v>2.89</v>
+        <v>2.11</v>
       </c>
       <c r="AC51">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="AD51">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>2.73</v>
+        <v>2.38</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="P52">
-        <v>3.01</v>
+        <v>3.57</v>
       </c>
       <c r="Q52">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="R52">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="S52">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T52">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="U52">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="V52">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="W52">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>4.95</v>
+        <v>6.99</v>
       </c>
       <c r="AA52">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AB52">
-        <v>2.35</v>
+        <v>3.03</v>
       </c>
       <c r="AC52">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AD52">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AE52">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF52">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG52">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="Q53">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R53">
+        <v>2.32</v>
+      </c>
+      <c r="S53">
+        <v>1.25</v>
+      </c>
+      <c r="T53">
+        <v>3.7</v>
+      </c>
+      <c r="U53">
+        <v>2.17</v>
+      </c>
+      <c r="V53">
+        <v>1.6</v>
+      </c>
+      <c r="W53">
+        <v>1.13</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
+        <v>1.11</v>
+      </c>
+      <c r="Z53">
+        <v>4.95</v>
+      </c>
+      <c r="AA53">
+        <v>1.53</v>
+      </c>
+      <c r="AB53">
+        <v>2.35</v>
+      </c>
+      <c r="AC53">
         <v>2.25</v>
       </c>
-      <c r="S53">
-        <v>1.29</v>
-      </c>
-      <c r="T53">
-        <v>3.3</v>
-      </c>
-      <c r="U53">
-        <v>2.4</v>
-      </c>
-      <c r="V53">
-        <v>1.5</v>
-      </c>
-      <c r="W53">
-        <v>1.12</v>
-      </c>
-      <c r="X53">
-        <v>1</v>
-      </c>
-      <c r="Y53">
+      <c r="AD53">
+        <v>1.57</v>
+      </c>
+      <c r="AE53">
         <v>1.18</v>
       </c>
-      <c r="Z53">
-        <v>3.9</v>
-      </c>
-      <c r="AA53">
-        <v>1.66</v>
-      </c>
-      <c r="AB53">
-        <v>2.11</v>
-      </c>
-      <c r="AC53">
-        <v>2.56</v>
-      </c>
-      <c r="AD53">
-        <v>1.4</v>
-      </c>
-      <c r="AE53">
-        <v>1.13</v>
-      </c>
       <c r="AF53">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="O55">
-        <v>3.49</v>
+        <v>3.36</v>
       </c>
       <c r="P55">
-        <v>3.92</v>
+        <v>3.76</v>
       </c>
       <c r="Q55">
         <v>2.69</v>
@@ -9935,34 +9935,34 @@
         <v>1.95</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA59">
         <v>1.95</v>
@@ -9971,19 +9971,19 @@
         <v>1.85</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10578,25 +10578,25 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="O63">
-        <v>3.72</v>
+        <v>3.67</v>
       </c>
       <c r="P63">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q63">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R63">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U63">
         <v>2.47</v>
@@ -10626,13 +10626,13 @@
         <v>2.61</v>
       </c>
       <c r="AD63">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE63">
         <v>1.14</v>
       </c>
       <c r="AF63">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG63">
         <v>2.3</v>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O66">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P66">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="Q66">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="R66">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S66">
         <v>1.36</v>
@@ -11103,13 +11103,13 @@
         <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="AA66">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB66">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC66">
         <v>3.25</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="O67">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q67">
         <v>3.8</v>
@@ -11245,10 +11245,10 @@
         <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T67">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="U67">
         <v>2.88</v>
@@ -11263,22 +11263,22 @@
         <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z67">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="AA67">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB67">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC67">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="AD67">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
         <v>1.03</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="O68">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P68">
-        <v>5.43</v>
+        <v>5.71</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O69">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P69">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="O70">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P70">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12211,16 +12211,16 @@
         <v>1.84</v>
       </c>
       <c r="O73">
-        <v>3.92</v>
+        <v>3.65</v>
       </c>
       <c r="P73">
-        <v>3.69</v>
+        <v>3.22</v>
       </c>
       <c r="Q73">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="R73">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S73">
         <v>1.25</v>
@@ -12229,10 +12229,10 @@
         <v>3.6</v>
       </c>
       <c r="U73">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="V73">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W73">
         <v>1.11</v>
@@ -12241,22 +12241,22 @@
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z73">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="AA73">
         <v>1.57</v>
       </c>
       <c r="AB73">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AC73">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AD73">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE73">
         <v>1.15</v>
@@ -12371,25 +12371,25 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="O74">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="P74">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="Q74">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="R74">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="U74">
         <v>2.3</v>
@@ -12398,7 +12398,7 @@
         <v>1.53</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X74">
         <v>1.01</v>
@@ -12407,16 +12407,16 @@
         <v>1.17</v>
       </c>
       <c r="Z74">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA74">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB74">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC74">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AD74">
         <v>1.45</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AK74">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13068,13 +13068,13 @@
         <v>3.7</v>
       </c>
       <c r="AC78">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AD78">
         <v>2.22</v>
       </c>
       <c r="AE78">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AF78">
         <v>2</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.47</v>
+        <v>3.35</v>
       </c>
       <c r="O83">
-        <v>3.73</v>
+        <v>3.45</v>
       </c>
       <c r="P83">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q83">
         <v>3.75</v>
@@ -13853,49 +13853,49 @@
         <v>2.25</v>
       </c>
       <c r="S83">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T83">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U83">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V83">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W83">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z83">
         <v>4.1</v>
       </c>
       <c r="AA83">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AC83">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="AD83">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE83">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG83">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="O84">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
-        <v>4.66</v>
+        <v>4.33</v>
       </c>
       <c r="Q84">
         <v>2.21</v>
@@ -14028,10 +14028,10 @@
         <v>1.48</v>
       </c>
       <c r="W84">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X84">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
         <v>1.24</v>
@@ -14040,10 +14040,10 @@
         <v>3.98</v>
       </c>
       <c r="AA84">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB84">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC84">
         <v>2.89</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O85">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="Q85">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="R85">
         <v>2.12</v>
@@ -14182,46 +14182,46 @@
         <v>1.36</v>
       </c>
       <c r="T85">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U85">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="V85">
         <v>1.39</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z85">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA85">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB85">
+        <v>1.89</v>
+      </c>
+      <c r="AC85">
+        <v>2.97</v>
+      </c>
+      <c r="AD85">
+        <v>1.3</v>
+      </c>
+      <c r="AE85">
+        <v>1.08</v>
+      </c>
+      <c r="AF85">
         <v>1.75</v>
       </c>
-      <c r="AC85">
-        <v>3.05</v>
-      </c>
-      <c r="AD85">
-        <v>1.28</v>
-      </c>
-      <c r="AE85">
-        <v>1.07</v>
-      </c>
-      <c r="AF85">
-        <v>1.76</v>
-      </c>
       <c r="AG85">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="O86">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P86">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q86">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="R86">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S86">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U86">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V86">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB86">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AC86">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AD86">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE86">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AG86">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="O87">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P87">
+        <v>1.95</v>
+      </c>
+      <c r="Q87">
+        <v>3.4</v>
+      </c>
+      <c r="R87">
+        <v>2.4</v>
+      </c>
+      <c r="S87">
+        <v>1.2</v>
+      </c>
+      <c r="T87">
+        <v>4</v>
+      </c>
+      <c r="U87">
+        <v>2.1</v>
+      </c>
+      <c r="V87">
+        <v>1.67</v>
+      </c>
+      <c r="W87">
+        <v>1.17</v>
+      </c>
+      <c r="X87">
+        <v>1.02</v>
+      </c>
+      <c r="Y87">
+        <v>1.08</v>
+      </c>
+      <c r="Z87">
+        <v>5.45</v>
+      </c>
+      <c r="AA87">
+        <v>1.47</v>
+      </c>
+      <c r="AB87">
         <v>2.6</v>
       </c>
-      <c r="Q87">
-        <v>2.8</v>
-      </c>
-      <c r="R87">
-        <v>2.25</v>
-      </c>
-      <c r="S87">
-        <v>1.25</v>
-      </c>
-      <c r="T87">
-        <v>3.5</v>
-      </c>
-      <c r="U87">
-        <v>2.38</v>
-      </c>
-      <c r="V87">
-        <v>1.53</v>
-      </c>
-      <c r="W87">
-        <v>1.13</v>
-      </c>
-      <c r="X87">
-        <v>1.01</v>
-      </c>
-      <c r="Y87">
-        <v>1.16</v>
-      </c>
-      <c r="Z87">
-        <v>4.15</v>
-      </c>
-      <c r="AA87">
-        <v>1.6</v>
-      </c>
-      <c r="AB87">
-        <v>2.15</v>
-      </c>
       <c r="AC87">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="AD87">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AE87">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF87">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AG87">
-        <v>2.36</v>
+        <v>2.73</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK87">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="O88">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="Q88">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="R88">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U88">
         <v>2.1</v>
       </c>
       <c r="V88">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>5.45</v>
+        <v>5.2</v>
       </c>
       <c r="AA88">
+        <v>1.44</v>
+      </c>
+      <c r="AB88">
+        <v>2.43</v>
+      </c>
+      <c r="AC88">
+        <v>2.18</v>
+      </c>
+      <c r="AD88">
+        <v>1.58</v>
+      </c>
+      <c r="AE88">
+        <v>1.2</v>
+      </c>
+      <c r="AF88">
         <v>1.41</v>
       </c>
-      <c r="AB88">
-        <v>2.52</v>
-      </c>
-      <c r="AC88">
-        <v>2.11</v>
-      </c>
-      <c r="AD88">
-        <v>1.62</v>
-      </c>
-      <c r="AE88">
-        <v>1.22</v>
-      </c>
-      <c r="AF88">
-        <v>1.38</v>
-      </c>
       <c r="AG88">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O89">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>3.48</v>
+        <v>2.8</v>
       </c>
       <c r="R89">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U89">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z89">
-        <v>5.55</v>
+        <v>4.15</v>
       </c>
       <c r="AA89">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB89">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AD89">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AE89">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF89">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AG89">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK89">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O90">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P90">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="Q90">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R90">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="S90">
         <v>1.25</v>
       </c>
       <c r="T90">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="U90">
         <v>2.25</v>
@@ -15012,31 +15012,31 @@
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z90">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA90">
+        <v>1.65</v>
+      </c>
+      <c r="AB90">
+        <v>2.2</v>
+      </c>
+      <c r="AC90">
+        <v>2.42</v>
+      </c>
+      <c r="AD90">
+        <v>1.44</v>
+      </c>
+      <c r="AE90">
+        <v>1.15</v>
+      </c>
+      <c r="AF90">
         <v>1.53</v>
       </c>
-      <c r="AB90">
-        <v>2.29</v>
-      </c>
-      <c r="AC90">
-        <v>2.28</v>
-      </c>
-      <c r="AD90">
-        <v>1.5</v>
-      </c>
-      <c r="AE90">
-        <v>1.18</v>
-      </c>
-      <c r="AF90">
-        <v>1.48</v>
-      </c>
       <c r="AG90">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK90">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>7.95</v>
+        <v>9</v>
       </c>
       <c r="O91">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="P91">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Q91">
         <v>7.5</v>
@@ -15157,43 +15157,43 @@
         <v>3.25</v>
       </c>
       <c r="S91">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T91">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="U91">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V91">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="W91">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z91">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA91">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB91">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC91">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AD91">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AE91">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AF91">
         <v>1.62</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.08</v>
+        <v>3.87</v>
       </c>
       <c r="AK91">
         <v>1.05</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="O94">
-        <v>3.87</v>
+        <v>3.55</v>
       </c>
       <c r="P94">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q94">
         <v>3.96</v>
@@ -15652,10 +15652,10 @@
         <v>3.3</v>
       </c>
       <c r="U94">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V94">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W94">
         <v>1.08</v>
@@ -15664,31 +15664,31 @@
         <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z94">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="AA94">
         <v>1.73</v>
       </c>
       <c r="AB94">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC94">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="AD94">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE94">
         <v>1.1</v>
       </c>
       <c r="AF94">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG94">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -20041,34 +20041,34 @@
         <v>4</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA121">
         <v>1.9</v>
@@ -20077,19 +20077,19 @@
         <v>1.9</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,34 +20204,34 @@
         <v>1.42</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA122">
         <v>1.5</v>
@@ -20240,19 +20240,19 @@
         <v>2.5</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="O132">
         <v>3.3</v>
       </c>
       <c r="P132">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="Q132">
         <v>3.74</v>
@@ -21864,10 +21864,10 @@
         <v>3.42</v>
       </c>
       <c r="AA132">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AB132">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AC132">
         <v>3.28</v>
@@ -21988,25 +21988,25 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="O133">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P133">
-        <v>2.98</v>
+        <v>2.53</v>
       </c>
       <c r="Q133">
         <v>3</v>
       </c>
       <c r="R133">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S133">
         <v>1.32</v>
       </c>
       <c r="T133">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U133">
         <v>2.63</v>
@@ -22015,7 +22015,7 @@
         <v>1.43</v>
       </c>
       <c r="W133">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X133">
         <v>1</v>
@@ -22027,10 +22027,10 @@
         <v>3.68</v>
       </c>
       <c r="AA133">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB133">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC133">
         <v>2.91</v>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK133">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -23138,55 +23138,55 @@
         <v>6</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>4.16</v>
+        <v>4.68</v>
       </c>
       <c r="O156">
-        <v>4.08</v>
+        <v>4.57</v>
       </c>
       <c r="P156">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="Q156">
-        <v>4.1</v>
+        <v>5.04</v>
       </c>
       <c r="R156">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="S156">
         <v>1.22</v>
       </c>
       <c r="T156">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="U156">
         <v>2.05</v>
       </c>
       <c r="V156">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W156">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X156">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z156">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA156">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AB156">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="AC156">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD156">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AE156">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AF156">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AG156">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AK156">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>4.68</v>
+        <v>4.16</v>
       </c>
       <c r="O157">
-        <v>4.57</v>
+        <v>4.08</v>
       </c>
       <c r="P157">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q157">
-        <v>5.04</v>
+        <v>4.1</v>
       </c>
       <c r="R157">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="S157">
         <v>1.22</v>
       </c>
       <c r="T157">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U157">
         <v>2.05</v>
       </c>
       <c r="V157">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W157">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z157">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AA157">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AB157">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="AC157">
+        <v>1.9</v>
+      </c>
+      <c r="AD157">
+        <v>1.8</v>
+      </c>
+      <c r="AE157">
+        <v>1.34</v>
+      </c>
+      <c r="AF157">
+        <v>1.35</v>
+      </c>
+      <c r="AG157">
+        <v>2.93</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>2</v>
       </c>
-      <c r="AD157">
-        <v>1.72</v>
-      </c>
-      <c r="AE157">
-        <v>1.23</v>
-      </c>
-      <c r="AF157">
-        <v>1.5</v>
-      </c>
-      <c r="AG157">
-        <v>2.4</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.17</v>
-      </c>
       <c r="AK157">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.62</v>
+        <v>1.56</v>
       </c>
       <c r="O169">
-        <v>3.24</v>
+        <v>3.68</v>
       </c>
       <c r="P169">
-        <v>2.34</v>
+        <v>5.16</v>
       </c>
       <c r="Q169">
+        <v>2.14</v>
+      </c>
+      <c r="R169">
+        <v>2.14</v>
+      </c>
+      <c r="S169">
+        <v>1.37</v>
+      </c>
+      <c r="T169">
+        <v>2.68</v>
+      </c>
+      <c r="U169">
+        <v>2.88</v>
+      </c>
+      <c r="V169">
+        <v>1.36</v>
+      </c>
+      <c r="W169">
+        <v>1.06</v>
+      </c>
+      <c r="X169">
+        <v>1.01</v>
+      </c>
+      <c r="Y169">
+        <v>1.27</v>
+      </c>
+      <c r="Z169">
+        <v>3.14</v>
+      </c>
+      <c r="AA169">
+        <v>1.95</v>
+      </c>
+      <c r="AB169">
+        <v>1.85</v>
+      </c>
+      <c r="AC169">
         <v>3.2</v>
       </c>
-      <c r="R169">
-        <v>2.2</v>
-      </c>
-      <c r="S169">
-        <v>1.32</v>
-      </c>
-      <c r="T169">
-        <v>3.2</v>
-      </c>
-      <c r="U169">
-        <v>2.65</v>
-      </c>
-      <c r="V169">
-        <v>1.45</v>
-      </c>
-      <c r="W169">
-        <v>1.07</v>
-      </c>
-      <c r="X169">
-        <v>1</v>
-      </c>
-      <c r="Y169">
-        <v>1.21</v>
-      </c>
-      <c r="Z169">
-        <v>3.58</v>
-      </c>
-      <c r="AA169">
-        <v>1.92</v>
-      </c>
-      <c r="AB169">
-        <v>1.83</v>
-      </c>
-      <c r="AC169">
-        <v>2.95</v>
-      </c>
       <c r="AD169">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AE169">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF169">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG169">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK169">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.56</v>
+        <v>3.16</v>
       </c>
       <c r="O170">
-        <v>3.68</v>
+        <v>3.02</v>
       </c>
       <c r="P170">
-        <v>5.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q170">
-        <v>2.14</v>
+        <v>3.82</v>
       </c>
       <c r="R170">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S170">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="T170">
-        <v>2.68</v>
+        <v>2.39</v>
       </c>
       <c r="U170">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="V170">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W170">
         <v>1.06</v>
       </c>
       <c r="X170">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y170">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Z170">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AA170">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="AB170">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC170">
-        <v>3.2</v>
+        <v>3.92</v>
       </c>
       <c r="AD170">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE170">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF170">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG170">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AK170">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>3.16</v>
+        <v>2.62</v>
       </c>
       <c r="O171">
-        <v>3.02</v>
+        <v>3.24</v>
       </c>
       <c r="P171">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="Q171">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="R171">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S171">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="T171">
-        <v>2.39</v>
+        <v>3.2</v>
       </c>
       <c r="U171">
-        <v>3.12</v>
+        <v>2.65</v>
       </c>
       <c r="V171">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="W171">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X171">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y171">
+        <v>1.21</v>
+      </c>
+      <c r="Z171">
+        <v>3.58</v>
+      </c>
+      <c r="AA171">
+        <v>1.92</v>
+      </c>
+      <c r="AB171">
+        <v>1.83</v>
+      </c>
+      <c r="AC171">
+        <v>2.95</v>
+      </c>
+      <c r="AD171">
         <v>1.37</v>
       </c>
-      <c r="Z171">
-        <v>2.66</v>
-      </c>
-      <c r="AA171">
-        <v>2.28</v>
-      </c>
-      <c r="AB171">
-        <v>1.61</v>
-      </c>
-      <c r="AC171">
-        <v>3.92</v>
-      </c>
-      <c r="AD171">
-        <v>1.21</v>
-      </c>
       <c r="AE171">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF171">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AG171">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AK171">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="O174">
-        <v>3.44</v>
+        <v>3.72</v>
       </c>
       <c r="P174">
-        <v>3.06</v>
+        <v>3.87</v>
       </c>
       <c r="Q174">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="R174">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S174">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T174">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U174">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="V174">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W174">
         <v>1.07</v>
       </c>
       <c r="X174">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z174">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA174">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB174">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC174">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AD174">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE174">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF174">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG174">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK174">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="O175">
         <v>3.72</v>
       </c>
       <c r="P175">
-        <v>3.87</v>
+        <v>1.94</v>
       </c>
       <c r="Q175">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="R175">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="S175">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T175">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="U175">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="V175">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X175">
         <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z175">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA175">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB175">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC175">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AD175">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE175">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF175">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG175">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK175">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="O176">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="P176">
-        <v>4.33</v>
+        <v>5.31</v>
       </c>
       <c r="Q176">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="R176">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S176">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T176">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="U176">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="V176">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="W176">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z176">
-        <v>4.1</v>
+        <v>6.12</v>
       </c>
       <c r="AA176">
-        <v>1.79</v>
+        <v>1.44</v>
       </c>
       <c r="AB176">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AC176">
-        <v>2.79</v>
+        <v>2.06</v>
       </c>
       <c r="AD176">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AE176">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF176">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG176">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK176">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="O177">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="P177">
-        <v>2.38</v>
+        <v>4.33</v>
       </c>
       <c r="Q177">
-        <v>3.12</v>
+        <v>2.18</v>
       </c>
       <c r="R177">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T177">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="U177">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V177">
         <v>1.52</v>
       </c>
       <c r="W177">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z177">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA177">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB177">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AC177">
-        <v>2.42</v>
+        <v>2.79</v>
       </c>
       <c r="AD177">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE177">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF177">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AG177">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK177">
-        <v>1.43</v>
+        <v>2.11</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,80 +29323,80 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="O178">
-        <v>4.45</v>
+        <v>3.56</v>
       </c>
       <c r="P178">
-        <v>5.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q178">
-        <v>1.75</v>
+        <v>3.12</v>
       </c>
       <c r="R178">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="S178">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T178">
-        <v>4.2</v>
+        <v>3.46</v>
       </c>
       <c r="U178">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="V178">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W178">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X178">
         <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z178">
-        <v>6.12</v>
+        <v>4.2</v>
       </c>
       <c r="AA178">
+        <v>1.88</v>
+      </c>
+      <c r="AB178">
+        <v>1.96</v>
+      </c>
+      <c r="AC178">
+        <v>2.42</v>
+      </c>
+      <c r="AD178">
         <v>1.44</v>
       </c>
-      <c r="AB178">
-        <v>2.7</v>
-      </c>
-      <c r="AC178">
-        <v>2.06</v>
-      </c>
-      <c r="AD178">
-        <v>1.7</v>
-      </c>
       <c r="AE178">
+        <v>1.15</v>
+      </c>
+      <c r="AF178">
+        <v>1.51</v>
+      </c>
+      <c r="AG178">
+        <v>2.35</v>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ178">
         <v>1.25</v>
       </c>
-      <c r="AF178">
-        <v>1.6</v>
-      </c>
-      <c r="AG178">
-        <v>2.14</v>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ178">
-        <v>1.13</v>
-      </c>
       <c r="AK178">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="O179">
-        <v>3.72</v>
+        <v>3.44</v>
       </c>
       <c r="P179">
-        <v>1.94</v>
+        <v>3.06</v>
       </c>
       <c r="Q179">
-        <v>4.11</v>
+        <v>2.78</v>
       </c>
       <c r="R179">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="S179">
+        <v>1.3</v>
+      </c>
+      <c r="T179">
+        <v>3</v>
+      </c>
+      <c r="U179">
+        <v>2.81</v>
+      </c>
+      <c r="V179">
+        <v>1.42</v>
+      </c>
+      <c r="W179">
+        <v>1.07</v>
+      </c>
+      <c r="X179">
+        <v>1</v>
+      </c>
+      <c r="Y179">
+        <v>1.24</v>
+      </c>
+      <c r="Z179">
+        <v>3.34</v>
+      </c>
+      <c r="AA179">
+        <v>1.87</v>
+      </c>
+      <c r="AB179">
+        <v>1.86</v>
+      </c>
+      <c r="AC179">
+        <v>3.14</v>
+      </c>
+      <c r="AD179">
         <v>1.27</v>
       </c>
-      <c r="T179">
-        <v>3.32</v>
-      </c>
-      <c r="U179">
-        <v>2.32</v>
-      </c>
-      <c r="V179">
-        <v>1.52</v>
-      </c>
-      <c r="W179">
-        <v>1.1</v>
-      </c>
-      <c r="X179">
-        <v>1.01</v>
-      </c>
-      <c r="Y179">
-        <v>1.21</v>
-      </c>
-      <c r="Z179">
-        <v>4.25</v>
-      </c>
-      <c r="AA179">
-        <v>1.79</v>
-      </c>
-      <c r="AB179">
-        <v>1.98</v>
-      </c>
-      <c r="AC179">
-        <v>2.62</v>
-      </c>
-      <c r="AD179">
-        <v>1.38</v>
-      </c>
       <c r="AE179">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF179">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG179">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
         <v>1.24</v>
       </c>
       <c r="AK179">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O182">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P182">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Q182">
         <v>2.8</v>
@@ -29990,28 +29990,28 @@
         <v>2.4</v>
       </c>
       <c r="S182">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T182">
         <v>4</v>
       </c>
       <c r="U182">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="V182">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W182">
+        <v>1.11</v>
+      </c>
+      <c r="X182">
+        <v>1.02</v>
+      </c>
+      <c r="Y182">
         <v>1.13</v>
       </c>
-      <c r="X182">
-        <v>1.01</v>
-      </c>
-      <c r="Y182">
-        <v>1.11</v>
-      </c>
       <c r="Z182">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="AA182">
         <v>1.5</v>
@@ -30020,19 +30020,19 @@
         <v>2.5</v>
       </c>
       <c r="AC182">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AD182">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE182">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF182">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG182">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31777,55 +31777,55 @@
         <v>2.97</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31940,55 +31940,55 @@
         <v>4.38</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32103,55 +32103,55 @@
         <v>2.87</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32266,55 +32266,55 @@
         <v>3.56</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O204">
-        <v>3.36</v>
+        <v>3.54</v>
       </c>
       <c r="P204">
-        <v>3.85</v>
+        <v>2.83</v>
       </c>
       <c r="Q204">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="R204">
+        <v>2.39</v>
+      </c>
+      <c r="S204">
+        <v>1.28</v>
+      </c>
+      <c r="T204">
+        <v>3.26</v>
+      </c>
+      <c r="U204">
+        <v>2.29</v>
+      </c>
+      <c r="V204">
+        <v>1.53</v>
+      </c>
+      <c r="W204">
+        <v>1.12</v>
+      </c>
+      <c r="X204">
+        <v>1.01</v>
+      </c>
+      <c r="Y204">
+        <v>1.16</v>
+      </c>
+      <c r="Z204">
+        <v>4.56</v>
+      </c>
+      <c r="AA204">
+        <v>1.65</v>
+      </c>
+      <c r="AB204">
         <v>2.1</v>
       </c>
-      <c r="S204">
-        <v>1.4</v>
-      </c>
-      <c r="T204">
-        <v>2.75</v>
-      </c>
-      <c r="U204">
-        <v>2.88</v>
-      </c>
-      <c r="V204">
-        <v>1.35</v>
-      </c>
-      <c r="W204">
-        <v>1.05</v>
-      </c>
-      <c r="X204">
-        <v>1.05</v>
-      </c>
-      <c r="Y204">
-        <v>1.31</v>
-      </c>
-      <c r="Z204">
-        <v>2.92</v>
-      </c>
-      <c r="AA204">
-        <v>2.08</v>
-      </c>
-      <c r="AB204">
-        <v>1.7</v>
-      </c>
       <c r="AC204">
-        <v>3.58</v>
+        <v>2.43</v>
       </c>
       <c r="AD204">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AE204">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF204">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AG204">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK204">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="O205">
-        <v>3.54</v>
+        <v>6</v>
       </c>
       <c r="P205">
-        <v>2.83</v>
+        <v>10.5</v>
       </c>
       <c r="Q205">
-        <v>2.81</v>
+        <v>1.62</v>
       </c>
       <c r="R205">
-        <v>2.39</v>
+        <v>2.76</v>
       </c>
       <c r="S205">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="T205">
-        <v>3.26</v>
+        <v>4.1</v>
       </c>
       <c r="U205">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="V205">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="W205">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X205">
         <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z205">
-        <v>4.56</v>
+        <v>5.55</v>
       </c>
       <c r="AA205">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AB205">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AC205">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AD205">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AE205">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AF205">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG205">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK205">
-        <v>1.62</v>
+        <v>3.94</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="O206">
-        <v>3.64</v>
+        <v>3.36</v>
       </c>
       <c r="P206">
+        <v>3.85</v>
+      </c>
+      <c r="Q206">
+        <v>2.45</v>
+      </c>
+      <c r="R206">
+        <v>2.1</v>
+      </c>
+      <c r="S206">
+        <v>1.4</v>
+      </c>
+      <c r="T206">
         <v>2.75</v>
       </c>
-      <c r="Q206">
-        <v>2.81</v>
-      </c>
-      <c r="R206">
-        <v>2.28</v>
-      </c>
-      <c r="S206">
-        <v>1.27</v>
-      </c>
-      <c r="T206">
-        <v>3.32</v>
-      </c>
       <c r="U206">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="V206">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="W206">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X206">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y206">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z206">
-        <v>4.33</v>
+        <v>2.92</v>
       </c>
       <c r="AA206">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="AB206">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC206">
-        <v>2.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD206">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE206">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="AF206">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG206">
-        <v>2.42</v>
+        <v>1.83</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK206">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="O207">
-        <v>6</v>
+        <v>3.48</v>
       </c>
       <c r="P207">
-        <v>10.5</v>
+        <v>3.42</v>
       </c>
       <c r="Q207">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="R207">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="S207">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T207">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="U207">
-        <v>2.06</v>
+        <v>2.53</v>
       </c>
       <c r="V207">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W207">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z207">
-        <v>5.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA207">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="AB207">
-        <v>2.59</v>
+        <v>1.95</v>
       </c>
       <c r="AC207">
-        <v>2.11</v>
+        <v>2.92</v>
       </c>
       <c r="AD207">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="AE207">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AF207">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG207">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AK207">
-        <v>3.94</v>
+        <v>1.73</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,19 +34213,19 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.67</v>
+        <v>2.84</v>
       </c>
       <c r="O208">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="P208">
-        <v>4.56</v>
+        <v>2.31</v>
       </c>
       <c r="Q208">
-        <v>2.19</v>
+        <v>3.23</v>
       </c>
       <c r="R208">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="S208">
         <v>1.3</v>
@@ -34234,43 +34234,43 @@
         <v>3.12</v>
       </c>
       <c r="U208">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="V208">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W208">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z208">
-        <v>4.27</v>
+        <v>4.15</v>
       </c>
       <c r="AA208">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AB208">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AC208">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD208">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE208">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF208">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG208">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK208">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="O209">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="P209">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="Q209">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="R209">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S209">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="T209">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="U209">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="V209">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W209">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z209">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AA209">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AB209">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC209">
-        <v>2.92</v>
+        <v>2.42</v>
       </c>
       <c r="AD209">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE209">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF209">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG209">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK209">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,19 +34539,19 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="O210">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="P210">
-        <v>2.31</v>
+        <v>4.56</v>
       </c>
       <c r="Q210">
-        <v>3.23</v>
+        <v>2.19</v>
       </c>
       <c r="R210">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="S210">
         <v>1.3</v>
@@ -34560,43 +34560,43 @@
         <v>3.12</v>
       </c>
       <c r="U210">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="V210">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W210">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X210">
         <v>1.01</v>
       </c>
       <c r="Y210">
+        <v>1.21</v>
+      </c>
+      <c r="Z210">
+        <v>4.27</v>
+      </c>
+      <c r="AA210">
+        <v>1.79</v>
+      </c>
+      <c r="AB210">
+        <v>2</v>
+      </c>
+      <c r="AC210">
+        <v>2.56</v>
+      </c>
+      <c r="AD210">
+        <v>1.4</v>
+      </c>
+      <c r="AE210">
         <v>1.16</v>
       </c>
-      <c r="Z210">
-        <v>4.15</v>
-      </c>
-      <c r="AA210">
-        <v>1.67</v>
-      </c>
-      <c r="AB210">
-        <v>2.21</v>
-      </c>
-      <c r="AC210">
-        <v>2.63</v>
-      </c>
-      <c r="AD210">
-        <v>1.47</v>
-      </c>
-      <c r="AE210">
-        <v>1.18</v>
-      </c>
       <c r="AF210">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG210">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK210">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q221">
         <v>3.18</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G234">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G235">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G236">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -42046,34 +42046,34 @@
         <v>7.1</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA256">
         <v>1.57</v>
@@ -42082,19 +42082,19 @@
         <v>2.35</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -45795,34 +45795,34 @@
         <v>2.5</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA279">
         <v>1.93</v>
@@ -45831,19 +45831,19 @@
         <v>1.81</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46284,55 +46284,55 @@
         <v>0</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA282">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB282">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -52478,34 +52478,34 @@
         <v>2.91</v>
       </c>
       <c r="Q320">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R320">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S320">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T320">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U320">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V320">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W320">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X320">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y320">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z320">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AA320">
         <v>2.5</v>
@@ -52514,19 +52514,19 @@
         <v>1.47</v>
       </c>
       <c r="AC320">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD320">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE320">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF320">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG320">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK320">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -54923,34 +54923,34 @@
         <v>1.95</v>
       </c>
       <c r="Q335">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R335">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S335">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T335">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U335">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V335">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W335">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X335">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y335">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z335">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA335">
         <v>2</v>
@@ -54959,19 +54959,19 @@
         <v>1.71</v>
       </c>
       <c r="AC335">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD335">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE335">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF335">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG335">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK335">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55249,55 +55249,55 @@
         <v>1.87</v>
       </c>
       <c r="Q337">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R337">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S337">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T337">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U337">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V337">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W337">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X337">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y337">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z337">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA337">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB337">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC337">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD337">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE337">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF337">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG337">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH337" t="inlineStr">
         <is>
@@ -55310,10 +55310,10 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK337">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL337">
         <v>0</v>
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G365">
@@ -59804,13 +59804,13 @@
         </is>
       </c>
       <c r="N365">
-        <v>3.25</v>
+        <v>1.58</v>
       </c>
       <c r="O365">
-        <v>3.8</v>
+        <v>4.69</v>
       </c>
       <c r="P365">
-        <v>1.98</v>
+        <v>5.36</v>
       </c>
       <c r="Q365">
         <v>0</v>
@@ -59849,10 +59849,10 @@
         <v>0</v>
       </c>
       <c r="AC365">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD365">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE365">
         <v>0</v>
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G366">
@@ -59967,13 +59967,13 @@
         </is>
       </c>
       <c r="N366">
-        <v>1.58</v>
+        <v>3.25</v>
       </c>
       <c r="O366">
-        <v>4.69</v>
+        <v>3.8</v>
       </c>
       <c r="P366">
-        <v>5.36</v>
+        <v>1.98</v>
       </c>
       <c r="Q366">
         <v>0</v>
@@ -60012,10 +60012,10 @@
         <v>0</v>
       </c>
       <c r="AC366">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD366">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE366">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="O6">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="Q6">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="R6">
         <v>2.06</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U6">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1323,28 +1323,28 @@
         <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
         <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AK6">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P7">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="Q7">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="R7">
         <v>2.06</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1486,28 +1486,28 @@
         <v>1.29</v>
       </c>
       <c r="Z7">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AB7">
         <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD7">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AK7">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>4.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q22">
-        <v>2.41</v>
+        <v>3.52</v>
       </c>
       <c r="R22">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>2.79</v>
+        <v>3.07</v>
       </c>
       <c r="U22">
+        <v>2.62</v>
+      </c>
+      <c r="V22">
+        <v>1.39</v>
+      </c>
+      <c r="W22">
+        <v>1.1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1.26</v>
+      </c>
+      <c r="Z22">
+        <v>3.68</v>
+      </c>
+      <c r="AA22">
+        <v>1.85</v>
+      </c>
+      <c r="AB22">
+        <v>1.93</v>
+      </c>
+      <c r="AC22">
         <v>3.09</v>
       </c>
-      <c r="V22">
-        <v>1.34</v>
-      </c>
-      <c r="W22">
-        <v>1.06</v>
-      </c>
-      <c r="X22">
-        <v>1.01</v>
-      </c>
-      <c r="Y22">
+      <c r="AD22">
+        <v>1.35</v>
+      </c>
+      <c r="AE22">
+        <v>1.08</v>
+      </c>
+      <c r="AF22">
+        <v>1.65</v>
+      </c>
+      <c r="AG22">
+        <v>2.08</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.33</v>
+      </c>
+      <c r="AK22">
         <v>1.36</v>
-      </c>
-      <c r="Z22">
-        <v>3.05</v>
-      </c>
-      <c r="AA22">
-        <v>2.08</v>
-      </c>
-      <c r="AB22">
-        <v>1.73</v>
-      </c>
-      <c r="AC22">
-        <v>3.68</v>
-      </c>
-      <c r="AD22">
-        <v>1.26</v>
-      </c>
-      <c r="AE22">
-        <v>1.04</v>
-      </c>
-      <c r="AF22">
-        <v>1.87</v>
-      </c>
-      <c r="AG22">
-        <v>1.82</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.21</v>
-      </c>
-      <c r="AK22">
-        <v>1.91</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="O23">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="P23">
-        <v>2.3</v>
+        <v>4.35</v>
       </c>
       <c r="Q23">
-        <v>3.52</v>
+        <v>2.41</v>
       </c>
       <c r="R23">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>3.07</v>
+        <v>2.79</v>
       </c>
       <c r="U23">
-        <v>2.62</v>
+        <v>3.09</v>
       </c>
       <c r="V23">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
+        <v>1.36</v>
+      </c>
+      <c r="Z23">
+        <v>3.05</v>
+      </c>
+      <c r="AA23">
+        <v>2.08</v>
+      </c>
+      <c r="AB23">
+        <v>1.73</v>
+      </c>
+      <c r="AC23">
+        <v>3.68</v>
+      </c>
+      <c r="AD23">
         <v>1.26</v>
       </c>
-      <c r="Z23">
-        <v>3.68</v>
-      </c>
-      <c r="AA23">
-        <v>1.85</v>
-      </c>
-      <c r="AB23">
-        <v>1.93</v>
-      </c>
-      <c r="AC23">
-        <v>3.09</v>
-      </c>
-      <c r="AD23">
-        <v>1.35</v>
-      </c>
       <c r="AE23">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG23">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -6684,7 +6684,7 @@
         <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="U39">
         <v>2.9</v>
@@ -6708,7 +6708,7 @@
         <v>2.14</v>
       </c>
       <c r="AB39">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC39">
         <v>3.79</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="O51">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
         <v>3.2</v>
       </c>
       <c r="Q51">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="R51">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U51">
         <v>2.15</v>
@@ -8661,10 +8661,10 @@
         <v>4.95</v>
       </c>
       <c r="AA51">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB51">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC51">
         <v>2.29</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O52">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="Q52">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R52">
         <v>2.3</v>
@@ -8812,31 +8812,31 @@
         <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AA52">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AC52">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
         <v>1.55</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O53">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P53">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="Q53">
         <v>2.05</v>
@@ -8993,10 +8993,10 @@
         <v>3.12</v>
       </c>
       <c r="AC53">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AD53">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AE53">
         <v>1.33</v>
@@ -9005,7 +9005,7 @@
         <v>1.39</v>
       </c>
       <c r="AG53">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>3.65</v>
       </c>
       <c r="U54">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V54">
         <v>1.6</v>
@@ -9156,7 +9156,7 @@
         <v>2.35</v>
       </c>
       <c r="AC54">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AD54">
         <v>1.57</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O67">
         <v>3.25</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="O69">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P69">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="Q69">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S69">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U69">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="V69">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W69">
+        <v>1.06</v>
+      </c>
+      <c r="X69">
+        <v>1.03</v>
+      </c>
+      <c r="Y69">
+        <v>1.26</v>
+      </c>
+      <c r="Z69">
+        <v>3.2</v>
+      </c>
+      <c r="AA69">
+        <v>2</v>
+      </c>
+      <c r="AB69">
+        <v>1.81</v>
+      </c>
+      <c r="AC69">
+        <v>3</v>
+      </c>
+      <c r="AD69">
+        <v>1.32</v>
+      </c>
+      <c r="AE69">
         <v>1.07</v>
       </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.28</v>
-      </c>
-      <c r="Z69">
-        <v>3.08</v>
-      </c>
-      <c r="AA69">
-        <v>1.97</v>
-      </c>
-      <c r="AB69">
-        <v>1.78</v>
-      </c>
-      <c r="AC69">
-        <v>3.28</v>
-      </c>
-      <c r="AD69">
-        <v>1.25</v>
-      </c>
-      <c r="AE69">
-        <v>1.06</v>
-      </c>
       <c r="AF69">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG69">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK69">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,43 +11719,43 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O70">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="P70">
-        <v>5.71</v>
+        <v>5.46</v>
       </c>
       <c r="Q70">
         <v>1.9</v>
       </c>
       <c r="R70">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="S70">
+        <v>1.15</v>
+      </c>
+      <c r="T70">
+        <v>4.3</v>
+      </c>
+      <c r="U70">
+        <v>1.96</v>
+      </c>
+      <c r="V70">
+        <v>1.78</v>
+      </c>
+      <c r="W70">
         <v>1.18</v>
       </c>
-      <c r="T70">
-        <v>4</v>
-      </c>
-      <c r="U70">
-        <v>2.05</v>
-      </c>
-      <c r="V70">
-        <v>1.7</v>
-      </c>
-      <c r="W70">
-        <v>1.15</v>
-      </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z70">
-        <v>5.95</v>
+        <v>6.75</v>
       </c>
       <c r="AA70">
         <v>1.44</v>
@@ -11764,19 +11764,19 @@
         <v>2.75</v>
       </c>
       <c r="AC70">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AD70">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AE70">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AF70">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AG70">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK70">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="O74">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="P74">
-        <v>3.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q74">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="R74">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
         <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="U74">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V74">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z74">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA74">
+        <v>1.66</v>
+      </c>
+      <c r="AB74">
+        <v>2.15</v>
+      </c>
+      <c r="AC74">
+        <v>2.71</v>
+      </c>
+      <c r="AD74">
+        <v>1.45</v>
+      </c>
+      <c r="AE74">
+        <v>1.13</v>
+      </c>
+      <c r="AF74">
         <v>1.57</v>
       </c>
-      <c r="AB74">
-        <v>2.36</v>
-      </c>
-      <c r="AC74">
-        <v>2.47</v>
-      </c>
-      <c r="AD74">
-        <v>1.54</v>
-      </c>
-      <c r="AE74">
-        <v>1.15</v>
-      </c>
-      <c r="AF74">
-        <v>1.53</v>
-      </c>
       <c r="AG74">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK74">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.9</v>
+        <v>1.84</v>
       </c>
       <c r="O75">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="P75">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="Q75">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="R75">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="S75">
         <v>1.25</v>
       </c>
       <c r="T75">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="U75">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V75">
+        <v>1.59</v>
+      </c>
+      <c r="W75">
+        <v>1.11</v>
+      </c>
+      <c r="X75">
+        <v>1.02</v>
+      </c>
+      <c r="Y75">
+        <v>1.18</v>
+      </c>
+      <c r="Z75">
+        <v>4.75</v>
+      </c>
+      <c r="AA75">
+        <v>1.57</v>
+      </c>
+      <c r="AB75">
+        <v>2.36</v>
+      </c>
+      <c r="AC75">
+        <v>2.47</v>
+      </c>
+      <c r="AD75">
+        <v>1.54</v>
+      </c>
+      <c r="AE75">
+        <v>1.15</v>
+      </c>
+      <c r="AF75">
         <v>1.53</v>
       </c>
-      <c r="W75">
-        <v>1.12</v>
-      </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
-      <c r="Y75">
-        <v>1.17</v>
-      </c>
-      <c r="Z75">
-        <v>4.05</v>
-      </c>
-      <c r="AA75">
-        <v>1.66</v>
-      </c>
-      <c r="AB75">
-        <v>2.15</v>
-      </c>
-      <c r="AC75">
-        <v>2.71</v>
-      </c>
-      <c r="AD75">
-        <v>1.45</v>
-      </c>
-      <c r="AE75">
-        <v>1.13</v>
-      </c>
-      <c r="AF75">
-        <v>1.57</v>
-      </c>
       <c r="AG75">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="O85">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="P85">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="Q85">
         <v>2.21</v>
@@ -14185,7 +14185,7 @@
         <v>3.3</v>
       </c>
       <c r="U85">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V85">
         <v>1.48</v>
@@ -14330,10 +14330,10 @@
         <v>1.8</v>
       </c>
       <c r="O86">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P86">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q86">
         <v>2.39</v>
@@ -14563,7 +14563,7 @@
         <v>1.19</v>
       </c>
       <c r="AK87">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,25 +14653,25 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O88">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P88">
         <v>2.7</v>
       </c>
       <c r="Q88">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R88">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U88">
         <v>2.25</v>
@@ -14683,34 +14683,34 @@
         <v>1.14</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z88">
-        <v>5.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA88">
+        <v>1.6</v>
+      </c>
+      <c r="AB88">
+        <v>2.15</v>
+      </c>
+      <c r="AC88">
+        <v>2.43</v>
+      </c>
+      <c r="AD88">
         <v>1.44</v>
       </c>
-      <c r="AB88">
-        <v>2.43</v>
-      </c>
-      <c r="AC88">
-        <v>2.18</v>
-      </c>
-      <c r="AD88">
-        <v>1.58</v>
-      </c>
       <c r="AE88">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF88">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AG88">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK88">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,25 +14816,25 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q89">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U89">
         <v>2.25</v>
@@ -14846,34 +14846,34 @@
         <v>1.14</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z89">
-        <v>4.15</v>
+        <v>5.2</v>
       </c>
       <c r="AA89">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB89">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AC89">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="AD89">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE89">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF89">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AG89">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK89">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14982,7 +14982,7 @@
         <v>2.4</v>
       </c>
       <c r="O90">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P90">
         <v>2.37</v>
@@ -15160,7 +15160,7 @@
         <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U91">
         <v>2.25</v>
@@ -15196,10 +15196,10 @@
         <v>1.15</v>
       </c>
       <c r="AF91">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>3.6</v>
       </c>
       <c r="AC92">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AD92">
         <v>2.08</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>3.87</v>
+        <v>3.76</v>
       </c>
       <c r="AK92">
         <v>1.05</v>
@@ -15839,7 +15839,7 @@
         <v>2.1</v>
       </c>
       <c r="AC95">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="AD95">
         <v>1.4</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O102">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P102">
         <v>2.9</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,34 +19054,34 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="O115">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="P115">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="Q115">
-        <v>4.11</v>
+        <v>4.57</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="S115">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T115">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="U115">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="V115">
         <v>1.38</v>
       </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
         <v>1.01</v>
@@ -19090,28 +19090,28 @@
         <v>1.29</v>
       </c>
       <c r="Z115">
-        <v>3.04</v>
+        <v>3.43</v>
       </c>
       <c r="AA115">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AB115">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC115">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="AD115">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE115">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF115">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG115">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,34 +19217,34 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="O116">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="P116">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="Q116">
-        <v>4.57</v>
+        <v>4.11</v>
       </c>
       <c r="R116">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="S116">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T116">
-        <v>2.95</v>
+        <v>2.69</v>
       </c>
       <c r="U116">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="V116">
         <v>1.38</v>
       </c>
       <c r="W116">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
         <v>1.01</v>
@@ -19253,28 +19253,28 @@
         <v>1.29</v>
       </c>
       <c r="Z116">
-        <v>3.43</v>
+        <v>3.04</v>
       </c>
       <c r="AA116">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AB116">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC116">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="AD116">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE116">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG116">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
+        <v>1.26</v>
+      </c>
+      <c r="AK116">
         <v>1.25</v>
-      </c>
-      <c r="AK116">
-        <v>1.16</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="O117">
         <v>3.5</v>
@@ -19389,10 +19389,10 @@
         <v>3.3</v>
       </c>
       <c r="Q117">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R117">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S117">
         <v>1.34</v>
@@ -19549,7 +19549,7 @@
         <v>3.52</v>
       </c>
       <c r="P118">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q118">
         <v>2.44</v>
@@ -19712,7 +19712,7 @@
         <v>3.4</v>
       </c>
       <c r="P119">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q119">
         <v>3.9</v>
@@ -19779,7 +19779,7 @@
         <v>1.29</v>
       </c>
       <c r="AK119">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19884,13 +19884,13 @@
         <v>1.94</v>
       </c>
       <c r="S120">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T120">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U120">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="V120">
         <v>1.35</v>
@@ -19899,25 +19899,25 @@
         <v>1.05</v>
       </c>
       <c r="X120">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y120">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z120">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="AA120">
         <v>2.2</v>
       </c>
       <c r="AB120">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC120">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AD120">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE120">
         <v>1.04</v>
@@ -19942,7 +19942,7 @@
         <v>1.29</v>
       </c>
       <c r="AK120">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="N122">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="O122">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P122">
         <v>1.4</v>
@@ -20364,7 +20364,7 @@
         <v>3.5</v>
       </c>
       <c r="P123">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q123">
         <v>2.34</v>
@@ -20376,7 +20376,7 @@
         <v>1.35</v>
       </c>
       <c r="T123">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U123">
         <v>2.74</v>
@@ -20530,55 +20530,55 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21013,7 +21013,7 @@
         <v>1.85</v>
       </c>
       <c r="O127">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P127">
         <v>3.5</v>
@@ -21378,7 +21378,7 @@
         <v>1.86</v>
       </c>
       <c r="AB129">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC129">
         <v>3.13</v>
@@ -21390,7 +21390,7 @@
         <v>1.12</v>
       </c>
       <c r="AF129">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG129">
         <v>1.85</v>
@@ -21508,7 +21508,7 @@
         <v>3.2</v>
       </c>
       <c r="Q130">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R130">
         <v>2.2</v>
@@ -21538,7 +21538,7 @@
         <v>3.8</v>
       </c>
       <c r="AA130">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB130">
         <v>2</v>
@@ -21553,10 +21553,10 @@
         <v>1.1</v>
       </c>
       <c r="AF130">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG130">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK130">
         <v>1.73</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O131">
         <v>5.25</v>
       </c>
       <c r="P131">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="Q131">
         <v>1.72</v>
@@ -21852,7 +21852,7 @@
         <v>1.36</v>
       </c>
       <c r="W132">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
         <v>1.01</v>
@@ -21879,10 +21879,10 @@
         <v>1.07</v>
       </c>
       <c r="AF132">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG132">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="O133">
         <v>3.3</v>
       </c>
       <c r="P133">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="Q133">
         <v>3.74</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="O134">
         <v>3.5</v>
       </c>
       <c r="P134">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -22190,7 +22190,7 @@
         <v>3.68</v>
       </c>
       <c r="AA134">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AB134">
         <v>1.97</v>
@@ -22809,10 +22809,10 @@
         <v>3.4</v>
       </c>
       <c r="P138">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q138">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R138">
         <v>2.3</v>
@@ -22821,46 +22821,46 @@
         <v>1.29</v>
       </c>
       <c r="T138">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U138">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V138">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W138">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X138">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z138">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA138">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AB138">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AC138">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AD138">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE138">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF138">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AG138">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>1.4</v>
       </c>
       <c r="AK138">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O139">
+        <v>3.1</v>
+      </c>
+      <c r="P139">
+        <v>2.87</v>
+      </c>
+      <c r="Q139">
         <v>3</v>
       </c>
-      <c r="P139">
-        <v>3.1</v>
-      </c>
-      <c r="Q139">
-        <v>2.78</v>
-      </c>
       <c r="R139">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S139">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T139">
         <v>2.8</v>
       </c>
       <c r="U139">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="V139">
         <v>1.36</v>
       </c>
       <c r="W139">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X139">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y139">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z139">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AA139">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB139">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC139">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD139">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE139">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF139">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG139">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>1.25</v>
       </c>
       <c r="AK139">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23802,7 +23802,7 @@
         <v>2.89</v>
       </c>
       <c r="U144">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="V144">
         <v>1.46</v>
@@ -24755,7 +24755,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N150">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25737,7 +25737,7 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O156">
         <v>4.1</v>
@@ -25746,10 +25746,10 @@
         <v>4</v>
       </c>
       <c r="Q156">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R156">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="S156">
         <v>1.25</v>
@@ -26232,7 +26232,7 @@
         <v>4</v>
       </c>
       <c r="P159">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q159">
         <v>4.1</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O161">
         <v>3.85</v>
       </c>
       <c r="P161">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q161">
         <v>2.23</v>
@@ -26606,10 +26606,10 @@
         <v>1.11</v>
       </c>
       <c r="AF161">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG161">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26718,16 +26718,16 @@
         <v>1.23</v>
       </c>
       <c r="O162">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="P162">
         <v>10</v>
       </c>
       <c r="Q162">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R162">
-        <v>3.06</v>
+        <v>3.28</v>
       </c>
       <c r="S162">
         <v>1.18</v>
@@ -26736,10 +26736,10 @@
         <v>4.6</v>
       </c>
       <c r="U162">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V162">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W162">
         <v>1.22</v>
@@ -26899,7 +26899,7 @@
         <v>3.58</v>
       </c>
       <c r="U163">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V163">
         <v>1.65</v>
@@ -26926,7 +26926,7 @@
         <v>2.25</v>
       </c>
       <c r="AD163">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE163">
         <v>1.2</v>
@@ -27406,10 +27406,10 @@
         <v>0</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC166">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>3.4</v>
+        <v>1.32</v>
       </c>
       <c r="O169">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="P169">
-        <v>1.85</v>
+        <v>6.7</v>
       </c>
       <c r="Q169">
-        <v>4.28</v>
+        <v>1.73</v>
       </c>
       <c r="R169">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="S169">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T169">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="U169">
-        <v>2.61</v>
+        <v>2.18</v>
       </c>
       <c r="V169">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="W169">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X169">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z169">
-        <v>3.84</v>
+        <v>4.7</v>
       </c>
       <c r="AA169">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AB169">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AC169">
-        <v>2.78</v>
+        <v>2.24</v>
       </c>
       <c r="AD169">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AE169">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF169">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AG169">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK169">
-        <v>1.2</v>
+        <v>3.25</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
+        <v>3.4</v>
+      </c>
+      <c r="O170">
+        <v>3.5</v>
+      </c>
+      <c r="P170">
+        <v>1.85</v>
+      </c>
+      <c r="Q170">
+        <v>4.28</v>
+      </c>
+      <c r="R170">
+        <v>2.19</v>
+      </c>
+      <c r="S170">
         <v>1.32</v>
       </c>
-      <c r="O170">
-        <v>4.7</v>
-      </c>
-      <c r="P170">
-        <v>6.7</v>
-      </c>
-      <c r="Q170">
-        <v>1.73</v>
-      </c>
-      <c r="R170">
-        <v>2.62</v>
-      </c>
-      <c r="S170">
-        <v>1.22</v>
-      </c>
       <c r="T170">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="U170">
-        <v>2.18</v>
+        <v>2.61</v>
       </c>
       <c r="V170">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="W170">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X170">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y170">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z170">
-        <v>4.7</v>
+        <v>3.84</v>
       </c>
       <c r="AA170">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="AB170">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AC170">
-        <v>2.24</v>
+        <v>2.78</v>
       </c>
       <c r="AD170">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AE170">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF170">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AG170">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK170">
-        <v>3.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,80 +28182,80 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="O171">
-        <v>3.18</v>
+        <v>3.74</v>
       </c>
       <c r="P171">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="Q171">
-        <v>3.18</v>
+        <v>2</v>
       </c>
       <c r="R171">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S171">
         <v>1.36</v>
       </c>
       <c r="T171">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="U171">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="V171">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W171">
         <v>1.06</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z171">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AA171">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB171">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AC171">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="AD171">
+        <v>1.27</v>
+      </c>
+      <c r="AE171">
+        <v>1.07</v>
+      </c>
+      <c r="AF171">
+        <v>1.9</v>
+      </c>
+      <c r="AG171">
+        <v>1.87</v>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ171">
         <v>1.22</v>
       </c>
-      <c r="AE171">
-        <v>1.05</v>
-      </c>
-      <c r="AF171">
-        <v>1.87</v>
-      </c>
-      <c r="AG171">
-        <v>1.9</v>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ171">
-        <v>1.25</v>
-      </c>
       <c r="AK171">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="O172">
-        <v>3.7</v>
+        <v>3.06</v>
       </c>
       <c r="P172">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="Q172">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="R172">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S172">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="T172">
-        <v>2.71</v>
+        <v>2.41</v>
       </c>
       <c r="U172">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="V172">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W172">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X172">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y172">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="Z172">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="AA172">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AB172">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC172">
-        <v>3.14</v>
+        <v>4.33</v>
       </c>
       <c r="AD172">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE172">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF172">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG172">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AK172">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O173">
         <v>3.3</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,80 +28671,80 @@
         </is>
       </c>
       <c r="N174">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O174">
-        <v>3.06</v>
+        <v>3.18</v>
       </c>
       <c r="P174">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="Q174">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="R174">
         <v>2.05</v>
       </c>
       <c r="S174">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="T174">
-        <v>2.41</v>
+        <v>2.73</v>
       </c>
       <c r="U174">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="V174">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W174">
+        <v>1.06</v>
+      </c>
+      <c r="X174">
         <v>1.02</v>
       </c>
-      <c r="X174">
-        <v>1.04</v>
-      </c>
       <c r="Y174">
+        <v>1.31</v>
+      </c>
+      <c r="Z174">
+        <v>2.92</v>
+      </c>
+      <c r="AA174">
+        <v>2.01</v>
+      </c>
+      <c r="AB174">
+        <v>1.69</v>
+      </c>
+      <c r="AC174">
+        <v>3.48</v>
+      </c>
+      <c r="AD174">
+        <v>1.22</v>
+      </c>
+      <c r="AE174">
+        <v>1.05</v>
+      </c>
+      <c r="AF174">
+        <v>1.87</v>
+      </c>
+      <c r="AG174">
+        <v>1.9</v>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ174">
+        <v>1.25</v>
+      </c>
+      <c r="AK174">
         <v>1.4</v>
-      </c>
-      <c r="Z174">
-        <v>2.84</v>
-      </c>
-      <c r="AA174">
-        <v>2.27</v>
-      </c>
-      <c r="AB174">
-        <v>1.61</v>
-      </c>
-      <c r="AC174">
-        <v>3.9</v>
-      </c>
-      <c r="AD174">
-        <v>1.18</v>
-      </c>
-      <c r="AE174">
-        <v>1.03</v>
-      </c>
-      <c r="AF174">
-        <v>1.91</v>
-      </c>
-      <c r="AG174">
-        <v>1.8</v>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ174">
-        <v>1.57</v>
-      </c>
-      <c r="AK174">
-        <v>1.3</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="O176">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="P176">
-        <v>6.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q176">
-        <v>1.75</v>
+        <v>3.12</v>
       </c>
       <c r="R176">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="S176">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>4.2</v>
+        <v>3.46</v>
       </c>
       <c r="U176">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="V176">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>6.12</v>
+        <v>4.2</v>
       </c>
       <c r="AA176">
+        <v>1.61</v>
+      </c>
+      <c r="AB176">
+        <v>2.21</v>
+      </c>
+      <c r="AC176">
+        <v>2.42</v>
+      </c>
+      <c r="AD176">
         <v>1.44</v>
       </c>
-      <c r="AB176">
-        <v>2.7</v>
-      </c>
-      <c r="AC176">
-        <v>2.06</v>
-      </c>
-      <c r="AD176">
-        <v>1.7</v>
-      </c>
       <c r="AE176">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF176">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AG176">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AK176">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="O177">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P177">
-        <v>2.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q177">
-        <v>2.78</v>
+        <v>4.11</v>
       </c>
       <c r="R177">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="S177">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T177">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="U177">
-        <v>2.98</v>
+        <v>2.32</v>
       </c>
       <c r="V177">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="W177">
         <v>1.1</v>
       </c>
       <c r="X177">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z177">
-        <v>3.34</v>
+        <v>4.25</v>
       </c>
       <c r="AA177">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AB177">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC177">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AD177">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE177">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG177">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>1.24</v>
       </c>
       <c r="AK177">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,80 +29323,80 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="O178">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P178">
-        <v>2.31</v>
+        <v>3.55</v>
       </c>
       <c r="Q178">
-        <v>3.12</v>
+        <v>2.36</v>
       </c>
       <c r="R178">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S178">
+        <v>1.34</v>
+      </c>
+      <c r="T178">
+        <v>2.92</v>
+      </c>
+      <c r="U178">
+        <v>2.77</v>
+      </c>
+      <c r="V178">
+        <v>1.41</v>
+      </c>
+      <c r="W178">
+        <v>1.07</v>
+      </c>
+      <c r="X178">
+        <v>1.02</v>
+      </c>
+      <c r="Y178">
+        <v>1.22</v>
+      </c>
+      <c r="Z178">
+        <v>3.5</v>
+      </c>
+      <c r="AA178">
+        <v>1.79</v>
+      </c>
+      <c r="AB178">
+        <v>1.92</v>
+      </c>
+      <c r="AC178">
+        <v>3</v>
+      </c>
+      <c r="AD178">
+        <v>1.33</v>
+      </c>
+      <c r="AE178">
+        <v>1.08</v>
+      </c>
+      <c r="AF178">
+        <v>1.71</v>
+      </c>
+      <c r="AG178">
+        <v>1.99</v>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ178">
         <v>1.25</v>
       </c>
-      <c r="T178">
-        <v>3.46</v>
-      </c>
-      <c r="U178">
-        <v>2.45</v>
-      </c>
-      <c r="V178">
-        <v>1.52</v>
-      </c>
-      <c r="W178">
-        <v>1.13</v>
-      </c>
-      <c r="X178">
-        <v>1.01</v>
-      </c>
-      <c r="Y178">
-        <v>1.15</v>
-      </c>
-      <c r="Z178">
-        <v>4.2</v>
-      </c>
-      <c r="AA178">
-        <v>1.61</v>
-      </c>
-      <c r="AB178">
-        <v>2.21</v>
-      </c>
-      <c r="AC178">
-        <v>2.42</v>
-      </c>
-      <c r="AD178">
-        <v>1.44</v>
-      </c>
-      <c r="AE178">
-        <v>1.15</v>
-      </c>
-      <c r="AF178">
-        <v>1.51</v>
-      </c>
-      <c r="AG178">
-        <v>2.35</v>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ178">
-        <v>1.44</v>
-      </c>
       <c r="AK178">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
+        <v>1.35</v>
+      </c>
+      <c r="O179">
+        <v>5.25</v>
+      </c>
+      <c r="P179">
+        <v>6.2</v>
+      </c>
+      <c r="Q179">
         <v>1.75</v>
       </c>
-      <c r="O179">
-        <v>3.55</v>
-      </c>
-      <c r="P179">
-        <v>4.4</v>
-      </c>
-      <c r="Q179">
-        <v>2.2</v>
-      </c>
       <c r="R179">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="S179">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="T179">
-        <v>3.08</v>
+        <v>4.2</v>
       </c>
       <c r="U179">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="V179">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="W179">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X179">
         <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z179">
-        <v>3.5</v>
+        <v>6.12</v>
       </c>
       <c r="AA179">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AB179">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AC179">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD179">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AE179">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AF179">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG179">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,65 +29649,65 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="O180">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P180">
-        <v>3.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q180">
+        <v>2.86</v>
+      </c>
+      <c r="R180">
+        <v>2.14</v>
+      </c>
+      <c r="S180">
+        <v>1.33</v>
+      </c>
+      <c r="T180">
+        <v>2.97</v>
+      </c>
+      <c r="U180">
+        <v>2.98</v>
+      </c>
+      <c r="V180">
+        <v>1.4</v>
+      </c>
+      <c r="W180">
+        <v>1.06</v>
+      </c>
+      <c r="X180">
+        <v>1.02</v>
+      </c>
+      <c r="Y180">
+        <v>1.27</v>
+      </c>
+      <c r="Z180">
+        <v>3.14</v>
+      </c>
+      <c r="AA180">
+        <v>1.94</v>
+      </c>
+      <c r="AB180">
+        <v>1.79</v>
+      </c>
+      <c r="AC180">
+        <v>3.34</v>
+      </c>
+      <c r="AD180">
+        <v>1.24</v>
+      </c>
+      <c r="AE180">
+        <v>1.05</v>
+      </c>
+      <c r="AF180">
+        <v>1.6</v>
+      </c>
+      <c r="AG180">
         <v>2.2</v>
       </c>
-      <c r="R180">
-        <v>2.3</v>
-      </c>
-      <c r="S180">
-        <v>1.29</v>
-      </c>
-      <c r="T180">
-        <v>3.3</v>
-      </c>
-      <c r="U180">
-        <v>2.42</v>
-      </c>
-      <c r="V180">
-        <v>1.48</v>
-      </c>
-      <c r="W180">
-        <v>1.08</v>
-      </c>
-      <c r="X180">
-        <v>1.04</v>
-      </c>
-      <c r="Y180">
-        <v>1.18</v>
-      </c>
-      <c r="Z180">
-        <v>3.82</v>
-      </c>
-      <c r="AA180">
-        <v>1.65</v>
-      </c>
-      <c r="AB180">
-        <v>2.1</v>
-      </c>
-      <c r="AC180">
-        <v>2.98</v>
-      </c>
-      <c r="AD180">
-        <v>1.34</v>
-      </c>
-      <c r="AE180">
-        <v>1.09</v>
-      </c>
-      <c r="AF180">
-        <v>1.57</v>
-      </c>
-      <c r="AG180">
-        <v>2.25</v>
-      </c>
       <c r="AH180" t="inlineStr">
         <is>
           <t>[]</t>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK180">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O181">
         <v>3.7</v>
       </c>
       <c r="P181">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q181">
-        <v>4.11</v>
+        <v>3.7</v>
       </c>
       <c r="R181">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S181">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T181">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U181">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="V181">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W181">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X181">
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z181">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="AA181">
         <v>1.68</v>
       </c>
       <c r="AB181">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC181">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD181">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE181">
         <v>1.15</v>
       </c>
       <c r="AF181">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG181">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK181">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>3.4</v>
+        <v>1.72</v>
       </c>
       <c r="O182">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P182">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="Q182">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="R182">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S182">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T182">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U182">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V182">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W182">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X182">
         <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z182">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="AA182">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB182">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC182">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD182">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE182">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF182">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG182">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK182">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,80 +30301,80 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="O184">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P184">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="Q184">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="R184">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S184">
+        <v>1.29</v>
+      </c>
+      <c r="T184">
+        <v>3.3</v>
+      </c>
+      <c r="U184">
+        <v>2.42</v>
+      </c>
+      <c r="V184">
+        <v>1.48</v>
+      </c>
+      <c r="W184">
+        <v>1.08</v>
+      </c>
+      <c r="X184">
+        <v>1.04</v>
+      </c>
+      <c r="Y184">
+        <v>1.18</v>
+      </c>
+      <c r="Z184">
+        <v>3.82</v>
+      </c>
+      <c r="AA184">
+        <v>1.65</v>
+      </c>
+      <c r="AB184">
+        <v>2.1</v>
+      </c>
+      <c r="AC184">
+        <v>2.98</v>
+      </c>
+      <c r="AD184">
         <v>1.34</v>
       </c>
-      <c r="T184">
-        <v>2.92</v>
-      </c>
-      <c r="U184">
-        <v>2.77</v>
-      </c>
-      <c r="V184">
-        <v>1.41</v>
-      </c>
-      <c r="W184">
-        <v>1.07</v>
-      </c>
-      <c r="X184">
-        <v>1.02</v>
-      </c>
-      <c r="Y184">
+      <c r="AE184">
+        <v>1.09</v>
+      </c>
+      <c r="AF184">
+        <v>1.57</v>
+      </c>
+      <c r="AG184">
+        <v>2.25</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ184">
         <v>1.22</v>
       </c>
-      <c r="Z184">
-        <v>3.5</v>
-      </c>
-      <c r="AA184">
-        <v>1.79</v>
-      </c>
-      <c r="AB184">
-        <v>1.92</v>
-      </c>
-      <c r="AC184">
-        <v>3</v>
-      </c>
-      <c r="AD184">
-        <v>1.33</v>
-      </c>
-      <c r="AE184">
-        <v>1.08</v>
-      </c>
-      <c r="AF184">
-        <v>1.71</v>
-      </c>
-      <c r="AG184">
-        <v>1.99</v>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ184">
-        <v>1.25</v>
-      </c>
       <c r="AK184">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O185">
         <v>3.5</v>
       </c>
       <c r="P185">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q185">
         <v>2.8</v>
@@ -30491,7 +30491,7 @@
         <v>1.61</v>
       </c>
       <c r="W185">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X185">
         <v>1.02</v>
@@ -30796,7 +30796,7 @@
         <v>3.34</v>
       </c>
       <c r="P187">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q187">
         <v>2.77</v>
@@ -30953,19 +30953,19 @@
         </is>
       </c>
       <c r="N188">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="O188">
         <v>3.65</v>
       </c>
       <c r="P188">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q188">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R188">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="S188">
         <v>1.11</v>
@@ -31007,10 +31007,10 @@
         <v>1.34</v>
       </c>
       <c r="AF188">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AG188">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>1.16</v>
       </c>
       <c r="AK188">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31442,25 +31442,25 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O191">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P191">
+        <v>2.7</v>
+      </c>
+      <c r="Q191">
+        <v>2.38</v>
+      </c>
+      <c r="R191">
         <v>2.75</v>
       </c>
-      <c r="Q191">
-        <v>2.3</v>
-      </c>
-      <c r="R191">
-        <v>2.8</v>
-      </c>
       <c r="S191">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T191">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="U191">
         <v>1.75</v>
@@ -31469,37 +31469,37 @@
         <v>2.03</v>
       </c>
       <c r="W191">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X191">
         <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z191">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="AA191">
+        <v>1.2</v>
+      </c>
+      <c r="AB191">
+        <v>3.7</v>
+      </c>
+      <c r="AC191">
+        <v>1.62</v>
+      </c>
+      <c r="AD191">
+        <v>2.28</v>
+      </c>
+      <c r="AE191">
+        <v>1.56</v>
+      </c>
+      <c r="AF191">
         <v>1.22</v>
       </c>
-      <c r="AB191">
-        <v>3.5</v>
-      </c>
-      <c r="AC191">
-        <v>1.67</v>
-      </c>
-      <c r="AD191">
-        <v>2.18</v>
-      </c>
-      <c r="AE191">
-        <v>1.51</v>
-      </c>
-      <c r="AF191">
-        <v>1.25</v>
-      </c>
       <c r="AG191">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK191">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -32100,7 +32100,7 @@
         <v>3.84</v>
       </c>
       <c r="P195">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>3.14</v>
       </c>
       <c r="AA197">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB197">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC197">
         <v>3.2</v>
@@ -32755,25 +32755,25 @@
         <v>3.5</v>
       </c>
       <c r="Q199">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="R199">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S199">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T199">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="U199">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V199">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W199">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X199">
         <v>1.01</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="O208">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P208">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q208">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="R208">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="S208">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T208">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="U208">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="V208">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W208">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z208">
-        <v>4.15</v>
+        <v>3.58</v>
       </c>
       <c r="AA208">
+        <v>1.81</v>
+      </c>
+      <c r="AB208">
+        <v>1.95</v>
+      </c>
+      <c r="AC208">
+        <v>2.92</v>
+      </c>
+      <c r="AD208">
+        <v>1.31</v>
+      </c>
+      <c r="AE208">
+        <v>1.13</v>
+      </c>
+      <c r="AF208">
         <v>1.67</v>
       </c>
-      <c r="AB208">
-        <v>2.21</v>
-      </c>
-      <c r="AC208">
-        <v>2.63</v>
-      </c>
-      <c r="AD208">
-        <v>1.47</v>
-      </c>
-      <c r="AE208">
-        <v>1.18</v>
-      </c>
-      <c r="AF208">
-        <v>1.5</v>
-      </c>
       <c r="AG208">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK208">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="O209">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P209">
-        <v>3.93</v>
+        <v>4.55</v>
       </c>
       <c r="Q209">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="R209">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="S209">
+        <v>1.3</v>
+      </c>
+      <c r="T209">
+        <v>3.12</v>
+      </c>
+      <c r="U209">
+        <v>2.42</v>
+      </c>
+      <c r="V209">
+        <v>1.48</v>
+      </c>
+      <c r="W209">
+        <v>1.11</v>
+      </c>
+      <c r="X209">
+        <v>1.01</v>
+      </c>
+      <c r="Y209">
+        <v>1.21</v>
+      </c>
+      <c r="Z209">
+        <v>4.27</v>
+      </c>
+      <c r="AA209">
+        <v>1.69</v>
+      </c>
+      <c r="AB209">
+        <v>2.18</v>
+      </c>
+      <c r="AC209">
+        <v>2.56</v>
+      </c>
+      <c r="AD209">
         <v>1.4</v>
       </c>
-      <c r="T209">
-        <v>2.6</v>
-      </c>
-      <c r="U209">
-        <v>3.02</v>
-      </c>
-      <c r="V209">
-        <v>1.32</v>
-      </c>
-      <c r="W209">
-        <v>1.05</v>
-      </c>
-      <c r="X209">
-        <v>1.05</v>
-      </c>
-      <c r="Y209">
-        <v>1.35</v>
-      </c>
-      <c r="Z209">
-        <v>2.74</v>
-      </c>
-      <c r="AA209">
-        <v>2.2</v>
-      </c>
-      <c r="AB209">
-        <v>1.6</v>
-      </c>
-      <c r="AC209">
-        <v>3.92</v>
-      </c>
-      <c r="AD209">
-        <v>1.18</v>
-      </c>
       <c r="AE209">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AF209">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AG209">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>1.22</v>
       </c>
       <c r="AK209">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O210">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P210">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="Q210">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="R210">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S210">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T210">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="U210">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V210">
         <v>1.51</v>
       </c>
       <c r="W210">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X210">
         <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z210">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="AA210">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB210">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC210">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AD210">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AE210">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF210">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AG210">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK210">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O211">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P211">
-        <v>3.4</v>
+        <v>3.93</v>
       </c>
       <c r="Q211">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="R211">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S211">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T211">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="U211">
-        <v>2.53</v>
+        <v>3.02</v>
       </c>
       <c r="V211">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W211">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X211">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y211">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z211">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="AA211">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AB211">
+        <v>1.6</v>
+      </c>
+      <c r="AC211">
+        <v>3.92</v>
+      </c>
+      <c r="AD211">
+        <v>1.18</v>
+      </c>
+      <c r="AE211">
+        <v>1.02</v>
+      </c>
+      <c r="AF211">
         <v>1.95</v>
       </c>
-      <c r="AC211">
-        <v>2.92</v>
-      </c>
-      <c r="AD211">
-        <v>1.31</v>
-      </c>
-      <c r="AE211">
-        <v>1.13</v>
-      </c>
-      <c r="AF211">
-        <v>1.67</v>
-      </c>
       <c r="AG211">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK211">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,65 +34865,65 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O212">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P212">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="Q212">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R212">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S212">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T212">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="U212">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="V212">
         <v>1.51</v>
       </c>
       <c r="W212">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z212">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="AA212">
+        <v>1.66</v>
+      </c>
+      <c r="AB212">
+        <v>2.1</v>
+      </c>
+      <c r="AC212">
+        <v>2.59</v>
+      </c>
+      <c r="AD212">
+        <v>1.39</v>
+      </c>
+      <c r="AE212">
+        <v>1.13</v>
+      </c>
+      <c r="AF212">
         <v>1.57</v>
       </c>
-      <c r="AB212">
+      <c r="AG212">
         <v>2.25</v>
       </c>
-      <c r="AC212">
-        <v>2.46</v>
-      </c>
-      <c r="AD212">
-        <v>1.49</v>
-      </c>
-      <c r="AE212">
-        <v>1.15</v>
-      </c>
-      <c r="AF212">
-        <v>1.51</v>
-      </c>
-      <c r="AG212">
-        <v>2.35</v>
-      </c>
       <c r="AH212" t="inlineStr">
         <is>
           <t>[]</t>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK212">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,19 +35028,19 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.68</v>
+        <v>2.41</v>
       </c>
       <c r="O213">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P213">
-        <v>4.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q213">
-        <v>2.19</v>
+        <v>3.18</v>
       </c>
       <c r="R213">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="S213">
         <v>1.3</v>
@@ -35049,43 +35049,43 @@
         <v>3.12</v>
       </c>
       <c r="U213">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="V213">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W213">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X213">
         <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z213">
-        <v>4.27</v>
+        <v>4.15</v>
       </c>
       <c r="AA213">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AB213">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC213">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AD213">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE213">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF213">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG213">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK213">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35194,10 +35194,10 @@
         <v>1.83</v>
       </c>
       <c r="O214">
+        <v>3.8</v>
+      </c>
+      <c r="P214">
         <v>3.72</v>
-      </c>
-      <c r="P214">
-        <v>3.23</v>
       </c>
       <c r="Q214">
         <v>2.35</v>
@@ -35680,7 +35680,7 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="O217">
         <v>3</v>
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="N219">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O219">
         <v>3.24</v>
@@ -36821,7 +36821,7 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O224">
         <v>3.4</v>
@@ -37147,7 +37147,7 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O226">
         <v>3.42</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="O227">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="P227">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Q227">
         <v>7</v>
@@ -38466,10 +38466,10 @@
         <v>2.62</v>
       </c>
       <c r="S234">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T234">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U234">
         <v>1.89</v>
@@ -38493,7 +38493,7 @@
         <v>1.29</v>
       </c>
       <c r="AB234">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="AC234">
         <v>1.79</v>
@@ -40108,7 +40108,7 @@
         <v>1.44</v>
       </c>
       <c r="W244">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X244">
         <v>1</v>
@@ -40120,7 +40120,7 @@
         <v>4.33</v>
       </c>
       <c r="AA244">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB244">
         <v>2.08</v>
@@ -40745,19 +40745,19 @@
         <v>2.69</v>
       </c>
       <c r="R248">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S248">
         <v>1.3</v>
       </c>
       <c r="T248">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U248">
         <v>2.58</v>
       </c>
       <c r="V248">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W248">
         <v>1.1</v>
@@ -41062,7 +41062,7 @@
         <v>1.98</v>
       </c>
       <c r="O250">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P250">
         <v>3.1</v>
@@ -41225,7 +41225,7 @@
         <v>2.55</v>
       </c>
       <c r="O251">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P251">
         <v>2.37</v>
@@ -41295,7 +41295,7 @@
         <v>1.24</v>
       </c>
       <c r="AK251">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41394,55 +41394,55 @@
         <v>4.5</v>
       </c>
       <c r="Q252">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R252">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S252">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T252">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U252">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V252">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W252">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X252">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z252">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA252">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB252">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC252">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD252">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE252">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF252">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG252">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK252">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41557,55 +41557,55 @@
         <v>2.65</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O258">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="P258">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="Q258">
         <v>1.59</v>
@@ -42529,7 +42529,7 @@
         <v>1.31</v>
       </c>
       <c r="O259">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="P259">
         <v>8.75</v>
@@ -43051,16 +43051,16 @@
         <v>1.25</v>
       </c>
       <c r="Z262">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA262">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB262">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC262">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD262">
         <v>1.33</v>
@@ -43344,10 +43344,10 @@
         <v>1.65</v>
       </c>
       <c r="O264">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P264">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q264">
         <v>2.19</v>
@@ -43513,43 +43513,43 @@
         <v>0</v>
       </c>
       <c r="Q265">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R265">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S265">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T265">
         <v>2.8</v>
       </c>
       <c r="U265">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="V265">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W265">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X265">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y265">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z265">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA265">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB265">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC265">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AD265">
         <v>1.22</v>
@@ -43558,10 +43558,10 @@
         <v>1.05</v>
       </c>
       <c r="AF265">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG265">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK265">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44032,10 +44032,10 @@
         <v>0</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC268">
         <v>0</v>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G270">
@@ -44850,7 +44850,7 @@
         <v>1.66</v>
       </c>
       <c r="AB273">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC273">
         <v>2.56</v>
@@ -44971,19 +44971,19 @@
         </is>
       </c>
       <c r="N274">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="O274">
-        <v>4.06</v>
+        <v>4.3</v>
       </c>
       <c r="P274">
         <v>1.59</v>
       </c>
       <c r="Q274">
-        <v>4.37</v>
+        <v>5.5</v>
       </c>
       <c r="R274">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S274">
         <v>1.25</v>
@@ -45134,25 +45134,25 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="O275">
         <v>3.6</v>
       </c>
       <c r="P275">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="Q275">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="R275">
         <v>2.23</v>
       </c>
       <c r="S275">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T275">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U275">
         <v>2.32</v>
@@ -45161,10 +45161,10 @@
         <v>1.52</v>
       </c>
       <c r="W275">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X275">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y275">
         <v>1.16</v>
@@ -45173,25 +45173,25 @@
         <v>4.15</v>
       </c>
       <c r="AA275">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB275">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AC275">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD275">
         <v>1.4</v>
       </c>
       <c r="AE275">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF275">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AG275">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>1.23</v>
       </c>
       <c r="AK275">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45303,13 +45303,13 @@
         <v>3.1</v>
       </c>
       <c r="P276">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q276">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="R276">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S276">
         <v>1.45</v>
@@ -45367,7 +45367,7 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK276">
         <v>1.44</v>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O277">
-        <v>3.93</v>
+        <v>3.6</v>
       </c>
       <c r="P277">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="Q277">
         <v>2.68</v>
@@ -45475,16 +45475,16 @@
         <v>2.31</v>
       </c>
       <c r="S277">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T277">
         <v>3.42</v>
       </c>
       <c r="U277">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V277">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W277">
         <v>1.13</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O278">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="P278">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="Q278">
         <v>2.51</v>
@@ -45638,10 +45638,10 @@
         <v>2.31</v>
       </c>
       <c r="S278">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T278">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="U278">
         <v>2.45</v>
@@ -45653,7 +45653,7 @@
         <v>1.08</v>
       </c>
       <c r="X278">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y278">
         <v>1.2</v>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK278">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="O279">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P279">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q279">
         <v>7.24</v>
@@ -45825,10 +45825,10 @@
         <v>3.58</v>
       </c>
       <c r="AA279">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB279">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC279">
         <v>2.94</v>
@@ -45840,7 +45840,7 @@
         <v>1.14</v>
       </c>
       <c r="AF279">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG279">
         <v>1.74</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O280">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P280">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="Q280">
         <v>2.58</v>
@@ -46115,16 +46115,16 @@
         <v>5.95</v>
       </c>
       <c r="O281">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="P281">
         <v>1.33</v>
       </c>
       <c r="Q281">
-        <v>5.74</v>
+        <v>5.58</v>
       </c>
       <c r="R281">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="S281">
         <v>1.13</v>
@@ -46163,7 +46163,7 @@
         <v>2.12</v>
       </c>
       <c r="AE281">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AF281">
         <v>1.39</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="O284">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="P284">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="Q284">
         <v>4.25</v>
@@ -46773,55 +46773,55 @@
         <v>0</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O286">
-        <v>8.35</v>
+        <v>7.5</v>
       </c>
       <c r="P286">
-        <v>11.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q286">
         <v>1.47</v>
@@ -46942,19 +46942,19 @@
         <v>3.33</v>
       </c>
       <c r="S286">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T286">
         <v>7</v>
       </c>
       <c r="U286">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V286">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="W286">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X286">
         <v>1</v>
@@ -46966,22 +46966,22 @@
         <v>15</v>
       </c>
       <c r="AA286">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB286">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AC286">
         <v>1.39</v>
       </c>
       <c r="AD286">
-        <v>3.06</v>
+        <v>2.68</v>
       </c>
       <c r="AE286">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AF286">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AG286">
         <v>2.8</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="O289">
-        <v>3.64</v>
+        <v>3.43</v>
       </c>
       <c r="P289">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q289">
         <v>3.79</v>
@@ -47489,7 +47489,7 @@
         <v>1.2</v>
       </c>
       <c r="AK289">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="O290">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P290">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="Q290">
         <v>2.1</v>
@@ -47784,7 +47784,7 @@
         <v>2.05</v>
       </c>
       <c r="AB291">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC291">
         <v>3.62</v>
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="N292">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="O292">
         <v>3.7</v>
@@ -48068,19 +48068,19 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O293">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P293">
         <v>3.25</v>
       </c>
       <c r="Q293">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R293">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S293">
         <v>1.36</v>
@@ -48089,43 +48089,43 @@
         <v>2.88</v>
       </c>
       <c r="U293">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="V293">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W293">
         <v>1.05</v>
       </c>
       <c r="X293">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y293">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z293">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA293">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB293">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC293">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD293">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE293">
         <v>1.05</v>
       </c>
       <c r="AF293">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG293">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>1.3</v>
       </c>
       <c r="AK293">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48270,10 +48270,10 @@
         <v>4.89</v>
       </c>
       <c r="AA294">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AB294">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AC294">
         <v>2.3</v>
@@ -48304,7 +48304,7 @@
         <v>1.36</v>
       </c>
       <c r="AK294">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48394,64 +48394,64 @@
         </is>
       </c>
       <c r="N295">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O295">
         <v>3.4</v>
       </c>
       <c r="P295">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="Q295">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="R295">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="S295">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T295">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="U295">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V295">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W295">
         <v>1.1</v>
       </c>
       <c r="X295">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y295">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z295">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AA295">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB295">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AC295">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="AD295">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE295">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF295">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG295">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK295">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48729,22 +48729,22 @@
         <v>3.36</v>
       </c>
       <c r="Q297">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R297">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S297">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T297">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U297">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V297">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W297">
         <v>1.08</v>
@@ -48756,19 +48756,19 @@
         <v>1.23</v>
       </c>
       <c r="Z297">
-        <v>3.89</v>
+        <v>4.5</v>
       </c>
       <c r="AA297">
         <v>1.76</v>
       </c>
       <c r="AB297">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC297">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD297">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE297">
         <v>1.14</v>
@@ -49046,64 +49046,64 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O299">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="P299">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q299">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R299">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S299">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T299">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U299">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V299">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W299">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X299">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y299">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z299">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC299">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD299">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE299">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF299">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG299">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK299">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="O300">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="P300">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q300">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R300">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S300">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T300">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U300">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V300">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W300">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X300">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y300">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z300">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC300">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD300">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE300">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF300">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG300">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK300">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O301">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P301">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q301">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R301">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S301">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T301">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U301">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V301">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W301">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X301">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y301">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Z301">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC301">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD301">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE301">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF301">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG301">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK301">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49535,37 +49535,37 @@
         </is>
       </c>
       <c r="N302">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="O302">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P302">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="Q302">
         <v>4.11</v>
       </c>
       <c r="R302">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="S302">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T302">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="U302">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="V302">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W302">
         <v>1.07</v>
       </c>
       <c r="X302">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y302">
         <v>1.25</v>
@@ -49577,19 +49577,19 @@
         <v>1.85</v>
       </c>
       <c r="AB302">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AC302">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD302">
         <v>1.3</v>
       </c>
       <c r="AE302">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF302">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG302">
         <v>2.05</v>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK302">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49864,10 +49864,10 @@
         <v>7.5</v>
       </c>
       <c r="O304">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="P304">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Q304">
         <v>6.45</v>
@@ -49906,7 +49906,7 @@
         <v>3.05</v>
       </c>
       <c r="AC304">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AD304">
         <v>1.98</v>
@@ -50024,22 +50024,22 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="O305">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P305">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q305">
-        <v>3.51</v>
+        <v>3.09</v>
       </c>
       <c r="R305">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S305">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T305">
         <v>3.2</v>
@@ -50051,7 +50051,7 @@
         <v>1.4</v>
       </c>
       <c r="W305">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X305">
         <v>1</v>
@@ -50063,7 +50063,7 @@
         <v>3.83</v>
       </c>
       <c r="AA305">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB305">
         <v>1.89</v>
@@ -50094,7 +50094,7 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK305">
         <v>1.4</v>
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="O306">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="P306">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50226,10 +50226,10 @@
         <v>2.25</v>
       </c>
       <c r="AA306">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB306">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC306">
         <v>0</v>
@@ -50359,55 +50359,55 @@
         <v>3</v>
       </c>
       <c r="Q307">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R307">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S307">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T307">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U307">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V307">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W307">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X307">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y307">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z307">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA307">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB307">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC307">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AD307">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF307">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG307">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK307">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O308">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P308">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="Q308">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="R308">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="S308">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T308">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="U308">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="V308">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W308">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X308">
         <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z308">
-        <v>5.61</v>
+        <v>5.25</v>
       </c>
       <c r="AA308">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB308">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AC308">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="AD308">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE308">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF308">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG308">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK308">
         <v>1.73</v>
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O310">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P310">
-        <v>4.75</v>
+        <v>4.84</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X310">
         <v>0</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O311">
-        <v>4.36</v>
+        <v>3.9</v>
       </c>
       <c r="P311">
-        <v>6.4</v>
+        <v>6.54</v>
       </c>
       <c r="Q311">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R311">
         <v>2.3</v>
       </c>
       <c r="S311">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T311">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="U311">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V311">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W311">
         <v>1.07</v>
       </c>
       <c r="X311">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y311">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z311">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="AA311">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AB311">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC311">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD311">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE311">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF311">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG311">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>1.22</v>
       </c>
       <c r="AK311">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>4.58</v>
+        <v>3.6</v>
       </c>
       <c r="O312">
-        <v>4.27</v>
+        <v>3.8</v>
       </c>
       <c r="P312">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="Q312">
         <v>4.45</v>
@@ -51328,19 +51328,19 @@
         </is>
       </c>
       <c r="N313">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="O313">
-        <v>4.58</v>
+        <v>3.65</v>
       </c>
       <c r="P313">
-        <v>5.91</v>
+        <v>4</v>
       </c>
       <c r="Q313">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="R313">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S313">
         <v>1.3</v>
@@ -51358,7 +51358,7 @@
         <v>1.08</v>
       </c>
       <c r="X313">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y313">
         <v>1.18</v>
@@ -51367,7 +51367,7 @@
         <v>4.2</v>
       </c>
       <c r="AA313">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB313">
         <v>2.1</v>
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK313">
         <v>2.05</v>
@@ -51657,16 +51657,16 @@
         <v>1.34</v>
       </c>
       <c r="O315">
-        <v>5.91</v>
+        <v>5.1</v>
       </c>
       <c r="P315">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="Q315">
         <v>1.82</v>
       </c>
       <c r="R315">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="S315">
         <v>1.28</v>
@@ -51696,10 +51696,10 @@
         <v>1.74</v>
       </c>
       <c r="AB315">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AC315">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AD315">
         <v>1.47</v>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK315">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>2.98</v>
+        <v>2.91</v>
       </c>
       <c r="O316">
         <v>3.74</v>
       </c>
       <c r="P316">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q316">
         <v>3.48</v>
@@ -51980,13 +51980,13 @@
         </is>
       </c>
       <c r="N317">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="O317">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="P317">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q317">
         <v>3.84</v>
@@ -52001,7 +52001,7 @@
         <v>3.25</v>
       </c>
       <c r="U317">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="V317">
         <v>1.53</v>
@@ -52028,7 +52028,7 @@
         <v>2.38</v>
       </c>
       <c r="AD317">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE317">
         <v>1.16</v>
@@ -52143,13 +52143,13 @@
         </is>
       </c>
       <c r="N318">
-        <v>3.79</v>
+        <v>3.2</v>
       </c>
       <c r="O318">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="P318">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q318">
         <v>4.3</v>
@@ -52170,28 +52170,28 @@
         <v>1.38</v>
       </c>
       <c r="W318">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X318">
         <v>1.03</v>
       </c>
       <c r="Y318">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z318">
         <v>3.28</v>
       </c>
       <c r="AA318">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB318">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC318">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="AD318">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE318">
         <v>1.11</v>
@@ -52306,13 +52306,13 @@
         </is>
       </c>
       <c r="N319">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O319">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="P319">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q319">
         <v>4</v>
@@ -52321,10 +52321,10 @@
         <v>2.09</v>
       </c>
       <c r="S319">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T319">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U319">
         <v>2.9</v>
@@ -52336,7 +52336,7 @@
         <v>1.06</v>
       </c>
       <c r="X319">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y319">
         <v>1.29</v>
@@ -52351,10 +52351,10 @@
         <v>1.8</v>
       </c>
       <c r="AC319">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AD319">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE319">
         <v>1.06</v>
@@ -52379,7 +52379,7 @@
         <v>1.34</v>
       </c>
       <c r="AK319">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52469,19 +52469,19 @@
         </is>
       </c>
       <c r="N320">
-        <v>7.55</v>
+        <v>6.5</v>
       </c>
       <c r="O320">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P320">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Q320">
-        <v>7.12</v>
+        <v>6.87</v>
       </c>
       <c r="R320">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="S320">
         <v>1.19</v>
@@ -52490,10 +52490,10 @@
         <v>3.8</v>
       </c>
       <c r="U320">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="V320">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W320">
         <v>1.14</v>
@@ -52502,25 +52502,25 @@
         <v>1.02</v>
       </c>
       <c r="Y320">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z320">
-        <v>5.62</v>
+        <v>5.12</v>
       </c>
       <c r="AA320">
         <v>1.53</v>
       </c>
       <c r="AB320">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AC320">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AD320">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AE320">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF320">
         <v>1.67</v>
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O321">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="P321">
-        <v>5.31</v>
+        <v>4.3</v>
       </c>
       <c r="Q321">
         <v>2</v>
@@ -52674,7 +52674,7 @@
         <v>1.44</v>
       </c>
       <c r="AB321">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC321">
         <v>2.15</v>
@@ -52795,25 +52795,25 @@
         </is>
       </c>
       <c r="N322">
-        <v>4.42</v>
+        <v>3.8</v>
       </c>
       <c r="O322">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P322">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q322">
         <v>3.73</v>
       </c>
       <c r="R322">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="S322">
         <v>1.17</v>
       </c>
       <c r="T322">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="U322">
         <v>1.76</v>
@@ -52831,13 +52831,13 @@
         <v>1.03</v>
       </c>
       <c r="Z322">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA322">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AB322">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AC322">
         <v>1.72</v>
@@ -52846,13 +52846,13 @@
         <v>2.03</v>
       </c>
       <c r="AE322">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF322">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AG322">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="O323">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P323">
-        <v>2.91</v>
+        <v>2.52</v>
       </c>
       <c r="Q323">
         <v>3.6</v>
@@ -53000,7 +53000,7 @@
         <v>2.5</v>
       </c>
       <c r="AB323">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC323">
         <v>4.8</v>
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O325">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="P325">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="Q325">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R325">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S325">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T325">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U325">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V325">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W325">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X325">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y325">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z325">
         <v>2.2</v>
       </c>
       <c r="AA325">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB325">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC325">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="AD325">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE325">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF325">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG325">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK325">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,64 +53447,64 @@
         </is>
       </c>
       <c r="N326">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="O326">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="P326">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="Q326">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R326">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S326">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T326">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U326">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V326">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W326">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X326">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y326">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z326">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA326">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB326">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC326">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD326">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE326">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF326">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG326">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK326">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="O327">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="P327">
-        <v>4.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q327">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R327">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S327">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T327">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U327">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V327">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W327">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X327">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y327">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="Z327">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AA327">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB327">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC327">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD327">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE327">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF327">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG327">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK327">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O328">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P328">
-        <v>3.97</v>
+        <v>3.6</v>
       </c>
       <c r="Q328">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R328">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S328">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T328">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U328">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V328">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W328">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X328">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y328">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z328">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AA328">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB328">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC328">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD328">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE328">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF328">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG328">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK328">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,80 +53936,80 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O329">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P329">
-        <v>7.7</v>
+        <v>7.25</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S329">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T329">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U329">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V329">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W329">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X329">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA329">
+        <v>2.4</v>
+      </c>
+      <c r="AB329">
+        <v>1.52</v>
+      </c>
+      <c r="AC329">
+        <v>4.7</v>
+      </c>
+      <c r="AD329">
+        <v>1.17</v>
+      </c>
+      <c r="AE329">
+        <v>1.01</v>
+      </c>
+      <c r="AF329">
+        <v>2.45</v>
+      </c>
+      <c r="AG329">
+        <v>1.48</v>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ329">
+        <v>1.22</v>
+      </c>
+      <c r="AK329">
         <v>2.3</v>
-      </c>
-      <c r="AB329">
-        <v>1.53</v>
-      </c>
-      <c r="AC329">
-        <v>0</v>
-      </c>
-      <c r="AD329">
-        <v>0</v>
-      </c>
-      <c r="AE329">
-        <v>0</v>
-      </c>
-      <c r="AF329">
-        <v>0</v>
-      </c>
-      <c r="AG329">
-        <v>0</v>
-      </c>
-      <c r="AH329" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI329" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ329">
-        <v>0</v>
-      </c>
-      <c r="AK329">
-        <v>0</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54105,7 +54105,7 @@
         <v>6</v>
       </c>
       <c r="P330">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="Q330">
         <v>0</v>
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G365">
@@ -59804,13 +59804,13 @@
         </is>
       </c>
       <c r="N365">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="O365">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="P365">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="Q365">
         <v>0</v>
@@ -59849,10 +59849,10 @@
         <v>0</v>
       </c>
       <c r="AC365">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD365">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AE365">
         <v>0</v>
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G366">
@@ -59967,13 +59967,13 @@
         </is>
       </c>
       <c r="N366">
-        <v>2.27</v>
+        <v>1.58</v>
       </c>
       <c r="O366">
-        <v>3.98</v>
+        <v>4.69</v>
       </c>
       <c r="P366">
-        <v>2.94</v>
+        <v>5.36</v>
       </c>
       <c r="Q366">
         <v>0</v>
@@ -60012,10 +60012,10 @@
         <v>0</v>
       </c>
       <c r="AC366">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD366">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE366">
         <v>0</v>
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G367">
@@ -60130,13 +60130,13 @@
         </is>
       </c>
       <c r="N367">
-        <v>1.58</v>
+        <v>3.25</v>
       </c>
       <c r="O367">
-        <v>4.69</v>
+        <v>3.8</v>
       </c>
       <c r="P367">
-        <v>5.36</v>
+        <v>1.98</v>
       </c>
       <c r="Q367">
         <v>0</v>
@@ -60175,10 +60175,10 @@
         <v>0</v>
       </c>
       <c r="AC367">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD367">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE367">
         <v>0</v>
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G368">
@@ -60293,13 +60293,13 @@
         </is>
       </c>
       <c r="N368">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O368">
-        <v>3.8</v>
+        <v>4.09</v>
       </c>
       <c r="P368">
-        <v>1.98</v>
+        <v>3.34</v>
       </c>
       <c r="Q368">
         <v>0</v>
@@ -60338,10 +60338,10 @@
         <v>0</v>
       </c>
       <c r="AC368">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD368">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AE368">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="P22">
-        <v>2.3</v>
+        <v>4.35</v>
       </c>
       <c r="Q22">
-        <v>3.52</v>
+        <v>2.41</v>
       </c>
       <c r="R22">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="S22">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>3.07</v>
+        <v>2.79</v>
       </c>
       <c r="U22">
-        <v>2.62</v>
+        <v>3.09</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
+        <v>1.36</v>
+      </c>
+      <c r="Z22">
+        <v>3.05</v>
+      </c>
+      <c r="AA22">
+        <v>2.08</v>
+      </c>
+      <c r="AB22">
+        <v>1.73</v>
+      </c>
+      <c r="AC22">
+        <v>3.68</v>
+      </c>
+      <c r="AD22">
         <v>1.26</v>
       </c>
-      <c r="Z22">
-        <v>3.68</v>
-      </c>
-      <c r="AA22">
-        <v>1.85</v>
-      </c>
-      <c r="AB22">
-        <v>1.93</v>
-      </c>
-      <c r="AC22">
-        <v>3.09</v>
-      </c>
-      <c r="AD22">
-        <v>1.35</v>
-      </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AG22">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK22">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>4.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q23">
-        <v>2.41</v>
+        <v>3.52</v>
       </c>
       <c r="R23">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="S23">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>2.79</v>
+        <v>3.07</v>
       </c>
       <c r="U23">
+        <v>2.62</v>
+      </c>
+      <c r="V23">
+        <v>1.39</v>
+      </c>
+      <c r="W23">
+        <v>1.1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1.26</v>
+      </c>
+      <c r="Z23">
+        <v>3.68</v>
+      </c>
+      <c r="AA23">
+        <v>1.85</v>
+      </c>
+      <c r="AB23">
+        <v>1.93</v>
+      </c>
+      <c r="AC23">
         <v>3.09</v>
       </c>
-      <c r="V23">
-        <v>1.34</v>
-      </c>
-      <c r="W23">
-        <v>1.06</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
+      <c r="AD23">
+        <v>1.35</v>
+      </c>
+      <c r="AE23">
+        <v>1.08</v>
+      </c>
+      <c r="AF23">
+        <v>1.65</v>
+      </c>
+      <c r="AG23">
+        <v>2.08</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.33</v>
+      </c>
+      <c r="AK23">
         <v>1.36</v>
-      </c>
-      <c r="Z23">
-        <v>3.05</v>
-      </c>
-      <c r="AA23">
-        <v>2.08</v>
-      </c>
-      <c r="AB23">
-        <v>1.73</v>
-      </c>
-      <c r="AC23">
-        <v>3.68</v>
-      </c>
-      <c r="AD23">
-        <v>1.26</v>
-      </c>
-      <c r="AE23">
-        <v>1.04</v>
-      </c>
-      <c r="AF23">
-        <v>1.87</v>
-      </c>
-      <c r="AG23">
-        <v>1.82</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.21</v>
-      </c>
-      <c r="AK23">
-        <v>1.91</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -6545,7 +6545,7 @@
         <v>1.7</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC38">
         <v>2.75</v>
@@ -6557,7 +6557,7 @@
         <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AG38">
         <v>2</v>
@@ -6838,55 +6838,55 @@
         <v>3.85</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P52">
-        <v>3.09</v>
+        <v>3.62</v>
       </c>
       <c r="Q52">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T52">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>3.98</v>
+        <v>7.25</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AB52">
-        <v>2.14</v>
+        <v>3.12</v>
       </c>
       <c r="AC52">
-        <v>2.52</v>
+        <v>1.94</v>
       </c>
       <c r="AD52">
-        <v>1.41</v>
+        <v>1.88</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AG52">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
+        <v>2.13</v>
+      </c>
+      <c r="O53">
+        <v>3.6</v>
+      </c>
+      <c r="P53">
+        <v>3</v>
+      </c>
+      <c r="Q53">
+        <v>2.6</v>
+      </c>
+      <c r="R53">
+        <v>2.32</v>
+      </c>
+      <c r="S53">
+        <v>1.21</v>
+      </c>
+      <c r="T53">
+        <v>3.65</v>
+      </c>
+      <c r="U53">
+        <v>2.16</v>
+      </c>
+      <c r="V53">
+        <v>1.6</v>
+      </c>
+      <c r="W53">
+        <v>1.13</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
+        <v>1.11</v>
+      </c>
+      <c r="Z53">
+        <v>4.95</v>
+      </c>
+      <c r="AA53">
+        <v>1.52</v>
+      </c>
+      <c r="AB53">
+        <v>2.35</v>
+      </c>
+      <c r="AC53">
+        <v>2.24</v>
+      </c>
+      <c r="AD53">
+        <v>1.57</v>
+      </c>
+      <c r="AE53">
+        <v>1.18</v>
+      </c>
+      <c r="AF53">
+        <v>1.44</v>
+      </c>
+      <c r="AG53">
+        <v>2.53</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.22</v>
+      </c>
+      <c r="AK53">
         <v>1.67</v>
-      </c>
-      <c r="O53">
-        <v>3.9</v>
-      </c>
-      <c r="P53">
-        <v>3.62</v>
-      </c>
-      <c r="Q53">
-        <v>2.05</v>
-      </c>
-      <c r="R53">
-        <v>2.81</v>
-      </c>
-      <c r="S53">
-        <v>1.17</v>
-      </c>
-      <c r="T53">
-        <v>3.54</v>
-      </c>
-      <c r="U53">
-        <v>1.99</v>
-      </c>
-      <c r="V53">
-        <v>1.84</v>
-      </c>
-      <c r="W53">
-        <v>1.17</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.1</v>
-      </c>
-      <c r="Z53">
-        <v>7.25</v>
-      </c>
-      <c r="AA53">
-        <v>1.37</v>
-      </c>
-      <c r="AB53">
-        <v>3.12</v>
-      </c>
-      <c r="AC53">
-        <v>1.94</v>
-      </c>
-      <c r="AD53">
-        <v>1.88</v>
-      </c>
-      <c r="AE53">
-        <v>1.33</v>
-      </c>
-      <c r="AF53">
-        <v>1.39</v>
-      </c>
-      <c r="AG53">
-        <v>2.88</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.23</v>
-      </c>
-      <c r="AK53">
-        <v>2.1</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="Q54">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R54">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="U54">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="V54">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W54">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>4.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA54">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AB54">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AC54">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="AD54">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG54">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK54">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10261,34 +10261,34 @@
         <v>1.95</v>
       </c>
       <c r="Q61">
-        <v>4.11</v>
+        <v>4.23</v>
       </c>
       <c r="R61">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T61">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="U61">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="V61">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W61">
         <v>1.07</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z61">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA61">
         <v>1.95</v>
@@ -10297,19 +10297,19 @@
         <v>1.85</v>
       </c>
       <c r="AC61">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD61">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE61">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF61">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG61">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10451,13 +10451,13 @@
         <v>1.36</v>
       </c>
       <c r="Z62">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="AA62">
         <v>2</v>
       </c>
       <c r="AB62">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC62">
         <v>3.7</v>
@@ -11556,34 +11556,34 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="O69">
         <v>3.4</v>
       </c>
       <c r="P69">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q69">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R69">
         <v>2.15</v>
       </c>
       <c r="S69">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T69">
         <v>3</v>
       </c>
       <c r="U69">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V69">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
         <v>1.03</v>
@@ -11598,22 +11598,22 @@
         <v>2</v>
       </c>
       <c r="AB69">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AC69">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AD69">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE69">
         <v>1.07</v>
       </c>
       <c r="AF69">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG69">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,34 +11719,34 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="O70">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="P70">
-        <v>5.46</v>
+        <v>4.91</v>
       </c>
       <c r="Q70">
+        <v>2</v>
+      </c>
+      <c r="R70">
+        <v>2.84</v>
+      </c>
+      <c r="S70">
+        <v>1.18</v>
+      </c>
+      <c r="T70">
+        <v>4.33</v>
+      </c>
+      <c r="U70">
         <v>1.9</v>
-      </c>
-      <c r="R70">
-        <v>2.63</v>
-      </c>
-      <c r="S70">
-        <v>1.15</v>
-      </c>
-      <c r="T70">
-        <v>4.3</v>
-      </c>
-      <c r="U70">
-        <v>1.96</v>
       </c>
       <c r="V70">
         <v>1.78</v>
       </c>
       <c r="W70">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
         <v>1.01</v>
@@ -11755,28 +11755,28 @@
         <v>1.04</v>
       </c>
       <c r="Z70">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="AA70">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB70">
-        <v>2.75</v>
+        <v>3.27</v>
       </c>
       <c r="AC70">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD70">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AE70">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG70">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK70">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11891,10 +11891,10 @@
         <v>4.4</v>
       </c>
       <c r="Q71">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R71">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S71">
         <v>1.33</v>
@@ -13216,7 +13216,7 @@
         <v>1.29</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y79">
         <v>1.02</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="O87">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P87">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="Q87">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R87">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T87">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U87">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V87">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z87">
-        <v>5.45</v>
+        <v>4.15</v>
       </c>
       <c r="AA87">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB87">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC87">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
       <c r="AD87">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AE87">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF87">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="AG87">
-        <v>2.73</v>
+        <v>2.36</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK87">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,25 +14653,25 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O88">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q88">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="R88">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S88">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U88">
         <v>2.25</v>
@@ -14683,34 +14683,34 @@
         <v>1.14</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>4.15</v>
+        <v>5.2</v>
       </c>
       <c r="AA88">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AC88">
-        <v>2.43</v>
+        <v>2.18</v>
       </c>
       <c r="AD88">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE88">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF88">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AG88">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="O89">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P89">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q89">
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="R89">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S89">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V89">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z89">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="AA89">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB89">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AC89">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AD89">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE89">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF89">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AG89">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.19</v>
       </c>
       <c r="AK89">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O92">
         <v>6</v>
       </c>
       <c r="P92">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Q92">
         <v>7.5</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O98">
         <v>3.8</v>
       </c>
       <c r="P98">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q98">
         <v>5.65</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O101">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P101">
         <v>2.9</v>
       </c>
       <c r="Q101">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="R101">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S101">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="T101">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="U101">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="V101">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W101">
+        <v>1.02</v>
+      </c>
+      <c r="X101">
         <v>1.01</v>
       </c>
-      <c r="X101">
-        <v>1.04</v>
-      </c>
       <c r="Y101">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z101">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="AA101">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AB101">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC101">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="AD101">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE101">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF101">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG101">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S102">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="U102">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="V102">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
+        <v>1.03</v>
+      </c>
+      <c r="X102">
         <v>1.02</v>
       </c>
-      <c r="X102">
-        <v>1.01</v>
-      </c>
       <c r="Y102">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z102">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AA102">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB102">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC102">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AD102">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE102">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG102">
+        <v>1.85</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.21</v>
+      </c>
+      <c r="AK102">
         <v>1.87</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.25</v>
-      </c>
-      <c r="AK102">
-        <v>1.52</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q103">
-        <v>2.35</v>
+        <v>3.06</v>
       </c>
       <c r="R103">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="S103">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T103">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="U103">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="V103">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W103">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z103">
-        <v>3.14</v>
+        <v>2.62</v>
       </c>
       <c r="AA103">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="AB103">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="AC103">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="AD103">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE103">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF103">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG103">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK103">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>2.8</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,31 +18076,31 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.84</v>
+        <v>2.53</v>
       </c>
       <c r="O109">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="P109">
-        <v>4.08</v>
+        <v>2.58</v>
       </c>
       <c r="Q109">
-        <v>2.67</v>
+        <v>3.27</v>
       </c>
       <c r="R109">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S109">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T109">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="U109">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="V109">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W109">
         <v>1.02</v>
@@ -18109,31 +18109,31 @@
         <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z109">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="AA109">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="AB109">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AC109">
-        <v>4.27</v>
+        <v>3.89</v>
       </c>
       <c r="AD109">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE109">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF109">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AG109">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK109">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="O110">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="P110">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q110">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="R110">
         <v>2.1</v>
       </c>
       <c r="S110">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T110">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="U110">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V110">
         <v>1.33</v>
       </c>
       <c r="W110">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X110">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z110">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="AA110">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AB110">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC110">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="AD110">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE110">
         <v>1.02</v>
       </c>
       <c r="AF110">
+        <v>1.82</v>
+      </c>
+      <c r="AG110">
         <v>1.84</v>
-      </c>
-      <c r="AG110">
-        <v>1.85</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.28</v>
       </c>
       <c r="AK110">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.58</v>
+        <v>3.73</v>
       </c>
       <c r="O111">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="P111">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q111">
-        <v>3.39</v>
+        <v>4.59</v>
       </c>
       <c r="R111">
+        <v>2.15</v>
+      </c>
+      <c r="S111">
+        <v>1.42</v>
+      </c>
+      <c r="T111">
+        <v>2.76</v>
+      </c>
+      <c r="U111">
+        <v>3.12</v>
+      </c>
+      <c r="V111">
+        <v>1.34</v>
+      </c>
+      <c r="W111">
+        <v>1.02</v>
+      </c>
+      <c r="X111">
+        <v>1.02</v>
+      </c>
+      <c r="Y111">
+        <v>1.34</v>
+      </c>
+      <c r="Z111">
+        <v>3.12</v>
+      </c>
+      <c r="AA111">
         <v>2.1</v>
       </c>
-      <c r="S111">
-        <v>1.43</v>
-      </c>
-      <c r="T111">
-        <v>2.71</v>
-      </c>
-      <c r="U111">
-        <v>3.2</v>
-      </c>
-      <c r="V111">
-        <v>1.33</v>
-      </c>
-      <c r="W111">
+      <c r="AB111">
+        <v>1.71</v>
+      </c>
+      <c r="AC111">
+        <v>3.7</v>
+      </c>
+      <c r="AD111">
+        <v>1.25</v>
+      </c>
+      <c r="AE111">
         <v>1.03</v>
       </c>
-      <c r="X111">
-        <v>1.01</v>
-      </c>
-      <c r="Y111">
-        <v>1.35</v>
-      </c>
-      <c r="Z111">
-        <v>3.03</v>
-      </c>
-      <c r="AA111">
-        <v>2.18</v>
-      </c>
-      <c r="AB111">
-        <v>1.6</v>
-      </c>
-      <c r="AC111">
-        <v>3.86</v>
-      </c>
-      <c r="AD111">
-        <v>1.24</v>
-      </c>
-      <c r="AE111">
-        <v>1.02</v>
-      </c>
       <c r="AF111">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AG111">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK111">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,65 +18565,65 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.73</v>
+        <v>3.42</v>
       </c>
       <c r="O112">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="P112">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q112">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="R112">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S112">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>2.76</v>
+        <v>3.12</v>
       </c>
       <c r="U112">
-        <v>3.12</v>
+        <v>2.61</v>
       </c>
       <c r="V112">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z112">
-        <v>3.12</v>
+        <v>3.97</v>
       </c>
       <c r="AA112">
+        <v>1.73</v>
+      </c>
+      <c r="AB112">
+        <v>1.95</v>
+      </c>
+      <c r="AC112">
+        <v>2.85</v>
+      </c>
+      <c r="AD112">
+        <v>1.39</v>
+      </c>
+      <c r="AE112">
+        <v>1.14</v>
+      </c>
+      <c r="AF112">
+        <v>1.62</v>
+      </c>
+      <c r="AG112">
         <v>2.1</v>
       </c>
-      <c r="AB112">
-        <v>1.71</v>
-      </c>
-      <c r="AC112">
-        <v>3.7</v>
-      </c>
-      <c r="AD112">
-        <v>1.25</v>
-      </c>
-      <c r="AE112">
-        <v>1.03</v>
-      </c>
-      <c r="AF112">
-        <v>1.89</v>
-      </c>
-      <c r="AG112">
-        <v>1.8</v>
-      </c>
       <c r="AH112" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK112">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
+        <v>3.23</v>
+      </c>
+      <c r="O113">
+        <v>3.14</v>
+      </c>
+      <c r="P113">
+        <v>2.09</v>
+      </c>
+      <c r="Q113">
+        <v>4.11</v>
+      </c>
+      <c r="R113">
+        <v>2</v>
+      </c>
+      <c r="S113">
+        <v>1.38</v>
+      </c>
+      <c r="T113">
+        <v>2.69</v>
+      </c>
+      <c r="U113">
+        <v>2.77</v>
+      </c>
+      <c r="V113">
+        <v>1.38</v>
+      </c>
+      <c r="W113">
+        <v>1.05</v>
+      </c>
+      <c r="X113">
+        <v>1.01</v>
+      </c>
+      <c r="Y113">
+        <v>1.29</v>
+      </c>
+      <c r="Z113">
+        <v>3.04</v>
+      </c>
+      <c r="AA113">
+        <v>1.99</v>
+      </c>
+      <c r="AB113">
+        <v>1.7</v>
+      </c>
+      <c r="AC113">
         <v>3.42</v>
       </c>
-      <c r="O113">
-        <v>3.42</v>
-      </c>
-      <c r="P113">
-        <v>1.92</v>
-      </c>
-      <c r="Q113">
-        <v>4.1</v>
-      </c>
-      <c r="R113">
-        <v>2.32</v>
-      </c>
-      <c r="S113">
-        <v>1.28</v>
-      </c>
-      <c r="T113">
-        <v>3.12</v>
-      </c>
-      <c r="U113">
-        <v>2.61</v>
-      </c>
-      <c r="V113">
-        <v>1.44</v>
-      </c>
-      <c r="W113">
-        <v>1.08</v>
-      </c>
-      <c r="X113">
-        <v>1.03</v>
-      </c>
-      <c r="Y113">
-        <v>1.22</v>
-      </c>
-      <c r="Z113">
-        <v>3.97</v>
-      </c>
-      <c r="AA113">
-        <v>1.73</v>
-      </c>
-      <c r="AB113">
-        <v>1.95</v>
-      </c>
-      <c r="AC113">
-        <v>2.85</v>
-      </c>
       <c r="AD113">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AE113">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AG113">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK113">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.13</v>
+        <v>1.84</v>
       </c>
       <c r="O114">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P114">
-        <v>2.15</v>
+        <v>4.08</v>
       </c>
       <c r="Q114">
-        <v>3.99</v>
+        <v>2.67</v>
       </c>
       <c r="R114">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="S114">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="T114">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="U114">
-        <v>2.81</v>
+        <v>3.12</v>
       </c>
       <c r="V114">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="Z114">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="AA114">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="AB114">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC114">
-        <v>3.58</v>
+        <v>4.27</v>
       </c>
       <c r="AD114">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE114">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF114">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="AG114">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.26</v>
       </c>
       <c r="AK114">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="O116">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P116">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q116">
-        <v>4.11</v>
+        <v>3.99</v>
       </c>
       <c r="R116">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S116">
         <v>1.38</v>
       </c>
       <c r="T116">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U116">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V116">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W116">
         <v>1.05</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z116">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA116">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB116">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC116">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD116">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE116">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF116">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG116">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.26</v>
       </c>
       <c r="AK116">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19733,19 +19733,19 @@
         <v>1.4</v>
       </c>
       <c r="W119">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X119">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
         <v>1.27</v>
       </c>
       <c r="Z119">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AA119">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB119">
         <v>1.98</v>
@@ -19754,16 +19754,16 @@
         <v>3.19</v>
       </c>
       <c r="AD119">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE119">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
         <v>1.7</v>
       </c>
       <c r="AG119">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>2.75</v>
       </c>
       <c r="U120">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="V120">
         <v>1.35</v>
@@ -19899,7 +19899,7 @@
         <v>1.05</v>
       </c>
       <c r="X120">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
         <v>1.36</v>
@@ -19908,16 +19908,16 @@
         <v>2.9</v>
       </c>
       <c r="AA120">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB120">
         <v>1.65</v>
       </c>
       <c r="AC120">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD120">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE120">
         <v>1.04</v>
@@ -19942,7 +19942,7 @@
         <v>1.29</v>
       </c>
       <c r="AK120">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -23132,7 +23132,7 @@
         <v>4.86</v>
       </c>
       <c r="O140">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P140">
         <v>1.67</v>
@@ -23295,10 +23295,10 @@
         <v>1.4</v>
       </c>
       <c r="O141">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P141">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q141">
         <v>1.8</v>
@@ -23331,10 +23331,10 @@
         <v>5.35</v>
       </c>
       <c r="AA141">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB141">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC141">
         <v>2.15</v>
@@ -23464,7 +23464,7 @@
         <v>1.94</v>
       </c>
       <c r="Q142">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="R142">
         <v>2.39</v>
@@ -23503,7 +23503,7 @@
         <v>2.46</v>
       </c>
       <c r="AD142">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE142">
         <v>1.19</v>
@@ -25257,55 +25257,55 @@
         <v>2.75</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA153">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB153">
         <v>1.61</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25420,55 +25420,55 @@
         <v>3.55</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA154">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB154">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -26063,10 +26063,10 @@
         </is>
       </c>
       <c r="N158">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O158">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="P158">
         <v>1.65</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="O159">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P159">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="Q159">
-        <v>4.1</v>
+        <v>3.04</v>
       </c>
       <c r="R159">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="S159">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T159">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="U159">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="V159">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="W159">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X159">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="Z159">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA159">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AB159">
-        <v>2.93</v>
+        <v>2.19</v>
       </c>
       <c r="AC159">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AD159">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="AE159">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AF159">
+        <v>1.47</v>
+      </c>
+      <c r="AG159">
+        <v>2.39</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
+        <v>1.23</v>
+      </c>
+      <c r="AK159">
         <v>1.35</v>
-      </c>
-      <c r="AG159">
-        <v>2.93</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>2</v>
-      </c>
-      <c r="AK159">
-        <v>1.27</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.87</v>
+        <v>3.18</v>
       </c>
       <c r="O160">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P160">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q160">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="R160">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="S160">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T160">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="U160">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="V160">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="W160">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X160">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y160">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z160">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA160">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AB160">
-        <v>2.19</v>
+        <v>2.93</v>
       </c>
       <c r="AC160">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AD160">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="AE160">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AF160">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AG160">
-        <v>2.39</v>
+        <v>2.93</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AK160">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26555,7 +26555,7 @@
         <v>1.73</v>
       </c>
       <c r="O161">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P161">
         <v>4.5</v>
@@ -26884,10 +26884,10 @@
         <v>3.7</v>
       </c>
       <c r="P163">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="Q163">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="R163">
         <v>2.3</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27406,10 +27406,10 @@
         <v>0</v>
       </c>
       <c r="AA166">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB166">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC166">
         <v>0</v>
@@ -27750,7 +27750,7 @@
         <v>1.58</v>
       </c>
       <c r="AG168">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>1.14</v>
       </c>
       <c r="X169">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y169">
         <v>1.12</v>
@@ -28224,7 +28224,7 @@
         <v>1.95</v>
       </c>
       <c r="AB171">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC171">
         <v>3.14</v>
@@ -28375,7 +28375,7 @@
         <v>1.02</v>
       </c>
       <c r="X172">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y172">
         <v>1.4</v>
@@ -28390,13 +28390,13 @@
         <v>1.61</v>
       </c>
       <c r="AC172">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AD172">
         <v>1.18</v>
       </c>
       <c r="AE172">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF172">
         <v>1.91</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,80 +28997,80 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="O176">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P176">
-        <v>2.31</v>
+        <v>3.55</v>
       </c>
       <c r="Q176">
-        <v>3.12</v>
+        <v>2.36</v>
       </c>
       <c r="R176">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S176">
+        <v>1.34</v>
+      </c>
+      <c r="T176">
+        <v>2.92</v>
+      </c>
+      <c r="U176">
+        <v>2.77</v>
+      </c>
+      <c r="V176">
+        <v>1.41</v>
+      </c>
+      <c r="W176">
+        <v>1.07</v>
+      </c>
+      <c r="X176">
+        <v>1.02</v>
+      </c>
+      <c r="Y176">
+        <v>1.22</v>
+      </c>
+      <c r="Z176">
+        <v>3.5</v>
+      </c>
+      <c r="AA176">
+        <v>1.79</v>
+      </c>
+      <c r="AB176">
+        <v>1.92</v>
+      </c>
+      <c r="AC176">
+        <v>3</v>
+      </c>
+      <c r="AD176">
+        <v>1.33</v>
+      </c>
+      <c r="AE176">
+        <v>1.08</v>
+      </c>
+      <c r="AF176">
+        <v>1.71</v>
+      </c>
+      <c r="AG176">
+        <v>1.99</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ176">
         <v>1.25</v>
       </c>
-      <c r="T176">
-        <v>3.46</v>
-      </c>
-      <c r="U176">
-        <v>2.45</v>
-      </c>
-      <c r="V176">
-        <v>1.52</v>
-      </c>
-      <c r="W176">
-        <v>1.13</v>
-      </c>
-      <c r="X176">
-        <v>1.01</v>
-      </c>
-      <c r="Y176">
-        <v>1.15</v>
-      </c>
-      <c r="Z176">
-        <v>4.2</v>
-      </c>
-      <c r="AA176">
-        <v>1.61</v>
-      </c>
-      <c r="AB176">
-        <v>2.21</v>
-      </c>
-      <c r="AC176">
-        <v>2.42</v>
-      </c>
-      <c r="AD176">
-        <v>1.44</v>
-      </c>
-      <c r="AE176">
-        <v>1.15</v>
-      </c>
-      <c r="AF176">
-        <v>1.51</v>
-      </c>
-      <c r="AG176">
-        <v>2.35</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ176">
-        <v>1.44</v>
-      </c>
       <c r="AK176">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>3.5</v>
+        <v>1.72</v>
       </c>
       <c r="O177">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P177">
-        <v>1.89</v>
+        <v>4.4</v>
       </c>
       <c r="Q177">
-        <v>4.11</v>
+        <v>2.2</v>
       </c>
       <c r="R177">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="S177">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="T177">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="U177">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="V177">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W177">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
         <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z177">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA177">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB177">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AC177">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="AD177">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE177">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF177">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG177">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK177">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="O178">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P178">
-        <v>3.55</v>
+        <v>2.31</v>
       </c>
       <c r="Q178">
-        <v>2.36</v>
+        <v>3.12</v>
       </c>
       <c r="R178">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S178">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T178">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
       <c r="U178">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="V178">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W178">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X178">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z178">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA178">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AB178">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="AC178">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="AD178">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE178">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF178">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AG178">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK178">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,80 +29486,80 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.35</v>
+        <v>3.5</v>
       </c>
       <c r="O179">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="P179">
-        <v>6.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q179">
-        <v>1.75</v>
+        <v>4.11</v>
       </c>
       <c r="R179">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="S179">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T179">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="U179">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="V179">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="W179">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X179">
         <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z179">
-        <v>6.12</v>
+        <v>4.25</v>
       </c>
       <c r="AA179">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AB179">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="AC179">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="AD179">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AE179">
+        <v>1.15</v>
+      </c>
+      <c r="AF179">
+        <v>1.61</v>
+      </c>
+      <c r="AG179">
+        <v>2.15</v>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ179">
+        <v>1.24</v>
+      </c>
+      <c r="AK179">
         <v>1.25</v>
-      </c>
-      <c r="AF179">
-        <v>1.6</v>
-      </c>
-      <c r="AG179">
-        <v>2.14</v>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ179">
-        <v>1.13</v>
-      </c>
-      <c r="AK179">
-        <v>3</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="O180">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P180">
-        <v>2.87</v>
+        <v>2.45</v>
       </c>
       <c r="Q180">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="R180">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S180">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T180">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="U180">
-        <v>2.98</v>
+        <v>2.48</v>
       </c>
       <c r="V180">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W180">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X180">
         <v>1.02</v>
       </c>
       <c r="Y180">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z180">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AA180">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB180">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AC180">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AD180">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AE180">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF180">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG180">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK180">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>3.4</v>
+        <v>1.35</v>
       </c>
       <c r="O181">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="P181">
-        <v>2.05</v>
+        <v>6.2</v>
       </c>
       <c r="Q181">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="R181">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S181">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T181">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="U181">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="V181">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W181">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X181">
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z181">
-        <v>3.94</v>
+        <v>6.12</v>
       </c>
       <c r="AA181">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AB181">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AC181">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AD181">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AE181">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF181">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG181">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK181">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,65 +29975,65 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="O182">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P182">
-        <v>4.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q182">
+        <v>2.86</v>
+      </c>
+      <c r="R182">
+        <v>2.14</v>
+      </c>
+      <c r="S182">
+        <v>1.33</v>
+      </c>
+      <c r="T182">
+        <v>2.97</v>
+      </c>
+      <c r="U182">
+        <v>2.98</v>
+      </c>
+      <c r="V182">
+        <v>1.4</v>
+      </c>
+      <c r="W182">
+        <v>1.06</v>
+      </c>
+      <c r="X182">
+        <v>1.02</v>
+      </c>
+      <c r="Y182">
+        <v>1.27</v>
+      </c>
+      <c r="Z182">
+        <v>3.14</v>
+      </c>
+      <c r="AA182">
+        <v>1.94</v>
+      </c>
+      <c r="AB182">
+        <v>1.79</v>
+      </c>
+      <c r="AC182">
+        <v>3.34</v>
+      </c>
+      <c r="AD182">
+        <v>1.24</v>
+      </c>
+      <c r="AE182">
+        <v>1.05</v>
+      </c>
+      <c r="AF182">
+        <v>1.6</v>
+      </c>
+      <c r="AG182">
         <v>2.2</v>
       </c>
-      <c r="R182">
-        <v>2.25</v>
-      </c>
-      <c r="S182">
-        <v>1.31</v>
-      </c>
-      <c r="T182">
-        <v>3.08</v>
-      </c>
-      <c r="U182">
-        <v>2.6</v>
-      </c>
-      <c r="V182">
-        <v>1.44</v>
-      </c>
-      <c r="W182">
-        <v>1.07</v>
-      </c>
-      <c r="X182">
-        <v>1.01</v>
-      </c>
-      <c r="Y182">
-        <v>1.22</v>
-      </c>
-      <c r="Z182">
-        <v>3.5</v>
-      </c>
-      <c r="AA182">
-        <v>1.75</v>
-      </c>
-      <c r="AB182">
-        <v>1.9</v>
-      </c>
-      <c r="AC182">
-        <v>3.05</v>
-      </c>
-      <c r="AD182">
-        <v>1.35</v>
-      </c>
-      <c r="AE182">
-        <v>1.07</v>
-      </c>
-      <c r="AF182">
-        <v>1.75</v>
-      </c>
-      <c r="AG182">
-        <v>1.95</v>
-      </c>
       <c r="AH182" t="inlineStr">
         <is>
           <t>[]</t>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK182">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.61</v>
+        <v>3.4</v>
       </c>
       <c r="O183">
+        <v>3.7</v>
+      </c>
+      <c r="P183">
+        <v>2.05</v>
+      </c>
+      <c r="Q183">
+        <v>3.7</v>
+      </c>
+      <c r="R183">
+        <v>2.3</v>
+      </c>
+      <c r="S183">
+        <v>1.29</v>
+      </c>
+      <c r="T183">
         <v>3.3</v>
       </c>
-      <c r="P183">
-        <v>2.45</v>
-      </c>
-      <c r="Q183">
-        <v>3.2</v>
-      </c>
-      <c r="R183">
-        <v>2.1</v>
-      </c>
-      <c r="S183">
-        <v>1.31</v>
-      </c>
-      <c r="T183">
-        <v>3.08</v>
-      </c>
       <c r="U183">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V183">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W183">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X183">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y183">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z183">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AA183">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AB183">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC183">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AD183">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AE183">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF183">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG183">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>1.25</v>
       </c>
       <c r="AK183">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="O189">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="P189">
-        <v>2.36</v>
+        <v>1.62</v>
       </c>
       <c r="Q189">
-        <v>2.93</v>
+        <v>3.8</v>
       </c>
       <c r="R189">
-        <v>2.37</v>
+        <v>3.11</v>
       </c>
       <c r="S189">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="T189">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="U189">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="V189">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="W189">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="X189">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y189">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z189">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AA189">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AB189">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="AC189">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AD189">
-        <v>1.71</v>
+        <v>2.56</v>
       </c>
       <c r="AE189">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AF189">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AG189">
-        <v>2.84</v>
+        <v>3.84</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK189">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="O190">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="P190">
-        <v>1.62</v>
+        <v>2.36</v>
       </c>
       <c r="Q190">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="R190">
-        <v>3.11</v>
+        <v>2.37</v>
       </c>
       <c r="S190">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="T190">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="U190">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="V190">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="W190">
+        <v>1.15</v>
+      </c>
+      <c r="X190">
+        <v>1.02</v>
+      </c>
+      <c r="Y190">
+        <v>1.08</v>
+      </c>
+      <c r="Z190">
+        <v>5.7</v>
+      </c>
+      <c r="AA190">
+        <v>1.42</v>
+      </c>
+      <c r="AB190">
+        <v>2.62</v>
+      </c>
+      <c r="AC190">
+        <v>2.05</v>
+      </c>
+      <c r="AD190">
+        <v>1.71</v>
+      </c>
+      <c r="AE190">
+        <v>1.33</v>
+      </c>
+      <c r="AF190">
         <v>1.36</v>
       </c>
-      <c r="X190">
-        <v>0</v>
-      </c>
-      <c r="Y190">
-        <v>1.04</v>
-      </c>
-      <c r="Z190">
-        <v>11</v>
-      </c>
-      <c r="AA190">
-        <v>1.12</v>
-      </c>
-      <c r="AB190">
-        <v>4.8</v>
-      </c>
-      <c r="AC190">
-        <v>1.4</v>
-      </c>
-      <c r="AD190">
-        <v>2.56</v>
-      </c>
-      <c r="AE190">
-        <v>1.75</v>
-      </c>
-      <c r="AF190">
-        <v>1.21</v>
-      </c>
       <c r="AG190">
-        <v>3.84</v>
+        <v>2.84</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK190">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>3.36</v>
+        <v>2.65</v>
       </c>
       <c r="O193">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P193">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,80 +32257,80 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="O196">
-        <v>3.48</v>
+        <v>3.32</v>
       </c>
       <c r="P196">
+        <v>2.62</v>
+      </c>
+      <c r="Q196">
         <v>3.18</v>
       </c>
-      <c r="Q196">
-        <v>2.7</v>
-      </c>
       <c r="R196">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="S196">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T196">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="U196">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="V196">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W196">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X196">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z196">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA196">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB196">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AC196">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AD196">
+        <v>1.29</v>
+      </c>
+      <c r="AE196">
+        <v>1.06</v>
+      </c>
+      <c r="AF196">
+        <v>1.74</v>
+      </c>
+      <c r="AG196">
+        <v>1.98</v>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ196">
         <v>1.3</v>
       </c>
-      <c r="AE196">
-        <v>1.07</v>
-      </c>
-      <c r="AF196">
-        <v>1.66</v>
-      </c>
-      <c r="AG196">
-        <v>2.09</v>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ196">
-        <v>1.28</v>
-      </c>
       <c r="AK196">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="O197">
+        <v>4.05</v>
+      </c>
+      <c r="P197">
+        <v>4.4</v>
+      </c>
+      <c r="Q197">
+        <v>2.2</v>
+      </c>
+      <c r="R197">
+        <v>2.35</v>
+      </c>
+      <c r="S197">
+        <v>1.27</v>
+      </c>
+      <c r="T197">
         <v>3.32</v>
       </c>
-      <c r="P197">
-        <v>2.62</v>
-      </c>
-      <c r="Q197">
-        <v>3.18</v>
-      </c>
-      <c r="R197">
-        <v>2.07</v>
-      </c>
-      <c r="S197">
-        <v>1.36</v>
-      </c>
-      <c r="T197">
-        <v>2.83</v>
-      </c>
       <c r="U197">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="V197">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W197">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X197">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z197">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="AA197">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="AB197">
-        <v>1.76</v>
+        <v>2.27</v>
       </c>
       <c r="AC197">
-        <v>3.2</v>
+        <v>2.41</v>
       </c>
       <c r="AD197">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AE197">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF197">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="AG197">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK197">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="O198">
-        <v>4.05</v>
+        <v>3.48</v>
       </c>
       <c r="P198">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="Q198">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="R198">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="S198">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="T198">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="U198">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="V198">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W198">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X198">
         <v>1.01</v>
       </c>
       <c r="Y198">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z198">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA198">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AB198">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="AC198">
-        <v>2.41</v>
+        <v>2.97</v>
       </c>
       <c r="AD198">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE198">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF198">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AG198">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK198">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32948,10 +32948,10 @@
         <v>0</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC200">
         <v>0</v>
@@ -33606,7 +33606,7 @@
         <v>2.37</v>
       </c>
       <c r="AC204">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AD204">
         <v>1.48</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.23</v>
+        <v>2.28</v>
       </c>
       <c r="O207">
-        <v>6.1</v>
+        <v>3.7</v>
       </c>
       <c r="P207">
-        <v>9.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q207">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="R207">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="S207">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="T207">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="U207">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="V207">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="W207">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z207">
-        <v>5.55</v>
+        <v>4.25</v>
       </c>
       <c r="AA207">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AB207">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC207">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="AD207">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AE207">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AF207">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AG207">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK207">
-        <v>3.94</v>
+        <v>1.55</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O208">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P208">
-        <v>3.4</v>
+        <v>3.93</v>
       </c>
       <c r="Q208">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="R208">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S208">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T208">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="U208">
-        <v>2.53</v>
+        <v>3.02</v>
       </c>
       <c r="V208">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W208">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X208">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y208">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z208">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="AA208">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AB208">
+        <v>1.6</v>
+      </c>
+      <c r="AC208">
+        <v>3.92</v>
+      </c>
+      <c r="AD208">
+        <v>1.18</v>
+      </c>
+      <c r="AE208">
+        <v>1.02</v>
+      </c>
+      <c r="AF208">
         <v>1.95</v>
       </c>
-      <c r="AC208">
-        <v>2.92</v>
-      </c>
-      <c r="AD208">
-        <v>1.31</v>
-      </c>
-      <c r="AE208">
-        <v>1.13</v>
-      </c>
-      <c r="AF208">
-        <v>1.67</v>
-      </c>
       <c r="AG208">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK208">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="O209">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="P209">
-        <v>4.55</v>
+        <v>9.5</v>
       </c>
       <c r="Q209">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="R209">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="S209">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T209">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="U209">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="V209">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="W209">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="Z209">
-        <v>4.27</v>
+        <v>5.8</v>
       </c>
       <c r="AA209">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AB209">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="AC209">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AD209">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AE209">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AF209">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AG209">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK209">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="O210">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="P210">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q210">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="R210">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S210">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T210">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="U210">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="V210">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W210">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X210">
         <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z210">
-        <v>4.25</v>
+        <v>3.58</v>
       </c>
       <c r="AA210">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB210">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC210">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="AD210">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AE210">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF210">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AG210">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK210">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="O211">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P211">
-        <v>3.93</v>
+        <v>2.5</v>
       </c>
       <c r="Q211">
-        <v>2.45</v>
+        <v>3.18</v>
       </c>
       <c r="R211">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="S211">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T211">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="U211">
-        <v>3.02</v>
+        <v>2.39</v>
       </c>
       <c r="V211">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W211">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X211">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="Z211">
-        <v>2.74</v>
+        <v>4.15</v>
       </c>
       <c r="AA211">
+        <v>1.6</v>
+      </c>
+      <c r="AB211">
         <v>2.2</v>
       </c>
-      <c r="AB211">
-        <v>1.6</v>
-      </c>
       <c r="AC211">
-        <v>3.92</v>
+        <v>2.49</v>
       </c>
       <c r="AD211">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AE211">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF211">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG211">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK211">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34868,10 +34868,10 @@
         <v>2.25</v>
       </c>
       <c r="O212">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="P212">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="Q212">
         <v>2.4</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,19 +35028,19 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.41</v>
+        <v>1.68</v>
       </c>
       <c r="O213">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P213">
-        <v>2.5</v>
+        <v>4.55</v>
       </c>
       <c r="Q213">
-        <v>3.18</v>
+        <v>2.19</v>
       </c>
       <c r="R213">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="S213">
         <v>1.3</v>
@@ -35049,43 +35049,43 @@
         <v>3.12</v>
       </c>
       <c r="U213">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="V213">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W213">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X213">
         <v>1.01</v>
       </c>
       <c r="Y213">
+        <v>1.21</v>
+      </c>
+      <c r="Z213">
+        <v>4.27</v>
+      </c>
+      <c r="AA213">
+        <v>1.69</v>
+      </c>
+      <c r="AB213">
+        <v>2.18</v>
+      </c>
+      <c r="AC213">
+        <v>2.56</v>
+      </c>
+      <c r="AD213">
+        <v>1.4</v>
+      </c>
+      <c r="AE213">
         <v>1.16</v>
       </c>
-      <c r="Z213">
-        <v>4.15</v>
-      </c>
-      <c r="AA213">
-        <v>1.6</v>
-      </c>
-      <c r="AB213">
-        <v>2.2</v>
-      </c>
-      <c r="AC213">
-        <v>2.49</v>
-      </c>
-      <c r="AD213">
-        <v>1.42</v>
-      </c>
-      <c r="AE213">
-        <v>1.13</v>
-      </c>
       <c r="AF213">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG213">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK213">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35194,7 +35194,7 @@
         <v>1.83</v>
       </c>
       <c r="O214">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="P214">
         <v>3.72</v>
@@ -37159,7 +37159,7 @@
         <v>3.75</v>
       </c>
       <c r="R226">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S226">
         <v>1.25</v>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK226">
         <v>1.25</v>
@@ -37310,7 +37310,7 @@
         </is>
       </c>
       <c r="N227">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="O227">
         <v>6.5</v>
@@ -39764,10 +39764,10 @@
         <v>6.58</v>
       </c>
       <c r="Q242">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R242">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S242">
         <v>1.24</v>
@@ -39797,22 +39797,22 @@
         <v>1.6</v>
       </c>
       <c r="AB242">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AC242">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AD242">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE242">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF242">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG242">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK242">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="O252">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="P252">
-        <v>4.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q252">
-        <v>2.19</v>
+        <v>3.22</v>
       </c>
       <c r="R252">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S252">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T252">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U252">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="V252">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W252">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X252">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y252">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z252">
-        <v>3.34</v>
+        <v>3.88</v>
       </c>
       <c r="AA252">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB252">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AC252">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="AD252">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE252">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF252">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AG252">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK252">
-        <v>2.04</v>
+        <v>1.38</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,64 +41548,64 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="O253">
+        <v>3.55</v>
+      </c>
+      <c r="P253">
+        <v>4.5</v>
+      </c>
+      <c r="Q253">
+        <v>2.19</v>
+      </c>
+      <c r="R253">
+        <v>2.14</v>
+      </c>
+      <c r="S253">
+        <v>1.32</v>
+      </c>
+      <c r="T253">
+        <v>2.9</v>
+      </c>
+      <c r="U253">
+        <v>2.58</v>
+      </c>
+      <c r="V253">
+        <v>1.4</v>
+      </c>
+      <c r="W253">
+        <v>1.07</v>
+      </c>
+      <c r="X253">
+        <v>1.01</v>
+      </c>
+      <c r="Y253">
+        <v>1.24</v>
+      </c>
+      <c r="Z253">
+        <v>3.34</v>
+      </c>
+      <c r="AA253">
+        <v>1.83</v>
+      </c>
+      <c r="AB253">
+        <v>1.83</v>
+      </c>
+      <c r="AC253">
         <v>3.05</v>
       </c>
-      <c r="P253">
-        <v>2.65</v>
-      </c>
-      <c r="Q253">
-        <v>3.22</v>
-      </c>
-      <c r="R253">
-        <v>2</v>
-      </c>
-      <c r="S253">
-        <v>1.34</v>
-      </c>
-      <c r="T253">
-        <v>2.8</v>
-      </c>
-      <c r="U253">
-        <v>2.48</v>
-      </c>
-      <c r="V253">
-        <v>1.43</v>
-      </c>
-      <c r="W253">
-        <v>1.06</v>
-      </c>
-      <c r="X253">
-        <v>1</v>
-      </c>
-      <c r="Y253">
-        <v>1.18</v>
-      </c>
-      <c r="Z253">
-        <v>3.88</v>
-      </c>
-      <c r="AA253">
-        <v>1.7</v>
-      </c>
-      <c r="AB253">
-        <v>1.99</v>
-      </c>
-      <c r="AC253">
-        <v>2.66</v>
-      </c>
       <c r="AD253">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE253">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF253">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG253">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK253">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -42043,7 +42043,7 @@
         <v>3.81</v>
       </c>
       <c r="P256">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="Q256">
         <v>2.32</v>
@@ -42239,10 +42239,10 @@
         <v>0</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC257">
         <v>0</v>
@@ -43235,7 +43235,7 @@
         <v>1.62</v>
       </c>
       <c r="AG263">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -44002,55 +44002,55 @@
         <v>3.45</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA268">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB268">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44823,19 +44823,19 @@
         <v>2.42</v>
       </c>
       <c r="S273">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T273">
         <v>3.18</v>
       </c>
       <c r="U273">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V273">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W273">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X273">
         <v>1.01</v>
@@ -44974,16 +44974,16 @@
         <v>4.9</v>
       </c>
       <c r="O274">
-        <v>4.3</v>
+        <v>4.06</v>
       </c>
       <c r="P274">
         <v>1.59</v>
       </c>
       <c r="Q274">
-        <v>5.5</v>
+        <v>4.37</v>
       </c>
       <c r="R274">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S274">
         <v>1.25</v>
@@ -45019,7 +45019,7 @@
         <v>2.47</v>
       </c>
       <c r="AD274">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE274">
         <v>1.15</v>
@@ -45466,7 +45466,7 @@
         <v>3.6</v>
       </c>
       <c r="P277">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q277">
         <v>2.68</v>
@@ -46948,13 +46948,13 @@
         <v>7</v>
       </c>
       <c r="U286">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V286">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="W286">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X286">
         <v>1</v>
@@ -46975,7 +46975,7 @@
         <v>1.39</v>
       </c>
       <c r="AD286">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AE286">
         <v>1.94</v>
@@ -47000,7 +47000,7 @@
         <v>1.06</v>
       </c>
       <c r="AK286">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O300">
         <v>2.95</v>
       </c>
       <c r="P300">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q300">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R300">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="S300">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="T300">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U300">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="V300">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W300">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X300">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y300">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="Z300">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="AA300">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="AB300">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AC300">
-        <v>5.1</v>
+        <v>6.05</v>
       </c>
       <c r="AD300">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE300">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF300">
-        <v>2.19</v>
+        <v>2.57</v>
       </c>
       <c r="AG300">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK300">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O301">
         <v>2.95</v>
       </c>
       <c r="P301">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q301">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R301">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="S301">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T301">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U301">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="V301">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W301">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X301">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y301">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="Z301">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="AA301">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="AB301">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AC301">
-        <v>6.05</v>
+        <v>5.1</v>
       </c>
       <c r="AD301">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AE301">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF301">
-        <v>2.57</v>
+        <v>2.19</v>
       </c>
       <c r="AG301">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK301">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49918,7 +49918,7 @@
         <v>1.55</v>
       </c>
       <c r="AG304">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O311">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P311">
-        <v>6.54</v>
+        <v>4.8</v>
       </c>
       <c r="Q311">
         <v>2</v>
@@ -51020,7 +51020,7 @@
         <v>1.35</v>
       </c>
       <c r="T311">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="U311">
         <v>2.6</v>
@@ -51044,7 +51044,7 @@
         <v>1.77</v>
       </c>
       <c r="AB311">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC311">
         <v>2.88</v>
@@ -51075,7 +51075,7 @@
         <v>1.22</v>
       </c>
       <c r="AK311">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51666,7 +51666,7 @@
         <v>1.82</v>
       </c>
       <c r="R315">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S315">
         <v>1.28</v>
@@ -51696,10 +51696,10 @@
         <v>1.74</v>
       </c>
       <c r="AB315">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC315">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AD315">
         <v>1.47</v>
@@ -52632,7 +52632,7 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O321">
         <v>4.45</v>
@@ -52659,7 +52659,7 @@
         <v>1.65</v>
       </c>
       <c r="W321">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X321">
         <v>1.02</v>
@@ -52668,7 +52668,7 @@
         <v>1.08</v>
       </c>
       <c r="Z321">
-        <v>5.83</v>
+        <v>5.77</v>
       </c>
       <c r="AA321">
         <v>1.44</v>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK321">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="O323">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="P323">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q323">
         <v>3.6</v>
@@ -52979,10 +52979,10 @@
         <v>2.5</v>
       </c>
       <c r="U323">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V323">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W323">
         <v>1.05</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,80 +53447,80 @@
         </is>
       </c>
       <c r="N326">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="O326">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="P326">
-        <v>3.6</v>
+        <v>7.25</v>
       </c>
       <c r="Q326">
-        <v>2.84</v>
+        <v>2.17</v>
       </c>
       <c r="R326">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="S326">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="T326">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="U326">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="V326">
+        <v>1.28</v>
+      </c>
+      <c r="W326">
+        <v>1.03</v>
+      </c>
+      <c r="X326">
+        <v>1.06</v>
+      </c>
+      <c r="Y326">
+        <v>1.48</v>
+      </c>
+      <c r="Z326">
+        <v>2.58</v>
+      </c>
+      <c r="AA326">
+        <v>2.4</v>
+      </c>
+      <c r="AB326">
+        <v>1.52</v>
+      </c>
+      <c r="AC326">
+        <v>4.7</v>
+      </c>
+      <c r="AD326">
+        <v>1.17</v>
+      </c>
+      <c r="AE326">
+        <v>1.01</v>
+      </c>
+      <c r="AF326">
+        <v>2.45</v>
+      </c>
+      <c r="AG326">
+        <v>1.48</v>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ326">
         <v>1.22</v>
       </c>
-      <c r="W326">
-        <v>1.04</v>
-      </c>
-      <c r="X326">
-        <v>1.08</v>
-      </c>
-      <c r="Y326">
-        <v>1.58</v>
-      </c>
-      <c r="Z326">
-        <v>2.18</v>
-      </c>
-      <c r="AA326">
-        <v>2.87</v>
-      </c>
-      <c r="AB326">
-        <v>1.4</v>
-      </c>
-      <c r="AC326">
-        <v>5.7</v>
-      </c>
-      <c r="AD326">
-        <v>1.08</v>
-      </c>
-      <c r="AE326">
-        <v>1.03</v>
-      </c>
-      <c r="AF326">
-        <v>2.32</v>
-      </c>
-      <c r="AG326">
-        <v>1.53</v>
-      </c>
-      <c r="AH326" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI326" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ326">
-        <v>1.32</v>
-      </c>
       <c r="AK326">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G328">
@@ -53776,61 +53776,61 @@
         <v>2.15</v>
       </c>
       <c r="O328">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P328">
         <v>3.6</v>
       </c>
       <c r="Q328">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="R328">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="S328">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="T328">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="U328">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="V328">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W328">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X328">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y328">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="Z328">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="AA328">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AB328">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AC328">
-        <v>6.55</v>
+        <v>5.7</v>
       </c>
       <c r="AD328">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE328">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF328">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="AG328">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK328">
         <v>1.62</v>
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="O329">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="P329">
-        <v>7.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q329">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="R329">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="S329">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="T329">
-        <v>2.47</v>
+        <v>1.96</v>
       </c>
       <c r="U329">
-        <v>3.12</v>
+        <v>4.33</v>
       </c>
       <c r="V329">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="W329">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X329">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y329">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="Z329">
-        <v>2.58</v>
+        <v>1.96</v>
       </c>
       <c r="AA329">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="AB329">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AC329">
-        <v>4.7</v>
+        <v>6.55</v>
       </c>
       <c r="AD329">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AE329">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF329">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="AG329">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK329">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -55403,31 +55403,31 @@
         </is>
       </c>
       <c r="N338">
-        <v>3.72</v>
+        <v>3</v>
       </c>
       <c r="O338">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P338">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q338">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R338">
         <v>2.14</v>
       </c>
       <c r="S338">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T338">
         <v>3</v>
       </c>
       <c r="U338">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="V338">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W338">
         <v>1.06</v>
@@ -55442,10 +55442,10 @@
         <v>3.34</v>
       </c>
       <c r="AA338">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB338">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC338">
         <v>3.14</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
+        <v>2.3</v>
+      </c>
+      <c r="O348">
         <v>3.9</v>
       </c>
-      <c r="O348">
-        <v>4.4</v>
-      </c>
       <c r="P348">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G349">
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="O349">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="P349">
-        <v>2.63</v>
+        <v>4.38</v>
       </c>
       <c r="Q349">
         <v>0</v>
@@ -57241,10 +57241,10 @@
         <v>0</v>
       </c>
       <c r="AC349">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD349">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE349">
         <v>0</v>
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G350">
@@ -57359,13 +57359,13 @@
         </is>
       </c>
       <c r="N350">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="O350">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P350">
-        <v>4.38</v>
+        <v>1.73</v>
       </c>
       <c r="Q350">
         <v>0</v>
@@ -57404,10 +57404,10 @@
         <v>0</v>
       </c>
       <c r="AC350">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD350">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE350">
         <v>0</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P7">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="R7">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
         <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="V7">
         <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
+        <v>1.29</v>
+      </c>
+      <c r="Z7">
+        <v>3.41</v>
+      </c>
+      <c r="AA7">
+        <v>1.99</v>
+      </c>
+      <c r="AB7">
+        <v>1.83</v>
+      </c>
+      <c r="AC7">
+        <v>3.35</v>
+      </c>
+      <c r="AD7">
         <v>1.3</v>
       </c>
-      <c r="Z7">
-        <v>3.32</v>
-      </c>
-      <c r="AA7">
-        <v>2.01</v>
-      </c>
-      <c r="AB7">
-        <v>1.78</v>
-      </c>
-      <c r="AC7">
-        <v>3.4</v>
-      </c>
-      <c r="AD7">
-        <v>1.29</v>
-      </c>
       <c r="AE7">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AK7">
-        <v>2.17</v>
+        <v>1.55</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="O8">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="Q8">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
         <v>2.9</v>
       </c>
       <c r="U8">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="V8">
         <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8">
+        <v>1.3</v>
+      </c>
+      <c r="Z8">
+        <v>3.32</v>
+      </c>
+      <c r="AA8">
+        <v>2.01</v>
+      </c>
+      <c r="AB8">
+        <v>1.78</v>
+      </c>
+      <c r="AC8">
+        <v>3.4</v>
+      </c>
+      <c r="AD8">
         <v>1.29</v>
       </c>
-      <c r="Z8">
-        <v>3.41</v>
-      </c>
-      <c r="AA8">
-        <v>1.99</v>
-      </c>
-      <c r="AB8">
-        <v>1.83</v>
-      </c>
-      <c r="AC8">
-        <v>3.35</v>
-      </c>
-      <c r="AD8">
-        <v>1.3</v>
-      </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>1.55</v>
+        <v>2.17</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="O25">
         <v>3.25</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="O35">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -7327,22 +7327,22 @@
         <v>3.35</v>
       </c>
       <c r="Q43">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R43">
         <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U43">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W43">
         <v>1.06</v>
@@ -7351,31 +7351,31 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA43">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB43">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC43">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD43">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE43">
         <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG43">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
         <v>0</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="P53">
-        <v>3.09</v>
+        <v>3.55</v>
       </c>
       <c r="Q53">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T53">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="V53">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="W53">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z53">
-        <v>3.98</v>
+        <v>7.25</v>
       </c>
       <c r="AA53">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AB53">
-        <v>2.14</v>
+        <v>3.12</v>
       </c>
       <c r="AC53">
-        <v>2.52</v>
+        <v>1.9</v>
       </c>
       <c r="AD53">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF53">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AG53">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="O54">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>3.55</v>
+        <v>3.09</v>
       </c>
       <c r="Q54">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="R54">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
+        <v>1.29</v>
+      </c>
+      <c r="T54">
+        <v>3.08</v>
+      </c>
+      <c r="U54">
+        <v>2.4</v>
+      </c>
+      <c r="V54">
+        <v>1.5</v>
+      </c>
+      <c r="W54">
+        <v>1.09</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
         <v>1.17</v>
       </c>
-      <c r="T54">
-        <v>3.54</v>
-      </c>
-      <c r="U54">
-        <v>1.99</v>
-      </c>
-      <c r="V54">
-        <v>1.84</v>
-      </c>
-      <c r="W54">
-        <v>1.17</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.1</v>
-      </c>
       <c r="Z54">
-        <v>7.25</v>
+        <v>3.98</v>
       </c>
       <c r="AA54">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AB54">
-        <v>3.12</v>
+        <v>2.14</v>
       </c>
       <c r="AC54">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="AD54">
-        <v>1.92</v>
+        <v>1.41</v>
       </c>
       <c r="AE54">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AG54">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK54">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10795,7 +10795,7 @@
         <v>1.14</v>
       </c>
       <c r="AF64">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG64">
         <v>2.3</v>
@@ -10913,55 +10913,55 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>1.29</v>
       </c>
       <c r="X79">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
         <v>1.02</v>
@@ -13234,7 +13234,7 @@
         <v>1.6</v>
       </c>
       <c r="AD79">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AE79">
         <v>1.49</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O87">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P87">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q87">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R87">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S87">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U87">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V87">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W87">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>4.15</v>
+        <v>5.45</v>
       </c>
       <c r="AA87">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AB87">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AC87">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AD87">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AE87">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF87">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AG87">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK87">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O88">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P88">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q88">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="R88">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S88">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V88">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W88">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>4.2</v>
+        <v>5.45</v>
       </c>
       <c r="AA88">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AB88">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC88">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="AD88">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AE88">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF88">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AG88">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P89">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R89">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U89">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z89">
-        <v>5.45</v>
+        <v>4.15</v>
       </c>
       <c r="AA89">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB89">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="AC89">
-        <v>2.11</v>
+        <v>2.43</v>
       </c>
       <c r="AD89">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AE89">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF89">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AG89">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK89">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="O91">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P91">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q91">
+        <v>2.5</v>
+      </c>
+      <c r="R91">
+        <v>2.24</v>
+      </c>
+      <c r="S91">
+        <v>1.25</v>
+      </c>
+      <c r="T91">
         <v>3.4</v>
       </c>
-      <c r="R91">
-        <v>2.4</v>
-      </c>
-      <c r="S91">
-        <v>1.2</v>
-      </c>
-      <c r="T91">
-        <v>4</v>
-      </c>
       <c r="U91">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V91">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W91">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z91">
-        <v>5.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA91">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AB91">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AC91">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="AD91">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AE91">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF91">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AG91">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>7.1</v>
       </c>
       <c r="AA92">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB92">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AC92">
         <v>1.76</v>
@@ -15356,7 +15356,7 @@
         <v>2.08</v>
       </c>
       <c r="AE92">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AF92">
         <v>1.62</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O98">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P98">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q98">
         <v>5.65</v>
@@ -16772,7 +16772,7 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O101">
         <v>3.1</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O114">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P114">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Q114">
-        <v>4.37</v>
+        <v>4.57</v>
       </c>
       <c r="R114">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="S114">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T114">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U114">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="V114">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z114">
-        <v>2.92</v>
+        <v>3.43</v>
       </c>
       <c r="AA114">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AB114">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC114">
-        <v>3.74</v>
+        <v>3.31</v>
       </c>
       <c r="AD114">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE114">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG114">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P115">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="Q115">
-        <v>4.01</v>
+        <v>4.37</v>
       </c>
       <c r="R115">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="S115">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T115">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U115">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="V115">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z115">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA115">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AB115">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC115">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD115">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE115">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG115">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,31 +19217,31 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="O116">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="Q116">
-        <v>4.57</v>
+        <v>4.01</v>
       </c>
       <c r="R116">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="S116">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T116">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="U116">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="V116">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W116">
         <v>1.06</v>
@@ -19250,31 +19250,31 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z116">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA116">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB116">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC116">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AD116">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE116">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF116">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG116">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19549,7 +19549,7 @@
         <v>3.54</v>
       </c>
       <c r="P118">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q118">
         <v>2.43</v>
@@ -19582,7 +19582,7 @@
         <v>3.5</v>
       </c>
       <c r="AA118">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AB118">
         <v>1.88</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O139">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P139">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -23295,7 +23295,7 @@
         <v>1.4</v>
       </c>
       <c r="O141">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="P141">
         <v>5.5</v>
@@ -23316,7 +23316,7 @@
         <v>2.13</v>
       </c>
       <c r="V141">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W141">
         <v>1.12</v>
@@ -23362,7 +23362,7 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK141">
         <v>2.75</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O142">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P142">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q142">
         <v>3.67</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O143">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="P143">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="Q143">
         <v>2.15</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="O144">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P144">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="Q144">
         <v>2.43</v>
@@ -25909,7 +25909,7 @@
         <v>1.61</v>
       </c>
       <c r="Q157">
-        <v>5.12</v>
+        <v>5.24</v>
       </c>
       <c r="R157">
         <v>2.51</v>
@@ -25918,7 +25918,7 @@
         <v>1.23</v>
       </c>
       <c r="T157">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U157">
         <v>2.05</v>
@@ -25948,7 +25948,7 @@
         <v>2.31</v>
       </c>
       <c r="AD157">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE157">
         <v>1.23</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,80 +26063,80 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="O158">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P158">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="Q158">
-        <v>4.1</v>
+        <v>3.04</v>
       </c>
       <c r="R158">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="S158">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T158">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="U158">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="V158">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="W158">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X158">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="Z158">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA158">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AB158">
-        <v>2.93</v>
+        <v>2.19</v>
       </c>
       <c r="AC158">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AD158">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="AE158">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AF158">
+        <v>1.47</v>
+      </c>
+      <c r="AG158">
+        <v>2.39</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ158">
+        <v>1.23</v>
+      </c>
+      <c r="AK158">
         <v>1.35</v>
-      </c>
-      <c r="AG158">
-        <v>2.93</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ158">
-        <v>2</v>
-      </c>
-      <c r="AK158">
-        <v>1.27</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.87</v>
+        <v>3.18</v>
       </c>
       <c r="O159">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P159">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q159">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="R159">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="S159">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T159">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="U159">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="V159">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="W159">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z159">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA159">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AB159">
-        <v>2.19</v>
+        <v>2.93</v>
       </c>
       <c r="AC159">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AD159">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="AE159">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AF159">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AG159">
-        <v>2.39</v>
+        <v>2.93</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AK159">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26398,7 +26398,7 @@
         <v>4.5</v>
       </c>
       <c r="Q160">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="R160">
         <v>2.27</v>
@@ -26410,22 +26410,22 @@
         <v>3.3</v>
       </c>
       <c r="U160">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V160">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W160">
         <v>1.08</v>
       </c>
       <c r="X160">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
         <v>1.2</v>
       </c>
       <c r="Z160">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="AA160">
         <v>1.74</v>
@@ -26434,7 +26434,7 @@
         <v>2.13</v>
       </c>
       <c r="AC160">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AD160">
         <v>1.39</v>
@@ -26443,10 +26443,10 @@
         <v>1.11</v>
       </c>
       <c r="AF160">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG160">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>1.14</v>
       </c>
       <c r="AK160">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.23</v>
+        <v>2.37</v>
       </c>
       <c r="O161">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="P161">
-        <v>10</v>
+        <v>2.55</v>
       </c>
       <c r="Q161">
-        <v>1.56</v>
+        <v>2.97</v>
       </c>
       <c r="R161">
-        <v>3.28</v>
+        <v>2.3</v>
       </c>
       <c r="S161">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T161">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="U161">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="V161">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="W161">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X161">
         <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z161">
-        <v>6.05</v>
+        <v>5</v>
       </c>
       <c r="AA161">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AB161">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC161">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AD161">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AE161">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AF161">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AG161">
-        <v>1.96</v>
+        <v>2.52</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AK161">
-        <v>4.33</v>
+        <v>1.6</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.37</v>
+        <v>1.23</v>
       </c>
       <c r="O162">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="P162">
-        <v>2.55</v>
+        <v>10</v>
       </c>
       <c r="Q162">
-        <v>2.97</v>
+        <v>1.56</v>
       </c>
       <c r="R162">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="S162">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T162">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="U162">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="V162">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="W162">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X162">
         <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z162">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="AA162">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AB162">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC162">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AD162">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AE162">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AF162">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG162">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AK162">
-        <v>1.6</v>
+        <v>4.33</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -27213,19 +27213,19 @@
         <v>2.22</v>
       </c>
       <c r="Q165">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="R165">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="S165">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T165">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U165">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="V165">
         <v>1.28</v>
@@ -27237,28 +27237,28 @@
         <v>1.06</v>
       </c>
       <c r="Y165">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z165">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AA165">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AB165">
         <v>1.53</v>
       </c>
       <c r="AC165">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD165">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE165">
         <v>1.01</v>
       </c>
       <c r="AF165">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AG165">
         <v>1.7</v>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK165">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27382,7 +27382,7 @@
         <v>2.3</v>
       </c>
       <c r="S166">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T166">
         <v>3.26</v>
@@ -27400,22 +27400,22 @@
         <v>1.03</v>
       </c>
       <c r="Y166">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z166">
         <v>3.88</v>
       </c>
       <c r="AA166">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB166">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC166">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AD166">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE166">
         <v>1.11</v>
@@ -27548,7 +27548,7 @@
         <v>1.25</v>
       </c>
       <c r="T167">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U167">
         <v>2.28</v>
@@ -27587,7 +27587,7 @@
         <v>1.58</v>
       </c>
       <c r="AG167">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>6.7</v>
       </c>
       <c r="Q168">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R168">
         <v>2.62</v>
@@ -27732,7 +27732,7 @@
         <v>4.7</v>
       </c>
       <c r="AA168">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AB168">
         <v>2.35</v>
@@ -27865,16 +27865,16 @@
         <v>1.85</v>
       </c>
       <c r="Q169">
-        <v>4.28</v>
+        <v>4.15</v>
       </c>
       <c r="R169">
         <v>2.19</v>
       </c>
       <c r="S169">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T169">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="U169">
         <v>2.61</v>
@@ -27895,7 +27895,7 @@
         <v>3.84</v>
       </c>
       <c r="AA169">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB169">
         <v>2.04</v>
@@ -28058,7 +28058,7 @@
         <v>2.84</v>
       </c>
       <c r="AA170">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AB170">
         <v>1.61</v>
@@ -28212,7 +28212,7 @@
         <v>1.06</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y171">
         <v>1.31</v>
@@ -28221,13 +28221,13 @@
         <v>2.92</v>
       </c>
       <c r="AA171">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AB171">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AC171">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AD171">
         <v>1.22</v>
@@ -28351,10 +28351,10 @@
         <v>3.74</v>
       </c>
       <c r="P172">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q172">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R172">
         <v>2.16</v>
@@ -28538,7 +28538,7 @@
         <v>1.07</v>
       </c>
       <c r="X173">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y173">
         <v>1.21</v>
@@ -28550,7 +28550,7 @@
         <v>1.74</v>
       </c>
       <c r="AB173">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC173">
         <v>2.96</v>
@@ -28559,13 +28559,13 @@
         <v>1.37</v>
       </c>
       <c r="AE173">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF173">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG173">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK173">
         <v>1.4</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="O176">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P176">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="Q176">
-        <v>4.11</v>
+        <v>3.12</v>
       </c>
       <c r="R176">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="S176">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>3.32</v>
+        <v>3.46</v>
       </c>
       <c r="U176">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="V176">
         <v>1.52</v>
       </c>
       <c r="W176">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X176">
         <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z176">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA176">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AB176">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AC176">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AD176">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE176">
         <v>1.15</v>
       </c>
       <c r="AF176">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG176">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK176">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,19 +29160,19 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.75</v>
+        <v>2.61</v>
       </c>
       <c r="O177">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P177">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q177">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R177">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S177">
         <v>1.31</v>
@@ -29181,43 +29181,43 @@
         <v>3.08</v>
       </c>
       <c r="U177">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V177">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W177">
         <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y177">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z177">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA177">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB177">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC177">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD177">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE177">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF177">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG177">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,80 +29323,80 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="O178">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P178">
-        <v>2.31</v>
+        <v>3.55</v>
       </c>
       <c r="Q178">
-        <v>3.12</v>
+        <v>2.36</v>
       </c>
       <c r="R178">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S178">
+        <v>1.34</v>
+      </c>
+      <c r="T178">
+        <v>2.92</v>
+      </c>
+      <c r="U178">
+        <v>2.77</v>
+      </c>
+      <c r="V178">
+        <v>1.41</v>
+      </c>
+      <c r="W178">
+        <v>1.07</v>
+      </c>
+      <c r="X178">
+        <v>1.02</v>
+      </c>
+      <c r="Y178">
+        <v>1.22</v>
+      </c>
+      <c r="Z178">
+        <v>3.5</v>
+      </c>
+      <c r="AA178">
+        <v>1.79</v>
+      </c>
+      <c r="AB178">
+        <v>1.92</v>
+      </c>
+      <c r="AC178">
+        <v>3</v>
+      </c>
+      <c r="AD178">
+        <v>1.33</v>
+      </c>
+      <c r="AE178">
+        <v>1.08</v>
+      </c>
+      <c r="AF178">
+        <v>1.71</v>
+      </c>
+      <c r="AG178">
+        <v>1.99</v>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ178">
         <v>1.25</v>
       </c>
-      <c r="T178">
-        <v>3.46</v>
-      </c>
-      <c r="U178">
-        <v>2.45</v>
-      </c>
-      <c r="V178">
-        <v>1.52</v>
-      </c>
-      <c r="W178">
-        <v>1.13</v>
-      </c>
-      <c r="X178">
-        <v>1.01</v>
-      </c>
-      <c r="Y178">
-        <v>1.15</v>
-      </c>
-      <c r="Z178">
-        <v>4.2</v>
-      </c>
-      <c r="AA178">
-        <v>1.61</v>
-      </c>
-      <c r="AB178">
-        <v>2.21</v>
-      </c>
-      <c r="AC178">
-        <v>2.42</v>
-      </c>
-      <c r="AD178">
-        <v>1.44</v>
-      </c>
-      <c r="AE178">
-        <v>1.15</v>
-      </c>
-      <c r="AF178">
-        <v>1.51</v>
-      </c>
-      <c r="AG178">
-        <v>2.35</v>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ178">
-        <v>1.44</v>
-      </c>
       <c r="AK178">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.35</v>
+        <v>2.35</v>
       </c>
       <c r="O179">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="P179">
-        <v>6.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q179">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="R179">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="S179">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T179">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="U179">
-        <v>2.09</v>
+        <v>2.98</v>
       </c>
       <c r="V179">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="W179">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X179">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y179">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="Z179">
-        <v>6.12</v>
+        <v>3.14</v>
       </c>
       <c r="AA179">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AB179">
-        <v>2.7</v>
+        <v>1.79</v>
       </c>
       <c r="AC179">
-        <v>2.06</v>
+        <v>3.34</v>
       </c>
       <c r="AD179">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AE179">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AF179">
         <v>1.6</v>
       </c>
       <c r="AG179">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK179">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="O180">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="P180">
-        <v>2.87</v>
+        <v>6.2</v>
       </c>
       <c r="Q180">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="R180">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="S180">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T180">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="U180">
-        <v>2.98</v>
+        <v>2.09</v>
       </c>
       <c r="V180">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="W180">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X180">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="Z180">
-        <v>3.14</v>
+        <v>6.12</v>
       </c>
       <c r="AA180">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AB180">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="AC180">
-        <v>3.34</v>
+        <v>2.06</v>
       </c>
       <c r="AD180">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="AE180">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AF180">
         <v>1.6</v>
       </c>
       <c r="AG180">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK180">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="O181">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P181">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q181">
-        <v>3.2</v>
+        <v>4.11</v>
       </c>
       <c r="R181">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="S181">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T181">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="U181">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="V181">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W181">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X181">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y181">
         <v>1.21</v>
       </c>
       <c r="Z181">
-        <v>3.58</v>
+        <v>4.25</v>
       </c>
       <c r="AA181">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AB181">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="AC181">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AD181">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE181">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF181">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG181">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
+        <v>1.24</v>
+      </c>
+      <c r="AK181">
         <v>1.25</v>
-      </c>
-      <c r="AK181">
-        <v>1.44</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O182">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P182">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="Q182">
         <v>2.2</v>
       </c>
       <c r="R182">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S182">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T182">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U182">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="V182">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W182">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X182">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z182">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AA182">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB182">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC182">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="AD182">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE182">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF182">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG182">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>1.22</v>
       </c>
       <c r="AK182">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,80 +30138,80 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="O183">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P183">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="Q183">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="R183">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S183">
+        <v>1.29</v>
+      </c>
+      <c r="T183">
+        <v>3.3</v>
+      </c>
+      <c r="U183">
+        <v>2.42</v>
+      </c>
+      <c r="V183">
+        <v>1.48</v>
+      </c>
+      <c r="W183">
+        <v>1.08</v>
+      </c>
+      <c r="X183">
+        <v>1.04</v>
+      </c>
+      <c r="Y183">
+        <v>1.18</v>
+      </c>
+      <c r="Z183">
+        <v>3.82</v>
+      </c>
+      <c r="AA183">
+        <v>1.65</v>
+      </c>
+      <c r="AB183">
+        <v>2.1</v>
+      </c>
+      <c r="AC183">
+        <v>2.98</v>
+      </c>
+      <c r="AD183">
         <v>1.34</v>
       </c>
-      <c r="T183">
-        <v>2.92</v>
-      </c>
-      <c r="U183">
-        <v>2.77</v>
-      </c>
-      <c r="V183">
-        <v>1.41</v>
-      </c>
-      <c r="W183">
-        <v>1.07</v>
-      </c>
-      <c r="X183">
-        <v>1.02</v>
-      </c>
-      <c r="Y183">
+      <c r="AE183">
+        <v>1.09</v>
+      </c>
+      <c r="AF183">
+        <v>1.57</v>
+      </c>
+      <c r="AG183">
+        <v>2.25</v>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ183">
         <v>1.22</v>
       </c>
-      <c r="Z183">
-        <v>3.5</v>
-      </c>
-      <c r="AA183">
-        <v>1.79</v>
-      </c>
-      <c r="AB183">
-        <v>1.92</v>
-      </c>
-      <c r="AC183">
-        <v>3</v>
-      </c>
-      <c r="AD183">
-        <v>1.33</v>
-      </c>
-      <c r="AE183">
-        <v>1.08</v>
-      </c>
-      <c r="AF183">
-        <v>1.71</v>
-      </c>
-      <c r="AG183">
-        <v>1.99</v>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ183">
-        <v>1.25</v>
-      </c>
       <c r="AK183">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30346,10 +30346,10 @@
         <v>2.5</v>
       </c>
       <c r="AC184">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AD184">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE184">
         <v>1.2</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,31 +31931,31 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="O194">
-        <v>3.58</v>
+        <v>3.48</v>
       </c>
       <c r="P194">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="Q194">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="R194">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S194">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T194">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="U194">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="V194">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W194">
         <v>1.07</v>
@@ -31964,31 +31964,31 @@
         <v>1.01</v>
       </c>
       <c r="Y194">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z194">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA194">
         <v>1.9</v>
       </c>
       <c r="AB194">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC194">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD194">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE194">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF194">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG194">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK194">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.13</v>
+        <v>2.65</v>
       </c>
       <c r="O195">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="P195">
-        <v>3.18</v>
+        <v>2.37</v>
       </c>
       <c r="Q195">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="R195">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S195">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T195">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="U195">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="V195">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="W195">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z195">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA195">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AB195">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AC195">
-        <v>2.97</v>
+        <v>2.52</v>
       </c>
       <c r="AD195">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE195">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF195">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AG195">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK195">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="O196">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="P196">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="Q196">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="R196">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="S196">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T196">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="U196">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="V196">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="W196">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X196">
         <v>1.02</v>
       </c>
       <c r="Y196">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="Z196">
-        <v>5.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA196">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AB196">
-        <v>2.56</v>
+        <v>1.72</v>
       </c>
       <c r="AC196">
-        <v>2.11</v>
+        <v>3.42</v>
       </c>
       <c r="AD196">
-        <v>1.68</v>
+        <v>1.23</v>
       </c>
       <c r="AE196">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AF196">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AG196">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK196">
-        <v>2.78</v>
+        <v>1.88</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="O197">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="P197">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="Q197">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="R197">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S197">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T197">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="U197">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V197">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W197">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X197">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z197">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA197">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AB197">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC197">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD197">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AE197">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF197">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AG197">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>1.26</v>
       </c>
       <c r="AK197">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.87</v>
+        <v>1.41</v>
       </c>
       <c r="O198">
-        <v>3.54</v>
+        <v>4.9</v>
       </c>
       <c r="P198">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="Q198">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="R198">
+        <v>2.63</v>
+      </c>
+      <c r="S198">
+        <v>1.22</v>
+      </c>
+      <c r="T198">
+        <v>4.1</v>
+      </c>
+      <c r="U198">
         <v>2.1</v>
       </c>
-      <c r="S198">
-        <v>1.38</v>
-      </c>
-      <c r="T198">
-        <v>2.74</v>
-      </c>
-      <c r="U198">
-        <v>2.88</v>
-      </c>
       <c r="V198">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="W198">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X198">
         <v>1.02</v>
       </c>
       <c r="Y198">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="Z198">
-        <v>3.14</v>
+        <v>5.2</v>
       </c>
       <c r="AA198">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AB198">
-        <v>1.72</v>
+        <v>2.56</v>
       </c>
       <c r="AC198">
-        <v>3.42</v>
+        <v>2.11</v>
       </c>
       <c r="AD198">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="AE198">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AF198">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AG198">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK198">
-        <v>1.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="O201">
         <v>3.6</v>
@@ -33087,7 +33087,7 @@
         <v>2.17</v>
       </c>
       <c r="S201">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T201">
         <v>2.96</v>
@@ -33425,7 +33425,7 @@
         <v>1.53</v>
       </c>
       <c r="W203">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X203">
         <v>1.01</v>
@@ -33443,7 +33443,7 @@
         <v>2.3</v>
       </c>
       <c r="AC203">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AD203">
         <v>1.48</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O207">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="P207">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q207">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="R207">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="S207">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T207">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="U207">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="V207">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W207">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z207">
-        <v>4.21</v>
+        <v>3.58</v>
       </c>
       <c r="AA207">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AB207">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC207">
-        <v>2.59</v>
+        <v>2.92</v>
       </c>
       <c r="AD207">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AE207">
         <v>1.13</v>
       </c>
       <c r="AF207">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG207">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK207">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,80 +34213,80 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.14</v>
+        <v>1.92</v>
       </c>
       <c r="O208">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="P208">
-        <v>9.5</v>
+        <v>3.93</v>
       </c>
       <c r="Q208">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="R208">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="S208">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="T208">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="U208">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="V208">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="W208">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X208">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y208">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="Z208">
-        <v>5.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA208">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AB208">
-        <v>2.69</v>
+        <v>1.6</v>
       </c>
       <c r="AC208">
-        <v>2.05</v>
+        <v>3.92</v>
       </c>
       <c r="AD208">
-        <v>1.72</v>
+        <v>1.18</v>
       </c>
       <c r="AE208">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AF208">
+        <v>1.95</v>
+      </c>
+      <c r="AG208">
+        <v>1.76</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ208">
+        <v>1.22</v>
+      </c>
+      <c r="AK208">
         <v>1.83</v>
-      </c>
-      <c r="AG208">
-        <v>1.87</v>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ208">
-        <v>1.09</v>
-      </c>
-      <c r="AK208">
-        <v>4.05</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="O209">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P209">
-        <v>3.93</v>
+        <v>2.65</v>
       </c>
       <c r="Q209">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R209">
+        <v>2.21</v>
+      </c>
+      <c r="S209">
+        <v>1.3</v>
+      </c>
+      <c r="T209">
+        <v>3.14</v>
+      </c>
+      <c r="U209">
+        <v>2.35</v>
+      </c>
+      <c r="V209">
+        <v>1.51</v>
+      </c>
+      <c r="W209">
+        <v>1.12</v>
+      </c>
+      <c r="X209">
+        <v>1.01</v>
+      </c>
+      <c r="Y209">
+        <v>1.22</v>
+      </c>
+      <c r="Z209">
+        <v>4.21</v>
+      </c>
+      <c r="AA209">
+        <v>1.66</v>
+      </c>
+      <c r="AB209">
         <v>2.1</v>
       </c>
-      <c r="S209">
-        <v>1.4</v>
-      </c>
-      <c r="T209">
-        <v>2.6</v>
-      </c>
-      <c r="U209">
-        <v>3.02</v>
-      </c>
-      <c r="V209">
-        <v>1.32</v>
-      </c>
-      <c r="W209">
-        <v>1.05</v>
-      </c>
-      <c r="X209">
-        <v>1.05</v>
-      </c>
-      <c r="Y209">
-        <v>1.35</v>
-      </c>
-      <c r="Z209">
-        <v>2.74</v>
-      </c>
-      <c r="AA209">
-        <v>2.2</v>
-      </c>
-      <c r="AB209">
-        <v>1.6</v>
-      </c>
       <c r="AC209">
-        <v>3.92</v>
+        <v>2.59</v>
       </c>
       <c r="AD209">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE209">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF209">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AG209">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK209">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="O210">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P210">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q210">
-        <v>2.51</v>
+        <v>3.18</v>
       </c>
       <c r="R210">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="S210">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T210">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U210">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="V210">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W210">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X210">
         <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z210">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="AA210">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AB210">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC210">
-        <v>2.92</v>
+        <v>2.49</v>
       </c>
       <c r="AD210">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE210">
         <v>1.13</v>
       </c>
       <c r="AF210">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG210">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK210">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,19 +34702,19 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.41</v>
+        <v>1.68</v>
       </c>
       <c r="O211">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P211">
-        <v>2.5</v>
+        <v>4.55</v>
       </c>
       <c r="Q211">
-        <v>3.18</v>
+        <v>2.19</v>
       </c>
       <c r="R211">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="S211">
         <v>1.3</v>
@@ -34723,43 +34723,43 @@
         <v>3.12</v>
       </c>
       <c r="U211">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="V211">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W211">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X211">
         <v>1.01</v>
       </c>
       <c r="Y211">
+        <v>1.21</v>
+      </c>
+      <c r="Z211">
+        <v>4.27</v>
+      </c>
+      <c r="AA211">
+        <v>1.69</v>
+      </c>
+      <c r="AB211">
+        <v>2.18</v>
+      </c>
+      <c r="AC211">
+        <v>2.56</v>
+      </c>
+      <c r="AD211">
+        <v>1.4</v>
+      </c>
+      <c r="AE211">
         <v>1.16</v>
       </c>
-      <c r="Z211">
-        <v>4.15</v>
-      </c>
-      <c r="AA211">
-        <v>1.57</v>
-      </c>
-      <c r="AB211">
-        <v>2.25</v>
-      </c>
-      <c r="AC211">
-        <v>2.49</v>
-      </c>
-      <c r="AD211">
-        <v>1.42</v>
-      </c>
-      <c r="AE211">
-        <v>1.13</v>
-      </c>
       <c r="AF211">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG211">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK211">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.68</v>
+        <v>1.14</v>
       </c>
       <c r="O212">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="P212">
-        <v>4.55</v>
+        <v>9.5</v>
       </c>
       <c r="Q212">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="R212">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="S212">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T212">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="U212">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="V212">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="W212">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="Z212">
-        <v>4.27</v>
+        <v>5.8</v>
       </c>
       <c r="AA212">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AB212">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="AC212">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AD212">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AE212">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AF212">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AG212">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK212">
-        <v>2.15</v>
+        <v>4.05</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -36015,55 +36015,55 @@
         <v>0</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U219">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V219">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W219">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y219">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z219">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA219">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB219">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE219">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF219">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG219">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK219">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36178,55 +36178,55 @@
         <v>0</v>
       </c>
       <c r="Q220">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R220">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S220">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T220">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U220">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V220">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W220">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X220">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z220">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC220">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD220">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE220">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF220">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG220">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK220">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -37201,7 +37201,7 @@
         <v>1.53</v>
       </c>
       <c r="AF226">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG226">
         <v>2.45</v>
@@ -37319,7 +37319,7 @@
         <v>2.75</v>
       </c>
       <c r="Q227">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="R227">
         <v>2.54</v>
@@ -37331,7 +37331,7 @@
         <v>3.9</v>
       </c>
       <c r="U227">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="V227">
         <v>1.67</v>
@@ -37355,10 +37355,10 @@
         <v>2.6</v>
       </c>
       <c r="AC227">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AD227">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE227">
         <v>1.23</v>
@@ -37383,7 +37383,7 @@
         <v>1.22</v>
       </c>
       <c r="AK227">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Club Portugalete</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G236">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Club Portugalete</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X237">
         <v>0</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE237">
         <v>0</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,64 +39103,64 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X238">
         <v>0</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE238">
         <v>0</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39471,7 +39471,7 @@
         <v>2.15</v>
       </c>
       <c r="AB240">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC240">
         <v>3.86</v>
@@ -40419,7 +40419,7 @@
         <v>1.78</v>
       </c>
       <c r="R246">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="S246">
         <v>1.18</v>
@@ -40443,22 +40443,22 @@
         <v>1.03</v>
       </c>
       <c r="Z246">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA246">
         <v>1.27</v>
       </c>
       <c r="AB246">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AC246">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD246">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AE246">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AF246">
         <v>1.42</v>
@@ -41252,7 +41252,7 @@
         <v>1.06</v>
       </c>
       <c r="X251">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y251">
         <v>1.18</v>
@@ -41895,7 +41895,7 @@
         <v>3.24</v>
       </c>
       <c r="U255">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V255">
         <v>1.5</v>
@@ -43015,7 +43015,7 @@
         </is>
       </c>
       <c r="N262">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O262">
         <v>5.25</v>
@@ -43039,7 +43039,7 @@
         <v>1.91</v>
       </c>
       <c r="V262">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W262">
         <v>1.2</v>
@@ -43350,22 +43350,22 @@
         <v>0</v>
       </c>
       <c r="Q264">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R264">
         <v>2.05</v>
       </c>
       <c r="S264">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T264">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U264">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V264">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W264">
         <v>1.05</v>
@@ -43377,16 +43377,16 @@
         <v>1.33</v>
       </c>
       <c r="Z264">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA264">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AB264">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AC264">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD264">
         <v>1.22</v>
@@ -43398,7 +43398,7 @@
         <v>1.78</v>
       </c>
       <c r="AG264">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43414,7 +43414,7 @@
         <v>1.29</v>
       </c>
       <c r="AK264">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q266">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S266">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T266">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U266">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V266">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W266">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X266">
         <v>0</v>
       </c>
       <c r="Y266">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z266">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA266">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB266">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC266">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD266">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE266">
         <v>0</v>
       </c>
       <c r="AF266">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG266">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK266">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44817,10 +44817,10 @@
         <v>1.59</v>
       </c>
       <c r="Q273">
-        <v>4.37</v>
+        <v>5.5</v>
       </c>
       <c r="R273">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S273">
         <v>1.25</v>
@@ -44856,13 +44856,13 @@
         <v>2.47</v>
       </c>
       <c r="AD273">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE273">
         <v>1.15</v>
       </c>
       <c r="AF273">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG273">
         <v>2.07</v>
@@ -44881,7 +44881,7 @@
         <v>1.17</v>
       </c>
       <c r="AK273">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -45309,7 +45309,7 @@
         <v>2.68</v>
       </c>
       <c r="R276">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S276">
         <v>1.3</v>
@@ -46284,10 +46284,10 @@
         <v>2.3</v>
       </c>
       <c r="Q282">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="R282">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S282">
         <v>1.36</v>
@@ -46296,13 +46296,13 @@
         <v>2.88</v>
       </c>
       <c r="U282">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V282">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W282">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X282">
         <v>1.02</v>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK282">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46936,55 +46936,55 @@
         <v>0</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47099,55 +47099,55 @@
         <v>0</v>
       </c>
       <c r="Q287">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R287">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T287">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U287">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V287">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W287">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X287">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB287">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC287">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD287">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE287">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG287">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK287">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47262,10 +47262,10 @@
         <v>1.9</v>
       </c>
       <c r="Q288">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="R288">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="S288">
         <v>1.22</v>
@@ -47274,10 +47274,10 @@
         <v>3.75</v>
       </c>
       <c r="U288">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V288">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W288">
         <v>1.17</v>
@@ -47289,28 +47289,28 @@
         <v>1.14</v>
       </c>
       <c r="Z288">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA288">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AB288">
         <v>2.53</v>
       </c>
       <c r="AC288">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AD288">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE288">
         <v>1.25</v>
       </c>
       <c r="AF288">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG288">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>1.2</v>
       </c>
       <c r="AK288">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47446,13 +47446,13 @@
         <v>1.11</v>
       </c>
       <c r="X289">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y289">
         <v>1.17</v>
       </c>
       <c r="Z289">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA289">
         <v>1.69</v>
@@ -47473,7 +47473,7 @@
         <v>1.67</v>
       </c>
       <c r="AG289">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="O292">
         <v>3.1</v>
@@ -48566,40 +48566,40 @@
         <v>3.36</v>
       </c>
       <c r="Q296">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R296">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S296">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T296">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U296">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V296">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W296">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X296">
         <v>1</v>
       </c>
       <c r="Y296">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z296">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA296">
         <v>1.76</v>
       </c>
       <c r="AB296">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC296">
         <v>2.7</v>
@@ -48611,10 +48611,10 @@
         <v>1.14</v>
       </c>
       <c r="AF296">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG296">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK296">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P302">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -49707,7 +49707,7 @@
         <v>1.22</v>
       </c>
       <c r="Q303">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="R303">
         <v>2.79</v>
@@ -50854,10 +50854,10 @@
         <v>2.3</v>
       </c>
       <c r="S310">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T310">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="U310">
         <v>2.63</v>
@@ -52330,7 +52330,7 @@
         <v>2.29</v>
       </c>
       <c r="V319">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W319">
         <v>1.14</v>
@@ -52484,10 +52484,10 @@
         <v>2.6</v>
       </c>
       <c r="S320">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T320">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U320">
         <v>2.1</v>
@@ -52508,10 +52508,10 @@
         <v>5.69</v>
       </c>
       <c r="AA320">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB320">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC320">
         <v>2.15</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,64 +53447,64 @@
         </is>
       </c>
       <c r="N326">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="O326">
+        <v>2.75</v>
+      </c>
+      <c r="P326">
+        <v>2.62</v>
+      </c>
+      <c r="Q326">
+        <v>3.74</v>
+      </c>
+      <c r="R326">
+        <v>1.82</v>
+      </c>
+      <c r="S326">
+        <v>1.68</v>
+      </c>
+      <c r="T326">
+        <v>2.13</v>
+      </c>
+      <c r="U326">
+        <v>4.2</v>
+      </c>
+      <c r="V326">
+        <v>1.2</v>
+      </c>
+      <c r="W326">
+        <v>1.03</v>
+      </c>
+      <c r="X326">
+        <v>1.08</v>
+      </c>
+      <c r="Y326">
+        <v>1.63</v>
+      </c>
+      <c r="Z326">
+        <v>2.1</v>
+      </c>
+      <c r="AA326">
         <v>2.87</v>
       </c>
-      <c r="P326">
-        <v>3.1</v>
-      </c>
-      <c r="Q326">
-        <v>3.16</v>
-      </c>
-      <c r="R326">
-        <v>1.86</v>
-      </c>
-      <c r="S326">
-        <v>1.44</v>
-      </c>
-      <c r="T326">
-        <v>2.5</v>
-      </c>
-      <c r="U326">
-        <v>3.15</v>
-      </c>
-      <c r="V326">
-        <v>1.3</v>
-      </c>
-      <c r="W326">
-        <v>1.05</v>
-      </c>
-      <c r="X326">
-        <v>1.06</v>
-      </c>
-      <c r="Y326">
-        <v>1.46</v>
-      </c>
-      <c r="Z326">
-        <v>2.46</v>
-      </c>
-      <c r="AA326">
-        <v>2.7</v>
-      </c>
       <c r="AB326">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AC326">
-        <v>4.5</v>
+        <v>6.24</v>
       </c>
       <c r="AD326">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE326">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF326">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AG326">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>1.4</v>
       </c>
       <c r="AK326">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="O327">
         <v>2.75</v>
       </c>
       <c r="P327">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="Q327">
-        <v>3.74</v>
+        <v>2.84</v>
       </c>
       <c r="R327">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="S327">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="T327">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="U327">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="V327">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W327">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X327">
         <v>1.08</v>
       </c>
       <c r="Y327">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z327">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA327">
         <v>2.87</v>
       </c>
       <c r="AB327">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC327">
-        <v>6.24</v>
+        <v>5.55</v>
       </c>
       <c r="AD327">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE327">
         <v>1.03</v>
       </c>
       <c r="AF327">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG327">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AK327">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G328">
@@ -53773,64 +53773,64 @@
         </is>
       </c>
       <c r="N328">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O328">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="P328">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q328">
-        <v>2.84</v>
+        <v>3.16</v>
       </c>
       <c r="R328">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="S328">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="T328">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U328">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="V328">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W328">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X328">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y328">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="Z328">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AA328">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB328">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AC328">
-        <v>5.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD328">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE328">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF328">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AG328">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -53843,10 +53843,10 @@
         </is>
       </c>
       <c r="AJ328">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK328">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O330">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P330">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q330">
         <v>0</v>
@@ -54914,13 +54914,13 @@
         </is>
       </c>
       <c r="N335">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O335">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P335">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q335">
         <v>2</v>
@@ -56085,7 +56085,7 @@
         <v>1.14</v>
       </c>
       <c r="X342">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y342">
         <v>1.13</v>
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O352">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="P352">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q352">
         <v>2.79</v>
@@ -57887,7 +57887,7 @@
         <v>3.42</v>
       </c>
       <c r="AA353">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB353">
         <v>1.87</v>
@@ -58050,7 +58050,7 @@
         <v>3.84</v>
       </c>
       <c r="AA354">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB354">
         <v>2.1</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -638,7 +638,7 @@
         <v>2.4</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
         <v>2.87</v>
@@ -1296,7 +1296,7 @@
         <v>2.6</v>
       </c>
       <c r="Q6">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="R6">
         <v>2.06</v>
@@ -1326,7 +1326,7 @@
         <v>3.43</v>
       </c>
       <c r="AA6">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
         <v>1.83</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="O7">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="Q7">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
         <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="V7">
         <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
+        <v>1.3</v>
+      </c>
+      <c r="Z7">
+        <v>3.32</v>
+      </c>
+      <c r="AA7">
+        <v>2.01</v>
+      </c>
+      <c r="AB7">
+        <v>1.78</v>
+      </c>
+      <c r="AC7">
+        <v>3.4</v>
+      </c>
+      <c r="AD7">
         <v>1.29</v>
       </c>
-      <c r="Z7">
-        <v>3.41</v>
-      </c>
-      <c r="AA7">
-        <v>1.99</v>
-      </c>
-      <c r="AB7">
-        <v>1.83</v>
-      </c>
-      <c r="AC7">
-        <v>3.35</v>
-      </c>
-      <c r="AD7">
-        <v>1.3</v>
-      </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>1.55</v>
+        <v>2.17</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P8">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="R8">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
         <v>2.9</v>
       </c>
       <c r="U8">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
         <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z8">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="AA8">
         <v>2.01</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AK8">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>1.17</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
         <v>1.11</v>
@@ -1815,10 +1815,10 @@
         <v>4.8</v>
       </c>
       <c r="AA9">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB9">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AC9">
         <v>2.28</v>
@@ -1827,7 +1827,7 @@
         <v>1.5</v>
       </c>
       <c r="AE9">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
         <v>1.46</v>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O10">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q10">
         <v>3.28</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S10">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="T10">
         <v>2.5</v>
       </c>
       <c r="U10">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V10">
         <v>1.3</v>
@@ -1969,28 +1969,28 @@
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z10">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="AA10">
         <v>2.4</v>
       </c>
       <c r="AB10">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AC10">
-        <v>4.63</v>
+        <v>4.53</v>
       </c>
       <c r="AD10">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF10">
         <v>1.95</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AK10">
         <v>1.39</v>
@@ -2132,7 +2132,7 @@
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.22</v>
@@ -2431,28 +2431,28 @@
         <v>1.33</v>
       </c>
       <c r="O13">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="P13">
         <v>6.8</v>
       </c>
       <c r="Q13">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="S13">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T13">
         <v>4</v>
       </c>
       <c r="U13">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V13">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W13">
         <v>1.18</v>
@@ -2464,28 +2464,28 @@
         <v>1.09</v>
       </c>
       <c r="Z13">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AC13">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AD13">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2597,22 +2597,22 @@
         <v>3.5</v>
       </c>
       <c r="P14">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q14">
         <v>3.75</v>
       </c>
       <c r="R14">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
         <v>3.2</v>
       </c>
       <c r="U14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V14">
         <v>1.44</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O15">
         <v>3.5</v>
       </c>
       <c r="P15">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q15">
         <v>5.39</v>
@@ -2769,10 +2769,10 @@
         <v>2.06</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
         <v>2.9</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O16">
         <v>3.57</v>
       </c>
       <c r="P16">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="Q16">
         <v>2.36</v>
@@ -3083,7 +3083,7 @@
         <v>2.5</v>
       </c>
       <c r="O17">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="P17">
         <v>2.3</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="O23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q23">
         <v>3.52</v>
@@ -4073,7 +4073,7 @@
         <v>2.13</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
         <v>3.07</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
         <v>3.5</v>
       </c>
       <c r="P24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q24">
         <v>2.3</v>
@@ -4242,7 +4242,7 @@
         <v>3</v>
       </c>
       <c r="U24">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="V24">
         <v>1.4</v>
@@ -4251,34 +4251,34 @@
         <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z24">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA24">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC24">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="AD24">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>3.8</v>
       </c>
       <c r="O27">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="P27">
         <v>1.8</v>
@@ -4731,10 +4731,10 @@
         <v>4.3</v>
       </c>
       <c r="U27">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="V27">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W27">
         <v>1.18</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q28">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R28">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
         <v>1.27</v>
       </c>
       <c r="T28">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
         <v>2.38</v>
@@ -4906,10 +4906,10 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="AA28">
         <v>1.65</v>
@@ -4918,19 +4918,19 @@
         <v>2.2</v>
       </c>
       <c r="AC28">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="AD28">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
         <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6560,7 +6560,7 @@
         <v>1.74</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.32</v>
       </c>
       <c r="AK38">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6847,10 +6847,10 @@
         <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="V40">
         <v>1.33</v>
@@ -6880,7 +6880,7 @@
         <v>1.2</v>
       </c>
       <c r="AE40">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
         <v>1.85</v>
@@ -7357,10 +7357,10 @@
         <v>2.97</v>
       </c>
       <c r="AA43">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB43">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC43">
         <v>3.58</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q44">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB44">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC44">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7849,7 +7849,7 @@
         <v>1.6</v>
       </c>
       <c r="AB46">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC46">
         <v>2.36</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="O51">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="Q51">
         <v>2.39</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O53">
         <v>4.25</v>
       </c>
       <c r="P53">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q53">
         <v>2.05</v>
       </c>
       <c r="R53">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="S53">
         <v>1.17</v>
@@ -8969,10 +8969,10 @@
         <v>3.54</v>
       </c>
       <c r="U53">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V53">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W53">
         <v>1.17</v>
@@ -10261,22 +10261,22 @@
         <v>1.95</v>
       </c>
       <c r="Q61">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S61">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T61">
+        <v>2.61</v>
+      </c>
+      <c r="U61">
         <v>2.88</v>
       </c>
-      <c r="U61">
-        <v>2.85</v>
-      </c>
       <c r="V61">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W61">
         <v>1.07</v>
@@ -10424,7 +10424,7 @@
         <v>2.91</v>
       </c>
       <c r="Q62">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R62">
         <v>2.12</v>
@@ -10448,7 +10448,7 @@
         <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z62">
         <v>2.85</v>
@@ -10581,7 +10581,7 @@
         <v>3.1</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P63">
         <v>2</v>
@@ -10617,10 +10617,10 @@
         <v>3.42</v>
       </c>
       <c r="AA63">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB63">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC63">
         <v>3.04</v>
@@ -10783,7 +10783,7 @@
         <v>1.6</v>
       </c>
       <c r="AB64">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
         <v>2.61</v>
@@ -11260,7 +11260,7 @@
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
         <v>1.25</v>
@@ -11269,10 +11269,10 @@
         <v>3.61</v>
       </c>
       <c r="AA67">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC67">
         <v>3.17</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="O69">
         <v>3.4</v>
       </c>
       <c r="P69">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -11577,7 +11577,7 @@
         <v>3</v>
       </c>
       <c r="U69">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="V69">
         <v>1.4</v>
@@ -11604,7 +11604,7 @@
         <v>3.05</v>
       </c>
       <c r="AD69">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE69">
         <v>1.07</v>
@@ -11761,19 +11761,19 @@
         <v>1.28</v>
       </c>
       <c r="AB70">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="AC70">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD70">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AE70">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AF70">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG70">
         <v>2.69</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK70">
         <v>2.54</v>
@@ -11888,16 +11888,16 @@
         <v>3.6</v>
       </c>
       <c r="P71">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q71">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R71">
         <v>2.15</v>
       </c>
       <c r="S71">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T71">
         <v>2.74</v>
@@ -12374,10 +12374,10 @@
         <v>2.9</v>
       </c>
       <c r="O74">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="P74">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q74">
         <v>3.5</v>
@@ -12401,7 +12401,7 @@
         <v>1.12</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
         <v>1.17</v>
@@ -12537,7 +12537,7 @@
         <v>1.84</v>
       </c>
       <c r="O75">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P75">
         <v>3.21</v>
@@ -12866,10 +12866,10 @@
         <v>4.05</v>
       </c>
       <c r="P77">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="Q77">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="R77">
         <v>2.4</v>
@@ -12887,7 +12887,7 @@
         <v>1.6</v>
       </c>
       <c r="W77">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X77">
         <v>1.01</v>
@@ -12899,7 +12899,7 @@
         <v>5</v>
       </c>
       <c r="AA77">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AB77">
         <v>2.29</v>
@@ -12911,7 +12911,7 @@
         <v>1.54</v>
       </c>
       <c r="AE77">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF77">
         <v>1.53</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
         <v>1.86</v>
@@ -13032,71 +13032,71 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>3.48</v>
+        <v>3.83</v>
       </c>
       <c r="R78">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="S78">
         <v>1.25</v>
       </c>
       <c r="T78">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U78">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="V78">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W78">
         <v>1.15</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
+        <v>1.13</v>
+      </c>
+      <c r="Z78">
+        <v>5.25</v>
+      </c>
+      <c r="AA78">
+        <v>1.5</v>
+      </c>
+      <c r="AB78">
+        <v>2.36</v>
+      </c>
+      <c r="AC78">
+        <v>2.2</v>
+      </c>
+      <c r="AD78">
+        <v>1.63</v>
+      </c>
+      <c r="AE78">
+        <v>1.25</v>
+      </c>
+      <c r="AF78">
+        <v>1.62</v>
+      </c>
+      <c r="AG78">
+        <v>2.2</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.2</v>
+      </c>
+      <c r="AK78">
         <v>1.14</v>
-      </c>
-      <c r="Z78">
-        <v>5</v>
-      </c>
-      <c r="AA78">
-        <v>1.54</v>
-      </c>
-      <c r="AB78">
-        <v>2.27</v>
-      </c>
-      <c r="AC78">
-        <v>2.33</v>
-      </c>
-      <c r="AD78">
-        <v>1.6</v>
-      </c>
-      <c r="AE78">
-        <v>1.23</v>
-      </c>
-      <c r="AF78">
-        <v>1.55</v>
-      </c>
-      <c r="AG78">
-        <v>2.3</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.1</v>
-      </c>
-      <c r="AK78">
-        <v>1.2</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="O82">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P82">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q82">
         <v>2.15</v>
@@ -13723,7 +13723,7 @@
         <v>1.74</v>
       </c>
       <c r="AD82">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AE82">
         <v>1.44</v>
@@ -14237,7 +14237,7 @@
         <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14499,25 +14499,25 @@
         <v>2.37</v>
       </c>
       <c r="Q87">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="R87">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T87">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U87">
         <v>2.1</v>
       </c>
       <c r="V87">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="O88">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q88">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="R88">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S88">
+        <v>1.18</v>
+      </c>
+      <c r="T88">
+        <v>3.85</v>
+      </c>
+      <c r="U88">
+        <v>2.25</v>
+      </c>
+      <c r="V88">
+        <v>1.57</v>
+      </c>
+      <c r="W88">
+        <v>1.14</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.1</v>
+      </c>
+      <c r="Z88">
+        <v>5.2</v>
+      </c>
+      <c r="AA88">
+        <v>1.44</v>
+      </c>
+      <c r="AB88">
+        <v>2.43</v>
+      </c>
+      <c r="AC88">
+        <v>2.18</v>
+      </c>
+      <c r="AD88">
+        <v>1.58</v>
+      </c>
+      <c r="AE88">
         <v>1.2</v>
       </c>
-      <c r="T88">
-        <v>4</v>
-      </c>
-      <c r="U88">
-        <v>2.1</v>
-      </c>
-      <c r="V88">
-        <v>1.67</v>
-      </c>
-      <c r="W88">
-        <v>1.17</v>
-      </c>
-      <c r="X88">
-        <v>1.02</v>
-      </c>
-      <c r="Y88">
-        <v>1.08</v>
-      </c>
-      <c r="Z88">
-        <v>5.45</v>
-      </c>
-      <c r="AA88">
-        <v>1.47</v>
-      </c>
-      <c r="AB88">
-        <v>2.6</v>
-      </c>
-      <c r="AC88">
-        <v>2.08</v>
-      </c>
-      <c r="AD88">
-        <v>1.64</v>
-      </c>
-      <c r="AE88">
-        <v>1.23</v>
-      </c>
       <c r="AF88">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AG88">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="O89">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="Q89">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T89">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="U89">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V89">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z89">
-        <v>4.15</v>
+        <v>5.45</v>
       </c>
       <c r="AA89">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AB89">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AC89">
-        <v>2.43</v>
+        <v>2.08</v>
       </c>
       <c r="AD89">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AE89">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF89">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AG89">
-        <v>2.36</v>
+        <v>2.73</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK89">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O90">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P90">
         <v>2.8</v>
       </c>
       <c r="Q90">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R90">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S90">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U90">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V90">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z90">
-        <v>5.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA90">
+        <v>1.6</v>
+      </c>
+      <c r="AB90">
+        <v>2.15</v>
+      </c>
+      <c r="AC90">
+        <v>2.43</v>
+      </c>
+      <c r="AD90">
         <v>1.44</v>
       </c>
-      <c r="AB90">
-        <v>2.35</v>
-      </c>
-      <c r="AC90">
-        <v>2.18</v>
-      </c>
-      <c r="AD90">
-        <v>1.58</v>
-      </c>
       <c r="AE90">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF90">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AG90">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK90">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15148,13 +15148,13 @@
         <v>3.6</v>
       </c>
       <c r="P91">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q91">
         <v>2.5</v>
       </c>
       <c r="R91">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S91">
         <v>1.25</v>
@@ -15163,13 +15163,13 @@
         <v>3.4</v>
       </c>
       <c r="U91">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V91">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W91">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -15199,7 +15199,7 @@
         <v>1.52</v>
       </c>
       <c r="AG91">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK91">
         <v>1.62</v>
@@ -15815,10 +15815,10 @@
         <v>3.3</v>
       </c>
       <c r="U95">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V95">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W95">
         <v>1.08</v>
@@ -15827,31 +15827,31 @@
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z95">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="AA95">
         <v>1.73</v>
       </c>
       <c r="AB95">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC95">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AD95">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE95">
         <v>1.1</v>
       </c>
       <c r="AF95">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG95">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O99">
         <v>3.1</v>
@@ -16944,55 +16944,55 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T102">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U102">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V102">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W102">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X102">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z102">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC102">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD102">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG102">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK102">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17445,10 +17445,10 @@
         <v>3.25</v>
       </c>
       <c r="U105">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="V105">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W105">
         <v>1.12</v>
@@ -17934,10 +17934,10 @@
         <v>3.48</v>
       </c>
       <c r="U108">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="V108">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W108">
         <v>1.11</v>
@@ -17952,7 +17952,7 @@
         <v>4.75</v>
       </c>
       <c r="AA108">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB108">
         <v>2.35</v>
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O110">
         <v>3.05</v>
@@ -18405,7 +18405,7 @@
         <v>3.35</v>
       </c>
       <c r="O111">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="P111">
         <v>1.91</v>
@@ -18734,7 +18734,7 @@
         <v>3.2</v>
       </c>
       <c r="P113">
-        <v>3.35</v>
+        <v>4.08</v>
       </c>
       <c r="Q113">
         <v>2.67</v>
@@ -18749,13 +18749,13 @@
         <v>2.58</v>
       </c>
       <c r="U113">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="V113">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W113">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X113">
         <v>1.03</v>
@@ -18779,13 +18779,13 @@
         <v>1.2</v>
       </c>
       <c r="AE113">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF113">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG113">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK113">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="O115">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="Q115">
-        <v>4.37</v>
+        <v>4.01</v>
       </c>
       <c r="R115">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="S115">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T115">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U115">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="V115">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z115">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA115">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AB115">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC115">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="AD115">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE115">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG115">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>1.25</v>
       </c>
       <c r="AK115">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q116">
-        <v>4.01</v>
+        <v>4.51</v>
       </c>
       <c r="R116">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S116">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T116">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U116">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="V116">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W116">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z116">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA116">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB116">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC116">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AD116">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE116">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG116">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="O118">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="P118">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q118">
-        <v>2.43</v>
+        <v>2.87</v>
       </c>
       <c r="R118">
+        <v>1.94</v>
+      </c>
+      <c r="S118">
+        <v>1.45</v>
+      </c>
+      <c r="T118">
+        <v>2.75</v>
+      </c>
+      <c r="U118">
+        <v>2.87</v>
+      </c>
+      <c r="V118">
+        <v>1.35</v>
+      </c>
+      <c r="W118">
+        <v>1.05</v>
+      </c>
+      <c r="X118">
+        <v>1.03</v>
+      </c>
+      <c r="Y118">
+        <v>1.36</v>
+      </c>
+      <c r="Z118">
+        <v>2.9</v>
+      </c>
+      <c r="AA118">
         <v>2.15</v>
       </c>
-      <c r="S118">
-        <v>1.36</v>
-      </c>
-      <c r="T118">
-        <v>3.03</v>
-      </c>
-      <c r="U118">
-        <v>2.75</v>
-      </c>
-      <c r="V118">
-        <v>1.4</v>
-      </c>
-      <c r="W118">
-        <v>1.07</v>
-      </c>
-      <c r="X118">
-        <v>1</v>
-      </c>
-      <c r="Y118">
-        <v>1.22</v>
-      </c>
-      <c r="Z118">
-        <v>3.5</v>
-      </c>
-      <c r="AA118">
-        <v>1.94</v>
-      </c>
       <c r="AB118">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AC118">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="AD118">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE118">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF118">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG118">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="O119">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P119">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="Q119">
-        <v>2.87</v>
+        <v>2.43</v>
       </c>
       <c r="R119">
+        <v>2.15</v>
+      </c>
+      <c r="S119">
+        <v>1.36</v>
+      </c>
+      <c r="T119">
+        <v>3.03</v>
+      </c>
+      <c r="U119">
+        <v>2.75</v>
+      </c>
+      <c r="V119">
+        <v>1.4</v>
+      </c>
+      <c r="W119">
+        <v>1.07</v>
+      </c>
+      <c r="X119">
+        <v>1</v>
+      </c>
+      <c r="Y119">
+        <v>1.22</v>
+      </c>
+      <c r="Z119">
+        <v>3.5</v>
+      </c>
+      <c r="AA119">
         <v>1.94</v>
       </c>
-      <c r="S119">
-        <v>1.45</v>
-      </c>
-      <c r="T119">
-        <v>2.75</v>
-      </c>
-      <c r="U119">
-        <v>2.87</v>
-      </c>
-      <c r="V119">
-        <v>1.35</v>
-      </c>
-      <c r="W119">
-        <v>1.05</v>
-      </c>
-      <c r="X119">
-        <v>1.03</v>
-      </c>
-      <c r="Y119">
-        <v>1.36</v>
-      </c>
-      <c r="Z119">
-        <v>2.9</v>
-      </c>
-      <c r="AA119">
-        <v>2.15</v>
-      </c>
       <c r="AB119">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AC119">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="AD119">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF119">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG119">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK119">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20252,7 +20252,7 @@
         <v>1.66</v>
       </c>
       <c r="AG122">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>3.5</v>
       </c>
       <c r="P123">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q123">
         <v>2.34</v>
@@ -20530,55 +20530,55 @@
         <v>0</v>
       </c>
       <c r="Q124">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R124">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S124">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T124">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U124">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V124">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W124">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X124">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y124">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z124">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AA124">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB124">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC124">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD124">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE124">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF124">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG124">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK124">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK130">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O133">
         <v>3.3</v>
       </c>
       <c r="P133">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="Q133">
         <v>3.74</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O134">
         <v>3.5</v>
       </c>
       <c r="P134">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="Q134">
         <v>3</v>
@@ -22812,7 +22812,7 @@
         <v>2.62</v>
       </c>
       <c r="Q138">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R138">
         <v>2.3</v>
@@ -22827,7 +22827,7 @@
         <v>2.5</v>
       </c>
       <c r="V138">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W138">
         <v>1.09</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O139">
         <v>3.1</v>
       </c>
       <c r="P139">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q139">
         <v>2.88</v>
@@ -23005,10 +23005,10 @@
         <v>3.1</v>
       </c>
       <c r="AA139">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB139">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC139">
         <v>3.48</v>
@@ -25094,10 +25094,10 @@
         <v>2.75</v>
       </c>
       <c r="Q152">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R152">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S152">
         <v>1.4</v>
@@ -25112,10 +25112,10 @@
         <v>1.3</v>
       </c>
       <c r="W152">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X152">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y152">
         <v>1.35</v>
@@ -25127,7 +25127,7 @@
         <v>2.18</v>
       </c>
       <c r="AB152">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC152">
         <v>4.15</v>
@@ -25136,7 +25136,7 @@
         <v>1.16</v>
       </c>
       <c r="AE152">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF152">
         <v>1.87</v>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK152">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25254,7 +25254,7 @@
         <v>3.12</v>
       </c>
       <c r="P153">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25420,13 +25420,13 @@
         <v>3.55</v>
       </c>
       <c r="Q154">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R154">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S154">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T154">
         <v>2.69</v>
@@ -25462,13 +25462,13 @@
         <v>1.21</v>
       </c>
       <c r="AE154">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF154">
         <v>1.84</v>
       </c>
       <c r="AG154">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK154">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25583,10 +25583,10 @@
         <v>4</v>
       </c>
       <c r="Q155">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R155">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="S155">
         <v>1.25</v>
@@ -25746,10 +25746,10 @@
         <v>2.41</v>
       </c>
       <c r="Q156">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="R156">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="S156">
         <v>1.2</v>
@@ -25782,10 +25782,10 @@
         <v>2.68</v>
       </c>
       <c r="AC156">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD156">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE156">
         <v>1.27</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O157">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="P157">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="Q157">
-        <v>5.24</v>
+        <v>3.04</v>
       </c>
       <c r="R157">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="S157">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T157">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U157">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="V157">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W157">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X157">
         <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Z157">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA157">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AB157">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AC157">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="AD157">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AE157">
+        <v>1.2</v>
+      </c>
+      <c r="AF157">
+        <v>1.47</v>
+      </c>
+      <c r="AG157">
+        <v>2.39</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>1.23</v>
       </c>
-      <c r="AF157">
-        <v>1.51</v>
-      </c>
-      <c r="AG157">
-        <v>2.4</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.22</v>
-      </c>
       <c r="AK157">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.87</v>
+        <v>3.18</v>
       </c>
       <c r="O158">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P158">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q158">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="R158">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="S158">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T158">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="U158">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="V158">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="W158">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X158">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z158">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA158">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AB158">
-        <v>2.19</v>
+        <v>2.93</v>
       </c>
       <c r="AC158">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AD158">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="AE158">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AF158">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AG158">
-        <v>2.39</v>
+        <v>2.93</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AK158">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="O159">
+        <v>4.35</v>
+      </c>
+      <c r="P159">
+        <v>1.61</v>
+      </c>
+      <c r="Q159">
+        <v>5.2</v>
+      </c>
+      <c r="R159">
+        <v>2.51</v>
+      </c>
+      <c r="S159">
+        <v>1.23</v>
+      </c>
+      <c r="T159">
         <v>4</v>
       </c>
-      <c r="P159">
-        <v>1.8</v>
-      </c>
-      <c r="Q159">
-        <v>4.1</v>
-      </c>
-      <c r="R159">
-        <v>2.41</v>
-      </c>
-      <c r="S159">
+      <c r="U159">
+        <v>2.05</v>
+      </c>
+      <c r="V159">
+        <v>1.7</v>
+      </c>
+      <c r="W159">
+        <v>1.15</v>
+      </c>
+      <c r="X159">
+        <v>1.01</v>
+      </c>
+      <c r="Y159">
+        <v>1.09</v>
+      </c>
+      <c r="Z159">
+        <v>5.3</v>
+      </c>
+      <c r="AA159">
+        <v>1.44</v>
+      </c>
+      <c r="AB159">
+        <v>2.7</v>
+      </c>
+      <c r="AC159">
+        <v>2.32</v>
+      </c>
+      <c r="AD159">
+        <v>1.71</v>
+      </c>
+      <c r="AE159">
+        <v>1.23</v>
+      </c>
+      <c r="AF159">
+        <v>1.51</v>
+      </c>
+      <c r="AG159">
+        <v>2.4</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.22</v>
       </c>
-      <c r="T159">
-        <v>3.94</v>
-      </c>
-      <c r="U159">
-        <v>2.01</v>
-      </c>
-      <c r="V159">
-        <v>1.81</v>
-      </c>
-      <c r="W159">
-        <v>1.2</v>
-      </c>
-      <c r="X159">
-        <v>1.02</v>
-      </c>
-      <c r="Y159">
-        <v>1.05</v>
-      </c>
-      <c r="Z159">
-        <v>6.4</v>
-      </c>
-      <c r="AA159">
-        <v>1.34</v>
-      </c>
-      <c r="AB159">
-        <v>2.93</v>
-      </c>
-      <c r="AC159">
-        <v>1.98</v>
-      </c>
-      <c r="AD159">
-        <v>1.96</v>
-      </c>
-      <c r="AE159">
-        <v>1.34</v>
-      </c>
-      <c r="AF159">
-        <v>1.35</v>
-      </c>
-      <c r="AG159">
-        <v>2.93</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>2</v>
-      </c>
       <c r="AK159">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26434,7 +26434,7 @@
         <v>2.13</v>
       </c>
       <c r="AC160">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AD160">
         <v>1.39</v>
@@ -26606,10 +26606,10 @@
         <v>1.2</v>
       </c>
       <c r="AF161">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG161">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26724,10 +26724,10 @@
         <v>10</v>
       </c>
       <c r="Q162">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R162">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="S162">
         <v>1.18</v>
@@ -26736,10 +26736,10 @@
         <v>4.6</v>
       </c>
       <c r="U162">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="V162">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W162">
         <v>1.22</v>
@@ -26760,19 +26760,19 @@
         <v>3.1</v>
       </c>
       <c r="AC162">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD162">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AE162">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF162">
         <v>1.75</v>
       </c>
       <c r="AG162">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="O175">
         <v>3.7</v>
       </c>
       <c r="P175">
-        <v>2.05</v>
+        <v>3.55</v>
       </c>
       <c r="Q175">
-        <v>3.7</v>
+        <v>2.36</v>
       </c>
       <c r="R175">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S175">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T175">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="U175">
-        <v>2.54</v>
+        <v>2.77</v>
       </c>
       <c r="V175">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="W175">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X175">
         <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z175">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="AA175">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AB175">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AC175">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD175">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE175">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF175">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AG175">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.28</v>
+        <v>1.88</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="O176">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P176">
-        <v>2.31</v>
+        <v>2.87</v>
       </c>
       <c r="Q176">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="R176">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="S176">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T176">
-        <v>3.46</v>
+        <v>2.97</v>
       </c>
       <c r="U176">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="V176">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W176">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X176">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z176">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA176">
-        <v>1.61</v>
+        <v>1.94</v>
       </c>
       <c r="AB176">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="AC176">
-        <v>2.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD176">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AE176">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF176">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AG176">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK176">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="O178">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P178">
-        <v>3.55</v>
+        <v>2.31</v>
       </c>
       <c r="Q178">
-        <v>2.36</v>
+        <v>3.12</v>
       </c>
       <c r="R178">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S178">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T178">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
       <c r="U178">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="V178">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W178">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X178">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z178">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA178">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AB178">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="AC178">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="AD178">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE178">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF178">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AG178">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK178">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="O179">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="P179">
-        <v>2.87</v>
+        <v>6.2</v>
       </c>
       <c r="Q179">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="R179">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="S179">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T179">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="U179">
-        <v>2.98</v>
+        <v>2.09</v>
       </c>
       <c r="V179">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="W179">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X179">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="Z179">
-        <v>3.14</v>
+        <v>6.12</v>
       </c>
       <c r="AA179">
-        <v>1.94</v>
+        <v>1.43</v>
       </c>
       <c r="AB179">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="AC179">
-        <v>3.34</v>
+        <v>2.06</v>
       </c>
       <c r="AD179">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="AE179">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AF179">
         <v>1.6</v>
       </c>
       <c r="AG179">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK179">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,80 +29649,80 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.35</v>
+        <v>3.5</v>
       </c>
       <c r="O180">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="P180">
-        <v>6.2</v>
+        <v>1.95</v>
       </c>
       <c r="Q180">
-        <v>1.75</v>
+        <v>4.11</v>
       </c>
       <c r="R180">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="S180">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T180">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="U180">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="V180">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="W180">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X180">
         <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z180">
-        <v>6.12</v>
+        <v>4.25</v>
       </c>
       <c r="AA180">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AB180">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="AC180">
-        <v>2.06</v>
+        <v>2.62</v>
       </c>
       <c r="AD180">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AE180">
+        <v>1.15</v>
+      </c>
+      <c r="AF180">
+        <v>1.61</v>
+      </c>
+      <c r="AG180">
+        <v>2.15</v>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ180">
+        <v>1.24</v>
+      </c>
+      <c r="AK180">
         <v>1.25</v>
-      </c>
-      <c r="AF180">
-        <v>1.6</v>
-      </c>
-      <c r="AG180">
-        <v>2.14</v>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ180">
-        <v>1.13</v>
-      </c>
-      <c r="AK180">
-        <v>3</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O181">
         <v>3.7</v>
       </c>
       <c r="P181">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q181">
-        <v>4.11</v>
+        <v>3.7</v>
       </c>
       <c r="R181">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S181">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T181">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U181">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="V181">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W181">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X181">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y181">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z181">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="AA181">
         <v>1.68</v>
       </c>
       <c r="AB181">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC181">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD181">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE181">
         <v>1.15</v>
       </c>
       <c r="AF181">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG181">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK181">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30636,7 +30636,7 @@
         <v>3.1</v>
       </c>
       <c r="Q186">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="R186">
         <v>2.07</v>
@@ -30700,7 +30700,7 @@
         <v>1.3</v>
       </c>
       <c r="AK186">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30790,16 +30790,16 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="O187">
         <v>3.6</v>
       </c>
       <c r="P187">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="Q187">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="R187">
         <v>2.8</v>
@@ -30808,7 +30808,7 @@
         <v>1.11</v>
       </c>
       <c r="T187">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="U187">
         <v>1.94</v>
@@ -30863,7 +30863,7 @@
         <v>1.16</v>
       </c>
       <c r="AK187">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30974,10 +30974,10 @@
         <v>6.1</v>
       </c>
       <c r="U188">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V188">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="W188">
         <v>1.36</v>
@@ -31279,19 +31279,19 @@
         </is>
       </c>
       <c r="N190">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O190">
         <v>3.75</v>
       </c>
       <c r="P190">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="Q190">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="R190">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="S190">
         <v>1.1</v>
@@ -31327,10 +31327,10 @@
         <v>1.62</v>
       </c>
       <c r="AD190">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AE190">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF190">
         <v>1.22</v>
@@ -31445,10 +31445,10 @@
         <v>1.7</v>
       </c>
       <c r="O191">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P191">
-        <v>4.51</v>
+        <v>4.8</v>
       </c>
       <c r="Q191">
         <v>2.23</v>
@@ -31457,19 +31457,19 @@
         <v>2.22</v>
       </c>
       <c r="S191">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T191">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="U191">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V191">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W191">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X191">
         <v>1.01</v>
@@ -31478,7 +31478,7 @@
         <v>1.22</v>
       </c>
       <c r="Z191">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA191">
         <v>1.8</v>
@@ -31499,7 +31499,7 @@
         <v>1.75</v>
       </c>
       <c r="AG191">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O192">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P192">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q192">
         <v>3.18</v>
@@ -31629,7 +31629,7 @@
         <v>2.75</v>
       </c>
       <c r="V192">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W192">
         <v>1.05</v>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK192">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31771,10 +31771,10 @@
         <v>1.68</v>
       </c>
       <c r="O193">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P193">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q193">
         <v>2.2</v>
@@ -31810,7 +31810,7 @@
         <v>1.59</v>
       </c>
       <c r="AB193">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC193">
         <v>2.41</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="O194">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P194">
-        <v>3.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q194">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="R194">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S194">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T194">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="U194">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="V194">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W194">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z194">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA194">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AB194">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AC194">
-        <v>2.97</v>
+        <v>2.52</v>
       </c>
       <c r="AD194">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE194">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF194">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AG194">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK194">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="O195">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P195">
-        <v>2.37</v>
+        <v>3.95</v>
       </c>
       <c r="Q195">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="R195">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S195">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T195">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="U195">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="V195">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W195">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X195">
         <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z195">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA195">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AB195">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AC195">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="AD195">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE195">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF195">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AG195">
-        <v>2.37</v>
+        <v>1.88</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK195">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="O196">
-        <v>3.54</v>
+        <v>5</v>
       </c>
       <c r="P196">
-        <v>3.95</v>
+        <v>6.5</v>
       </c>
       <c r="Q196">
-        <v>2.46</v>
+        <v>1.85</v>
       </c>
       <c r="R196">
+        <v>2.63</v>
+      </c>
+      <c r="S196">
+        <v>1.2</v>
+      </c>
+      <c r="T196">
+        <v>4</v>
+      </c>
+      <c r="U196">
         <v>2.1</v>
       </c>
-      <c r="S196">
-        <v>1.38</v>
-      </c>
-      <c r="T196">
-        <v>2.74</v>
-      </c>
-      <c r="U196">
-        <v>2.88</v>
-      </c>
       <c r="V196">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="W196">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="X196">
         <v>1.02</v>
       </c>
       <c r="Y196">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="Z196">
-        <v>3.14</v>
+        <v>5.2</v>
       </c>
       <c r="AA196">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AB196">
-        <v>1.72</v>
+        <v>2.56</v>
       </c>
       <c r="AC196">
-        <v>3.42</v>
+        <v>2.11</v>
       </c>
       <c r="AD196">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="AE196">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AF196">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AG196">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK196">
-        <v>1.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,10 +32420,10 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O197">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P197">
         <v>3.5</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,80 +32583,80 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="O198">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P198">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q198">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="R198">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="S198">
+        <v>1.31</v>
+      </c>
+      <c r="T198">
+        <v>3.08</v>
+      </c>
+      <c r="U198">
+        <v>2.57</v>
+      </c>
+      <c r="V198">
+        <v>1.43</v>
+      </c>
+      <c r="W198">
+        <v>1.07</v>
+      </c>
+      <c r="X198">
+        <v>1.01</v>
+      </c>
+      <c r="Y198">
         <v>1.22</v>
       </c>
-      <c r="T198">
-        <v>4.1</v>
-      </c>
-      <c r="U198">
-        <v>2.1</v>
-      </c>
-      <c r="V198">
+      <c r="Z198">
+        <v>3.5</v>
+      </c>
+      <c r="AA198">
+        <v>1.9</v>
+      </c>
+      <c r="AB198">
+        <v>1.91</v>
+      </c>
+      <c r="AC198">
+        <v>2.97</v>
+      </c>
+      <c r="AD198">
+        <v>1.3</v>
+      </c>
+      <c r="AE198">
+        <v>1.07</v>
+      </c>
+      <c r="AF198">
+        <v>1.66</v>
+      </c>
+      <c r="AG198">
+        <v>2.09</v>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ198">
+        <v>1.28</v>
+      </c>
+      <c r="AK198">
         <v>1.67</v>
-      </c>
-      <c r="W198">
-        <v>1.15</v>
-      </c>
-      <c r="X198">
-        <v>1.02</v>
-      </c>
-      <c r="Y198">
-        <v>1.1</v>
-      </c>
-      <c r="Z198">
-        <v>5.2</v>
-      </c>
-      <c r="AA198">
-        <v>1.44</v>
-      </c>
-      <c r="AB198">
-        <v>2.56</v>
-      </c>
-      <c r="AC198">
-        <v>2.11</v>
-      </c>
-      <c r="AD198">
-        <v>1.68</v>
-      </c>
-      <c r="AE198">
-        <v>1.25</v>
-      </c>
-      <c r="AF198">
-        <v>1.6</v>
-      </c>
-      <c r="AG198">
-        <v>2.19</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ198">
-        <v>1.15</v>
-      </c>
-      <c r="AK198">
-        <v>2.78</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="O201">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P201">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="Q201">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="R201">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S201">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T201">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U201">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="V201">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W201">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X201">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y201">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z201">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AA201">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB201">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AC201">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD201">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE201">
         <v>1.1</v>
       </c>
       <c r="AF201">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG201">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK201">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="O202">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P202">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="Q202">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="R202">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S202">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T202">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U202">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="V202">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W202">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X202">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y202">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z202">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA202">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB202">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC202">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD202">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE202">
         <v>1.1</v>
       </c>
       <c r="AF202">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG202">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK202">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33778,10 +33778,10 @@
         <v>1.15</v>
       </c>
       <c r="AF205">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG205">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -34068,7 +34068,7 @@
         <v>1.33</v>
       </c>
       <c r="T207">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="U207">
         <v>2.53</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="O208">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P208">
-        <v>3.93</v>
+        <v>4.55</v>
       </c>
       <c r="Q208">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="R208">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="S208">
+        <v>1.3</v>
+      </c>
+      <c r="T208">
+        <v>3.12</v>
+      </c>
+      <c r="U208">
+        <v>2.42</v>
+      </c>
+      <c r="V208">
+        <v>1.48</v>
+      </c>
+      <c r="W208">
+        <v>1.11</v>
+      </c>
+      <c r="X208">
+        <v>1.01</v>
+      </c>
+      <c r="Y208">
+        <v>1.21</v>
+      </c>
+      <c r="Z208">
+        <v>4.27</v>
+      </c>
+      <c r="AA208">
+        <v>1.69</v>
+      </c>
+      <c r="AB208">
+        <v>2.18</v>
+      </c>
+      <c r="AC208">
+        <v>2.56</v>
+      </c>
+      <c r="AD208">
         <v>1.4</v>
       </c>
-      <c r="T208">
-        <v>2.6</v>
-      </c>
-      <c r="U208">
-        <v>3.02</v>
-      </c>
-      <c r="V208">
-        <v>1.32</v>
-      </c>
-      <c r="W208">
-        <v>1.05</v>
-      </c>
-      <c r="X208">
-        <v>1.05</v>
-      </c>
-      <c r="Y208">
-        <v>1.35</v>
-      </c>
-      <c r="Z208">
-        <v>2.74</v>
-      </c>
-      <c r="AA208">
-        <v>2.2</v>
-      </c>
-      <c r="AB208">
-        <v>1.6</v>
-      </c>
-      <c r="AC208">
-        <v>3.92</v>
-      </c>
-      <c r="AD208">
-        <v>1.18</v>
-      </c>
       <c r="AE208">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AF208">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AG208">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>1.22</v>
       </c>
       <c r="AK208">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.41</v>
+        <v>1.14</v>
       </c>
       <c r="O210">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="P210">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q210">
-        <v>3.18</v>
+        <v>1.65</v>
       </c>
       <c r="R210">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="S210">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T210">
-        <v>3.12</v>
+        <v>4.05</v>
       </c>
       <c r="U210">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="V210">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W210">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X210">
         <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z210">
-        <v>4.15</v>
+        <v>5.55</v>
       </c>
       <c r="AA210">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AB210">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AC210">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="AD210">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AE210">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AF210">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AG210">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK210">
-        <v>1.43</v>
+        <v>3.74</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="O211">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P211">
-        <v>4.55</v>
+        <v>3.93</v>
       </c>
       <c r="Q211">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="R211">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="S211">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T211">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="U211">
-        <v>2.42</v>
+        <v>3.02</v>
       </c>
       <c r="V211">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="W211">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X211">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y211">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="Z211">
-        <v>4.27</v>
+        <v>2.74</v>
       </c>
       <c r="AA211">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AB211">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="AC211">
-        <v>2.56</v>
+        <v>3.92</v>
       </c>
       <c r="AD211">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AE211">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AF211">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AG211">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>1.22</v>
       </c>
       <c r="AK211">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.14</v>
+        <v>2.41</v>
       </c>
       <c r="O212">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="P212">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q212">
-        <v>1.57</v>
+        <v>3.18</v>
       </c>
       <c r="R212">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="S212">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="T212">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="U212">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="V212">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="W212">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z212">
-        <v>5.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA212">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB212">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="AC212">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AD212">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AE212">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AF212">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG212">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK212">
-        <v>4.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35028,7 +35028,7 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O213">
         <v>3.88</v>
@@ -35363,10 +35363,10 @@
         <v>2.26</v>
       </c>
       <c r="Q215">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R215">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S215">
         <v>1.38</v>
@@ -36006,64 +36006,64 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q219">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R219">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S219">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T219">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U219">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V219">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W219">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X219">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y219">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z219">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA219">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB219">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC219">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AD219">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE219">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF219">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG219">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK219">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36169,64 +36169,64 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q220">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="R220">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S220">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T220">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U220">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="V220">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W220">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X220">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y220">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z220">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA220">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB220">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC220">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD220">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE220">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF220">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG220">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK220">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36341,22 +36341,22 @@
         <v>1.8</v>
       </c>
       <c r="Q221">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="R221">
         <v>2.2</v>
       </c>
       <c r="S221">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T221">
         <v>3.08</v>
       </c>
       <c r="U221">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V221">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W221">
         <v>1.1</v>
@@ -36402,7 +36402,7 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK221">
         <v>1.18</v>
@@ -36658,10 +36658,10 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O223">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P223">
         <v>2.25</v>
@@ -37808,55 +37808,55 @@
         <v>0</v>
       </c>
       <c r="Q230">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R230">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S230">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T230">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U230">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V230">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W230">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X230">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y230">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z230">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA230">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB230">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC230">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AD230">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE230">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF230">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG230">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK230">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O234">
         <v>3.6</v>
       </c>
       <c r="P234">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q234">
         <v>3.4</v>
@@ -38629,7 +38629,7 @@
         <v>2.58</v>
       </c>
       <c r="S235">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T235">
         <v>3.9</v>
@@ -38638,7 +38638,7 @@
         <v>2.1</v>
       </c>
       <c r="V235">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W235">
         <v>1.18</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,22 +38940,22 @@
         </is>
       </c>
       <c r="N237">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="O237">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P237">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="Q237">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="R237">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S237">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T237">
         <v>2.75</v>
@@ -38973,10 +38973,10 @@
         <v>0</v>
       </c>
       <c r="Y237">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z237">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA237">
         <v>2.1</v>
@@ -38994,10 +38994,10 @@
         <v>0</v>
       </c>
       <c r="AF237">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AG237">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK237">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,22 +39103,22 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="O238">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P238">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="Q238">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="R238">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S238">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T238">
         <v>2.75</v>
@@ -39136,10 +39136,10 @@
         <v>0</v>
       </c>
       <c r="Y238">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z238">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA238">
         <v>2.1</v>
@@ -39157,10 +39157,10 @@
         <v>0</v>
       </c>
       <c r="AF238">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AG238">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK238">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39438,16 +39438,16 @@
         <v>2.71</v>
       </c>
       <c r="Q240">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R240">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S240">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T240">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U240">
         <v>2.9</v>
@@ -39468,7 +39468,7 @@
         <v>2.88</v>
       </c>
       <c r="AA240">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB240">
         <v>1.63</v>
@@ -39499,7 +39499,7 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK240">
         <v>1.45</v>
@@ -39601,7 +39601,7 @@
         <v>6.58</v>
       </c>
       <c r="Q241">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R241">
         <v>2.32</v>
@@ -39610,10 +39610,10 @@
         <v>1.24</v>
       </c>
       <c r="T241">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="U241">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V241">
         <v>1.53</v>
@@ -39649,7 +39649,7 @@
         <v>1.67</v>
       </c>
       <c r="AG241">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK241">
         <v>2.38</v>
@@ -42200,19 +42200,19 @@
         </is>
       </c>
       <c r="N257">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O257">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="P257">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q257">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R257">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="S257">
         <v>1.22</v>
@@ -42233,31 +42233,31 @@
         <v>1.02</v>
       </c>
       <c r="Y257">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z257">
         <v>4.75</v>
       </c>
       <c r="AA257">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB257">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AC257">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD257">
         <v>1.59</v>
       </c>
       <c r="AE257">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF257">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG257">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42366,40 +42366,40 @@
         <v>1.31</v>
       </c>
       <c r="O258">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="P258">
         <v>8.75</v>
       </c>
       <c r="Q258">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="R258">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S258">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T258">
         <v>3.5</v>
       </c>
       <c r="U258">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="V258">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W258">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X258">
         <v>1.02</v>
       </c>
       <c r="Y258">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z258">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="AA258">
         <v>1.57</v>
@@ -42408,19 +42408,19 @@
         <v>2.35</v>
       </c>
       <c r="AC258">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AD258">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AE258">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF258">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG258">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42870,13 +42870,13 @@
         <v>1.35</v>
       </c>
       <c r="T261">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="U261">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="V261">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W261">
         <v>1.07</v>
@@ -42900,7 +42900,7 @@
         <v>3.3</v>
       </c>
       <c r="AD261">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE261">
         <v>1.07</v>
@@ -43187,10 +43187,10 @@
         <v>4.2</v>
       </c>
       <c r="Q263">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R263">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S263">
         <v>1.33</v>
@@ -43211,16 +43211,16 @@
         <v>1.01</v>
       </c>
       <c r="Y263">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z263">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AA263">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AB263">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="AC263">
         <v>2.56</v>
@@ -43248,7 +43248,7 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK263">
         <v>2.12</v>
@@ -43356,37 +43356,37 @@
         <v>2.05</v>
       </c>
       <c r="S264">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T264">
         <v>2.9</v>
       </c>
       <c r="U264">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="V264">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W264">
         <v>1.05</v>
       </c>
       <c r="X264">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y264">
         <v>1.33</v>
       </c>
       <c r="Z264">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA264">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB264">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC264">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD264">
         <v>1.22</v>
@@ -43395,10 +43395,10 @@
         <v>1.05</v>
       </c>
       <c r="AF264">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG264">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK264">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43854,13 +43854,13 @@
         <v>3</v>
       </c>
       <c r="V267">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W267">
         <v>1.05</v>
       </c>
       <c r="X267">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y267">
         <v>1.3</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O268">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P268">
-        <v>6.98</v>
+        <v>6.6</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44989,7 +44989,7 @@
         <v>1.29</v>
       </c>
       <c r="T274">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U274">
         <v>2.32</v>
@@ -45134,7 +45134,7 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O275">
         <v>3.1</v>
@@ -45143,16 +45143,16 @@
         <v>2.55</v>
       </c>
       <c r="Q275">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="R275">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="S275">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T275">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="U275">
         <v>3.08</v>
@@ -45173,16 +45173,16 @@
         <v>2.83</v>
       </c>
       <c r="AA275">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB275">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC275">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="AD275">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE275">
         <v>1.03</v>
@@ -45306,7 +45306,7 @@
         <v>3</v>
       </c>
       <c r="Q276">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="R276">
         <v>2.5</v>
@@ -45674,7 +45674,7 @@
         <v>1.39</v>
       </c>
       <c r="AE278">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF278">
         <v>1.95</v>
@@ -46022,7 +46022,7 @@
         <v>1.12</v>
       </c>
       <c r="AK280">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46121,7 +46121,7 @@
         <v>2.5</v>
       </c>
       <c r="Q281">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R281">
         <v>2.15</v>
@@ -46151,10 +46151,10 @@
         <v>3.28</v>
       </c>
       <c r="AA281">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB281">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC281">
         <v>3.28</v>
@@ -46610,55 +46610,55 @@
         <v>0</v>
       </c>
       <c r="Q284">
-        <v>5.92</v>
+        <v>0</v>
       </c>
       <c r="R284">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S284">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T284">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="U284">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V284">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W284">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X284">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y284">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z284">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA284">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB284">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AC284">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD284">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE284">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF284">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG284">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK284">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46779,7 +46779,7 @@
         <v>3.33</v>
       </c>
       <c r="S285">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T285">
         <v>7</v>
@@ -46791,16 +46791,16 @@
         <v>2.25</v>
       </c>
       <c r="W285">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X285">
         <v>1</v>
       </c>
       <c r="Y285">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z285">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA285">
         <v>1.1</v>
@@ -46809,19 +46809,19 @@
         <v>5</v>
       </c>
       <c r="AC285">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AD285">
         <v>2.7</v>
       </c>
       <c r="AE285">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AF285">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG285">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q286">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R286">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S286">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T286">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U286">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V286">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W286">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X286">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y286">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z286">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA286">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB286">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC286">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD286">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE286">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF286">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG286">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK286">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q287">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R287">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S287">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T287">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U287">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V287">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W287">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X287">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y287">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z287">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA287">
         <v>2</v>
       </c>
       <c r="AB287">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC287">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD287">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE287">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF287">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG287">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK287">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -48068,16 +48068,16 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="O293">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P293">
         <v>2.83</v>
       </c>
       <c r="Q293">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R293">
         <v>2.38</v>
@@ -48086,31 +48086,31 @@
         <v>1.25</v>
       </c>
       <c r="T293">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U293">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V293">
         <v>1.54</v>
       </c>
       <c r="W293">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X293">
         <v>1.02</v>
       </c>
       <c r="Y293">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z293">
-        <v>4.89</v>
+        <v>4.4</v>
       </c>
       <c r="AA293">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB293">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC293">
         <v>2.3</v>
@@ -48125,7 +48125,7 @@
         <v>1.48</v>
       </c>
       <c r="AG293">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48231,10 +48231,10 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O294">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="P294">
         <v>2.7</v>
@@ -48273,7 +48273,7 @@
         <v>1.75</v>
       </c>
       <c r="AB294">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC294">
         <v>2.83</v>
@@ -48282,7 +48282,7 @@
         <v>1.34</v>
       </c>
       <c r="AE294">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF294">
         <v>1.61</v>
@@ -48895,7 +48895,7 @@
         <v>2.92</v>
       </c>
       <c r="R298">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S298">
         <v>1.59</v>
@@ -48953,7 +48953,7 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK298">
         <v>1.67</v>
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,80 +49046,80 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O299">
         <v>2.95</v>
       </c>
       <c r="P299">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q299">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="R299">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="S299">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="T299">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="U299">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="V299">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W299">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X299">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y299">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="Z299">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AA299">
-        <v>3.4</v>
+        <v>2.56</v>
       </c>
       <c r="AB299">
+        <v>1.46</v>
+      </c>
+      <c r="AC299">
+        <v>5.18</v>
+      </c>
+      <c r="AD299">
+        <v>1.14</v>
+      </c>
+      <c r="AE299">
+        <v>1.04</v>
+      </c>
+      <c r="AF299">
+        <v>2.19</v>
+      </c>
+      <c r="AG299">
+        <v>1.59</v>
+      </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ299">
         <v>1.33</v>
       </c>
-      <c r="AC299">
-        <v>6.05</v>
-      </c>
-      <c r="AD299">
-        <v>1.06</v>
-      </c>
-      <c r="AE299">
-        <v>1.02</v>
-      </c>
-      <c r="AF299">
-        <v>2.57</v>
-      </c>
-      <c r="AG299">
-        <v>1.42</v>
-      </c>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI299" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ299">
-        <v>1.1</v>
-      </c>
       <c r="AK299">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O300">
         <v>2.95</v>
       </c>
       <c r="P300">
+        <v>4.8</v>
+      </c>
+      <c r="Q300">
+        <v>2.6</v>
+      </c>
+      <c r="R300">
+        <v>1.87</v>
+      </c>
+      <c r="S300">
+        <v>1.67</v>
+      </c>
+      <c r="T300">
+        <v>2.15</v>
+      </c>
+      <c r="U300">
+        <v>4.1</v>
+      </c>
+      <c r="V300">
+        <v>1.2</v>
+      </c>
+      <c r="W300">
+        <v>1.03</v>
+      </c>
+      <c r="X300">
+        <v>1.1</v>
+      </c>
+      <c r="Y300">
+        <v>1.66</v>
+      </c>
+      <c r="Z300">
+        <v>2.15</v>
+      </c>
+      <c r="AA300">
         <v>3.4</v>
       </c>
-      <c r="Q300">
-        <v>2.88</v>
-      </c>
-      <c r="R300">
-        <v>1.83</v>
-      </c>
-      <c r="S300">
-        <v>1.5</v>
-      </c>
-      <c r="T300">
-        <v>2.5</v>
-      </c>
-      <c r="U300">
-        <v>3.58</v>
-      </c>
-      <c r="V300">
-        <v>1.21</v>
-      </c>
-      <c r="W300">
-        <v>1.04</v>
-      </c>
-      <c r="X300">
-        <v>1.11</v>
-      </c>
-      <c r="Y300">
-        <v>1.53</v>
-      </c>
-      <c r="Z300">
-        <v>2.43</v>
-      </c>
-      <c r="AA300">
-        <v>2.56</v>
-      </c>
       <c r="AB300">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AC300">
-        <v>5.15</v>
+        <v>6.05</v>
       </c>
       <c r="AD300">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE300">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF300">
-        <v>2.19</v>
+        <v>2.57</v>
       </c>
       <c r="AG300">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK300">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49378,7 +49378,7 @@
         <v>3.45</v>
       </c>
       <c r="P301">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q301">
         <v>3.5</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="O305">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="P305">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50220,7 +50220,7 @@
         <v>1.04</v>
       </c>
       <c r="Y306">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z306">
         <v>2.7</v>
@@ -50244,7 +50244,7 @@
         <v>2.05</v>
       </c>
       <c r="AG306">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>3.65</v>
       </c>
       <c r="P307">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="Q307">
         <v>2.55</v>
@@ -50715,7 +50715,7 @@
         <v>7.5</v>
       </c>
       <c r="AA309">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB309">
         <v>3.1</v>
@@ -51859,16 +51859,16 @@
         <v>1.63</v>
       </c>
       <c r="AB316">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AC316">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AD316">
         <v>1.45</v>
       </c>
       <c r="AE316">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF316">
         <v>1.51</v>
@@ -52025,10 +52025,10 @@
         <v>1.83</v>
       </c>
       <c r="AC317">
-        <v>3.18</v>
+        <v>2.91</v>
       </c>
       <c r="AD317">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE317">
         <v>1.11</v>
@@ -52795,19 +52795,19 @@
         </is>
       </c>
       <c r="N322">
+        <v>2.63</v>
+      </c>
+      <c r="O322">
+        <v>2.9</v>
+      </c>
+      <c r="P322">
         <v>2.6</v>
-      </c>
-      <c r="O322">
-        <v>2.98</v>
-      </c>
-      <c r="P322">
-        <v>2.5</v>
       </c>
       <c r="Q322">
         <v>3.6</v>
       </c>
       <c r="R322">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S322">
         <v>1.44</v>
@@ -52825,7 +52825,7 @@
         <v>1.05</v>
       </c>
       <c r="X322">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y322">
         <v>1.47</v>
@@ -52846,7 +52846,7 @@
         <v>1.18</v>
       </c>
       <c r="AE322">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF322">
         <v>2</v>
@@ -53133,19 +53133,19 @@
         <v>2.9</v>
       </c>
       <c r="R324">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="S324">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="T324">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="U324">
         <v>4.3</v>
       </c>
       <c r="V324">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W324">
         <v>1.02</v>
@@ -53178,7 +53178,7 @@
         <v>2.54</v>
       </c>
       <c r="AG324">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="O325">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="P325">
-        <v>7.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q325">
-        <v>2.17</v>
+        <v>3.74</v>
       </c>
       <c r="R325">
-        <v>2.09</v>
+        <v>1.82</v>
       </c>
       <c r="S325">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="T325">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="U325">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="V325">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W325">
+        <v>1.03</v>
+      </c>
+      <c r="X325">
+        <v>1.08</v>
+      </c>
+      <c r="Y325">
+        <v>1.63</v>
+      </c>
+      <c r="Z325">
+        <v>2.1</v>
+      </c>
+      <c r="AA325">
+        <v>2.87</v>
+      </c>
+      <c r="AB325">
+        <v>1.31</v>
+      </c>
+      <c r="AC325">
+        <v>6.4</v>
+      </c>
+      <c r="AD325">
         <v>1.05</v>
       </c>
-      <c r="X325">
-        <v>1.06</v>
-      </c>
-      <c r="Y325">
-        <v>1.48</v>
-      </c>
-      <c r="Z325">
-        <v>2.58</v>
-      </c>
-      <c r="AA325">
-        <v>2.4</v>
-      </c>
-      <c r="AB325">
-        <v>1.52</v>
-      </c>
-      <c r="AC325">
-        <v>4.7</v>
-      </c>
-      <c r="AD325">
-        <v>1.17</v>
-      </c>
       <c r="AE325">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF325">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AG325">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK325">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,64 +53447,64 @@
         </is>
       </c>
       <c r="N326">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="O326">
         <v>2.75</v>
       </c>
       <c r="P326">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="Q326">
-        <v>3.74</v>
+        <v>2.84</v>
       </c>
       <c r="R326">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="S326">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="T326">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="U326">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="V326">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W326">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X326">
         <v>1.08</v>
       </c>
       <c r="Y326">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z326">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA326">
         <v>2.87</v>
       </c>
       <c r="AB326">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC326">
-        <v>6.24</v>
+        <v>5.55</v>
       </c>
       <c r="AD326">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE326">
         <v>1.03</v>
       </c>
       <c r="AF326">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AG326">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AK326">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,80 +53610,80 @@
         </is>
       </c>
       <c r="N327">
-        <v>2.15</v>
+        <v>1.48</v>
       </c>
       <c r="O327">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="P327">
-        <v>3.6</v>
+        <v>7.25</v>
       </c>
       <c r="Q327">
-        <v>2.84</v>
+        <v>2.17</v>
       </c>
       <c r="R327">
-        <v>1.79</v>
+        <v>2.09</v>
       </c>
       <c r="S327">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="T327">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U327">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="V327">
+        <v>1.3</v>
+      </c>
+      <c r="W327">
+        <v>1.05</v>
+      </c>
+      <c r="X327">
+        <v>1.06</v>
+      </c>
+      <c r="Y327">
+        <v>1.48</v>
+      </c>
+      <c r="Z327">
+        <v>2.58</v>
+      </c>
+      <c r="AA327">
+        <v>2.4</v>
+      </c>
+      <c r="AB327">
+        <v>1.52</v>
+      </c>
+      <c r="AC327">
+        <v>4.7</v>
+      </c>
+      <c r="AD327">
+        <v>1.17</v>
+      </c>
+      <c r="AE327">
+        <v>1.01</v>
+      </c>
+      <c r="AF327">
+        <v>2.45</v>
+      </c>
+      <c r="AG327">
+        <v>1.46</v>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ327">
         <v>1.22</v>
       </c>
-      <c r="W327">
-        <v>1.04</v>
-      </c>
-      <c r="X327">
-        <v>1.08</v>
-      </c>
-      <c r="Y327">
-        <v>1.57</v>
-      </c>
-      <c r="Z327">
-        <v>2.2</v>
-      </c>
-      <c r="AA327">
-        <v>2.87</v>
-      </c>
-      <c r="AB327">
-        <v>1.36</v>
-      </c>
-      <c r="AC327">
-        <v>5.55</v>
-      </c>
-      <c r="AD327">
-        <v>1.08</v>
-      </c>
-      <c r="AE327">
-        <v>1.03</v>
-      </c>
-      <c r="AF327">
-        <v>2.28</v>
-      </c>
-      <c r="AG327">
-        <v>1.53</v>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ327">
-        <v>1.32</v>
-      </c>
       <c r="AK327">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53806,10 +53806,10 @@
         <v>1.06</v>
       </c>
       <c r="Y328">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z328">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AA328">
         <v>2.7</v>
@@ -53830,7 +53830,7 @@
         <v>2.03</v>
       </c>
       <c r="AG328">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         </is>
       </c>
       <c r="N337">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="O337">
         <v>3.3</v>
@@ -55255,7 +55255,7 @@
         <v>2.14</v>
       </c>
       <c r="S337">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="T337">
         <v>3</v>
@@ -55270,7 +55270,7 @@
         <v>1.06</v>
       </c>
       <c r="X337">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y337">
         <v>1.24</v>
@@ -55578,7 +55578,7 @@
         <v>3.6</v>
       </c>
       <c r="R339">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S339">
         <v>1.2</v>
@@ -55605,22 +55605,22 @@
         <v>4.5</v>
       </c>
       <c r="AA339">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB339">
         <v>2.24</v>
       </c>
       <c r="AC339">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="AD339">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE339">
         <v>1.16</v>
       </c>
       <c r="AF339">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG339">
         <v>2.3</v>
@@ -55636,10 +55636,10 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK339">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55738,13 +55738,13 @@
         <v>2.11</v>
       </c>
       <c r="Q340">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="R340">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S340">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T340">
         <v>3.54</v>
@@ -55771,7 +55771,7 @@
         <v>1.61</v>
       </c>
       <c r="AB340">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC340">
         <v>2.43</v>
@@ -55786,7 +55786,7 @@
         <v>1.49</v>
       </c>
       <c r="AG340">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH340" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         </is>
       </c>
       <c r="AJ340">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK340">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL340">
         <v>0</v>
@@ -55907,7 +55907,7 @@
         <v>2.6</v>
       </c>
       <c r="S341">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T341">
         <v>3.75</v>
@@ -56112,7 +56112,7 @@
         <v>1.57</v>
       </c>
       <c r="AG342">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH342" t="inlineStr">
         <is>
@@ -56227,7 +56227,7 @@
         <v>2.44</v>
       </c>
       <c r="Q343">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="R343">
         <v>2.1</v>
@@ -56257,22 +56257,22 @@
         <v>4.45</v>
       </c>
       <c r="AA343">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB343">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AC343">
         <v>2.38</v>
       </c>
       <c r="AD343">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE343">
         <v>1.15</v>
       </c>
       <c r="AF343">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AG343">
         <v>2.4</v>
@@ -56288,10 +56288,10 @@
         </is>
       </c>
       <c r="AJ343">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK343">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL343">
         <v>0</v>
@@ -56402,7 +56402,7 @@
         <v>2.57</v>
       </c>
       <c r="U344">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="V344">
         <v>1.3</v>
@@ -56571,7 +56571,7 @@
         <v>1.31</v>
       </c>
       <c r="W345">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X345">
         <v>1.05</v>
@@ -57543,10 +57543,10 @@
         <v>4</v>
       </c>
       <c r="U351">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V351">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="W351">
         <v>1.18</v>
@@ -57685,10 +57685,10 @@
         </is>
       </c>
       <c r="N352">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="O352">
-        <v>3.01</v>
+        <v>3.05</v>
       </c>
       <c r="P352">
         <v>3.5</v>
@@ -57866,7 +57866,7 @@
         <v>1.33</v>
       </c>
       <c r="T353">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="U353">
         <v>2.6</v>
@@ -58026,7 +58026,7 @@
         <v>2.3</v>
       </c>
       <c r="S354">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T354">
         <v>3.24</v>
@@ -58047,7 +58047,7 @@
         <v>1.21</v>
       </c>
       <c r="Z354">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA354">
         <v>1.73</v>
@@ -58056,7 +58056,7 @@
         <v>2.1</v>
       </c>
       <c r="AC354">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AD354">
         <v>1.39</v>
@@ -58503,7 +58503,7 @@
         <v>2.7</v>
       </c>
       <c r="O357">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="P357">
         <v>2.2</v>
@@ -58663,13 +58663,13 @@
         </is>
       </c>
       <c r="N358">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="O358">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="P358">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Q358">
         <v>2.38</v>
@@ -58687,10 +58687,10 @@
         <v>2.25</v>
       </c>
       <c r="V358">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W358">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X358">
         <v>1.03</v>
@@ -58702,16 +58702,16 @@
         <v>4.2</v>
       </c>
       <c r="AA358">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AB358">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AC358">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="AD358">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE358">
         <v>1.15</v>
@@ -58733,10 +58733,10 @@
         </is>
       </c>
       <c r="AJ358">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK358">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL358">
         <v>0</v>
@@ -58989,16 +58989,16 @@
         </is>
       </c>
       <c r="N360">
-        <v>3.44</v>
+        <v>2.85</v>
       </c>
       <c r="O360">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="P360">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q360">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="R360">
         <v>2.3</v>
@@ -59010,13 +59010,13 @@
         <v>3.6</v>
       </c>
       <c r="U360">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V360">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W360">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X360">
         <v>1.01</v>
@@ -59031,13 +59031,13 @@
         <v>1.6</v>
       </c>
       <c r="AB360">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AC360">
         <v>2.4</v>
       </c>
       <c r="AD360">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE360">
         <v>1.17</v>
@@ -59059,7 +59059,7 @@
         </is>
       </c>
       <c r="AJ360">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK360">
         <v>1.36</v>
@@ -59487,10 +59487,10 @@
         <v>1.96</v>
       </c>
       <c r="Q363">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
       <c r="R363">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="S363">
         <v>1.21</v>
@@ -59548,7 +59548,7 @@
         </is>
       </c>
       <c r="AJ363">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AK363">
         <v>1.28</v>
@@ -59976,16 +59976,16 @@
         <v>3.26</v>
       </c>
       <c r="Q366">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="R366">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S366">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T366">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U366">
         <v>1.93</v>
@@ -60006,7 +60006,7 @@
         <v>6.25</v>
       </c>
       <c r="AA366">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB366">
         <v>3</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -4393,55 +4393,55 @@
         <v>2.02</v>
       </c>
       <c r="Q25">
-        <v>4.2</v>
+        <v>3.57</v>
       </c>
       <c r="R25">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="S25">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T25">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U25">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="V25">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z25">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA25">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB25">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC25">
-        <v>3.28</v>
+        <v>3.69</v>
       </c>
       <c r="AD25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG25">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK25">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -6684,7 +6684,7 @@
         <v>1.36</v>
       </c>
       <c r="T39">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U39">
         <v>2.75</v>
@@ -6708,10 +6708,10 @@
         <v>1.99</v>
       </c>
       <c r="AB39">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
-        <v>3.79</v>
+        <v>3.61</v>
       </c>
       <c r="AD39">
         <v>1.24</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="O52">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="Q52">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R52">
         <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="U52">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z52">
-        <v>4.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA52">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AC52">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="AD52">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AE52">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG52">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK52">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.65</v>
+        <v>2.13</v>
       </c>
       <c r="O53">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Q53">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="R53">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T53">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="U53">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="V53">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W53">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>7.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA53">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AB53">
-        <v>3.12</v>
+        <v>2.31</v>
       </c>
       <c r="AC53">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AD53">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AE53">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="P54">
-        <v>3.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q54">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T54">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="U54">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="W54">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>3.98</v>
+        <v>7.25</v>
       </c>
       <c r="AA54">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AB54">
-        <v>2.14</v>
+        <v>3.12</v>
       </c>
       <c r="AC54">
-        <v>2.52</v>
+        <v>1.9</v>
       </c>
       <c r="AD54">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="AE54">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AF54">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AG54">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.11</v>
+        <v>2.98</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="Q67">
-        <v>2.78</v>
+        <v>3.8</v>
       </c>
       <c r="R67">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
+        <v>1.38</v>
+      </c>
+      <c r="T67">
+        <v>2.74</v>
+      </c>
+      <c r="U67">
+        <v>2.92</v>
+      </c>
+      <c r="V67">
+        <v>1.34</v>
+      </c>
+      <c r="W67">
+        <v>1.03</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67">
+        <v>1.31</v>
+      </c>
+      <c r="Z67">
+        <v>3.3</v>
+      </c>
+      <c r="AA67">
+        <v>2.01</v>
+      </c>
+      <c r="AB67">
+        <v>1.79</v>
+      </c>
+      <c r="AC67">
+        <v>3.51</v>
+      </c>
+      <c r="AD67">
+        <v>1.28</v>
+      </c>
+      <c r="AE67">
+        <v>1.03</v>
+      </c>
+      <c r="AF67">
+        <v>1.75</v>
+      </c>
+      <c r="AG67">
+        <v>1.95</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.57</v>
+      </c>
+      <c r="AK67">
         <v>1.35</v>
-      </c>
-      <c r="T67">
-        <v>3.02</v>
-      </c>
-      <c r="U67">
-        <v>2.77</v>
-      </c>
-      <c r="V67">
-        <v>1.41</v>
-      </c>
-      <c r="W67">
-        <v>1.06</v>
-      </c>
-      <c r="X67">
-        <v>1.04</v>
-      </c>
-      <c r="Y67">
-        <v>1.25</v>
-      </c>
-      <c r="Z67">
-        <v>3.61</v>
-      </c>
-      <c r="AA67">
-        <v>1.9</v>
-      </c>
-      <c r="AB67">
-        <v>1.9</v>
-      </c>
-      <c r="AC67">
-        <v>3.05</v>
-      </c>
-      <c r="AD67">
-        <v>1.34</v>
-      </c>
-      <c r="AE67">
-        <v>1.08</v>
-      </c>
-      <c r="AF67">
-        <v>1.69</v>
-      </c>
-      <c r="AG67">
-        <v>2.05</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.25</v>
-      </c>
-      <c r="AK67">
-        <v>1.58</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.98</v>
+        <v>2.11</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="Q68">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S68">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T68">
-        <v>2.74</v>
+        <v>3.02</v>
       </c>
       <c r="U68">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="V68">
+        <v>1.41</v>
+      </c>
+      <c r="W68">
+        <v>1.06</v>
+      </c>
+      <c r="X68">
+        <v>1.04</v>
+      </c>
+      <c r="Y68">
+        <v>1.25</v>
+      </c>
+      <c r="Z68">
+        <v>3.61</v>
+      </c>
+      <c r="AA68">
+        <v>1.9</v>
+      </c>
+      <c r="AB68">
+        <v>1.9</v>
+      </c>
+      <c r="AC68">
+        <v>3.05</v>
+      </c>
+      <c r="AD68">
         <v>1.34</v>
       </c>
-      <c r="W68">
-        <v>1.03</v>
-      </c>
-      <c r="X68">
-        <v>1</v>
-      </c>
-      <c r="Y68">
-        <v>1.31</v>
-      </c>
-      <c r="Z68">
-        <v>3.3</v>
-      </c>
-      <c r="AA68">
-        <v>2.01</v>
-      </c>
-      <c r="AB68">
-        <v>1.79</v>
-      </c>
-      <c r="AC68">
-        <v>3.51</v>
-      </c>
-      <c r="AD68">
-        <v>1.28</v>
-      </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG68">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>2.95</v>
       </c>
       <c r="Q69">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="R69">
         <v>2.2</v>
@@ -11580,7 +11580,7 @@
         <v>2.62</v>
       </c>
       <c r="V69">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
         <v>1.06</v>
@@ -11629,7 +11629,7 @@
         <v>1.4</v>
       </c>
       <c r="AK69">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,16 +11719,16 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O70">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="P70">
         <v>5.31</v>
       </c>
       <c r="Q70">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R70">
         <v>2.7</v>
@@ -11761,7 +11761,7 @@
         <v>1.33</v>
       </c>
       <c r="AB70">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="AC70">
         <v>1.94</v>
@@ -11900,7 +11900,7 @@
         <v>1.33</v>
       </c>
       <c r="T71">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="U71">
         <v>2.56</v>
@@ -11909,7 +11909,7 @@
         <v>1.42</v>
       </c>
       <c r="W71">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
         <v>1.01</v>
@@ -12054,55 +12054,55 @@
         <v>3</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="O74">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="P74">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="Q74">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="R74">
         <v>2.38</v>
       </c>
       <c r="S74">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T74">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="U74">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="V74">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W74">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z74">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA74">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB74">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AC74">
-        <v>2.72</v>
+        <v>2.47</v>
       </c>
       <c r="AD74">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AE74">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF74">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG74">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK74">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="O75">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P75">
-        <v>3.21</v>
+        <v>2.09</v>
       </c>
       <c r="Q75">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="R75">
         <v>2.38</v>
       </c>
       <c r="S75">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="U75">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="V75">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X75">
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z75">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA75">
+        <v>1.66</v>
+      </c>
+      <c r="AB75">
+        <v>2.15</v>
+      </c>
+      <c r="AC75">
+        <v>2.72</v>
+      </c>
+      <c r="AD75">
+        <v>1.45</v>
+      </c>
+      <c r="AE75">
+        <v>1.13</v>
+      </c>
+      <c r="AF75">
         <v>1.57</v>
       </c>
-      <c r="AB75">
-        <v>2.36</v>
-      </c>
-      <c r="AC75">
-        <v>2.47</v>
-      </c>
-      <c r="AD75">
-        <v>1.54</v>
-      </c>
-      <c r="AE75">
-        <v>1.15</v>
-      </c>
-      <c r="AF75">
-        <v>1.53</v>
-      </c>
       <c r="AG75">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK75">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O87">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P87">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q87">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="R87">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S87">
         <v>1.25</v>
       </c>
       <c r="T87">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U87">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="V87">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W87">
         <v>1.15</v>
@@ -14523,47 +14523,47 @@
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z87">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="AA87">
+        <v>1.54</v>
+      </c>
+      <c r="AB87">
+        <v>2.35</v>
+      </c>
+      <c r="AC87">
+        <v>2.42</v>
+      </c>
+      <c r="AD87">
+        <v>1.48</v>
+      </c>
+      <c r="AE87">
+        <v>1.17</v>
+      </c>
+      <c r="AF87">
+        <v>1.48</v>
+      </c>
+      <c r="AG87">
+        <v>2.5</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
+        <v>1.2</v>
+      </c>
+      <c r="AK87">
         <v>1.6</v>
-      </c>
-      <c r="AB87">
-        <v>2.15</v>
-      </c>
-      <c r="AC87">
-        <v>2.43</v>
-      </c>
-      <c r="AD87">
-        <v>1.44</v>
-      </c>
-      <c r="AE87">
-        <v>1.15</v>
-      </c>
-      <c r="AF87">
-        <v>1.51</v>
-      </c>
-      <c r="AG87">
-        <v>2.36</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.21</v>
-      </c>
-      <c r="AK87">
-        <v>1.55</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="O88">
         <v>3.6</v>
       </c>
       <c r="P88">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="Q88">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="R88">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S88">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U88">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V88">
+        <v>1.6</v>
+      </c>
+      <c r="W88">
+        <v>1.15</v>
+      </c>
+      <c r="X88">
+        <v>1.02</v>
+      </c>
+      <c r="Y88">
+        <v>1.1</v>
+      </c>
+      <c r="Z88">
+        <v>5.1</v>
+      </c>
+      <c r="AA88">
         <v>1.53</v>
       </c>
-      <c r="W88">
-        <v>1.1</v>
-      </c>
-      <c r="X88">
-        <v>1.01</v>
-      </c>
-      <c r="Y88">
-        <v>1.16</v>
-      </c>
-      <c r="Z88">
-        <v>4.2</v>
-      </c>
-      <c r="AA88">
-        <v>1.59</v>
-      </c>
       <c r="AB88">
+        <v>2.41</v>
+      </c>
+      <c r="AC88">
         <v>2.2</v>
       </c>
-      <c r="AC88">
-        <v>2.42</v>
-      </c>
       <c r="AD88">
+        <v>1.57</v>
+      </c>
+      <c r="AE88">
+        <v>1.19</v>
+      </c>
+      <c r="AF88">
+        <v>1.41</v>
+      </c>
+      <c r="AG88">
+        <v>2.66</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
+        <v>1.2</v>
+      </c>
+      <c r="AK88">
         <v>1.44</v>
-      </c>
-      <c r="AE88">
-        <v>1.15</v>
-      </c>
-      <c r="AF88">
-        <v>1.52</v>
-      </c>
-      <c r="AG88">
-        <v>2.34</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.27</v>
-      </c>
-      <c r="AK88">
-        <v>1.62</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="O89">
         <v>3.6</v>
       </c>
       <c r="P89">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="Q89">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="R89">
         <v>2.45</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U89">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V89">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W89">
+        <v>1.14</v>
+      </c>
+      <c r="X89">
+        <v>1.03</v>
+      </c>
+      <c r="Y89">
         <v>1.15</v>
       </c>
-      <c r="X89">
-        <v>1.02</v>
-      </c>
-      <c r="Y89">
-        <v>1.08</v>
-      </c>
       <c r="Z89">
-        <v>5.45</v>
+        <v>5.05</v>
       </c>
       <c r="AA89">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AB89">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="AC89">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="AD89">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AE89">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF89">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG89">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,58 +14979,58 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="O90">
+        <v>3.7</v>
+      </c>
+      <c r="P90">
+        <v>1.95</v>
+      </c>
+      <c r="Q90">
         <v>3.5</v>
       </c>
-      <c r="P90">
-        <v>2.8</v>
-      </c>
-      <c r="Q90">
-        <v>2.71</v>
-      </c>
       <c r="R90">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S90">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T90">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U90">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V90">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z90">
-        <v>5.2</v>
+        <v>5.32</v>
       </c>
       <c r="AA90">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB90">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AC90">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AD90">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AE90">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF90">
         <v>1.41</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK90">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="O91">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="Q91">
-        <v>3.5</v>
+        <v>2.89</v>
       </c>
       <c r="R91">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S91">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="T91">
-        <v>3.85</v>
+        <v>3.42</v>
       </c>
       <c r="U91">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V91">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z91">
-        <v>5.45</v>
+        <v>4.7</v>
       </c>
       <c r="AA91">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AB91">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="AC91">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD91">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AE91">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AF91">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AG91">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15320,7 +15320,7 @@
         <v>3.25</v>
       </c>
       <c r="S92">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T92">
         <v>4.6</v>
@@ -15809,10 +15809,10 @@
         <v>2.14</v>
       </c>
       <c r="S95">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U95">
         <v>2.65</v>
@@ -15833,7 +15833,7 @@
         <v>3.64</v>
       </c>
       <c r="AA95">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB95">
         <v>2.08</v>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R102">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S102">
         <v>1.36</v>
@@ -16974,7 +16974,7 @@
         <v>3.14</v>
       </c>
       <c r="AA102">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB102">
         <v>1.74</v>
@@ -17436,7 +17436,7 @@
         <v>2.45</v>
       </c>
       <c r="R105">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S105">
         <v>1.29</v>
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
+        <v>2.88</v>
+      </c>
+      <c r="R107">
+        <v>2.03</v>
+      </c>
+      <c r="S107">
+        <v>1.36</v>
+      </c>
+      <c r="T107">
+        <v>2.72</v>
+      </c>
+      <c r="U107">
+        <v>2.76</v>
+      </c>
+      <c r="V107">
+        <v>1.4</v>
+      </c>
+      <c r="W107">
+        <v>1.03</v>
+      </c>
+      <c r="X107">
+        <v>1.01</v>
+      </c>
+      <c r="Y107">
+        <v>1.25</v>
+      </c>
+      <c r="Z107">
+        <v>3.28</v>
+      </c>
+      <c r="AA107">
+        <v>1.9</v>
+      </c>
+      <c r="AB107">
+        <v>1.9</v>
+      </c>
+      <c r="AC107">
         <v>3.2</v>
       </c>
-      <c r="R107">
-        <v>2.07</v>
-      </c>
-      <c r="S107">
-        <v>1.33</v>
-      </c>
-      <c r="T107">
-        <v>2.85</v>
-      </c>
-      <c r="U107">
-        <v>2.68</v>
-      </c>
-      <c r="V107">
-        <v>1.37</v>
-      </c>
-      <c r="W107">
-        <v>1.04</v>
-      </c>
-      <c r="X107">
-        <v>1</v>
-      </c>
-      <c r="Y107">
-        <v>1.23</v>
-      </c>
-      <c r="Z107">
-        <v>3.42</v>
-      </c>
-      <c r="AA107">
-        <v>1.83</v>
-      </c>
-      <c r="AB107">
-        <v>1.84</v>
-      </c>
-      <c r="AC107">
-        <v>3.08</v>
-      </c>
       <c r="AD107">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE107">
         <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG107">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.37</v>
+        <v>3.55</v>
       </c>
       <c r="O109">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P109">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="Q109">
-        <v>3.27</v>
+        <v>4.51</v>
       </c>
       <c r="R109">
+        <v>1.99</v>
+      </c>
+      <c r="S109">
+        <v>1.36</v>
+      </c>
+      <c r="T109">
+        <v>2.88</v>
+      </c>
+      <c r="U109">
+        <v>2.81</v>
+      </c>
+      <c r="V109">
+        <v>1.34</v>
+      </c>
+      <c r="W109">
+        <v>1.05</v>
+      </c>
+      <c r="X109">
+        <v>1.02</v>
+      </c>
+      <c r="Y109">
+        <v>1.31</v>
+      </c>
+      <c r="Z109">
+        <v>2.92</v>
+      </c>
+      <c r="AA109">
         <v>2.1</v>
       </c>
-      <c r="S109">
-        <v>1.44</v>
-      </c>
-      <c r="T109">
-        <v>2.45</v>
-      </c>
-      <c r="U109">
-        <v>3.19</v>
-      </c>
-      <c r="V109">
-        <v>1.33</v>
-      </c>
-      <c r="W109">
-        <v>1.02</v>
-      </c>
-      <c r="X109">
-        <v>1.03</v>
-      </c>
-      <c r="Y109">
-        <v>1.36</v>
-      </c>
-      <c r="Z109">
-        <v>3.02</v>
-      </c>
-      <c r="AA109">
-        <v>2.16</v>
-      </c>
       <c r="AB109">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC109">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="AD109">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE109">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF109">
         <v>1.84</v>
       </c>
       <c r="AG109">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
       <c r="O110">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P110">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="Q110">
-        <v>3.39</v>
+        <v>3.27</v>
       </c>
       <c r="R110">
         <v>2.1</v>
       </c>
       <c r="S110">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T110">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="U110">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="V110">
         <v>1.33</v>
       </c>
       <c r="W110">
+        <v>1.02</v>
+      </c>
+      <c r="X110">
         <v>1.03</v>
       </c>
-      <c r="X110">
-        <v>1.01</v>
-      </c>
       <c r="Y110">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z110">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="AA110">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AB110">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC110">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="AD110">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE110">
         <v>1.02</v>
       </c>
       <c r="AF110">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG110">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.28</v>
       </c>
       <c r="AK110">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="O111">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="P111">
-        <v>1.91</v>
+        <v>2.52</v>
       </c>
       <c r="Q111">
-        <v>4.59</v>
+        <v>3.39</v>
       </c>
       <c r="R111">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T111">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="U111">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V111">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W111">
+        <v>1.03</v>
+      </c>
+      <c r="X111">
+        <v>1.01</v>
+      </c>
+      <c r="Y111">
+        <v>1.35</v>
+      </c>
+      <c r="Z111">
+        <v>3.03</v>
+      </c>
+      <c r="AA111">
+        <v>2.18</v>
+      </c>
+      <c r="AB111">
+        <v>1.66</v>
+      </c>
+      <c r="AC111">
+        <v>3.86</v>
+      </c>
+      <c r="AD111">
+        <v>1.24</v>
+      </c>
+      <c r="AE111">
         <v>1.02</v>
       </c>
-      <c r="X111">
-        <v>1.02</v>
-      </c>
-      <c r="Y111">
-        <v>1.34</v>
-      </c>
-      <c r="Z111">
-        <v>3.12</v>
-      </c>
-      <c r="AA111">
-        <v>2.1</v>
-      </c>
-      <c r="AB111">
-        <v>1.71</v>
-      </c>
-      <c r="AC111">
-        <v>3.7</v>
-      </c>
-      <c r="AD111">
-        <v>1.25</v>
-      </c>
-      <c r="AE111">
-        <v>1.03</v>
-      </c>
       <c r="AF111">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AG111">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK111">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O112">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="P112">
         <v>1.91</v>
       </c>
       <c r="Q112">
-        <v>4.1</v>
+        <v>4.59</v>
       </c>
       <c r="R112">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S112">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T112">
-        <v>3.24</v>
+        <v>2.76</v>
       </c>
       <c r="U112">
-        <v>2.61</v>
+        <v>3.12</v>
       </c>
       <c r="V112">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="W112">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X112">
+        <v>1.02</v>
+      </c>
+      <c r="Y112">
+        <v>1.34</v>
+      </c>
+      <c r="Z112">
+        <v>3.12</v>
+      </c>
+      <c r="AA112">
+        <v>2.1</v>
+      </c>
+      <c r="AB112">
+        <v>1.71</v>
+      </c>
+      <c r="AC112">
+        <v>3.7</v>
+      </c>
+      <c r="AD112">
+        <v>1.25</v>
+      </c>
+      <c r="AE112">
         <v>1.03</v>
       </c>
-      <c r="Y112">
-        <v>1.22</v>
-      </c>
-      <c r="Z112">
-        <v>3.97</v>
-      </c>
-      <c r="AA112">
-        <v>1.73</v>
-      </c>
-      <c r="AB112">
-        <v>1.95</v>
-      </c>
-      <c r="AC112">
-        <v>2.85</v>
-      </c>
-      <c r="AD112">
-        <v>1.39</v>
-      </c>
-      <c r="AE112">
-        <v>1.14</v>
-      </c>
       <c r="AF112">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="O113">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P113">
-        <v>4.08</v>
+        <v>1.91</v>
       </c>
       <c r="Q113">
-        <v>2.67</v>
+        <v>4.1</v>
       </c>
       <c r="R113">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="S113">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="T113">
-        <v>2.58</v>
+        <v>3.24</v>
       </c>
       <c r="U113">
-        <v>3.06</v>
+        <v>2.61</v>
       </c>
       <c r="V113">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="W113">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X113">
         <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>2.79</v>
+        <v>3.97</v>
       </c>
       <c r="AA113">
-        <v>2.33</v>
+        <v>1.73</v>
       </c>
       <c r="AB113">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AC113">
-        <v>4.27</v>
+        <v>2.85</v>
       </c>
       <c r="AD113">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AE113">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF113">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG113">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK113">
-        <v>1.71</v>
+        <v>1.22</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>3.55</v>
+        <v>1.96</v>
       </c>
       <c r="O114">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P114">
-        <v>2.15</v>
+        <v>4.08</v>
       </c>
       <c r="Q114">
-        <v>4.51</v>
+        <v>2.67</v>
       </c>
       <c r="R114">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="S114">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T114">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="U114">
-        <v>2.81</v>
+        <v>3.06</v>
       </c>
       <c r="V114">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X114">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="Z114">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="AA114">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AB114">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC114">
-        <v>3.74</v>
+        <v>4.27</v>
       </c>
       <c r="AD114">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE114">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF114">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AG114">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK114">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="O117">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="P117">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q117">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="S117">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T117">
-        <v>3.14</v>
+        <v>2.54</v>
       </c>
       <c r="U117">
-        <v>2.42</v>
+        <v>2.87</v>
       </c>
       <c r="V117">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="W117">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="Z117">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="AA117">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="AB117">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="AC117">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="AD117">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE117">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF117">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG117">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK117">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="O118">
-        <v>3.05</v>
+        <v>3.54</v>
       </c>
       <c r="P118">
-        <v>2.87</v>
+        <v>3.7</v>
       </c>
       <c r="Q118">
-        <v>2.87</v>
+        <v>2.54</v>
       </c>
       <c r="R118">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="S118">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T118">
-        <v>2.54</v>
+        <v>3.01</v>
       </c>
       <c r="U118">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="V118">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W118">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X118">
         <v>1.03</v>
       </c>
       <c r="Y118">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z118">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA118">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB118">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AC118">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD118">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AE118">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF118">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG118">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK118">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="O119">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P119">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q119">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R119">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S119">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T119">
-        <v>3.03</v>
+        <v>3.14</v>
       </c>
       <c r="U119">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="V119">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W119">
         <v>1.07</v>
       </c>
       <c r="X119">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z119">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA119">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AB119">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AC119">
-        <v>3.31</v>
+        <v>2.7</v>
       </c>
       <c r="AD119">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE119">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AG119">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK119">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19905,16 +19905,16 @@
         <v>1.2</v>
       </c>
       <c r="Z120">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA120">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AB120">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC120">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="AD120">
         <v>1.35</v>
@@ -19942,7 +19942,7 @@
         <v>1.29</v>
       </c>
       <c r="AK120">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="O122">
         <v>5</v>
       </c>
       <c r="P122">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q122">
         <v>4.94</v>
@@ -20554,10 +20554,10 @@
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z124">
-        <v>4.81</v>
+        <v>4.83</v>
       </c>
       <c r="AA124">
         <v>1.65</v>
@@ -20566,16 +20566,16 @@
         <v>2.2</v>
       </c>
       <c r="AC124">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD124">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE124">
         <v>1.16</v>
       </c>
       <c r="AF124">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG124">
         <v>1.83</v>
@@ -20693,16 +20693,16 @@
         <v>3.25</v>
       </c>
       <c r="Q125">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="R125">
         <v>1.97</v>
       </c>
       <c r="S125">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T125">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="U125">
         <v>3.32</v>
@@ -20723,16 +20723,16 @@
         <v>2.62</v>
       </c>
       <c r="AA125">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB125">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC125">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="AD125">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE125">
         <v>1</v>
@@ -21013,10 +21013,10 @@
         <v>1.87</v>
       </c>
       <c r="O127">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="P127">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O130">
         <v>3.4</v>
       </c>
       <c r="P130">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q130">
         <v>2.5</v>
@@ -21514,49 +21514,49 @@
         <v>2.3</v>
       </c>
       <c r="S130">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T130">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U130">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="V130">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W130">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X130">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z130">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA130">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB130">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AC130">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD130">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE130">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF130">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG130">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>1.3</v>
       </c>
       <c r="AK130">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21834,7 +21834,7 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R132">
         <v>2.2</v>
@@ -21846,40 +21846,40 @@
         <v>3</v>
       </c>
       <c r="U132">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="V132">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W132">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X132">
         <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z132">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="AA132">
         <v>1.87</v>
       </c>
       <c r="AB132">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC132">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="AD132">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE132">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF132">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG132">
         <v>2.1</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK132">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22151,7 +22151,7 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O134">
         <v>3.4</v>
@@ -22169,16 +22169,16 @@
         <v>1.32</v>
       </c>
       <c r="T134">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U134">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V134">
         <v>1.43</v>
       </c>
       <c r="W134">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X134">
         <v>1</v>
@@ -22224,7 +22224,7 @@
         <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22966,7 +22966,7 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O139">
         <v>3.1</v>
@@ -22987,7 +22987,7 @@
         <v>2.8</v>
       </c>
       <c r="U139">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V139">
         <v>1.36</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O142">
         <v>3.45</v>
       </c>
       <c r="P142">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q142">
         <v>3.67</v>
@@ -23633,19 +23633,19 @@
         <v>2.45</v>
       </c>
       <c r="S143">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T143">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U143">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="V143">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W143">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X143">
         <v>1.01</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="O144">
         <v>3.45</v>
       </c>
       <c r="P144">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q144">
         <v>2.43</v>
@@ -23820,10 +23820,10 @@
         <v>3.8</v>
       </c>
       <c r="AA144">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB144">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AC144">
         <v>2.92</v>
@@ -25254,7 +25254,7 @@
         <v>3.12</v>
       </c>
       <c r="P153">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,80 +26063,80 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="O158">
+        <v>4.35</v>
+      </c>
+      <c r="P158">
+        <v>1.61</v>
+      </c>
+      <c r="Q158">
+        <v>5.2</v>
+      </c>
+      <c r="R158">
+        <v>2.51</v>
+      </c>
+      <c r="S158">
+        <v>1.23</v>
+      </c>
+      <c r="T158">
         <v>4</v>
       </c>
-      <c r="P158">
-        <v>1.8</v>
-      </c>
-      <c r="Q158">
-        <v>4.1</v>
-      </c>
-      <c r="R158">
-        <v>2.41</v>
-      </c>
-      <c r="S158">
+      <c r="U158">
+        <v>2.05</v>
+      </c>
+      <c r="V158">
+        <v>1.7</v>
+      </c>
+      <c r="W158">
+        <v>1.15</v>
+      </c>
+      <c r="X158">
+        <v>1.01</v>
+      </c>
+      <c r="Y158">
+        <v>1.09</v>
+      </c>
+      <c r="Z158">
+        <v>5.3</v>
+      </c>
+      <c r="AA158">
+        <v>1.44</v>
+      </c>
+      <c r="AB158">
+        <v>2.7</v>
+      </c>
+      <c r="AC158">
+        <v>2.32</v>
+      </c>
+      <c r="AD158">
+        <v>1.71</v>
+      </c>
+      <c r="AE158">
+        <v>1.23</v>
+      </c>
+      <c r="AF158">
+        <v>1.51</v>
+      </c>
+      <c r="AG158">
+        <v>2.4</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ158">
         <v>1.22</v>
       </c>
-      <c r="T158">
-        <v>3.94</v>
-      </c>
-      <c r="U158">
-        <v>2.01</v>
-      </c>
-      <c r="V158">
-        <v>1.81</v>
-      </c>
-      <c r="W158">
-        <v>1.2</v>
-      </c>
-      <c r="X158">
-        <v>1.02</v>
-      </c>
-      <c r="Y158">
-        <v>1.05</v>
-      </c>
-      <c r="Z158">
-        <v>6.4</v>
-      </c>
-      <c r="AA158">
-        <v>1.34</v>
-      </c>
-      <c r="AB158">
-        <v>2.93</v>
-      </c>
-      <c r="AC158">
-        <v>1.98</v>
-      </c>
-      <c r="AD158">
-        <v>1.96</v>
-      </c>
-      <c r="AE158">
-        <v>1.34</v>
-      </c>
-      <c r="AF158">
-        <v>1.35</v>
-      </c>
-      <c r="AG158">
-        <v>2.93</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ158">
-        <v>2</v>
-      </c>
       <c r="AK158">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,64 +26226,64 @@
         </is>
       </c>
       <c r="N159">
-        <v>4.5</v>
+        <v>3.18</v>
       </c>
       <c r="O159">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="P159">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="Q159">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="R159">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="S159">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T159">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U159">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="V159">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="W159">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X159">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z159">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AA159">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AB159">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="AC159">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="AD159">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="AE159">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AF159">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="AG159">
-        <v>2.4</v>
+        <v>2.93</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.22</v>
+        <v>2</v>
       </c>
       <c r="AK159">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26416,7 +26416,7 @@
         <v>1.49</v>
       </c>
       <c r="W160">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X160">
         <v>1.01</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="O161">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="P161">
-        <v>2.55</v>
+        <v>10</v>
       </c>
       <c r="Q161">
-        <v>2.92</v>
+        <v>1.57</v>
       </c>
       <c r="R161">
-        <v>2.3</v>
+        <v>3.06</v>
       </c>
       <c r="S161">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="T161">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="U161">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="V161">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="W161">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X161">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z161">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AA161">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AB161">
-        <v>2.33</v>
+        <v>2.98</v>
       </c>
       <c r="AC161">
-        <v>2.29</v>
+        <v>1.87</v>
       </c>
       <c r="AD161">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AE161">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AF161">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AG161">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AK161">
-        <v>1.6</v>
+        <v>4.26</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="O162">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="P162">
-        <v>11</v>
+        <v>2.55</v>
       </c>
       <c r="Q162">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="R162">
-        <v>3.06</v>
+        <v>2.45</v>
       </c>
       <c r="S162">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="T162">
-        <v>4.45</v>
+        <v>3.58</v>
       </c>
       <c r="U162">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="V162">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="W162">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X162">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y162">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z162">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AA162">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AB162">
-        <v>2.98</v>
+        <v>2.33</v>
       </c>
       <c r="AC162">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AD162">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AE162">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AF162">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG162">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AK162">
-        <v>4.26</v>
+        <v>1.6</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -27243,7 +27243,7 @@
         <v>2.52</v>
       </c>
       <c r="AA165">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AB165">
         <v>1.57</v>
@@ -27367,58 +27367,58 @@
         </is>
       </c>
       <c r="N166">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="O166">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P166">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="Q166">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="R166">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S166">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T166">
         <v>3.26</v>
       </c>
       <c r="U166">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V166">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W166">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X166">
         <v>1.03</v>
       </c>
       <c r="Y166">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z166">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AA166">
         <v>1.72</v>
       </c>
       <c r="AB166">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC166">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD166">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE166">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF166">
         <v>1.62</v>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AK166">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -28076,7 +28076,7 @@
         <v>1.91</v>
       </c>
       <c r="AG170">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28562,10 +28562,10 @@
         <v>1.1</v>
       </c>
       <c r="AF173">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG173">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="O174">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="P174">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="Q174">
-        <v>2.81</v>
+        <v>1.75</v>
       </c>
       <c r="R174">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="S174">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="T174">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="U174">
-        <v>2.96</v>
+        <v>2.09</v>
       </c>
       <c r="V174">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="W174">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X174">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
+        <v>1.11</v>
+      </c>
+      <c r="Z174">
+        <v>6.12</v>
+      </c>
+      <c r="AA174">
+        <v>1.4</v>
+      </c>
+      <c r="AB174">
+        <v>2.56</v>
+      </c>
+      <c r="AC174">
+        <v>2.06</v>
+      </c>
+      <c r="AD174">
+        <v>1.72</v>
+      </c>
+      <c r="AE174">
         <v>1.25</v>
       </c>
-      <c r="Z174">
-        <v>3.28</v>
-      </c>
-      <c r="AA174">
-        <v>1.91</v>
-      </c>
-      <c r="AB174">
-        <v>1.82</v>
-      </c>
-      <c r="AC174">
-        <v>3.28</v>
-      </c>
-      <c r="AD174">
-        <v>1.29</v>
-      </c>
-      <c r="AE174">
-        <v>1.05</v>
-      </c>
       <c r="AF174">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG174">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK174">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="O175">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P175">
-        <v>3.55</v>
+        <v>2.87</v>
       </c>
       <c r="Q175">
-        <v>2.36</v>
+        <v>2.86</v>
       </c>
       <c r="R175">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S175">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T175">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="U175">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="V175">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W175">
         <v>1.06</v>
       </c>
       <c r="X175">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z175">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA175">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AB175">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AC175">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AD175">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE175">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF175">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG175">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK175">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="O176">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="P176">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q176">
-        <v>2.21</v>
+        <v>2.81</v>
       </c>
       <c r="R176">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S176">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T176">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U176">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="V176">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W176">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X176">
         <v>1.04</v>
       </c>
       <c r="Y176">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z176">
-        <v>3.82</v>
+        <v>3.28</v>
       </c>
       <c r="AA176">
+        <v>1.91</v>
+      </c>
+      <c r="AB176">
+        <v>1.82</v>
+      </c>
+      <c r="AC176">
+        <v>3.28</v>
+      </c>
+      <c r="AD176">
+        <v>1.29</v>
+      </c>
+      <c r="AE176">
+        <v>1.05</v>
+      </c>
+      <c r="AF176">
         <v>1.73</v>
       </c>
-      <c r="AB176">
-        <v>2.1</v>
-      </c>
-      <c r="AC176">
-        <v>2.98</v>
-      </c>
-      <c r="AD176">
-        <v>1.34</v>
-      </c>
-      <c r="AE176">
-        <v>1.09</v>
-      </c>
-      <c r="AF176">
-        <v>1.57</v>
-      </c>
       <c r="AG176">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK176">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="O177">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P177">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="Q177">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="R177">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S177">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T177">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="U177">
-        <v>2.48</v>
+        <v>2.77</v>
       </c>
       <c r="V177">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W177">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X177">
         <v>1.04</v>
       </c>
       <c r="Y177">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z177">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA177">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB177">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC177">
         <v>2.92</v>
       </c>
       <c r="AD177">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE177">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF177">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG177">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK177">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.53</v>
+        <v>1.7</v>
       </c>
       <c r="O178">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P178">
-        <v>2.31</v>
+        <v>3.95</v>
       </c>
       <c r="Q178">
-        <v>3.12</v>
+        <v>2.21</v>
       </c>
       <c r="R178">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S178">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T178">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="U178">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V178">
+        <v>1.48</v>
+      </c>
+      <c r="W178">
+        <v>1.08</v>
+      </c>
+      <c r="X178">
+        <v>1.04</v>
+      </c>
+      <c r="Y178">
+        <v>1.18</v>
+      </c>
+      <c r="Z178">
+        <v>3.82</v>
+      </c>
+      <c r="AA178">
+        <v>1.73</v>
+      </c>
+      <c r="AB178">
+        <v>2.1</v>
+      </c>
+      <c r="AC178">
+        <v>2.98</v>
+      </c>
+      <c r="AD178">
+        <v>1.34</v>
+      </c>
+      <c r="AE178">
+        <v>1.09</v>
+      </c>
+      <c r="AF178">
         <v>1.57</v>
       </c>
-      <c r="W178">
-        <v>1.13</v>
-      </c>
-      <c r="X178">
-        <v>1.02</v>
-      </c>
-      <c r="Y178">
-        <v>1.15</v>
-      </c>
-      <c r="Z178">
-        <v>4.2</v>
-      </c>
-      <c r="AA178">
-        <v>1.62</v>
-      </c>
-      <c r="AB178">
-        <v>2.12</v>
-      </c>
-      <c r="AC178">
-        <v>2.66</v>
-      </c>
-      <c r="AD178">
-        <v>1.44</v>
-      </c>
-      <c r="AE178">
-        <v>1.15</v>
-      </c>
-      <c r="AF178">
-        <v>1.51</v>
-      </c>
       <c r="AG178">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="AK178">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O179">
         <v>3.7</v>
       </c>
       <c r="P179">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q179">
-        <v>3.7</v>
+        <v>4.11</v>
       </c>
       <c r="R179">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S179">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T179">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="U179">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="V179">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W179">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X179">
         <v>1.02</v>
       </c>
       <c r="Y179">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z179">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="AA179">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB179">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AC179">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD179">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE179">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF179">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG179">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK179">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="O180">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="P180">
-        <v>6.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q180">
-        <v>1.75</v>
+        <v>3.12</v>
       </c>
       <c r="R180">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="S180">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T180">
+        <v>3.46</v>
+      </c>
+      <c r="U180">
+        <v>2.45</v>
+      </c>
+      <c r="V180">
+        <v>1.57</v>
+      </c>
+      <c r="W180">
+        <v>1.13</v>
+      </c>
+      <c r="X180">
+        <v>1.02</v>
+      </c>
+      <c r="Y180">
+        <v>1.15</v>
+      </c>
+      <c r="Z180">
         <v>4.2</v>
       </c>
-      <c r="U180">
-        <v>2.09</v>
-      </c>
-      <c r="V180">
-        <v>1.7</v>
-      </c>
-      <c r="W180">
-        <v>1.17</v>
-      </c>
-      <c r="X180">
-        <v>1.01</v>
-      </c>
-      <c r="Y180">
-        <v>1.11</v>
-      </c>
-      <c r="Z180">
-        <v>6.12</v>
-      </c>
       <c r="AA180">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AB180">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="AC180">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="AD180">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AE180">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AF180">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AG180">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.09</v>
+        <v>1.44</v>
       </c>
       <c r="AK180">
-        <v>3</v>
+        <v>1.43</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O181">
         <v>3.7</v>
       </c>
       <c r="P181">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q181">
-        <v>4.11</v>
+        <v>3.7</v>
       </c>
       <c r="R181">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S181">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T181">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="U181">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="V181">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W181">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X181">
         <v>1.02</v>
       </c>
       <c r="Y181">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z181">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="AA181">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB181">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AC181">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD181">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE181">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF181">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG181">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK181">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O182">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P182">
-        <v>2.87</v>
+        <v>4.4</v>
       </c>
       <c r="Q182">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="R182">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S182">
+        <v>1.31</v>
+      </c>
+      <c r="T182">
+        <v>3.08</v>
+      </c>
+      <c r="U182">
+        <v>2.6</v>
+      </c>
+      <c r="V182">
+        <v>1.44</v>
+      </c>
+      <c r="W182">
+        <v>1.07</v>
+      </c>
+      <c r="X182">
+        <v>1.03</v>
+      </c>
+      <c r="Y182">
+        <v>1.22</v>
+      </c>
+      <c r="Z182">
+        <v>3.6</v>
+      </c>
+      <c r="AA182">
+        <v>1.8</v>
+      </c>
+      <c r="AB182">
+        <v>1.9</v>
+      </c>
+      <c r="AC182">
+        <v>3.05</v>
+      </c>
+      <c r="AD182">
         <v>1.33</v>
       </c>
-      <c r="T182">
-        <v>2.87</v>
-      </c>
-      <c r="U182">
-        <v>2.98</v>
-      </c>
-      <c r="V182">
-        <v>1.4</v>
-      </c>
-      <c r="W182">
-        <v>1.06</v>
-      </c>
-      <c r="X182">
-        <v>1.02</v>
-      </c>
-      <c r="Y182">
-        <v>1.27</v>
-      </c>
-      <c r="Z182">
-        <v>3.14</v>
-      </c>
-      <c r="AA182">
-        <v>1.94</v>
-      </c>
-      <c r="AB182">
-        <v>1.79</v>
-      </c>
-      <c r="AC182">
-        <v>3.34</v>
-      </c>
-      <c r="AD182">
-        <v>1.24</v>
-      </c>
       <c r="AE182">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF182">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG182">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK182">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,19 +30138,19 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.75</v>
+        <v>2.61</v>
       </c>
       <c r="O183">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P183">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q183">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R183">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S183">
         <v>1.31</v>
@@ -30159,43 +30159,43 @@
         <v>3.08</v>
       </c>
       <c r="U183">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="V183">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W183">
         <v>1.07</v>
       </c>
       <c r="X183">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y183">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z183">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA183">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB183">
         <v>1.9</v>
       </c>
       <c r="AC183">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD183">
         <v>1.33</v>
       </c>
       <c r="AE183">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF183">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG183">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK183">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30313,7 +30313,7 @@
         <v>2.67</v>
       </c>
       <c r="R184">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S184">
         <v>1.23</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.73</v>
+        <v>2.37</v>
       </c>
       <c r="O187">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P187">
-        <v>2.11</v>
+        <v>2.34</v>
       </c>
       <c r="Q187">
-        <v>2.97</v>
+        <v>2.93</v>
       </c>
       <c r="R187">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="S187">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="T187">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="U187">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="V187">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="W187">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X187">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y187">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z187">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="AA187">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AB187">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC187">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AD187">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="AE187">
         <v>1.33</v>
       </c>
       <c r="AF187">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AG187">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK187">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,80 +30953,80 @@
         </is>
       </c>
       <c r="N188">
-        <v>3.7</v>
+        <v>2.73</v>
       </c>
       <c r="O188">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="P188">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="Q188">
-        <v>4.08</v>
+        <v>2.97</v>
       </c>
       <c r="R188">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="S188">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="T188">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="U188">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="V188">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="W188">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y188">
         <v>1.04</v>
       </c>
       <c r="Z188">
-        <v>11</v>
+        <v>6.44</v>
       </c>
       <c r="AA188">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AB188">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="AC188">
+        <v>1.89</v>
+      </c>
+      <c r="AD188">
+        <v>1.9</v>
+      </c>
+      <c r="AE188">
+        <v>1.33</v>
+      </c>
+      <c r="AF188">
+        <v>1.32</v>
+      </c>
+      <c r="AG188">
+        <v>3.1</v>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ188">
+        <v>1.16</v>
+      </c>
+      <c r="AK188">
         <v>1.4</v>
-      </c>
-      <c r="AD188">
-        <v>2.56</v>
-      </c>
-      <c r="AE188">
-        <v>1.75</v>
-      </c>
-      <c r="AF188">
-        <v>1.21</v>
-      </c>
-      <c r="AG188">
-        <v>3.84</v>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ188">
-        <v>1.14</v>
-      </c>
-      <c r="AK188">
-        <v>1.18</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.37</v>
+        <v>3.7</v>
       </c>
       <c r="O189">
-        <v>3.55</v>
+        <v>4.35</v>
       </c>
       <c r="P189">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="Q189">
-        <v>2.93</v>
+        <v>4.08</v>
       </c>
       <c r="R189">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="S189">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T189">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="U189">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="V189">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="W189">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="X189">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y189">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z189">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AA189">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AB189">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="AC189">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AD189">
-        <v>1.71</v>
+        <v>2.56</v>
       </c>
       <c r="AE189">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AF189">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AG189">
-        <v>2.9</v>
+        <v>3.84</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK189">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O191">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P191">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q191">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R191">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S191">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T191">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U191">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="V191">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W191">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z191">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA191">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AB191">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC191">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD191">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE191">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF191">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG191">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK191">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,65 +31605,65 @@
         </is>
       </c>
       <c r="N192">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="O192">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="P192">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q192">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="R192">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S192">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T192">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="U192">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V192">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W192">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X192">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y192">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z192">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AA192">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB192">
+        <v>1.9</v>
+      </c>
+      <c r="AC192">
+        <v>2.82</v>
+      </c>
+      <c r="AD192">
+        <v>1.36</v>
+      </c>
+      <c r="AE192">
+        <v>1.1</v>
+      </c>
+      <c r="AF192">
+        <v>1.75</v>
+      </c>
+      <c r="AG192">
         <v>1.97</v>
       </c>
-      <c r="AC192">
-        <v>2.88</v>
-      </c>
-      <c r="AD192">
-        <v>1.32</v>
-      </c>
-      <c r="AE192">
-        <v>1.08</v>
-      </c>
-      <c r="AF192">
-        <v>1.65</v>
-      </c>
-      <c r="AG192">
-        <v>2.11</v>
-      </c>
       <c r="AH192" t="inlineStr">
         <is>
           <t>[]</t>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK192">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="O193">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P193">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q193">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R193">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S193">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T193">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U193">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="V193">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W193">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X193">
         <v>1.03</v>
       </c>
       <c r="Y193">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z193">
-        <v>3.5</v>
+        <v>4.03</v>
       </c>
       <c r="AA193">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB193">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AC193">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="AD193">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE193">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF193">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AG193">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AK193">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="O194">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P194">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q194">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="R194">
         <v>2.3</v>
       </c>
       <c r="S194">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T194">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U194">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V194">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W194">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X194">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y194">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z194">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AA194">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB194">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC194">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="AD194">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE194">
         <v>1.12</v>
       </c>
       <c r="AF194">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG194">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AK194">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="O195">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P195">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="Q195">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R195">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S195">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T195">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="U195">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="V195">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W195">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X195">
         <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z195">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA195">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB195">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC195">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AD195">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE195">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF195">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG195">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK195">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="O196">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P196">
-        <v>6.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q196">
+        <v>2.5</v>
+      </c>
+      <c r="R196">
+        <v>2.15</v>
+      </c>
+      <c r="S196">
+        <v>1.38</v>
+      </c>
+      <c r="T196">
+        <v>2.74</v>
+      </c>
+      <c r="U196">
+        <v>2.9</v>
+      </c>
+      <c r="V196">
+        <v>1.36</v>
+      </c>
+      <c r="W196">
+        <v>1.03</v>
+      </c>
+      <c r="X196">
+        <v>1.01</v>
+      </c>
+      <c r="Y196">
+        <v>1.32</v>
+      </c>
+      <c r="Z196">
+        <v>3.14</v>
+      </c>
+      <c r="AA196">
+        <v>1.98</v>
+      </c>
+      <c r="AB196">
+        <v>1.77</v>
+      </c>
+      <c r="AC196">
+        <v>3.42</v>
+      </c>
+      <c r="AD196">
+        <v>1.23</v>
+      </c>
+      <c r="AE196">
+        <v>1.04</v>
+      </c>
+      <c r="AF196">
         <v>1.85</v>
       </c>
-      <c r="R196">
-        <v>2.63</v>
-      </c>
-      <c r="S196">
-        <v>1.21</v>
-      </c>
-      <c r="T196">
-        <v>4.1</v>
-      </c>
-      <c r="U196">
-        <v>2</v>
-      </c>
-      <c r="V196">
-        <v>1.75</v>
-      </c>
-      <c r="W196">
-        <v>1.15</v>
-      </c>
-      <c r="X196">
-        <v>1.02</v>
-      </c>
-      <c r="Y196">
-        <v>1.1</v>
-      </c>
-      <c r="Z196">
-        <v>5.2</v>
-      </c>
-      <c r="AA196">
-        <v>1.4</v>
-      </c>
-      <c r="AB196">
-        <v>2.53</v>
-      </c>
-      <c r="AC196">
-        <v>2.11</v>
-      </c>
-      <c r="AD196">
-        <v>1.68</v>
-      </c>
-      <c r="AE196">
-        <v>1.25</v>
-      </c>
-      <c r="AF196">
-        <v>1.6</v>
-      </c>
       <c r="AG196">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK196">
-        <v>2.78</v>
+        <v>1.88</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,80 +32420,80 @@
         </is>
       </c>
       <c r="N197">
+        <v>1.42</v>
+      </c>
+      <c r="O197">
+        <v>4.9</v>
+      </c>
+      <c r="P197">
+        <v>6.5</v>
+      </c>
+      <c r="Q197">
+        <v>1.85</v>
+      </c>
+      <c r="R197">
+        <v>2.63</v>
+      </c>
+      <c r="S197">
+        <v>1.21</v>
+      </c>
+      <c r="T197">
+        <v>4.1</v>
+      </c>
+      <c r="U197">
+        <v>2</v>
+      </c>
+      <c r="V197">
+        <v>1.75</v>
+      </c>
+      <c r="W197">
+        <v>1.15</v>
+      </c>
+      <c r="X197">
+        <v>1.02</v>
+      </c>
+      <c r="Y197">
+        <v>1.1</v>
+      </c>
+      <c r="Z197">
+        <v>5.2</v>
+      </c>
+      <c r="AA197">
+        <v>1.4</v>
+      </c>
+      <c r="AB197">
+        <v>2.88</v>
+      </c>
+      <c r="AC197">
+        <v>2.11</v>
+      </c>
+      <c r="AD197">
         <v>1.68</v>
       </c>
-      <c r="O197">
-        <v>4.1</v>
-      </c>
-      <c r="P197">
-        <v>4.5</v>
-      </c>
-      <c r="Q197">
-        <v>2.15</v>
-      </c>
-      <c r="R197">
-        <v>2.4</v>
-      </c>
-      <c r="S197">
-        <v>1.27</v>
-      </c>
-      <c r="T197">
-        <v>3.32</v>
-      </c>
-      <c r="U197">
-        <v>2.4</v>
-      </c>
-      <c r="V197">
-        <v>1.5</v>
-      </c>
-      <c r="W197">
-        <v>1.09</v>
-      </c>
-      <c r="X197">
-        <v>1.01</v>
-      </c>
-      <c r="Y197">
-        <v>1.14</v>
-      </c>
-      <c r="Z197">
-        <v>4.4</v>
-      </c>
-      <c r="AA197">
-        <v>1.59</v>
-      </c>
-      <c r="AB197">
-        <v>2.27</v>
-      </c>
-      <c r="AC197">
-        <v>2.36</v>
-      </c>
-      <c r="AD197">
-        <v>1.45</v>
-      </c>
       <c r="AE197">
+        <v>1.25</v>
+      </c>
+      <c r="AF197">
+        <v>1.6</v>
+      </c>
+      <c r="AG197">
+        <v>2.19</v>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ197">
         <v>1.15</v>
       </c>
-      <c r="AF197">
-        <v>1.59</v>
-      </c>
-      <c r="AG197">
-        <v>2.21</v>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ197">
-        <v>1.25</v>
-      </c>
       <c r="AK197">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="O198">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P198">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q198">
+        <v>2.61</v>
+      </c>
+      <c r="R198">
         <v>2.2</v>
       </c>
-      <c r="R198">
-        <v>2.22</v>
-      </c>
       <c r="S198">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T198">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U198">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V198">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W198">
         <v>1.07</v>
       </c>
       <c r="X198">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y198">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z198">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="AA198">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB198">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC198">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="AD198">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE198">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF198">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG198">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK198">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="O201">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P201">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="Q201">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="R201">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S201">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T201">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U201">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V201">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W201">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X201">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y201">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z201">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AA201">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB201">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AC201">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD201">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE201">
         <v>1.1</v>
       </c>
       <c r="AF201">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG201">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK201">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="O202">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P202">
-        <v>2.02</v>
+        <v>3.9</v>
       </c>
       <c r="Q202">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="R202">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S202">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T202">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="U202">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="V202">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W202">
         <v>1.11</v>
       </c>
       <c r="X202">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y202">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z202">
-        <v>4.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA202">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AB202">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="AC202">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="AD202">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AE202">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF202">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AG202">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK202">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,80 +33398,80 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O203">
+        <v>3.63</v>
+      </c>
+      <c r="P203">
+        <v>2.02</v>
+      </c>
+      <c r="Q203">
         <v>3.5</v>
       </c>
-      <c r="P203">
-        <v>2.62</v>
-      </c>
-      <c r="Q203">
-        <v>3.08</v>
-      </c>
       <c r="R203">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S203">
+        <v>1.28</v>
+      </c>
+      <c r="T203">
+        <v>3.24</v>
+      </c>
+      <c r="U203">
+        <v>2.29</v>
+      </c>
+      <c r="V203">
+        <v>1.53</v>
+      </c>
+      <c r="W203">
+        <v>1.11</v>
+      </c>
+      <c r="X203">
+        <v>1.01</v>
+      </c>
+      <c r="Y203">
+        <v>1.14</v>
+      </c>
+      <c r="Z203">
+        <v>4.8</v>
+      </c>
+      <c r="AA203">
+        <v>1.61</v>
+      </c>
+      <c r="AB203">
+        <v>2.29</v>
+      </c>
+      <c r="AC203">
+        <v>2.33</v>
+      </c>
+      <c r="AD203">
+        <v>1.48</v>
+      </c>
+      <c r="AE203">
+        <v>1.17</v>
+      </c>
+      <c r="AF203">
+        <v>1.55</v>
+      </c>
+      <c r="AG203">
+        <v>2.42</v>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ203">
+        <v>1.2</v>
+      </c>
+      <c r="AK203">
         <v>1.3</v>
-      </c>
-      <c r="T203">
-        <v>3.25</v>
-      </c>
-      <c r="U203">
-        <v>2.53</v>
-      </c>
-      <c r="V203">
-        <v>1.44</v>
-      </c>
-      <c r="W203">
-        <v>1.07</v>
-      </c>
-      <c r="X203">
-        <v>1.03</v>
-      </c>
-      <c r="Y203">
-        <v>1.19</v>
-      </c>
-      <c r="Z203">
-        <v>3.8</v>
-      </c>
-      <c r="AA203">
-        <v>1.73</v>
-      </c>
-      <c r="AB203">
-        <v>2.03</v>
-      </c>
-      <c r="AC203">
-        <v>2.7</v>
-      </c>
-      <c r="AD203">
-        <v>1.36</v>
-      </c>
-      <c r="AE203">
-        <v>1.1</v>
-      </c>
-      <c r="AF203">
-        <v>1.62</v>
-      </c>
-      <c r="AG203">
-        <v>2.2</v>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ203">
-        <v>1.28</v>
-      </c>
-      <c r="AK203">
-        <v>1.48</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O205">
         <v>3.7</v>
       </c>
       <c r="P205">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Q205">
         <v>3.95</v>
@@ -33766,7 +33766,7 @@
         <v>1.67</v>
       </c>
       <c r="AB205">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AC205">
         <v>2.49</v>
@@ -33778,10 +33778,10 @@
         <v>1.15</v>
       </c>
       <c r="AF205">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG205">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="O207">
-        <v>3.63</v>
+        <v>6.2</v>
       </c>
       <c r="P207">
-        <v>2.65</v>
+        <v>9.5</v>
       </c>
       <c r="Q207">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="R207">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="S207">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T207">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="U207">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="V207">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="W207">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X207">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="Z207">
-        <v>4.21</v>
+        <v>5.8</v>
       </c>
       <c r="AA207">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="AB207">
-        <v>2.15</v>
+        <v>2.69</v>
       </c>
       <c r="AC207">
-        <v>2.59</v>
+        <v>2.04</v>
       </c>
       <c r="AD207">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="AE207">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AF207">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AG207">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK207">
-        <v>1.58</v>
+        <v>4.05</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="O208">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P208">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="Q208">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="R208">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="S208">
         <v>1.3</v>
       </c>
       <c r="T208">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U208">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="V208">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W208">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X208">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y208">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z208">
-        <v>3.58</v>
+        <v>4.21</v>
       </c>
       <c r="AA208">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AB208">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AC208">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="AD208">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AE208">
         <v>1.13</v>
       </c>
       <c r="AF208">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG208">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK208">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="O209">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P209">
-        <v>3.93</v>
+        <v>4.55</v>
       </c>
       <c r="Q209">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="R209">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="S209">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T209">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="U209">
-        <v>3.02</v>
+        <v>2.53</v>
       </c>
       <c r="V209">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W209">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X209">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y209">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="Z209">
-        <v>2.74</v>
+        <v>4.27</v>
       </c>
       <c r="AA209">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AB209">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AC209">
-        <v>3.92</v>
+        <v>2.56</v>
       </c>
       <c r="AD209">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AE209">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AF209">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AG209">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK209">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.41</v>
+        <v>1.94</v>
       </c>
       <c r="O210">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P210">
-        <v>2.5</v>
+        <v>3.93</v>
       </c>
       <c r="Q210">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="R210">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S210">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T210">
-        <v>3.12</v>
+        <v>2.6</v>
       </c>
       <c r="U210">
-        <v>2.39</v>
+        <v>3.02</v>
       </c>
       <c r="V210">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="W210">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X210">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y210">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Z210">
-        <v>4.15</v>
+        <v>2.74</v>
       </c>
       <c r="AA210">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="AB210">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AC210">
-        <v>2.58</v>
+        <v>3.92</v>
       </c>
       <c r="AD210">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="AE210">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="AF210">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AG210">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>1.25</v>
       </c>
       <c r="AK210">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="O211">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="P211">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="Q211">
-        <v>2.19</v>
+        <v>2.51</v>
       </c>
       <c r="R211">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="S211">
         <v>1.3</v>
       </c>
       <c r="T211">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U211">
         <v>2.53</v>
       </c>
       <c r="V211">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W211">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X211">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y211">
         <v>1.21</v>
       </c>
       <c r="Z211">
-        <v>4.27</v>
+        <v>3.58</v>
       </c>
       <c r="AA211">
+        <v>1.81</v>
+      </c>
+      <c r="AB211">
+        <v>1.96</v>
+      </c>
+      <c r="AC211">
+        <v>2.92</v>
+      </c>
+      <c r="AD211">
+        <v>1.31</v>
+      </c>
+      <c r="AE211">
+        <v>1.13</v>
+      </c>
+      <c r="AF211">
         <v>1.67</v>
       </c>
-      <c r="AB211">
-        <v>2.15</v>
-      </c>
-      <c r="AC211">
-        <v>2.56</v>
-      </c>
-      <c r="AD211">
-        <v>1.4</v>
-      </c>
-      <c r="AE211">
-        <v>1.16</v>
-      </c>
-      <c r="AF211">
-        <v>1.66</v>
-      </c>
       <c r="AG211">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK211">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.14</v>
+        <v>2.41</v>
       </c>
       <c r="O212">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="P212">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q212">
-        <v>1.61</v>
+        <v>3.22</v>
       </c>
       <c r="R212">
-        <v>2.99</v>
+        <v>2.21</v>
       </c>
       <c r="S212">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="T212">
-        <v>4.15</v>
+        <v>3.12</v>
       </c>
       <c r="U212">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="V212">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="W212">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z212">
-        <v>5.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA212">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AB212">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AC212">
-        <v>2.04</v>
+        <v>2.58</v>
       </c>
       <c r="AD212">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AE212">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF212">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG212">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK212">
-        <v>4.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35034,7 +35034,7 @@
         <v>3.88</v>
       </c>
       <c r="P213">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="Q213">
         <v>2.35</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="O216">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P216">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q216">
         <v>3</v>
@@ -36568,7 +36568,7 @@
         <v>1.25</v>
       </c>
       <c r="AK222">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,19 +36658,19 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="O223">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P223">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q223">
-        <v>3.26</v>
+        <v>3.85</v>
       </c>
       <c r="R223">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S223">
         <v>1.25</v>
@@ -36679,37 +36679,37 @@
         <v>3.5</v>
       </c>
       <c r="U223">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="V223">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W223">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X223">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z223">
-        <v>4.33</v>
+        <v>4.83</v>
       </c>
       <c r="AA223">
         <v>1.57</v>
       </c>
       <c r="AB223">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC223">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="AD223">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE223">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF223">
         <v>1.49</v>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
+        <v>1.25</v>
+      </c>
+      <c r="AK223">
         <v>1.3</v>
-      </c>
-      <c r="AK223">
-        <v>1.4</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37014,7 +37014,7 @@
         <v>1.14</v>
       </c>
       <c r="X225">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y225">
         <v>1.15</v>
@@ -37177,7 +37177,7 @@
         <v>1.29</v>
       </c>
       <c r="X226">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y226">
         <v>1.02</v>
@@ -38300,7 +38300,7 @@
         <v>2.3</v>
       </c>
       <c r="R233">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="S233">
         <v>1.14</v>
@@ -38330,22 +38330,22 @@
         <v>1.3</v>
       </c>
       <c r="AB233">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AC233">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AD233">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AE233">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AF233">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG233">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>1.17</v>
       </c>
       <c r="AK233">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38620,7 +38620,7 @@
         <v>5.2</v>
       </c>
       <c r="P235">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q235">
         <v>6.97</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,31 +38940,31 @@
         </is>
       </c>
       <c r="N237">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="O237">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P237">
-        <v>4</v>
+        <v>2.89</v>
       </c>
       <c r="Q237">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="R237">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S237">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T237">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="U237">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="V237">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W237">
         <v>1.04</v>
@@ -38973,16 +38973,16 @@
         <v>1.03</v>
       </c>
       <c r="Y237">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z237">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA237">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB237">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC237">
         <v>3.58</v>
@@ -38994,11 +38994,11 @@
         <v>1.05</v>
       </c>
       <c r="AF237">
+        <v>1.81</v>
+      </c>
+      <c r="AG237">
         <v>1.88</v>
       </c>
-      <c r="AG237">
-        <v>1.81</v>
-      </c>
       <c r="AH237" t="inlineStr">
         <is>
           <t>[]</t>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK237">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,31 +39103,31 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="O238">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P238">
-        <v>2.89</v>
+        <v>4</v>
       </c>
       <c r="Q238">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="R238">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S238">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T238">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="U238">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="V238">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W238">
         <v>1.04</v>
@@ -39136,16 +39136,16 @@
         <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z238">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA238">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AB238">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC238">
         <v>3.58</v>
@@ -39157,11 +39157,11 @@
         <v>1.05</v>
       </c>
       <c r="AF238">
+        <v>1.88</v>
+      </c>
+      <c r="AG238">
         <v>1.81</v>
       </c>
-      <c r="AG238">
-        <v>1.88</v>
-      </c>
       <c r="AH238" t="inlineStr">
         <is>
           <t>[]</t>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK238">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -40096,7 +40096,7 @@
         <v>2.8</v>
       </c>
       <c r="S244">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T244">
         <v>4.6</v>
@@ -41726,10 +41726,10 @@
         <v>1.91</v>
       </c>
       <c r="S254">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T254">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U254">
         <v>3.3</v>
@@ -41756,7 +41756,7 @@
         <v>1.52</v>
       </c>
       <c r="AC254">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AD254">
         <v>1.14</v>
@@ -41765,10 +41765,10 @@
         <v>1.01</v>
       </c>
       <c r="AF254">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG254">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         </is>
       </c>
       <c r="N257">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O257">
         <v>6</v>
@@ -42405,7 +42405,7 @@
         <v>1.54</v>
       </c>
       <c r="AB258">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC258">
         <v>2.44</v>
@@ -43398,7 +43398,7 @@
         <v>1.8</v>
       </c>
       <c r="AG264">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43851,7 +43851,7 @@
         <v>2.64</v>
       </c>
       <c r="U267">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V267">
         <v>1.32</v>
@@ -44808,7 +44808,7 @@
         </is>
       </c>
       <c r="N273">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O273">
         <v>4.3</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="O274">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P274">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q274">
-        <v>2.26</v>
+        <v>3.39</v>
       </c>
       <c r="R274">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="S274">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T274">
-        <v>3.32</v>
+        <v>2.64</v>
       </c>
       <c r="U274">
-        <v>2.32</v>
+        <v>3.08</v>
       </c>
       <c r="V274">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="W274">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X274">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y274">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z274">
-        <v>4.15</v>
+        <v>2.83</v>
       </c>
       <c r="AA274">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AB274">
-        <v>2.14</v>
+        <v>1.62</v>
       </c>
       <c r="AC274">
-        <v>2.63</v>
+        <v>4.04</v>
       </c>
       <c r="AD274">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE274">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF274">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG274">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="AK274">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="O275">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P275">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q275">
-        <v>3.39</v>
+        <v>2.26</v>
       </c>
       <c r="R275">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="S275">
+        <v>1.3</v>
+      </c>
+      <c r="T275">
+        <v>3.32</v>
+      </c>
+      <c r="U275">
+        <v>2.32</v>
+      </c>
+      <c r="V275">
+        <v>1.52</v>
+      </c>
+      <c r="W275">
+        <v>1.11</v>
+      </c>
+      <c r="X275">
+        <v>1.01</v>
+      </c>
+      <c r="Y275">
+        <v>1.16</v>
+      </c>
+      <c r="Z275">
+        <v>4.15</v>
+      </c>
+      <c r="AA275">
+        <v>1.67</v>
+      </c>
+      <c r="AB275">
+        <v>2.14</v>
+      </c>
+      <c r="AC275">
+        <v>2.63</v>
+      </c>
+      <c r="AD275">
         <v>1.4</v>
       </c>
-      <c r="T275">
-        <v>2.64</v>
-      </c>
-      <c r="U275">
-        <v>3.08</v>
-      </c>
-      <c r="V275">
-        <v>1.31</v>
-      </c>
-      <c r="W275">
-        <v>1.06</v>
-      </c>
-      <c r="X275">
-        <v>1.02</v>
-      </c>
-      <c r="Y275">
-        <v>1.33</v>
-      </c>
-      <c r="Z275">
-        <v>2.83</v>
-      </c>
-      <c r="AA275">
-        <v>2.25</v>
-      </c>
-      <c r="AB275">
-        <v>1.62</v>
-      </c>
-      <c r="AC275">
-        <v>4.04</v>
-      </c>
-      <c r="AD275">
-        <v>1.22</v>
-      </c>
       <c r="AE275">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF275">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AG275">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="AK275">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45460,7 +45460,7 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O277">
         <v>3.4</v>
@@ -45859,7 +45859,7 @@
         <v>1.29</v>
       </c>
       <c r="AK279">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45952,13 +45952,13 @@
         <v>5.95</v>
       </c>
       <c r="O280">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P280">
         <v>1.33</v>
       </c>
       <c r="Q280">
-        <v>5.73</v>
+        <v>5.74</v>
       </c>
       <c r="R280">
         <v>3.15</v>
@@ -45979,7 +45979,7 @@
         <v>1.28</v>
       </c>
       <c r="X280">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y280">
         <v>1.02</v>
@@ -46317,7 +46317,7 @@
         <v>1.93</v>
       </c>
       <c r="AB282">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC282">
         <v>3.34</v>
@@ -46610,49 +46610,49 @@
         <v>0</v>
       </c>
       <c r="Q284">
-        <v>5.92</v>
+        <v>6.16</v>
       </c>
       <c r="R284">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="S284">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T284">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="U284">
         <v>2</v>
       </c>
       <c r="V284">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="W284">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X284">
         <v>1.01</v>
       </c>
       <c r="Y284">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z284">
-        <v>5.9</v>
+        <v>6.05</v>
       </c>
       <c r="AA284">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB284">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AC284">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AD284">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE284">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF284">
         <v>1.6</v>
@@ -46764,7 +46764,7 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O285">
         <v>7.5</v>
@@ -47132,7 +47132,7 @@
         <v>2</v>
       </c>
       <c r="AB287">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC287">
         <v>3.34</v>
@@ -47745,10 +47745,10 @@
         <v>3.84</v>
       </c>
       <c r="O291">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P291">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47905,7 +47905,7 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="O292">
         <v>3.1</v>
@@ -47926,7 +47926,7 @@
         <v>2.88</v>
       </c>
       <c r="U292">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="V292">
         <v>1.34</v>
@@ -48071,10 +48071,10 @@
         <v>1.95</v>
       </c>
       <c r="O293">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P293">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Q293">
         <v>2.75</v>
@@ -48110,7 +48110,7 @@
         <v>2.7</v>
       </c>
       <c r="AB293">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC293">
         <v>5.4</v>
@@ -48231,16 +48231,16 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O294">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P294">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q294">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R294">
         <v>2.38</v>
@@ -48279,7 +48279,7 @@
         <v>2.3</v>
       </c>
       <c r="AD294">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE294">
         <v>1.17</v>
@@ -48753,7 +48753,7 @@
         <v>1</v>
       </c>
       <c r="Y297">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z297">
         <v>3.7</v>
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,64 +49046,64 @@
         </is>
       </c>
       <c r="N299">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O299">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P299">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q299">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="R299">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="S299">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="T299">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U299">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="V299">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W299">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X299">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y299">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="Z299">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="AA299">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AB299">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AC299">
-        <v>5.18</v>
+        <v>6.05</v>
       </c>
       <c r="AD299">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AE299">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF299">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="AG299">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK299">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,80 +49209,80 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O300">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P300">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q300">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="R300">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="S300">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="T300">
+        <v>2.5</v>
+      </c>
+      <c r="U300">
+        <v>3.58</v>
+      </c>
+      <c r="V300">
+        <v>1.21</v>
+      </c>
+      <c r="W300">
+        <v>1.04</v>
+      </c>
+      <c r="X300">
+        <v>1.11</v>
+      </c>
+      <c r="Y300">
+        <v>1.54</v>
+      </c>
+      <c r="Z300">
+        <v>2.42</v>
+      </c>
+      <c r="AA300">
+        <v>2.56</v>
+      </c>
+      <c r="AB300">
+        <v>1.46</v>
+      </c>
+      <c r="AC300">
+        <v>5.18</v>
+      </c>
+      <c r="AD300">
+        <v>1.14</v>
+      </c>
+      <c r="AE300">
+        <v>1.04</v>
+      </c>
+      <c r="AF300">
         <v>2.15</v>
       </c>
-      <c r="U300">
-        <v>4.1</v>
-      </c>
-      <c r="V300">
-        <v>1.2</v>
-      </c>
-      <c r="W300">
-        <v>1.03</v>
-      </c>
-      <c r="X300">
-        <v>1.1</v>
-      </c>
-      <c r="Y300">
-        <v>1.66</v>
-      </c>
-      <c r="Z300">
-        <v>2.05</v>
-      </c>
-      <c r="AA300">
-        <v>3.4</v>
-      </c>
-      <c r="AB300">
+      <c r="AG300">
+        <v>1.61</v>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ300">
         <v>1.33</v>
       </c>
-      <c r="AC300">
-        <v>6.05</v>
-      </c>
-      <c r="AD300">
-        <v>1.06</v>
-      </c>
-      <c r="AE300">
-        <v>1.02</v>
-      </c>
-      <c r="AF300">
-        <v>2.57</v>
-      </c>
-      <c r="AG300">
-        <v>1.42</v>
-      </c>
-      <c r="AH300" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI300" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ300">
-        <v>1.1</v>
-      </c>
       <c r="AK300">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49719,7 +49719,7 @@
         <v>5.2</v>
       </c>
       <c r="U303">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V303">
         <v>1.88</v>
@@ -49864,7 +49864,7 @@
         <v>2.62</v>
       </c>
       <c r="O304">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P304">
         <v>2.3</v>
@@ -50389,10 +50389,10 @@
         <v>4.95</v>
       </c>
       <c r="AA307">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB307">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AC307">
         <v>2.25</v>
@@ -50715,7 +50715,7 @@
         <v>6.25</v>
       </c>
       <c r="AA309">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB309">
         <v>3.1</v>
@@ -50881,7 +50881,7 @@
         <v>1.78</v>
       </c>
       <c r="AB310">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC310">
         <v>2.88</v>
@@ -51005,7 +51005,7 @@
         <v>3.6</v>
       </c>
       <c r="O311">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="P311">
         <v>1.82</v>
@@ -51041,10 +51041,10 @@
         <v>4.8</v>
       </c>
       <c r="AA311">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB311">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC311">
         <v>2.33</v>
@@ -51207,7 +51207,7 @@
         <v>1.72</v>
       </c>
       <c r="AB312">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC312">
         <v>2.61</v>
@@ -51491,31 +51491,31 @@
         </is>
       </c>
       <c r="N314">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="O314">
-        <v>4.88</v>
+        <v>4.66</v>
       </c>
       <c r="P314">
         <v>8</v>
       </c>
       <c r="Q314">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="R314">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="S314">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T314">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="U314">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="V314">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W314">
         <v>1.08</v>
@@ -51524,31 +51524,31 @@
         <v>1.01</v>
       </c>
       <c r="Y314">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z314">
         <v>4.33</v>
       </c>
       <c r="AA314">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB314">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC314">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AD314">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE314">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF314">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG314">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK314">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51859,7 +51859,7 @@
         <v>1.66</v>
       </c>
       <c r="AB316">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AC316">
         <v>2.6</v>
@@ -52146,7 +52146,7 @@
         <v>3.4</v>
       </c>
       <c r="O318">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="P318">
         <v>2.13</v>
@@ -52309,7 +52309,7 @@
         <v>6.5</v>
       </c>
       <c r="O319">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="P319">
         <v>1.3</v>
@@ -52472,10 +52472,10 @@
         <v>1.61</v>
       </c>
       <c r="O320">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="P320">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q320">
         <v>1.95</v>
@@ -52511,7 +52511,7 @@
         <v>1.47</v>
       </c>
       <c r="AB320">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC320">
         <v>2.15</v>
@@ -52804,34 +52804,34 @@
         <v>2.6</v>
       </c>
       <c r="Q322">
+        <v>3.5</v>
+      </c>
+      <c r="R322">
+        <v>1.91</v>
+      </c>
+      <c r="S322">
+        <v>1.52</v>
+      </c>
+      <c r="T322">
+        <v>2.27</v>
+      </c>
+      <c r="U322">
         <v>3.6</v>
-      </c>
-      <c r="R322">
-        <v>2</v>
-      </c>
-      <c r="S322">
-        <v>1.44</v>
-      </c>
-      <c r="T322">
-        <v>2.5</v>
-      </c>
-      <c r="U322">
-        <v>3.4</v>
       </c>
       <c r="V322">
         <v>1.29</v>
       </c>
       <c r="W322">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X322">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y322">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z322">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="AA322">
         <v>2.5</v>
@@ -52840,19 +52840,19 @@
         <v>1.5</v>
       </c>
       <c r="AC322">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AD322">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE322">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF322">
         <v>2</v>
       </c>
       <c r="AG322">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AK322">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -53797,7 +53797,7 @@
         <v>3.42</v>
       </c>
       <c r="V328">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W328">
         <v>1.01</v>
@@ -54434,7 +54434,7 @@
         <v>2.1</v>
       </c>
       <c r="Q332">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R332">
         <v>2.14</v>
@@ -55086,10 +55086,10 @@
         <v>7.13</v>
       </c>
       <c r="Q336">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="R336">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S336">
         <v>1.18</v>
@@ -55113,28 +55113,28 @@
         <v>1.11</v>
       </c>
       <c r="Z336">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA336">
         <v>1.53</v>
       </c>
       <c r="AB336">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC336">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AD336">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE336">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF336">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG336">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55147,10 +55147,10 @@
         </is>
       </c>
       <c r="AJ336">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK336">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55575,16 +55575,16 @@
         <v>4.31</v>
       </c>
       <c r="Q339">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R339">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S339">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T339">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="U339">
         <v>3.2</v>
@@ -55596,34 +55596,34 @@
         <v>1.01</v>
       </c>
       <c r="X339">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y339">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z339">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA339">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB339">
         <v>1.6</v>
       </c>
       <c r="AC339">
-        <v>3.84</v>
+        <v>3.98</v>
       </c>
       <c r="AD339">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE339">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF339">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG339">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>1.24</v>
       </c>
       <c r="AK339">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55750,10 +55750,10 @@
         <v>2.34</v>
       </c>
       <c r="U340">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V340">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W340">
         <v>1.03</v>
@@ -56067,7 +56067,7 @@
         <v>2.75</v>
       </c>
       <c r="R342">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S342">
         <v>1.22</v>
@@ -56079,10 +56079,10 @@
         <v>1.95</v>
       </c>
       <c r="V342">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W342">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X342">
         <v>0</v>
@@ -56091,16 +56091,16 @@
         <v>1.09</v>
       </c>
       <c r="Z342">
-        <v>6.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA342">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB342">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC342">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AD342">
         <v>1.72</v>
@@ -56565,10 +56565,10 @@
         <v>3.25</v>
       </c>
       <c r="U345">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="V345">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W345">
         <v>1.11</v>
@@ -56586,7 +56586,7 @@
         <v>1.65</v>
       </c>
       <c r="AB345">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC345">
         <v>2.75</v>
@@ -56716,7 +56716,7 @@
         <v>2.87</v>
       </c>
       <c r="Q346">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R346">
         <v>2.5</v>
@@ -56873,7 +56873,7 @@
         <v>2.06</v>
       </c>
       <c r="O347">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="P347">
         <v>3.5</v>
@@ -57033,10 +57033,10 @@
         </is>
       </c>
       <c r="N348">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="O348">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P348">
         <v>3.4</v>
@@ -57060,7 +57060,7 @@
         <v>1.44</v>
       </c>
       <c r="W348">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X348">
         <v>1</v>
@@ -57087,10 +57087,10 @@
         <v>1.08</v>
       </c>
       <c r="AF348">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG348">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH348" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         </is>
       </c>
       <c r="AJ349">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK349">
         <v>1.73</v>
@@ -57531,7 +57531,7 @@
         <v>1.67</v>
       </c>
       <c r="Q351">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R351">
         <v>2.6</v>
@@ -57685,7 +57685,7 @@
         </is>
       </c>
       <c r="N352">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O352">
         <v>3.8</v>
@@ -58835,7 +58835,7 @@
         <v>2.88</v>
       </c>
       <c r="Q359">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R359">
         <v>2.5</v>
@@ -59001,13 +59001,13 @@
         <v>1.91</v>
       </c>
       <c r="R360">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S360">
         <v>1.2</v>
       </c>
       <c r="T360">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U360">
         <v>2.02</v>
@@ -59161,10 +59161,10 @@
         <v>3.26</v>
       </c>
       <c r="Q361">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="R361">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="S361">
         <v>1.14</v>
@@ -59315,7 +59315,7 @@
         </is>
       </c>
       <c r="N362">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="O362">
         <v>3.7</v>
@@ -59336,7 +59336,7 @@
         <v>4</v>
       </c>
       <c r="U362">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="V362">
         <v>1.65</v>
@@ -59354,25 +59354,25 @@
         <v>6</v>
       </c>
       <c r="AA362">
+        <v>1.44</v>
+      </c>
+      <c r="AB362">
+        <v>2.63</v>
+      </c>
+      <c r="AC362">
+        <v>2.08</v>
+      </c>
+      <c r="AD362">
+        <v>1.64</v>
+      </c>
+      <c r="AE362">
+        <v>1.25</v>
+      </c>
+      <c r="AF362">
         <v>1.4</v>
       </c>
-      <c r="AB362">
-        <v>2.8</v>
-      </c>
-      <c r="AC362">
-        <v>2.01</v>
-      </c>
-      <c r="AD362">
-        <v>1.69</v>
-      </c>
-      <c r="AE362">
-        <v>1.29</v>
-      </c>
-      <c r="AF362">
-        <v>1.36</v>
-      </c>
       <c r="AG362">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH362" t="inlineStr">
         <is>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O2">
         <v>3.3</v>
@@ -644,10 +644,10 @@
         <v>2.87</v>
       </c>
       <c r="Q2">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S2">
         <v>1.39</v>
@@ -674,10 +674,10 @@
         <v>3.35</v>
       </c>
       <c r="AA2">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC2">
         <v>3.55</v>
@@ -686,13 +686,13 @@
         <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.26</v>
+        <v>1.6</v>
       </c>
       <c r="O7">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="Q7">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
         <v>2.9</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V7">
         <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="AA7">
         <v>2.01</v>
       </c>
       <c r="AB7">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE7">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="P8">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="R8">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
         <v>2.9</v>
       </c>
       <c r="U8">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
         <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z8">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="AA8">
         <v>2.01</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC8">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AK8">
-        <v>2.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -4713,16 +4713,16 @@
         <v>3.8</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P27">
         <v>1.8</v>
       </c>
       <c r="Q27">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="R27">
-        <v>2.73</v>
+        <v>2.52</v>
       </c>
       <c r="S27">
         <v>1.17</v>
@@ -4731,7 +4731,7 @@
         <v>4.3</v>
       </c>
       <c r="U27">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V27">
         <v>1.73</v>
@@ -4758,16 +4758,16 @@
         <v>2</v>
       </c>
       <c r="AD27">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AE27">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG27">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>1.74</v>
       </c>
       <c r="AG38">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -7653,40 +7653,40 @@
         <v>0</v>
       </c>
       <c r="Q45">
+        <v>2.47</v>
+      </c>
+      <c r="R45">
+        <v>2.17</v>
+      </c>
+      <c r="S45">
+        <v>1.28</v>
+      </c>
+      <c r="T45">
+        <v>3.12</v>
+      </c>
+      <c r="U45">
         <v>2.4</v>
       </c>
-      <c r="R45">
-        <v>2.25</v>
-      </c>
-      <c r="S45">
-        <v>1.3</v>
-      </c>
-      <c r="T45">
-        <v>3.2</v>
-      </c>
-      <c r="U45">
-        <v>2.63</v>
-      </c>
       <c r="V45">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z45">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA45">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB45">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC45">
         <v>2.78</v>
@@ -7698,10 +7698,10 @@
         <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG45">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="O47">
         <v>3.05</v>
       </c>
       <c r="P47">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q47">
-        <v>3.38</v>
+        <v>3.52</v>
       </c>
       <c r="R47">
         <v>1.96</v>
@@ -8009,10 +8009,10 @@
         <v>2.88</v>
       </c>
       <c r="AA47">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB47">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC47">
         <v>3.74</v>
@@ -10916,52 +10916,52 @@
         <v>3.1</v>
       </c>
       <c r="R65">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S65">
         <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U65">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V65">
         <v>1.4</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z65">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA65">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AB65">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC65">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD65">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF65">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG65">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O70">
         <v>4.45</v>
@@ -11882,55 +11882,55 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="O71">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P71">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q71">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T71">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="U71">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="V71">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W71">
         <v>1.07</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z71">
-        <v>3.28</v>
+        <v>3.83</v>
       </c>
       <c r="AA71">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AC71">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="AD71">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE71">
         <v>1.08</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="O74">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="P74">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="Q74">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="R74">
         <v>2.38</v>
       </c>
       <c r="S74">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="U74">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="V74">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X74">
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z74">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA74">
+        <v>1.66</v>
+      </c>
+      <c r="AB74">
+        <v>2.15</v>
+      </c>
+      <c r="AC74">
+        <v>2.72</v>
+      </c>
+      <c r="AD74">
+        <v>1.45</v>
+      </c>
+      <c r="AE74">
+        <v>1.13</v>
+      </c>
+      <c r="AF74">
         <v>1.57</v>
       </c>
-      <c r="AB74">
-        <v>2.36</v>
-      </c>
-      <c r="AC74">
-        <v>2.47</v>
-      </c>
-      <c r="AD74">
-        <v>1.54</v>
-      </c>
-      <c r="AE74">
-        <v>1.15</v>
-      </c>
-      <c r="AF74">
-        <v>1.53</v>
-      </c>
       <c r="AG74">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK74">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="O75">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="P75">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="Q75">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="R75">
         <v>2.38</v>
       </c>
       <c r="S75">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T75">
-        <v>3.46</v>
+        <v>3.65</v>
       </c>
       <c r="U75">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="V75">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W75">
+        <v>1.11</v>
+      </c>
+      <c r="X75">
+        <v>1.03</v>
+      </c>
+      <c r="Y75">
         <v>1.12</v>
       </c>
-      <c r="X75">
-        <v>1.02</v>
-      </c>
-      <c r="Y75">
-        <v>1.17</v>
-      </c>
       <c r="Z75">
-        <v>4.05</v>
+        <v>4.44</v>
       </c>
       <c r="AA75">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB75">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AC75">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="AD75">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE75">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF75">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG75">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.29</v>
+        <v>1.93</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13201,10 +13201,10 @@
         <v>3.54</v>
       </c>
       <c r="S79">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T79">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U79">
         <v>1.74</v>
@@ -13521,25 +13521,25 @@
         <v>2.38</v>
       </c>
       <c r="Q81">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S81">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T81">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="U81">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V81">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W81">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
         <v>1</v>
@@ -13551,10 +13551,10 @@
         <v>3.2</v>
       </c>
       <c r="AA81">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB81">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC81">
         <v>3.2</v>
@@ -13569,7 +13569,7 @@
         <v>1.69</v>
       </c>
       <c r="AG81">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK81">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,61 +14816,61 @@
         </is>
       </c>
       <c r="N89">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P89">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q89">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="R89">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T89">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="U89">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z89">
-        <v>5.05</v>
+        <v>4.7</v>
       </c>
       <c r="AA89">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB89">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC89">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="AD89">
         <v>1.51</v>
       </c>
       <c r="AE89">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF89">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG89">
         <v>2.45</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK89">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,61 +15142,61 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O91">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P91">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q91">
-        <v>2.89</v>
+        <v>2.38</v>
       </c>
       <c r="R91">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S91">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="U91">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V91">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W91">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z91">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="AA91">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AB91">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC91">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AD91">
         <v>1.51</v>
       </c>
       <c r="AE91">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF91">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG91">
         <v>2.45</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O98">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P98">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="Q98">
-        <v>5.65</v>
+        <v>5.05</v>
       </c>
       <c r="R98">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="S98">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T98">
         <v>3.1</v>
       </c>
       <c r="U98">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V98">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W98">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X98">
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z98">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AA98">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB98">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC98">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD98">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE98">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF98">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AG98">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="AK98">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16944,16 +16944,16 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R102">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
         <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
         <v>2.88</v>
@@ -16962,22 +16962,22 @@
         <v>1.36</v>
       </c>
       <c r="W102">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z102">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA102">
         <v>2</v>
       </c>
       <c r="AB102">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC102">
         <v>3.42</v>
@@ -16989,11 +16989,11 @@
         <v>1.04</v>
       </c>
       <c r="AF102">
+        <v>1.85</v>
+      </c>
+      <c r="AG102">
         <v>1.82</v>
       </c>
-      <c r="AG102">
-        <v>1.85</v>
-      </c>
       <c r="AH102" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>2.8</v>
       </c>
       <c r="Q106">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R106">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T106">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U106">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V106">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W106">
         <v>1.06</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z106">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AA106">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AB106">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AC106">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD106">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE106">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF106">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG106">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK106">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -19407,7 +19407,7 @@
         <v>1.35</v>
       </c>
       <c r="W117">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X117">
         <v>1.03</v>
@@ -19552,16 +19552,16 @@
         <v>3.7</v>
       </c>
       <c r="Q118">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="R118">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S118">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T118">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="U118">
         <v>2.75</v>
@@ -19588,10 +19588,10 @@
         <v>1.88</v>
       </c>
       <c r="AC118">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="AD118">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE118">
         <v>1.11</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
         <v>1.88</v>
@@ -19706,7 +19706,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="O119">
         <v>3.6</v>
@@ -19718,7 +19718,7 @@
         <v>2.52</v>
       </c>
       <c r="R119">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S119">
         <v>1.34</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -23304,19 +23304,19 @@
         <v>1.8</v>
       </c>
       <c r="R141">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="S141">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T141">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U141">
         <v>2.13</v>
       </c>
       <c r="V141">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="W141">
         <v>1.12</v>
@@ -23331,10 +23331,10 @@
         <v>5.35</v>
       </c>
       <c r="AA141">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB141">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC141">
         <v>2.15</v>
@@ -23343,7 +23343,7 @@
         <v>1.6</v>
       </c>
       <c r="AE141">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF141">
         <v>1.62</v>
@@ -23365,7 +23365,7 @@
         <v>1.11</v>
       </c>
       <c r="AK141">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23663,7 +23663,7 @@
         <v>2.39</v>
       </c>
       <c r="AC143">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD143">
         <v>1.59</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="O157">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P157">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q157">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="R157">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="S157">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T157">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="U157">
-        <v>2.29</v>
+        <v>2.01</v>
       </c>
       <c r="V157">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="W157">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X157">
         <v>1.01</v>
       </c>
       <c r="Y157">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z157">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AA157">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AB157">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AC157">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="AD157">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="AE157">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AF157">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AG157">
-        <v>2.39</v>
+        <v>2.93</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AK157">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,80 +26063,80 @@
         </is>
       </c>
       <c r="N158">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O158">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="P158">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="Q158">
-        <v>5.2</v>
+        <v>3.04</v>
       </c>
       <c r="R158">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="S158">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T158">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U158">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="V158">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W158">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X158">
         <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Z158">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA158">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AB158">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC158">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="AD158">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AE158">
+        <v>1.2</v>
+      </c>
+      <c r="AF158">
+        <v>1.47</v>
+      </c>
+      <c r="AG158">
+        <v>2.39</v>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ158">
         <v>1.23</v>
       </c>
-      <c r="AF158">
-        <v>1.51</v>
-      </c>
-      <c r="AG158">
-        <v>2.4</v>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ158">
-        <v>1.22</v>
-      </c>
       <c r="AK158">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="O159">
+        <v>4.35</v>
+      </c>
+      <c r="P159">
+        <v>1.61</v>
+      </c>
+      <c r="Q159">
+        <v>5.2</v>
+      </c>
+      <c r="R159">
+        <v>2.51</v>
+      </c>
+      <c r="S159">
+        <v>1.23</v>
+      </c>
+      <c r="T159">
         <v>4</v>
       </c>
-      <c r="P159">
-        <v>1.8</v>
-      </c>
-      <c r="Q159">
-        <v>4.1</v>
-      </c>
-      <c r="R159">
-        <v>2.41</v>
-      </c>
-      <c r="S159">
+      <c r="U159">
+        <v>2.05</v>
+      </c>
+      <c r="V159">
+        <v>1.7</v>
+      </c>
+      <c r="W159">
+        <v>1.15</v>
+      </c>
+      <c r="X159">
+        <v>1.01</v>
+      </c>
+      <c r="Y159">
+        <v>1.09</v>
+      </c>
+      <c r="Z159">
+        <v>5.3</v>
+      </c>
+      <c r="AA159">
+        <v>1.44</v>
+      </c>
+      <c r="AB159">
+        <v>2.7</v>
+      </c>
+      <c r="AC159">
+        <v>2.32</v>
+      </c>
+      <c r="AD159">
+        <v>1.71</v>
+      </c>
+      <c r="AE159">
+        <v>1.23</v>
+      </c>
+      <c r="AF159">
+        <v>1.51</v>
+      </c>
+      <c r="AG159">
+        <v>2.4</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.22</v>
       </c>
-      <c r="T159">
-        <v>3.94</v>
-      </c>
-      <c r="U159">
-        <v>2.01</v>
-      </c>
-      <c r="V159">
-        <v>1.81</v>
-      </c>
-      <c r="W159">
-        <v>1.2</v>
-      </c>
-      <c r="X159">
-        <v>1.02</v>
-      </c>
-      <c r="Y159">
-        <v>1.05</v>
-      </c>
-      <c r="Z159">
-        <v>6.4</v>
-      </c>
-      <c r="AA159">
-        <v>1.34</v>
-      </c>
-      <c r="AB159">
-        <v>2.93</v>
-      </c>
-      <c r="AC159">
-        <v>1.98</v>
-      </c>
-      <c r="AD159">
-        <v>1.96</v>
-      </c>
-      <c r="AE159">
-        <v>1.34</v>
-      </c>
-      <c r="AF159">
-        <v>1.35</v>
-      </c>
-      <c r="AG159">
-        <v>2.93</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>2</v>
-      </c>
       <c r="AK159">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="O161">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="P161">
-        <v>10</v>
+        <v>2.55</v>
       </c>
       <c r="Q161">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="R161">
-        <v>3.06</v>
+        <v>2.45</v>
       </c>
       <c r="S161">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="T161">
-        <v>4.45</v>
+        <v>3.58</v>
       </c>
       <c r="U161">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="V161">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="W161">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X161">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y161">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z161">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AA161">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AB161">
-        <v>2.98</v>
+        <v>2.33</v>
       </c>
       <c r="AC161">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="AD161">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AE161">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AF161">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AG161">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AK161">
-        <v>4.26</v>
+        <v>1.6</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="O162">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="P162">
-        <v>2.55</v>
+        <v>10</v>
       </c>
       <c r="Q162">
-        <v>2.92</v>
+        <v>1.57</v>
       </c>
       <c r="R162">
-        <v>2.45</v>
+        <v>3.06</v>
       </c>
       <c r="S162">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="T162">
-        <v>3.58</v>
+        <v>4.45</v>
       </c>
       <c r="U162">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="V162">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="W162">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X162">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z162">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AA162">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AB162">
-        <v>2.33</v>
+        <v>2.98</v>
       </c>
       <c r="AC162">
-        <v>2.29</v>
+        <v>1.87</v>
       </c>
       <c r="AD162">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AE162">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AF162">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG162">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AK162">
-        <v>1.6</v>
+        <v>4.26</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -27409,7 +27409,7 @@
         <v>1.72</v>
       </c>
       <c r="AB166">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AC166">
         <v>2.74</v>
@@ -27548,7 +27548,7 @@
         <v>1.25</v>
       </c>
       <c r="T167">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U167">
         <v>2.28</v>
@@ -27587,7 +27587,7 @@
         <v>1.58</v>
       </c>
       <c r="AG167">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -28022,13 +28022,13 @@
         <v>3.14</v>
       </c>
       <c r="O170">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P170">
         <v>2.18</v>
       </c>
       <c r="Q170">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R170">
         <v>2.05</v>
@@ -28061,7 +28061,7 @@
         <v>2.18</v>
       </c>
       <c r="AB170">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC170">
         <v>3.94</v>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AK170">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,61 +28834,61 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O175">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P175">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="Q175">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="R175">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S175">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T175">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="U175">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V175">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W175">
         <v>1.06</v>
       </c>
       <c r="X175">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y175">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z175">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA175">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AB175">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC175">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD175">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE175">
         <v>1.05</v>
       </c>
       <c r="AF175">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG175">
         <v>1.97</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK175">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,31 +28997,31 @@
         </is>
       </c>
       <c r="N176">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O176">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P176">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q176">
-        <v>2.81</v>
+        <v>2.36</v>
       </c>
       <c r="R176">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S176">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T176">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="U176">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="V176">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W176">
         <v>1.06</v>
@@ -29030,31 +29030,31 @@
         <v>1.04</v>
       </c>
       <c r="Y176">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z176">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA176">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AB176">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AC176">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD176">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE176">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF176">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG176">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK176">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="O177">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P177">
-        <v>3.9</v>
+        <v>2.31</v>
       </c>
       <c r="Q177">
-        <v>2.36</v>
+        <v>3.12</v>
       </c>
       <c r="R177">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S177">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T177">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
       <c r="U177">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="V177">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W177">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X177">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y177">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z177">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA177">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AB177">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AC177">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AD177">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE177">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AG177">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK177">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,65 +29323,65 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.7</v>
+        <v>2.61</v>
       </c>
       <c r="O178">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P178">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q178">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="R178">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S178">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T178">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U178">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V178">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W178">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X178">
         <v>1.04</v>
       </c>
       <c r="Y178">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z178">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA178">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB178">
+        <v>1.9</v>
+      </c>
+      <c r="AC178">
+        <v>2.92</v>
+      </c>
+      <c r="AD178">
+        <v>1.33</v>
+      </c>
+      <c r="AE178">
+        <v>1.13</v>
+      </c>
+      <c r="AF178">
+        <v>1.65</v>
+      </c>
+      <c r="AG178">
         <v>2.1</v>
       </c>
-      <c r="AC178">
-        <v>2.98</v>
-      </c>
-      <c r="AD178">
-        <v>1.34</v>
-      </c>
-      <c r="AE178">
-        <v>1.09</v>
-      </c>
-      <c r="AF178">
-        <v>1.57</v>
-      </c>
-      <c r="AG178">
-        <v>2.25</v>
-      </c>
       <c r="AH178" t="inlineStr">
         <is>
           <t>[]</t>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK178">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O179">
         <v>3.7</v>
       </c>
       <c r="P179">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q179">
-        <v>4.11</v>
+        <v>3.7</v>
       </c>
       <c r="R179">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S179">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T179">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="U179">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="V179">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W179">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X179">
         <v>1.02</v>
       </c>
       <c r="Y179">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z179">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="AA179">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB179">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AC179">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD179">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE179">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF179">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG179">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK179">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="O180">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P180">
-        <v>2.31</v>
+        <v>2.87</v>
       </c>
       <c r="Q180">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="R180">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="S180">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T180">
-        <v>3.46</v>
+        <v>2.87</v>
       </c>
       <c r="U180">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="V180">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W180">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X180">
         <v>1.02</v>
       </c>
       <c r="Y180">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z180">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA180">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AB180">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="AC180">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="AD180">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AE180">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF180">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AG180">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK180">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="O181">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P181">
-        <v>2.05</v>
+        <v>3.95</v>
       </c>
       <c r="Q181">
-        <v>3.7</v>
+        <v>2.21</v>
       </c>
       <c r="R181">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S181">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T181">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U181">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="V181">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W181">
+        <v>1.08</v>
+      </c>
+      <c r="X181">
+        <v>1.04</v>
+      </c>
+      <c r="Y181">
+        <v>1.18</v>
+      </c>
+      <c r="Z181">
+        <v>3.82</v>
+      </c>
+      <c r="AA181">
+        <v>1.73</v>
+      </c>
+      <c r="AB181">
+        <v>2.1</v>
+      </c>
+      <c r="AC181">
+        <v>2.98</v>
+      </c>
+      <c r="AD181">
+        <v>1.34</v>
+      </c>
+      <c r="AE181">
         <v>1.09</v>
-      </c>
-      <c r="X181">
-        <v>1.02</v>
-      </c>
-      <c r="Y181">
-        <v>1.17</v>
-      </c>
-      <c r="Z181">
-        <v>3.94</v>
-      </c>
-      <c r="AA181">
-        <v>1.67</v>
-      </c>
-      <c r="AB181">
-        <v>2.06</v>
-      </c>
-      <c r="AC181">
-        <v>2.56</v>
-      </c>
-      <c r="AD181">
-        <v>1.4</v>
-      </c>
-      <c r="AE181">
-        <v>1.13</v>
       </c>
       <c r="AF181">
         <v>1.57</v>
       </c>
       <c r="AG181">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK181">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="O182">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P182">
-        <v>4.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q182">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="R182">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="S182">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T182">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="U182">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="V182">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W182">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X182">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y182">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z182">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA182">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AB182">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC182">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="AD182">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE182">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF182">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG182">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>1.22</v>
       </c>
       <c r="AK182">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,19 +30138,19 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.61</v>
+        <v>1.75</v>
       </c>
       <c r="O183">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P183">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q183">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R183">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S183">
         <v>1.31</v>
@@ -30159,43 +30159,43 @@
         <v>3.08</v>
       </c>
       <c r="U183">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="V183">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W183">
         <v>1.07</v>
       </c>
       <c r="X183">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y183">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z183">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA183">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB183">
         <v>1.9</v>
       </c>
       <c r="AC183">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD183">
         <v>1.33</v>
       </c>
       <c r="AE183">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF183">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG183">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK183">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30340,16 +30340,16 @@
         <v>5</v>
       </c>
       <c r="AA184">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB184">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC184">
         <v>2.36</v>
       </c>
       <c r="AD184">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE184">
         <v>1.2</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30636,7 +30636,7 @@
         <v>3</v>
       </c>
       <c r="Q186">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="R186">
         <v>2.07</v>
@@ -30672,7 +30672,7 @@
         <v>1.78</v>
       </c>
       <c r="AC186">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="AD186">
         <v>1.25</v>
@@ -31442,37 +31442,37 @@
         </is>
       </c>
       <c r="N191">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O191">
         <v>3.54</v>
       </c>
       <c r="P191">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q191">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R191">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S191">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T191">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="U191">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="V191">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W191">
         <v>1.07</v>
       </c>
       <c r="X191">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
         <v>1.22</v>
@@ -31487,19 +31487,19 @@
         <v>1.9</v>
       </c>
       <c r="AC191">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD191">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE191">
         <v>1.07</v>
       </c>
       <c r="AF191">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG191">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK191">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31611,10 +31611,10 @@
         <v>3.8</v>
       </c>
       <c r="P192">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="Q192">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="R192">
         <v>2.22</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="O193">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P193">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q193">
         <v>3.4</v>
@@ -31783,7 +31783,7 @@
         <v>2.3</v>
       </c>
       <c r="S193">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T193">
         <v>3.18</v>
@@ -31804,25 +31804,25 @@
         <v>1.23</v>
       </c>
       <c r="Z193">
-        <v>4.03</v>
+        <v>3.55</v>
       </c>
       <c r="AA193">
         <v>1.69</v>
       </c>
       <c r="AB193">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC193">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AD193">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE193">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF193">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG193">
         <v>2.25</v>
@@ -31946,10 +31946,10 @@
         <v>2.3</v>
       </c>
       <c r="S194">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T194">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U194">
         <v>2.4</v>
@@ -31958,37 +31958,37 @@
         <v>1.5</v>
       </c>
       <c r="W194">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X194">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
         <v>1.17</v>
       </c>
       <c r="Z194">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA194">
         <v>1.67</v>
       </c>
       <c r="AB194">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC194">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AD194">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE194">
         <v>1.12</v>
       </c>
       <c r="AF194">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG194">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>1.25</v>
       </c>
       <c r="AK194">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.6</v>
+        <v>1.49</v>
       </c>
       <c r="O195">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P195">
-        <v>2.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q195">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="R195">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="S195">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="T195">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="U195">
-        <v>2.83</v>
+        <v>2</v>
       </c>
       <c r="V195">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="W195">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="Z195">
-        <v>3.28</v>
+        <v>5.99</v>
       </c>
       <c r="AA195">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="AB195">
-        <v>1.81</v>
+        <v>2.88</v>
       </c>
       <c r="AC195">
-        <v>3.05</v>
+        <v>2.07</v>
       </c>
       <c r="AD195">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="AE195">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AF195">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AG195">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK195">
-        <v>1.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O196">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P196">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="Q196">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R196">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S196">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T196">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="U196">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V196">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W196">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X196">
         <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z196">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA196">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB196">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC196">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AD196">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE196">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF196">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG196">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK196">
-        <v>1.88</v>
+        <v>1.47</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.42</v>
+        <v>1.91</v>
       </c>
       <c r="O197">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P197">
-        <v>6.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q197">
+        <v>2.5</v>
+      </c>
+      <c r="R197">
+        <v>2.15</v>
+      </c>
+      <c r="S197">
+        <v>1.38</v>
+      </c>
+      <c r="T197">
+        <v>2.74</v>
+      </c>
+      <c r="U197">
+        <v>2.9</v>
+      </c>
+      <c r="V197">
+        <v>1.36</v>
+      </c>
+      <c r="W197">
+        <v>1.03</v>
+      </c>
+      <c r="X197">
+        <v>1.01</v>
+      </c>
+      <c r="Y197">
+        <v>1.32</v>
+      </c>
+      <c r="Z197">
+        <v>3.14</v>
+      </c>
+      <c r="AA197">
+        <v>1.98</v>
+      </c>
+      <c r="AB197">
+        <v>1.77</v>
+      </c>
+      <c r="AC197">
+        <v>3.42</v>
+      </c>
+      <c r="AD197">
+        <v>1.23</v>
+      </c>
+      <c r="AE197">
+        <v>1.04</v>
+      </c>
+      <c r="AF197">
         <v>1.85</v>
       </c>
-      <c r="R197">
-        <v>2.63</v>
-      </c>
-      <c r="S197">
-        <v>1.21</v>
-      </c>
-      <c r="T197">
-        <v>4.1</v>
-      </c>
-      <c r="U197">
-        <v>2</v>
-      </c>
-      <c r="V197">
-        <v>1.75</v>
-      </c>
-      <c r="W197">
-        <v>1.15</v>
-      </c>
-      <c r="X197">
-        <v>1.02</v>
-      </c>
-      <c r="Y197">
-        <v>1.1</v>
-      </c>
-      <c r="Z197">
-        <v>5.2</v>
-      </c>
-      <c r="AA197">
-        <v>1.4</v>
-      </c>
-      <c r="AB197">
-        <v>2.88</v>
-      </c>
-      <c r="AC197">
-        <v>2.11</v>
-      </c>
-      <c r="AD197">
-        <v>1.68</v>
-      </c>
-      <c r="AE197">
-        <v>1.25</v>
-      </c>
-      <c r="AF197">
-        <v>1.6</v>
-      </c>
       <c r="AG197">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK197">
-        <v>2.78</v>
+        <v>1.88</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32592,7 +32592,7 @@
         <v>3.25</v>
       </c>
       <c r="Q198">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="R198">
         <v>2.2</v>
@@ -32631,10 +32631,10 @@
         <v>2.97</v>
       </c>
       <c r="AD198">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE198">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF198">
         <v>1.66</v>
@@ -33730,7 +33730,7 @@
         <v>3.7</v>
       </c>
       <c r="P205">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q205">
         <v>3.95</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,80 +34050,80 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.22</v>
+        <v>1.94</v>
       </c>
       <c r="O207">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="P207">
-        <v>9.5</v>
+        <v>3.93</v>
       </c>
       <c r="Q207">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="R207">
-        <v>2.76</v>
+        <v>2.1</v>
       </c>
       <c r="S207">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="T207">
-        <v>4.15</v>
+        <v>2.6</v>
       </c>
       <c r="U207">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="V207">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="W207">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X207">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y207">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="Z207">
-        <v>5.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA207">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AB207">
-        <v>2.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC207">
-        <v>2.04</v>
+        <v>3.92</v>
       </c>
       <c r="AD207">
-        <v>1.73</v>
+        <v>1.18</v>
       </c>
       <c r="AE207">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AF207">
+        <v>1.95</v>
+      </c>
+      <c r="AG207">
+        <v>1.76</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
+        <v>1.25</v>
+      </c>
+      <c r="AK207">
         <v>1.83</v>
-      </c>
-      <c r="AG207">
-        <v>1.87</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.1</v>
-      </c>
-      <c r="AK207">
-        <v>4.05</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="O208">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P208">
-        <v>2.63</v>
+        <v>4.55</v>
       </c>
       <c r="Q208">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="R208">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
       <c r="S208">
         <v>1.3</v>
       </c>
       <c r="T208">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U208">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="V208">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W208">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X208">
         <v>1.02</v>
       </c>
       <c r="Y208">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z208">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="AA208">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB208">
         <v>2.15</v>
       </c>
       <c r="AC208">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD208">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE208">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF208">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG208">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK208">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="O209">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="P209">
-        <v>4.55</v>
+        <v>2.68</v>
       </c>
       <c r="Q209">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="R209">
-        <v>2.44</v>
+        <v>2.21</v>
       </c>
       <c r="S209">
         <v>1.3</v>
       </c>
       <c r="T209">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U209">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="V209">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W209">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X209">
         <v>1.02</v>
       </c>
       <c r="Y209">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z209">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="AA209">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB209">
         <v>2.15</v>
       </c>
       <c r="AC209">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD209">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE209">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF209">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG209">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK209">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.94</v>
+        <v>2.41</v>
       </c>
       <c r="O210">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P210">
-        <v>3.93</v>
+        <v>2.5</v>
       </c>
       <c r="Q210">
-        <v>2.45</v>
+        <v>3.22</v>
       </c>
       <c r="R210">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S210">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T210">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="U210">
-        <v>3.02</v>
+        <v>2.39</v>
       </c>
       <c r="V210">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="W210">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X210">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="Z210">
-        <v>2.74</v>
+        <v>4.15</v>
       </c>
       <c r="AA210">
+        <v>1.64</v>
+      </c>
+      <c r="AB210">
         <v>2.2</v>
       </c>
-      <c r="AB210">
-        <v>1.65</v>
-      </c>
       <c r="AC210">
-        <v>3.92</v>
+        <v>2.58</v>
       </c>
       <c r="AD210">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="AE210">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="AF210">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AG210">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>1.25</v>
       </c>
       <c r="AK210">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.41</v>
+        <v>1.22</v>
       </c>
       <c r="O212">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="P212">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q212">
-        <v>3.22</v>
+        <v>1.61</v>
       </c>
       <c r="R212">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
       <c r="S212">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T212">
-        <v>3.12</v>
+        <v>4.15</v>
       </c>
       <c r="U212">
-        <v>2.39</v>
+        <v>2.01</v>
       </c>
       <c r="V212">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="W212">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X212">
         <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z212">
-        <v>4.15</v>
+        <v>5.8</v>
       </c>
       <c r="AA212">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AB212">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AC212">
-        <v>2.58</v>
+        <v>2.03</v>
       </c>
       <c r="AD212">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AE212">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AF212">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AG212">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK212">
-        <v>1.43</v>
+        <v>4.05</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35028,7 +35028,7 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O213">
         <v>3.88</v>
@@ -35366,7 +35366,7 @@
         <v>3.8</v>
       </c>
       <c r="R215">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S215">
         <v>1.38</v>
@@ -36045,10 +36045,10 @@
         <v>2.88</v>
       </c>
       <c r="AA219">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB219">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC219">
         <v>3.84</v>
@@ -36202,10 +36202,10 @@
         <v>1.01</v>
       </c>
       <c r="Y220">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z220">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA220">
         <v>1.88</v>
@@ -36226,7 +36226,7 @@
         <v>1.84</v>
       </c>
       <c r="AG220">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -37005,10 +37005,10 @@
         <v>3.5</v>
       </c>
       <c r="U225">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V225">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W225">
         <v>1.14</v>
@@ -37023,13 +37023,13 @@
         <v>4.8</v>
       </c>
       <c r="AA225">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB225">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC225">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AD225">
         <v>1.47</v>
@@ -37054,7 +37054,7 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK225">
         <v>1.25</v>
@@ -37156,7 +37156,7 @@
         <v>1.17</v>
       </c>
       <c r="Q226">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R226">
         <v>3</v>
@@ -37171,13 +37171,13 @@
         <v>1.76</v>
       </c>
       <c r="V226">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="W226">
         <v>1.29</v>
       </c>
       <c r="X226">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y226">
         <v>1.02</v>
@@ -37346,7 +37346,7 @@
         <v>1.08</v>
       </c>
       <c r="Z227">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AA227">
         <v>1.47</v>
@@ -38137,7 +38137,7 @@
         <v>1.57</v>
       </c>
       <c r="R232">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="S232">
         <v>1.25</v>
@@ -38161,7 +38161,7 @@
         <v>1.15</v>
       </c>
       <c r="Z232">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA232">
         <v>1.58</v>
@@ -38179,10 +38179,10 @@
         <v>1.16</v>
       </c>
       <c r="AF232">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AG232">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -39604,10 +39604,10 @@
         <v>1.91</v>
       </c>
       <c r="R241">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="S241">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T241">
         <v>3.6</v>
@@ -39616,7 +39616,7 @@
         <v>2.25</v>
       </c>
       <c r="V241">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W241">
         <v>1.14</v>
@@ -39628,16 +39628,16 @@
         <v>1.14</v>
       </c>
       <c r="Z241">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
       <c r="AA241">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB241">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC241">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD241">
         <v>1.44</v>
@@ -39649,7 +39649,7 @@
         <v>1.67</v>
       </c>
       <c r="AG241">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK241">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -41231,28 +41231,28 @@
         <v>2.65</v>
       </c>
       <c r="Q251">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R251">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S251">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T251">
         <v>2.8</v>
       </c>
       <c r="U251">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V251">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W251">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X251">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y251">
         <v>1.18</v>
@@ -41261,7 +41261,7 @@
         <v>3.88</v>
       </c>
       <c r="AA251">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB251">
         <v>1.99</v>
@@ -41295,7 +41295,7 @@
         <v>1.27</v>
       </c>
       <c r="AK251">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41394,55 +41394,55 @@
         <v>4.5</v>
       </c>
       <c r="Q252">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R252">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S252">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T252">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U252">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="V252">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W252">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X252">
         <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z252">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AA252">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB252">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC252">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD252">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE252">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF252">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG252">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK252">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -42037,7 +42037,7 @@
         </is>
       </c>
       <c r="N256">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O256">
         <v>3.34</v>
@@ -42689,64 +42689,64 @@
         </is>
       </c>
       <c r="N260">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O260">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P260">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE260">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -46317,7 +46317,7 @@
         <v>1.93</v>
       </c>
       <c r="AB282">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC282">
         <v>3.34</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="O286">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P286">
-        <v>3.58</v>
+        <v>3.02</v>
       </c>
       <c r="Q286">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="R286">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S286">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T286">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U286">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V286">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W286">
         <v>1.03</v>
       </c>
       <c r="X286">
+        <v>1.01</v>
+      </c>
+      <c r="Y286">
+        <v>1.28</v>
+      </c>
+      <c r="Z286">
+        <v>3.08</v>
+      </c>
+      <c r="AA286">
+        <v>2</v>
+      </c>
+      <c r="AB286">
+        <v>1.8</v>
+      </c>
+      <c r="AC286">
+        <v>3.34</v>
+      </c>
+      <c r="AD286">
+        <v>1.24</v>
+      </c>
+      <c r="AE286">
         <v>1.05</v>
       </c>
-      <c r="Y286">
-        <v>1.4</v>
-      </c>
-      <c r="Z286">
-        <v>2.56</v>
-      </c>
-      <c r="AA286">
-        <v>2.35</v>
-      </c>
-      <c r="AB286">
-        <v>1.57</v>
-      </c>
-      <c r="AC286">
-        <v>4.15</v>
-      </c>
-      <c r="AD286">
-        <v>1.16</v>
-      </c>
-      <c r="AE286">
-        <v>1.02</v>
-      </c>
       <c r="AF286">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AG286">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK286">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="O287">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="P287">
-        <v>3.02</v>
+        <v>3.58</v>
       </c>
       <c r="Q287">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R287">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S287">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T287">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="U287">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V287">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W287">
         <v>1.03</v>
       </c>
       <c r="X287">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y287">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z287">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="AA287">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AB287">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC287">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="AD287">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AE287">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF287">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AG287">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK287">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47253,28 +47253,28 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="O288">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="P288">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q288">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R288">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="S288">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T288">
         <v>3.75</v>
       </c>
       <c r="U288">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="V288">
         <v>1.64</v>
@@ -47289,28 +47289,28 @@
         <v>1.14</v>
       </c>
       <c r="Z288">
-        <v>5.25</v>
+        <v>5.21</v>
       </c>
       <c r="AA288">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB288">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AC288">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD288">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AE288">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF288">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG288">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>1.2</v>
       </c>
       <c r="AK288">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -48883,64 +48883,64 @@
         </is>
       </c>
       <c r="N298">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O298">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P298">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q298">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R298">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S298">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T298">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U298">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V298">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W298">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X298">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y298">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z298">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA298">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB298">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC298">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD298">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE298">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF298">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG298">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK298">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O309">
-        <v>4.68</v>
+        <v>4.51</v>
       </c>
       <c r="P309">
-        <v>4.84</v>
+        <v>4.98</v>
       </c>
       <c r="Q309">
         <v>1.91</v>
@@ -50691,7 +50691,7 @@
         <v>2.75</v>
       </c>
       <c r="S309">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T309">
         <v>4.8</v>
@@ -50709,10 +50709,10 @@
         <v>0</v>
       </c>
       <c r="Y309">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z309">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="AA309">
         <v>1.33</v>
@@ -50721,10 +50721,10 @@
         <v>3.1</v>
       </c>
       <c r="AC309">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AD309">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE309">
         <v>1.36</v>
@@ -51497,13 +51497,13 @@
         <v>4.66</v>
       </c>
       <c r="P314">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q314">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R314">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="S314">
         <v>1.31</v>
@@ -51533,10 +51533,10 @@
         <v>1.79</v>
       </c>
       <c r="AB314">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC314">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AD314">
         <v>1.47</v>
@@ -52360,7 +52360,7 @@
         <v>1.21</v>
       </c>
       <c r="AF319">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG319">
         <v>2.05</v>
@@ -53486,7 +53486,7 @@
         <v>5.5</v>
       </c>
       <c r="AA326">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB326">
         <v>2.63</v>
@@ -54923,25 +54923,25 @@
         <v>2.11</v>
       </c>
       <c r="Q335">
-        <v>3.3</v>
+        <v>3.97</v>
       </c>
       <c r="R335">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S335">
         <v>1.25</v>
       </c>
       <c r="T335">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="U335">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="V335">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W335">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X335">
         <v>1.01</v>
@@ -54950,25 +54950,25 @@
         <v>1.13</v>
       </c>
       <c r="Z335">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA335">
         <v>1.61</v>
       </c>
       <c r="AB335">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AC335">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AD335">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE335">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF335">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG335">
         <v>2.38</v>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="AJ335">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK335">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AL335">
         <v>0</v>
@@ -55086,71 +55086,71 @@
         <v>7.13</v>
       </c>
       <c r="Q336">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="R336">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="S336">
+        <v>1.21</v>
+      </c>
+      <c r="T336">
+        <v>3.3</v>
+      </c>
+      <c r="U336">
+        <v>2.47</v>
+      </c>
+      <c r="V336">
+        <v>1.51</v>
+      </c>
+      <c r="W336">
+        <v>1.12</v>
+      </c>
+      <c r="X336">
+        <v>1.02</v>
+      </c>
+      <c r="Y336">
+        <v>1.21</v>
+      </c>
+      <c r="Z336">
+        <v>4.5</v>
+      </c>
+      <c r="AA336">
+        <v>1.65</v>
+      </c>
+      <c r="AB336">
+        <v>2.19</v>
+      </c>
+      <c r="AC336">
+        <v>2.66</v>
+      </c>
+      <c r="AD336">
+        <v>1.45</v>
+      </c>
+      <c r="AE336">
+        <v>1.16</v>
+      </c>
+      <c r="AF336">
+        <v>1.72</v>
+      </c>
+      <c r="AG336">
+        <v>1.95</v>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ336">
         <v>1.18</v>
       </c>
-      <c r="T336">
-        <v>3.75</v>
-      </c>
-      <c r="U336">
-        <v>2.25</v>
-      </c>
-      <c r="V336">
-        <v>1.57</v>
-      </c>
-      <c r="W336">
-        <v>1.14</v>
-      </c>
-      <c r="X336">
-        <v>1.01</v>
-      </c>
-      <c r="Y336">
-        <v>1.11</v>
-      </c>
-      <c r="Z336">
-        <v>4.9</v>
-      </c>
-      <c r="AA336">
-        <v>1.53</v>
-      </c>
-      <c r="AB336">
-        <v>2.33</v>
-      </c>
-      <c r="AC336">
-        <v>2.31</v>
-      </c>
-      <c r="AD336">
-        <v>1.52</v>
-      </c>
-      <c r="AE336">
-        <v>1.17</v>
-      </c>
-      <c r="AF336">
-        <v>1.75</v>
-      </c>
-      <c r="AG336">
-        <v>1.92</v>
-      </c>
-      <c r="AH336" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI336" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ336">
-        <v>1.03</v>
-      </c>
       <c r="AK336">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55575,13 +55575,13 @@
         <v>4.31</v>
       </c>
       <c r="Q339">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R339">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S339">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T339">
         <v>2.51</v>
@@ -55593,37 +55593,37 @@
         <v>1.3</v>
       </c>
       <c r="W339">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X339">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y339">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="Z339">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="AA339">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AB339">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC339">
-        <v>3.98</v>
+        <v>4.51</v>
       </c>
       <c r="AD339">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE339">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF339">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AG339">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AH339" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>1.24</v>
       </c>
       <c r="AK339">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL339">
         <v>0</v>
@@ -55753,7 +55753,7 @@
         <v>3</v>
       </c>
       <c r="V340">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W340">
         <v>1.03</v>
@@ -56058,10 +56058,10 @@
         <v>2.52</v>
       </c>
       <c r="O342">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="P342">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Q342">
         <v>2.75</v>
@@ -56097,7 +56097,7 @@
         <v>1.37</v>
       </c>
       <c r="AB342">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC342">
         <v>2.02</v>
@@ -56221,10 +56221,10 @@
         <v>1.67</v>
       </c>
       <c r="O343">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P343">
-        <v>4.37</v>
+        <v>3.81</v>
       </c>
       <c r="Q343">
         <v>2.1</v>
@@ -56263,19 +56263,19 @@
         <v>3.13</v>
       </c>
       <c r="AC343">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD343">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AE343">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AF343">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG343">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH343" t="inlineStr">
         <is>
@@ -56288,10 +56288,10 @@
         </is>
       </c>
       <c r="AJ343">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK343">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL343">
         <v>0</v>
@@ -56381,19 +56381,19 @@
         </is>
       </c>
       <c r="N344">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O344">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="P344">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="Q344">
         <v>3.4</v>
       </c>
       <c r="R344">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="S344">
         <v>1.18</v>
@@ -56402,10 +56402,10 @@
         <v>4.6</v>
       </c>
       <c r="U344">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V344">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W344">
         <v>1.25</v>
@@ -56414,22 +56414,22 @@
         <v>0</v>
       </c>
       <c r="Y344">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z344">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA344">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB344">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC344">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AD344">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AE344">
         <v>1.44</v>
@@ -56451,10 +56451,10 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK344">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56707,7 +56707,7 @@
         </is>
       </c>
       <c r="N346">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="O346">
         <v>3.9</v>
@@ -56716,7 +56716,7 @@
         <v>2.87</v>
       </c>
       <c r="Q346">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R346">
         <v>2.5</v>
@@ -56728,40 +56728,40 @@
         <v>4</v>
       </c>
       <c r="U346">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V346">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W346">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X346">
         <v>0</v>
       </c>
       <c r="Y346">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z346">
-        <v>7</v>
+        <v>5.82</v>
       </c>
       <c r="AA346">
+        <v>1.4</v>
+      </c>
+      <c r="AB346">
+        <v>2.74</v>
+      </c>
+      <c r="AC346">
+        <v>2.06</v>
+      </c>
+      <c r="AD346">
+        <v>1.75</v>
+      </c>
+      <c r="AE346">
+        <v>1.29</v>
+      </c>
+      <c r="AF346">
         <v>1.36</v>
-      </c>
-      <c r="AB346">
-        <v>3</v>
-      </c>
-      <c r="AC346">
-        <v>1.9</v>
-      </c>
-      <c r="AD346">
-        <v>1.78</v>
-      </c>
-      <c r="AE346">
-        <v>1.33</v>
-      </c>
-      <c r="AF346">
-        <v>1.33</v>
       </c>
       <c r="AG346">
         <v>2.8</v>
@@ -57235,7 +57235,7 @@
         <v>3.85</v>
       </c>
       <c r="AA349">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB349">
         <v>2.1</v>
@@ -58174,19 +58174,19 @@
         </is>
       </c>
       <c r="N355">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O355">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="P355">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q355">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="R355">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S355">
         <v>1.25</v>
@@ -58195,7 +58195,7 @@
         <v>3.6</v>
       </c>
       <c r="U355">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="V355">
         <v>1.55</v>
@@ -58204,28 +58204,28 @@
         <v>1.15</v>
       </c>
       <c r="X355">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y355">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z355">
-        <v>4.87</v>
+        <v>4.6</v>
       </c>
       <c r="AA355">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB355">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="AC355">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD355">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE355">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF355">
         <v>1.5</v>
@@ -58247,7 +58247,7 @@
         <v>1.22</v>
       </c>
       <c r="AK355">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL355">
         <v>0</v>
@@ -59001,7 +59001,7 @@
         <v>1.91</v>
       </c>
       <c r="R360">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S360">
         <v>1.2</v>
@@ -59031,7 +59031,7 @@
         <v>1.4</v>
       </c>
       <c r="AB360">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC360">
         <v>2.03</v>

--- a/jogos_2026-10-17.xlsx
+++ b/jogos_2026-10-17.xlsx
@@ -813,10 +813,10 @@
         <v>2.12</v>
       </c>
       <c r="S3">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>3.12</v>
+        <v>2.92</v>
       </c>
       <c r="U3">
         <v>2.75</v>
@@ -834,13 +834,13 @@
         <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AB3">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AC3">
         <v>2.88</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O4">
         <v>3.1</v>
@@ -970,16 +970,16 @@
         <v>2.8</v>
       </c>
       <c r="Q4">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R4">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T4">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="U4">
         <v>2.76</v>
@@ -1000,16 +1000,16 @@
         <v>3.08</v>
       </c>
       <c r="AA4">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AB4">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
         <v>1.06</v>
@@ -1018,7 +1018,7 @@
         <v>1.74</v>
       </c>
       <c r="AG4">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1163,25 +1163,25 @@
         <v>4.15</v>
       </c>
       <c r="AA5">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB5">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC5">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AD5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
         <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2.6</v>
       </c>
       <c r="Q6">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="R6">
         <v>2.06</v>
@@ -1308,43 +1308,43 @@
         <v>2.88</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z6">
-        <v>3.43</v>
+        <v>3.14</v>
       </c>
       <c r="AA6">
         <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="AD6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1462,22 +1462,22 @@
         <v>2.2</v>
       </c>
       <c r="R7">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V7">
         <v>1.4</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1</v>
@@ -1486,7 +1486,7 @@
         <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="AA7">
         <v>2.01</v>
@@ -1495,10 +1495,10 @@
         <v>1.78</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE7">
         <v>1.06</v>
@@ -1507,7 +1507,7 @@
         <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1622,13 +1622,13 @@
         <v>2.84</v>
       </c>
       <c r="Q8">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
         <v>2.9</v>
@@ -1637,7 +1637,7 @@
         <v>2.75</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
         <v>1.05</v>
@@ -1646,25 +1646,25 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z8">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA8">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AB8">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AD8">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
         <v>1.73</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,16 +1785,16 @@
         <v>2.04</v>
       </c>
       <c r="Q9">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="R9">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="U9">
         <v>2.24</v>
@@ -1806,7 +1806,7 @@
         <v>1.17</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.11</v>
@@ -1815,7 +1815,7 @@
         <v>4.8</v>
       </c>
       <c r="AA9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB9">
         <v>2.48</v>
@@ -1824,7 +1824,7 @@
         <v>2.28</v>
       </c>
       <c r="AD9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE9">
         <v>1.17</v>
@@ -1833,7 +1833,7 @@
         <v>1.46</v>
       </c>
       <c r="AG9">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK9">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,49 +1948,49 @@
         <v>2.81</v>
       </c>
       <c r="Q10">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="R10">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="S10">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U10">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
+        <v>1.03</v>
+      </c>
+      <c r="X10">
         <v>1.05</v>
       </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
       <c r="Y10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z10">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AA10">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC10">
-        <v>4.53</v>
+        <v>4.6</v>
       </c>
       <c r="AD10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE10">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
         <v>1.95</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
         <v>1.39</v>
@@ -2105,10 +2105,10 @@
         <v>3.2</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="P11">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -2129,7 +2129,7 @@
         <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.03</v>
@@ -2147,13 +2147,13 @@
         <v>1.99</v>
       </c>
       <c r="AC11">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AD11">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE11">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.61</v>
@@ -2274,10 +2274,10 @@
         <v>5.55</v>
       </c>
       <c r="Q12">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="R12">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="S12">
         <v>1.25</v>
@@ -2310,7 +2310,7 @@
         <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="AD12">
         <v>1.42</v>
@@ -2437,7 +2437,7 @@
         <v>6.8</v>
       </c>
       <c r="Q13">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="R13">
         <v>2.62</v>
@@ -2485,7 +2485,7 @@
         <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AC14">
         <v>2.83</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.73</v>
+        <v>1.28</v>
       </c>
       <c r="AK14">
         <v>1.29</v>
@@ -2787,7 +2787,7 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
         <v>2.92</v>
@@ -2802,7 +2802,7 @@
         <v>3.84</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
@@ -3083,19 +3083,19 @@
         <v>2.5</v>
       </c>
       <c r="O17">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
         <v>2.3</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="R17">
         <v>2.4</v>
       </c>
       <c r="S17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
         <v>4</v>
@@ -3107,22 +3107,22 @@
         <v>1.6</v>
       </c>
       <c r="W17">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z17">
-        <v>4.85</v>
+        <v>5.13</v>
       </c>
       <c r="AA17">
         <v>1.47</v>
       </c>
       <c r="AB17">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AC17">
         <v>2.32</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AK17">
         <v>1.43</v>
@@ -3249,19 +3249,19 @@
         <v>4.33</v>
       </c>
       <c r="P18">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Q18">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S18">
         <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="U18">
         <v>2.4</v>
@@ -3294,7 +3294,7 @@
         <v>1.41</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
         <v>1.73</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
         <v>2.63</v>
@@ -3415,7 +3415,7 @@
         <v>2</v>
       </c>
       <c r="Q19">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="R19">
         <v>2.05</v>
@@ -3424,7 +3424,7 @@
         <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
         <v>2.88</v>
@@ -3433,7 +3433,7 @@
         <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="AK19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3747,7 +3747,7 @@
         <v>2.25</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
         <v>3.3</v>
@@ -3789,7 +3789,7 @@
         <v>1.66</v>
       </c>
       <c r="AG21">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3904,22 +3904,22 @@
         <v>4.35</v>
       </c>
       <c r="Q22">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="U22">
-        <v>3.09</v>
+        <v>2.73</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -3928,22 +3928,22 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z22">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="AA22">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="AB22">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC22">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AD22">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE22">
         <v>1.04</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q23">
+        <v>3.58</v>
+      </c>
+      <c r="R23">
+        <v>2.15</v>
+      </c>
+      <c r="S23">
+        <v>1.4</v>
+      </c>
+      <c r="T23">
+        <v>2.84</v>
+      </c>
+      <c r="U23">
+        <v>2.75</v>
+      </c>
+      <c r="V23">
+        <v>1.34</v>
+      </c>
+      <c r="W23">
+        <v>1.08</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
+        <v>1.32</v>
+      </c>
+      <c r="Z23">
+        <v>3.27</v>
+      </c>
+      <c r="AA23">
+        <v>2.04</v>
+      </c>
+      <c r="AB23">
+        <v>1.76</v>
+      </c>
+      <c r="AC23">
         <v>3.52</v>
       </c>
-      <c r="R23">
-        <v>2.13</v>
-      </c>
-      <c r="S23">
-        <v>1.34</v>
-      </c>
-      <c r="T23">
-        <v>3.07</v>
-      </c>
-      <c r="U23">
-        <v>2.62</v>
-      </c>
-      <c r="V23">
-        <v>1.39</v>
-      </c>
-      <c r="W23">
-        <v>1.1</v>
-      </c>
-      <c r="X23">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>1.26</v>
-      </c>
-      <c r="Z23">
-        <v>3.68</v>
-      </c>
-      <c r="AA23">
-        <v>1.85</v>
-      </c>
-      <c r="AB23">
-        <v>1.93</v>
-      </c>
-      <c r="AC23">
-        <v>3.09</v>
-      </c>
       <c r="AD23">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>2.3</v>
       </c>
       <c r="R24">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S24">
         <v>1.33</v>
@@ -4257,22 +4257,22 @@
         <v>1.24</v>
       </c>
       <c r="Z24">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA24">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB24">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC24">
-        <v>2.97</v>
+        <v>3.19</v>
       </c>
       <c r="AD24">
         <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
         <v>1.73</v>
@@ -4885,10 +4885,10 @@
         <v>2.45</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S28">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
         <v>3.25</v>
@@ -4930,7 +4930,7 @@
         <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>2.45</v>
       </c>
       <c r="Q32">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R32">
         <v>2.05</v>
@@ -5546,10 +5546,10 @@
         <v>2.73</v>
       </c>
       <c r="U32">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W32">
         <v>1.05</v>
@@ -5558,31 +5558,31 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z32">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="AA32">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB32">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC32">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD32">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
         <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
         <v>1.39</v>
@@ -5854,10 +5854,10 @@
         <v>1.63</v>
       </c>
       <c r="O34">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P34">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>2.08</v>
@@ -5890,7 +5890,7 @@
         <v>4.4</v>
       </c>
       <c r="AA34">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB34">
         <v>2.36</v>
@@ -5902,7 +5902,7 @@
         <v>1.48</v>
       </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
         <v>1.61</v>
@@ -7327,10 +7327,10 @@
         <v>3.35</v>
       </c>
       <c r="Q43">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S43">
         <v>1.4</v>
@@ -7351,16 +7351,16 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA43">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB43">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC43">
         <v>3.58</v>
@@ -7372,10 +7372,10 @@
         <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG43">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7816,13 +7816,13 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R46">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T46">
         <v>3.5</v>
@@ -7834,31 +7834,31 @@
         <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA46">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB46">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AC46">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AD46">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
         <v>1.57</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="O51">
         <v>3.65</v>
       </c>
       <c r="P51">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q51">
         <v>2.39</v>
@@ -8643,7 +8643,7 @@
         <v>3.8</v>
       </c>
       <c r="U51">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V51">
         <v>1.59</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="Q52">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R52">
         <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="T52">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V52">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W52">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>3.98</v>
+        <v>4.95</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AB52">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AC52">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="AD52">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.13</v>
+        <v>1.67</v>
       </c>
       <c r="O53">
+        <v>4.25</v>
+      </c>
+      <c r="P53">
         <v>3.6</v>
       </c>
-      <c r="P53">
-        <v>3</v>
-      </c>
       <c r="Q53">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="S53">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T53">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="U53">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="V53">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W53">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z53">
-        <v>4.95</v>
+        <v>7.25</v>
       </c>
       <c r="AA53">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AB53">
-        <v>2.31</v>
+        <v>3.12</v>
       </c>
       <c r="AC53">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="AD53">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AE53">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF53">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG53">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
+        <v>2.08</v>
+      </c>
+      <c r="O54">
+        <v>3.5</v>
+      </c>
+      <c r="P54">
+        <v>3.09</v>
+      </c>
+      <c r="Q54">
+        <v>2.63</v>
+      </c>
+      <c r="R54">
+        <v>2.3</v>
+      </c>
+      <c r="S54">
+        <v>1.29</v>
+      </c>
+      <c r="T54">
+        <v>3.08</v>
+      </c>
+      <c r="U54">
+        <v>2.4</v>
+      </c>
+      <c r="V54">
+        <v>1.5</v>
+      </c>
+      <c r="W54">
+        <v>1.09</v>
+      </c>
+      <c r="X54">
+        <v>1</v>
+      </c>
+      <c r="Y54">
+        <v>1.17</v>
+      </c>
+      <c r="Z54">
+        <v>3.98</v>
+      </c>
+      <c r="AA54">
         <v>1.65</v>
       </c>
-      <c r="O54">
-        <v>4.25</v>
-      </c>
-      <c r="P54">
-        <v>3.6</v>
-      </c>
-      <c r="Q54">
-        <v>2.05</v>
-      </c>
-      <c r="R54">
-        <v>2.82</v>
-      </c>
-      <c r="S54">
-        <v>1.17</v>
-      </c>
-      <c r="T54">
-        <v>3.54</v>
-      </c>
-      <c r="U54">
-        <v>1.98</v>
-      </c>
-      <c r="V54">
-        <v>1.85</v>
-      </c>
-      <c r="W54">
-        <v>1.17</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.1</v>
-      </c>
-      <c r="Z54">
-        <v>7.25</v>
-      </c>
-      <c r="AA54">
-        <v>1.37</v>
-      </c>
       <c r="AB54">
-        <v>3.12</v>
+        <v>2.14</v>
       </c>
       <c r="AC54">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="AD54">
-        <v>1.92</v>
+        <v>1.41</v>
       </c>
       <c r="AE54">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AG54">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK54">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         <v>3.75</v>
       </c>
       <c r="Q55">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="R55">
         <v>2.21</v>
@@ -9301,19 +9301,19 @@
         <v>1.48</v>
       </c>
       <c r="W55">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
         <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA55">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB55">
         <v>2.04</v>
@@ -9325,13 +9325,13 @@
         <v>1.38</v>
       </c>
       <c r="AE55">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF55">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK55">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O63">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
         <v>2</v>
       </c>
       <c r="Q63">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="R63">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="S63">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U63">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V63">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z63">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="AA63">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB63">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC63">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="AD63">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE63">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG63">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>3.75</v>
       </c>
       <c r="R64">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
         <v>1.31</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
         <v>1.35</v>
@@ -12054,7 +12054,7 @@
         <v>3</v>
       </c>
       <c r="Q72">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R72">
         <v>2.07</v>
@@ -12072,7 +12072,7 @@
         <v>1.4</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X72">
         <v>1.01</v>
@@ -12902,7 +12902,7 @@
         <v>1.49</v>
       </c>
       <c r="AB77">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC77">
         <v>2.42</v>
@@ -12914,10 +12914,10 @@
         <v>1.17</v>
       </c>
       <c r="AF77">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG77">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK77">
         <v>1.86</v>
@@ -13032,10 +13032,10 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>3.83</v>
+        <v>4.9</v>
       </c>
       <c r="R78">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="S78">
         <v>1.25</v>
@@ -13044,10 +13044,10 @@
         <v>3.6</v>
       </c>
       <c r="U78">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V78">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W78">
         <v>1.15</v>
@@ -13062,22 +13062,22 @@
         <v>5.25</v>
       </c>
       <c r="AA78">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB78">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AC78">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD78">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE78">
         <v>1.25</v>
       </c>
       <c r="AF78">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG78">
         <v>2.2</v>
@@ -13096,7 +13096,7 @@
         <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13684,10 +13684,10 @@
         <v>3.65</v>
       </c>
       <c r="Q82">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="R82">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S82">
         <v>1.14</v>
@@ -13699,10 +13699,10 @@
         <v>1.79</v>
       </c>
       <c r="V82">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="W82">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13711,28 +13711,28 @@
         <v>1.05</v>
       </c>
       <c r="Z82">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA82">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB82">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="AC82">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AD82">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AE82">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF82">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG82">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK85">
         <v>2.25</v>
@@ -14496,7 +14496,7 @@
         <v>3.4</v>
       </c>
       <c r="P87">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="Q87">
         <v>2.64</v>
@@ -14547,7 +14547,7 @@
         <v>1.48</v>
       </c>
       <c r="AG87">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
+        <v>2.45</v>
+      </c>
+      <c r="O88">
+        <v>3.4</v>
+      </c>
+      <c r="P88">
         <v>2.4</v>
-      </c>
-      <c r="O88">
-        <v>3.6</v>
-      </c>
-      <c r="P88">
-        <v>2.37</v>
       </c>
       <c r="Q88">
         <v>2.9</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,61 +14816,61 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O89">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P89">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q89">
-        <v>2.89</v>
+        <v>2.38</v>
       </c>
       <c r="R89">
+        <v>2.45</v>
+      </c>
+      <c r="S89">
+        <v>1.25</v>
+      </c>
+      <c r="T89">
+        <v>3.7</v>
+      </c>
+      <c r="U89">
+        <v>2.2</v>
+      </c>
+      <c r="V89">
+        <v>1.61</v>
+      </c>
+      <c r="W89">
+        <v>1.14</v>
+      </c>
+      <c r="X89">
+        <v>1.02</v>
+      </c>
+      <c r="Y89">
+        <v>1.15</v>
+      </c>
+      <c r="Z89">
+        <v>5.05</v>
+      </c>
+      <c r="AA89">
+        <v>1.52</v>
+      </c>
+      <c r="AB89">
         <v>2.4</v>
       </c>
-      <c r="S89">
-        <v>1.23</v>
-      </c>
-      <c r="T89">
-        <v>3.42</v>
-      </c>
-      <c r="U89">
-        <v>2.25</v>
-      </c>
-      <c r="V89">
-        <v>1.57</v>
-      </c>
-      <c r="W89">
-        <v>1.12</v>
-      </c>
-      <c r="X89">
-        <v>1.01</v>
-      </c>
-      <c r="Y89">
-        <v>1.12</v>
-      </c>
-      <c r="Z89">
-        <v>4.7</v>
-      </c>
-      <c r="AA89">
-        <v>1.51</v>
-      </c>
-      <c r="AB89">
-        <v>2.33</v>
-      </c>
       <c r="AC89">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AD89">
         <v>1.51</v>
       </c>
       <c r="AE89">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF89">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG89">
         <v>2.45</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="O90">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P90">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q90">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="R90">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S90">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="U90">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V90">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z90">
-        <v>5.32</v>
+        <v>4.7</v>
       </c>
       <c r="AA90">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AB90">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AC90">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AD90">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AE90">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF90">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AG90">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK90">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O91">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P91">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="Q91">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="R91">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S91">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T91">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V91">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W91">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z91">
-        <v>5.05</v>
+        <v>5.32</v>
       </c>
       <c r="AA91">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB91">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC91">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AD91">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AE91">
+        <v>1.22</v>
+      </c>
+      <c r="AF91">
+        <v>1.41</v>
+      </c>
+      <c r="AG91">
+        <v>2.66</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
         <v>1.18</v>
       </c>
-      <c r="AF91">
-        <v>1.47</v>
-      </c>
-      <c r="AG91">
-        <v>2.45</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.25</v>
-      </c>
       <c r="AK91">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>3.69</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
         <v>0</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,55 +15640,55 @@
         <v>4.5</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X94">
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -18079,10 +18079,10 @@
         <v>3.55</v>
       </c>
       <c r="O109">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P109">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="Q109">
         <v>4.51</v>
@@ -18115,13 +18115,13 @@
         <v>2.92</v>
       </c>
       <c r="AA109">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB109">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC109">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AD109">
         <v>1.21</v>
@@ -18260,7 +18260,7 @@
         <v>2.45</v>
       </c>
       <c r="U110">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="V110">
         <v>1.33</v>
@@ -18272,19 +18272,19 @@
         <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z110">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="AA110">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AB110">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC110">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="AD110">
         <v>1.23</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="O111">
         <v>3.05</v>
@@ -18411,10 +18411,10 @@
         <v>2.52</v>
       </c>
       <c r="Q111">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="R111">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S111">
         <v>1.43</v>
@@ -18441,16 +18441,16 @@
         <v>3.03</v>
       </c>
       <c r="AA111">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AB111">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC111">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="AD111">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE111">
         <v>1.02</v>
@@ -18459,7 +18459,7 @@
         <v>1.82</v>
       </c>
       <c r="AG111">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>3.18</v>
       </c>
       <c r="P112">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q112">
         <v>4.59</v>
@@ -18583,13 +18583,13 @@
         <v>1.42</v>
       </c>
       <c r="T112">
-        <v>2.76</v>
+        <v>2.51</v>
       </c>
       <c r="U112">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="V112">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W112">
         <v>1.02</v>
@@ -18607,13 +18607,13 @@
         <v>2.1</v>
       </c>
       <c r="AB112">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AC112">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AD112">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE112">
         <v>1.03</v>
@@ -18737,22 +18737,22 @@
         <v>1.91</v>
       </c>
       <c r="Q113">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="R113">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S113">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T113">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U113">
         <v>2.61</v>
       </c>
       <c r="V113">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
         <v>1.08</v>
@@ -18761,10 +18761,10 @@
         <v>1.03</v>
       </c>
       <c r="Y113">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z113">
-        <v>3.97</v>
+        <v>3.78</v>
       </c>
       <c r="AA113">
         <v>1.73</v>
@@ -18773,13 +18773,13 @@
         <v>1.95</v>
       </c>
       <c r="AC113">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="AD113">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE113">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF113">
         <v>1.62</v>
@@ -18900,7 +18900,7 @@
         <v>4.08</v>
       </c>
       <c r="Q114">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="R114">
         <v>2.06</v>
@@ -18918,7 +18918,7 @@
         <v>1.29</v>
       </c>
       <c r="W114">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X114">
         <v>1.03</v>
@@ -18933,13 +18933,13 @@
         <v>2.33</v>
       </c>
       <c r="AB114">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC114">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="AD114">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE114">
         <v>1.01</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O115">
         <v>3.2</v>
       </c>
       <c r="P115">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q115">
         <v>4.01</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O116">
         <v>3.35</v>
       </c>
       <c r="P116">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q116">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="R116">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="S116">
         <v>1.37</v>
@@ -19250,25 +19250,25 @@
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z116">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA116">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB116">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC116">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AD116">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE116">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF116">
         <v>1.78</v>
@@ -20198,7 +20198,7 @@
         <v>6.5</v>
       </c>
       <c r="O122">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="P122">
         <v>1.39</v>
@@ -20231,7 +20231,7 @@
         <v>1.11</v>
       </c>
       <c r="Z122">
-        <v>5.41</v>
+        <v>5.43</v>
       </c>
       <c r="AA122">
         <v>1.48</v>
@@ -20246,7 +20246,7 @@
         <v>1.63</v>
       </c>
       <c r="AE122">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF122">
         <v>1.66</v>
@@ -20554,10 +20554,10 @@
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z124">
-        <v>4.83</v>
+        <v>4.91</v>
       </c>
       <c r="AA124">
         <v>1.65</v>
@@ -20572,7 +20572,7 @@
         <v>1.44</v>
       </c>
       <c r="AE124">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF124">
         <v>1.83</v>
@@ -21520,7 +21520,7 @@
         <v>3.3</v>
       </c>
       <c r="U130">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V130">
         <v>1.5</v>
@@ -21846,7 +21846,7 @@
         <v>3</v>
       </c>
       <c r="U132">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="V132">
         <v>1.41</v>
@@ -21861,16 +21861,16 @@
         <v>1.22</v>
       </c>
       <c r="Z132">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="AA132">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB132">
         <v>1.95</v>
       </c>
       <c r="AC132">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="AD132">
         <v>1.36</v>
@@ -22184,7 +22184,7 @@
         <v>1</v>
       </c>
       <c r="Y134">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z134">
         <v>3.9</v>
@@ -22199,7 +22199,7 @@
         <v>2.91</v>
       </c>
       <c r="AD134">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE134">
         <v>1.14</v>
@@ -22224,7 +22224,7 @@
         <v>1.3</v>
       </c>
       <c r="AK134">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22323,55 +22323,55 @@
         <v>3.51</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
         <v>0</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22975,7 +22975,7 @@
         <v>2.8</v>
       </c>
       <c r="Q139">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="R139">
         <v>2.01</v>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK139">
         <v>1.47</v>
@@ -24475,7 +24475,7 @@
         <v>1.58</v>
       </c>
       <c r="AB148">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC148">
         <v>2.4</v>
@@ -25601,7 +25601,7 @@
         <v>1.6</v>
       </c>
       <c r="W155">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X155">
         <v>1.02</v>
@@ -25625,7 +25625,7 @@
         <v>1.66</v>
       </c>
       <c r="AE155">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF155">
         <v>1.51</v>
@@ -25743,7 +25743,7 @@
         <v>3.93</v>
       </c>
       <c r="P156">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="Q156">
         <v>2.86</v>
@@ -25764,7 +25764,7 @@
         <v>1.77</v>
       </c>
       <c r="W156">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X156">
         <v>1.02</v>
@@ -25930,7 +25930,7 @@
         <v>1.2</v>
       </c>
       <c r="X157">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
         <v>1.05</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O158">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="P158">
-        <v>2.26</v>
+        <v>1.61</v>
       </c>
       <c r="Q158">
-        <v>3.04</v>
+        <v>5.2</v>
       </c>
       <c r="R158">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="S158">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T158">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U158">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="V158">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W158">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X158">
         <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="Z158">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA158">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AB158">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AC158">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AD158">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AE158">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF158">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AG158">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK158">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>4.5</v>
+        <v>2.82</v>
       </c>
       <c r="O159">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="P159">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="Q159">
-        <v>5.2</v>
+        <v>3.04</v>
       </c>
       <c r="R159">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="S159">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="T159">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U159">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="V159">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W159">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X159">
         <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Z159">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA159">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AB159">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC159">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="AD159">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AE159">
+        <v>1.2</v>
+      </c>
+      <c r="AF159">
+        <v>1.47</v>
+      </c>
+      <c r="AG159">
+        <v>2.39</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.23</v>
       </c>
-      <c r="AF159">
-        <v>1.51</v>
-      </c>
-      <c r="AG159">
-        <v>2.4</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>1.22</v>
-      </c>
       <c r="AK159">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26410,7 +26410,7 @@
         <v>3.3</v>
       </c>
       <c r="U160">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V160">
         <v>1.49</v>
@@ -26440,7 +26440,7 @@
         <v>1.4</v>
       </c>
       <c r="AE160">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF160">
         <v>1.69</v>
@@ -26552,7 +26552,7 @@
         </is>
       </c>
       <c r="N161">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O161">
         <v>3.6</v>
@@ -26622,7 +26622,7 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK161">
         <v>1.6</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,64 +28671,64 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="O174">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="P174">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="Q174">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="R174">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="S174">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="T174">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="U174">
-        <v>2.09</v>
+        <v>2.77</v>
       </c>
       <c r="V174">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="W174">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X174">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y174">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z174">
-        <v>6.12</v>
+        <v>3.5</v>
       </c>
       <c r="AA174">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AB174">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="AC174">
-        <v>2.06</v>
+        <v>2.92</v>
       </c>
       <c r="AD174">
-        <v>1.72</v>
+        <v>1.31</v>
       </c>
       <c r="AE174">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF174">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AG174">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK174">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="O175">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P175">
-        <v>3.25</v>
+        <v>2.31</v>
       </c>
       <c r="Q175">
-        <v>2.81</v>
+        <v>3.12</v>
       </c>
       <c r="R175">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S175">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T175">
-        <v>2.89</v>
+        <v>3.46</v>
       </c>
       <c r="U175">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="V175">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="W175">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X175">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y175">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z175">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="AA175">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AB175">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AC175">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="AD175">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AE175">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AF175">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AG175">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK175">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="O176">
         <v>3.7</v>
       </c>
       <c r="P176">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q176">
-        <v>2.36</v>
+        <v>3.7</v>
       </c>
       <c r="R176">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S176">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T176">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="U176">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="V176">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X176">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z176">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AA176">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AB176">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AC176">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="AD176">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE176">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF176">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG176">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK176">
-        <v>1.88</v>
+        <v>1.28</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="O177">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P177">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Q177">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="R177">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T177">
-        <v>3.46</v>
+        <v>3.08</v>
       </c>
       <c r="U177">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V177">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="W177">
+        <v>1.07</v>
+      </c>
+      <c r="X177">
+        <v>1.04</v>
+      </c>
+      <c r="Y177">
+        <v>1.21</v>
+      </c>
+      <c r="Z177">
+        <v>3.58</v>
+      </c>
+      <c r="AA177">
+        <v>1.79</v>
+      </c>
+      <c r="AB177">
+        <v>1.9</v>
+      </c>
+      <c r="AC177">
+        <v>2.92</v>
+      </c>
+      <c r="AD177">
+        <v>1.33</v>
+      </c>
+      <c r="AE177">
         <v>1.13</v>
       </c>
-      <c r="X177">
-        <v>1.02</v>
-      </c>
-      <c r="Y177">
-        <v>1.15</v>
-      </c>
-      <c r="Z177">
-        <v>4.2</v>
-      </c>
-      <c r="AA177">
-        <v>1.62</v>
-      </c>
-      <c r="AB177">
-        <v>2.12</v>
-      </c>
-      <c r="AC177">
-        <v>2.66</v>
-      </c>
-      <c r="AD177">
-        <v>1.44</v>
-      </c>
-      <c r="AE177">
-        <v>1.15</v>
-      </c>
       <c r="AF177">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG177">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK177">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,80 +29323,80 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.61</v>
+        <v>2</v>
       </c>
       <c r="O178">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P178">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="Q178">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="R178">
         <v>2.1</v>
       </c>
       <c r="S178">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T178">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="U178">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="V178">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="W178">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X178">
         <v>1.04</v>
       </c>
       <c r="Y178">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z178">
-   